--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -11694,6 +11694,14 @@
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
@@ -11750,7 +11758,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>Bild.</t>
+          <t>Ringhack.</t>
         </is>
       </c>
       <c r="AD101" t="b">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -24891,6 +24891,10 @@
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
       <c r="P219" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Laisdalen Päronberget, Pi lm</t>
@@ -24965,7 +24969,11 @@
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY219" t="inlineStr"/>
+      <c r="AY219" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -35936,48 +35936,51 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>80987073</v>
+        <v>135349920</v>
       </c>
       <c r="B317" t="n">
-        <v>92208</v>
+        <v>92369</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>658</v>
+        <v>298</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
+      <c r="J317" t="inlineStr"/>
+      <c r="K317" t="inlineStr"/>
+      <c r="N317" t="inlineStr"/>
       <c r="P317" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>608109</v>
+        <v>607959</v>
       </c>
       <c r="R317" t="n">
-        <v>7309518</v>
+        <v>7309608</v>
       </c>
       <c r="S317" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T317" t="inlineStr">
         <is>
@@ -36001,12 +36004,22 @@
       </c>
       <c r="Y317" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD317" t="b">
@@ -36015,28 +36028,33 @@
       <c r="AE317" t="b">
         <v>0</v>
       </c>
+      <c r="AF317" t="inlineStr"/>
       <c r="AG317" t="b">
         <v>0</v>
       </c>
       <c r="AT317" t="inlineStr"/>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY317" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY317" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>135349899</v>
+        <v>80987073</v>
       </c>
       <c r="B318" t="n">
-        <v>92245</v>
+        <v>92208</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -36064,17 +36082,17 @@
       <c r="I318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>608042</v>
+        <v>608109</v>
       </c>
       <c r="R318" t="n">
-        <v>7309698</v>
+        <v>7309518</v>
       </c>
       <c r="S318" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -36098,22 +36116,12 @@
       </c>
       <c r="Y318" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z318" t="inlineStr">
-        <is>
-          <t>15:32</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB318" t="inlineStr">
-        <is>
-          <t>15:32</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD318" t="b">
@@ -36128,26 +36136,22 @@
       <c r="AT318" t="inlineStr"/>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY318" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY318" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>80987078</v>
+        <v>135349899</v>
       </c>
       <c r="B319" t="n">
-        <v>91905</v>
+        <v>92245</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -36155,37 +36159,37 @@
         </is>
       </c>
       <c r="E319" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>608267</v>
+        <v>608042</v>
       </c>
       <c r="R319" t="n">
-        <v>7309545</v>
+        <v>7309698</v>
       </c>
       <c r="S319" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
@@ -36209,12 +36213,22 @@
       </c>
       <c r="Y319" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD319" t="b">
@@ -36229,19 +36243,23 @@
       <c r="AT319" t="inlineStr"/>
       <c r="AW319" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY319" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY319" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>80987084</v>
+        <v>80987078</v>
       </c>
       <c r="B320" t="n">
         <v>91905</v>
@@ -36276,10 +36294,10 @@
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>608262</v>
+        <v>608267</v>
       </c>
       <c r="R320" t="n">
-        <v>7309636</v>
+        <v>7309545</v>
       </c>
       <c r="S320" t="n">
         <v>10</v>
@@ -36338,10 +36356,10 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>135349895</v>
+        <v>80987084</v>
       </c>
       <c r="B321" t="n">
-        <v>91970</v>
+        <v>91905</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -36369,17 +36387,17 @@
       <c r="I321" t="inlineStr"/>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>608060</v>
+        <v>608262</v>
       </c>
       <c r="R321" t="n">
-        <v>7309692</v>
+        <v>7309636</v>
       </c>
       <c r="S321" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T321" t="inlineStr">
         <is>
@@ -36403,22 +36421,12 @@
       </c>
       <c r="Y321" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z321" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA321" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB321" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD321" t="b">
@@ -36433,23 +36441,19 @@
       <c r="AT321" t="inlineStr"/>
       <c r="AW321" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX321" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY321" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY321" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>135349906</v>
+        <v>135349895</v>
       </c>
       <c r="B322" t="n">
         <v>91970</v>
@@ -36484,10 +36488,10 @@
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>607999</v>
+        <v>608060</v>
       </c>
       <c r="R322" t="n">
-        <v>7309691</v>
+        <v>7309692</v>
       </c>
       <c r="S322" t="n">
         <v>3</v>
@@ -36519,7 +36523,7 @@
       </c>
       <c r="Z322" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
@@ -36529,7 +36533,7 @@
       </c>
       <c r="AB322" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -36560,10 +36564,10 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>80987116</v>
+        <v>135349906</v>
       </c>
       <c r="B323" t="n">
-        <v>83173</v>
+        <v>91970</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -36571,37 +36575,37 @@
         </is>
       </c>
       <c r="E323" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I323" t="inlineStr"/>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>608291</v>
+        <v>607999</v>
       </c>
       <c r="R323" t="n">
-        <v>7309538</v>
+        <v>7309691</v>
       </c>
       <c r="S323" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T323" t="inlineStr">
         <is>
@@ -36625,12 +36629,22 @@
       </c>
       <c r="Y323" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -36645,19 +36659,23 @@
       <c r="AT323" t="inlineStr"/>
       <c r="AW323" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX323" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY323" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY323" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>80987118</v>
+        <v>80987116</v>
       </c>
       <c r="B324" t="n">
         <v>83173</v>
@@ -36692,10 +36710,10 @@
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>608214</v>
+        <v>608291</v>
       </c>
       <c r="R324" t="n">
-        <v>7309675</v>
+        <v>7309538</v>
       </c>
       <c r="S324" t="n">
         <v>10</v>
@@ -36754,7 +36772,7 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>80987119</v>
+        <v>80987118</v>
       </c>
       <c r="B325" t="n">
         <v>83173</v>
@@ -36789,10 +36807,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>608153</v>
+        <v>608214</v>
       </c>
       <c r="R325" t="n">
-        <v>7309682</v>
+        <v>7309675</v>
       </c>
       <c r="S325" t="n">
         <v>10</v>
@@ -36851,7 +36869,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>80987121</v>
+        <v>80987119</v>
       </c>
       <c r="B326" t="n">
         <v>83173</v>
@@ -36886,10 +36904,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>608254</v>
+        <v>608153</v>
       </c>
       <c r="R326" t="n">
-        <v>7309641</v>
+        <v>7309682</v>
       </c>
       <c r="S326" t="n">
         <v>10</v>
@@ -36948,7 +36966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>80987123</v>
+        <v>80987121</v>
       </c>
       <c r="B327" t="n">
         <v>83173</v>
@@ -36983,10 +37001,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>608033</v>
+        <v>608254</v>
       </c>
       <c r="R327" t="n">
-        <v>7309564</v>
+        <v>7309641</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -37045,48 +37063,48 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>135349920</v>
+        <v>80987123</v>
       </c>
       <c r="B328" t="n">
-        <v>92329</v>
+        <v>83173</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E328" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I328" t="inlineStr"/>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>607959</v>
+        <v>608033</v>
       </c>
       <c r="R328" t="n">
-        <v>7309608</v>
+        <v>7309564</v>
       </c>
       <c r="S328" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T328" t="inlineStr">
         <is>
@@ -37110,29 +37128,19 @@
       </c>
       <c r="Y328" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z328" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB328" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD328" t="b">
         <v>0</v>
       </c>
       <c r="AE328" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG328" t="b">
         <v>0</v>
@@ -37140,19 +37148,15 @@
       <c r="AT328" t="inlineStr"/>
       <c r="AW328" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY328" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="n">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -36026,7 +36026,7 @@
         <v>0</v>
       </c>
       <c r="AE317" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF317" t="inlineStr"/>
       <c r="AG317" t="b">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY373"/>
+  <dimension ref="A1:AY374"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35936,32 +35936,27 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>135349920</v>
+        <v>135354071</v>
       </c>
       <c r="B317" t="n">
-        <v>92369</v>
+        <v>92323</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E317" t="n">
-        <v>298</v>
-      </c>
-      <c r="F317" t="inlineStr">
-        <is>
-          <t>Laxgröppa</t>
-        </is>
+        <v>6331023</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Meruliopsis rubicunda</t>
+          <t>Skeletocutis exilis</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
+          <t>Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I317" t="inlineStr"/>
@@ -35974,13 +35969,13 @@
         </is>
       </c>
       <c r="Q317" t="n">
-        <v>607959</v>
+        <v>607323</v>
       </c>
       <c r="R317" t="n">
-        <v>7309608</v>
+        <v>7311406</v>
       </c>
       <c r="S317" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T317" t="inlineStr">
         <is>
@@ -36009,7 +36004,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -36019,80 +36014,112 @@
       </c>
       <c r="AB317" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD317" t="b">
         <v>0</v>
       </c>
       <c r="AE317" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF317" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG317" t="b">
         <v>0</v>
+      </c>
+      <c r="AI317" t="inlineStr">
+        <is>
+          <t>Fjällnära grandominerad barrnaturskog.</t>
+        </is>
+      </c>
+      <c r="AJ317" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK317" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>Ved på låga rötad av ullticka. Även ostticka på lågan. # Picea abies</t>
+        </is>
+      </c>
+      <c r="AQ317" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
       </c>
       <c r="AT317" t="inlineStr"/>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>80987073</v>
+        <v>135349920</v>
       </c>
       <c r="B318" t="n">
-        <v>92208</v>
+        <v>92369</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E318" t="n">
-        <v>658</v>
+        <v>298</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Laxgröppa</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Meruliopsis rubicunda</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Litsch.) Spirin &amp; K.H.Larss.</t>
         </is>
       </c>
       <c r="I318" t="inlineStr"/>
+      <c r="J318" t="inlineStr"/>
+      <c r="K318" t="inlineStr"/>
+      <c r="N318" t="inlineStr"/>
       <c r="P318" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q318" t="n">
-        <v>608109</v>
+        <v>607959</v>
       </c>
       <c r="R318" t="n">
-        <v>7309518</v>
+        <v>7309608</v>
       </c>
       <c r="S318" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T318" t="inlineStr">
         <is>
@@ -36116,42 +36143,57 @@
       </c>
       <c r="Y318" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA318" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB318" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD318" t="b">
         <v>0</v>
       </c>
       <c r="AE318" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF318" t="inlineStr"/>
       <c r="AG318" t="b">
         <v>0</v>
       </c>
       <c r="AT318" t="inlineStr"/>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY318" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY318" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>135349899</v>
+        <v>80987073</v>
       </c>
       <c r="B319" t="n">
-        <v>92245</v>
+        <v>92208</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -36179,17 +36221,17 @@
       <c r="I319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q319" t="n">
-        <v>608042</v>
+        <v>608109</v>
       </c>
       <c r="R319" t="n">
-        <v>7309698</v>
+        <v>7309518</v>
       </c>
       <c r="S319" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T319" t="inlineStr">
         <is>
@@ -36213,22 +36255,12 @@
       </c>
       <c r="Y319" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z319" t="inlineStr">
-        <is>
-          <t>15:32</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA319" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB319" t="inlineStr">
-        <is>
-          <t>15:32</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD319" t="b">
@@ -36243,26 +36275,22 @@
       <c r="AT319" t="inlineStr"/>
       <c r="AW319" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX319" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY319" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY319" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>80987078</v>
+        <v>135349899</v>
       </c>
       <c r="B320" t="n">
-        <v>91905</v>
+        <v>92245</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -36270,37 +36298,37 @@
         </is>
       </c>
       <c r="E320" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I320" t="inlineStr"/>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q320" t="n">
-        <v>608267</v>
+        <v>608042</v>
       </c>
       <c r="R320" t="n">
-        <v>7309545</v>
+        <v>7309698</v>
       </c>
       <c r="S320" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T320" t="inlineStr">
         <is>
@@ -36324,12 +36352,22 @@
       </c>
       <c r="Y320" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA320" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB320" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD320" t="b">
@@ -36344,19 +36382,23 @@
       <c r="AT320" t="inlineStr"/>
       <c r="AW320" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX320" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY320" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY320" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>80987084</v>
+        <v>80987078</v>
       </c>
       <c r="B321" t="n">
         <v>91905</v>
@@ -36391,10 +36433,10 @@
         </is>
       </c>
       <c r="Q321" t="n">
-        <v>608262</v>
+        <v>608267</v>
       </c>
       <c r="R321" t="n">
-        <v>7309636</v>
+        <v>7309545</v>
       </c>
       <c r="S321" t="n">
         <v>10</v>
@@ -36453,10 +36495,10 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>135349895</v>
+        <v>80987084</v>
       </c>
       <c r="B322" t="n">
-        <v>91970</v>
+        <v>91905</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -36484,17 +36526,17 @@
       <c r="I322" t="inlineStr"/>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q322" t="n">
-        <v>608060</v>
+        <v>608262</v>
       </c>
       <c r="R322" t="n">
-        <v>7309692</v>
+        <v>7309636</v>
       </c>
       <c r="S322" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T322" t="inlineStr">
         <is>
@@ -36518,22 +36560,12 @@
       </c>
       <c r="Y322" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z322" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA322" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB322" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD322" t="b">
@@ -36548,23 +36580,19 @@
       <c r="AT322" t="inlineStr"/>
       <c r="AW322" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX322" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY322" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY322" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>135349906</v>
+        <v>135349895</v>
       </c>
       <c r="B323" t="n">
         <v>91970</v>
@@ -36599,10 +36627,10 @@
         </is>
       </c>
       <c r="Q323" t="n">
-        <v>607999</v>
+        <v>608060</v>
       </c>
       <c r="R323" t="n">
-        <v>7309691</v>
+        <v>7309692</v>
       </c>
       <c r="S323" t="n">
         <v>3</v>
@@ -36634,7 +36662,7 @@
       </c>
       <c r="Z323" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA323" t="inlineStr">
@@ -36644,7 +36672,7 @@
       </c>
       <c r="AB323" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD323" t="b">
@@ -36675,10 +36703,10 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>80987116</v>
+        <v>135349906</v>
       </c>
       <c r="B324" t="n">
-        <v>83173</v>
+        <v>91970</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -36686,37 +36714,37 @@
         </is>
       </c>
       <c r="E324" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I324" t="inlineStr"/>
       <c r="P324" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q324" t="n">
-        <v>608291</v>
+        <v>607999</v>
       </c>
       <c r="R324" t="n">
-        <v>7309538</v>
+        <v>7309691</v>
       </c>
       <c r="S324" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T324" t="inlineStr">
         <is>
@@ -36740,12 +36768,22 @@
       </c>
       <c r="Y324" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA324" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB324" t="inlineStr">
+        <is>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD324" t="b">
@@ -36760,19 +36798,23 @@
       <c r="AT324" t="inlineStr"/>
       <c r="AW324" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX324" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY324" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY324" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>80987118</v>
+        <v>80987116</v>
       </c>
       <c r="B325" t="n">
         <v>83173</v>
@@ -36807,10 +36849,10 @@
         </is>
       </c>
       <c r="Q325" t="n">
-        <v>608214</v>
+        <v>608291</v>
       </c>
       <c r="R325" t="n">
-        <v>7309675</v>
+        <v>7309538</v>
       </c>
       <c r="S325" t="n">
         <v>10</v>
@@ -36869,7 +36911,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>80987119</v>
+        <v>80987118</v>
       </c>
       <c r="B326" t="n">
         <v>83173</v>
@@ -36904,10 +36946,10 @@
         </is>
       </c>
       <c r="Q326" t="n">
-        <v>608153</v>
+        <v>608214</v>
       </c>
       <c r="R326" t="n">
-        <v>7309682</v>
+        <v>7309675</v>
       </c>
       <c r="S326" t="n">
         <v>10</v>
@@ -36966,7 +37008,7 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>80987121</v>
+        <v>80987119</v>
       </c>
       <c r="B327" t="n">
         <v>83173</v>
@@ -37001,10 +37043,10 @@
         </is>
       </c>
       <c r="Q327" t="n">
-        <v>608254</v>
+        <v>608153</v>
       </c>
       <c r="R327" t="n">
-        <v>7309641</v>
+        <v>7309682</v>
       </c>
       <c r="S327" t="n">
         <v>10</v>
@@ -37063,7 +37105,7 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>80987123</v>
+        <v>80987121</v>
       </c>
       <c r="B328" t="n">
         <v>83173</v>
@@ -37098,10 +37140,10 @@
         </is>
       </c>
       <c r="Q328" t="n">
-        <v>608033</v>
+        <v>608254</v>
       </c>
       <c r="R328" t="n">
-        <v>7309564</v>
+        <v>7309641</v>
       </c>
       <c r="S328" t="n">
         <v>10</v>
@@ -37160,32 +37202,32 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>80987085</v>
+        <v>80987123</v>
       </c>
       <c r="B329" t="n">
-        <v>92283</v>
+        <v>83173</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E329" t="n">
-        <v>2063</v>
+        <v>1312</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>Grantickeporing</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Skeletocutis chrysella</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I329" t="inlineStr"/>
@@ -37195,10 +37237,10 @@
         </is>
       </c>
       <c r="Q329" t="n">
-        <v>608259</v>
+        <v>608033</v>
       </c>
       <c r="R329" t="n">
-        <v>7309644</v>
+        <v>7309564</v>
       </c>
       <c r="S329" t="n">
         <v>10</v>
@@ -37257,48 +37299,48 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>135349911</v>
+        <v>80987085</v>
       </c>
       <c r="B330" t="n">
-        <v>96410</v>
+        <v>92283</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E330" t="n">
-        <v>2812</v>
+        <v>2063</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Grantickeporing</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Skeletocutis chrysella</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I330" t="inlineStr"/>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q330" t="n">
-        <v>608017</v>
+        <v>608259</v>
       </c>
       <c r="R330" t="n">
-        <v>7309630</v>
+        <v>7309644</v>
       </c>
       <c r="S330" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T330" t="inlineStr">
         <is>
@@ -37322,22 +37364,12 @@
       </c>
       <c r="Y330" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z330" t="inlineStr">
-        <is>
-          <t>15:46</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA330" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB330" t="inlineStr">
-        <is>
-          <t>15:46</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD330" t="b">
@@ -37352,26 +37384,22 @@
       <c r="AT330" t="inlineStr"/>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY330" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY330" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>135349919</v>
+        <v>135349911</v>
       </c>
       <c r="B331" t="n">
-        <v>92370</v>
+        <v>96410</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -37379,21 +37407,21 @@
         </is>
       </c>
       <c r="E331" t="n">
-        <v>4217</v>
+        <v>2812</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I331" t="inlineStr"/>
@@ -37403,10 +37431,10 @@
         </is>
       </c>
       <c r="Q331" t="n">
-        <v>607959</v>
+        <v>608017</v>
       </c>
       <c r="R331" t="n">
-        <v>7309608</v>
+        <v>7309630</v>
       </c>
       <c r="S331" t="n">
         <v>3</v>
@@ -37438,7 +37466,7 @@
       </c>
       <c r="Z331" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA331" t="inlineStr">
@@ -37448,7 +37476,7 @@
       </c>
       <c r="AB331" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD331" t="b">
@@ -37479,10 +37507,10 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>135349892</v>
+        <v>135349919</v>
       </c>
       <c r="B332" t="n">
-        <v>91937</v>
+        <v>92370</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -37490,21 +37518,21 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>5447</v>
+        <v>4217</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I332" t="inlineStr"/>
@@ -37514,10 +37542,10 @@
         </is>
       </c>
       <c r="Q332" t="n">
-        <v>608067</v>
+        <v>607959</v>
       </c>
       <c r="R332" t="n">
-        <v>7309686</v>
+        <v>7309608</v>
       </c>
       <c r="S332" t="n">
         <v>3</v>
@@ -37549,7 +37577,7 @@
       </c>
       <c r="Z332" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA332" t="inlineStr">
@@ -37559,7 +37587,7 @@
       </c>
       <c r="AB332" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD332" t="b">
@@ -37590,7 +37618,7 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>135349905</v>
+        <v>135349892</v>
       </c>
       <c r="B333" t="n">
         <v>91937</v>
@@ -37625,10 +37653,10 @@
         </is>
       </c>
       <c r="Q333" t="n">
-        <v>607999</v>
+        <v>608067</v>
       </c>
       <c r="R333" t="n">
-        <v>7309691</v>
+        <v>7309686</v>
       </c>
       <c r="S333" t="n">
         <v>3</v>
@@ -37660,7 +37688,7 @@
       </c>
       <c r="Z333" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA333" t="inlineStr">
@@ -37670,7 +37698,7 @@
       </c>
       <c r="AB333" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD333" t="b">
@@ -37701,32 +37729,32 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>135349898</v>
+        <v>135349905</v>
       </c>
       <c r="B334" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E334" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I334" t="inlineStr"/>
@@ -37736,10 +37764,10 @@
         </is>
       </c>
       <c r="Q334" t="n">
-        <v>608046</v>
+        <v>607999</v>
       </c>
       <c r="R334" t="n">
-        <v>7309697</v>
+        <v>7309691</v>
       </c>
       <c r="S334" t="n">
         <v>3</v>
@@ -37771,7 +37799,7 @@
       </c>
       <c r="Z334" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA334" t="inlineStr">
@@ -37781,7 +37809,7 @@
       </c>
       <c r="AB334" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD334" t="b">
@@ -37812,7 +37840,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>135349900</v>
+        <v>135349898</v>
       </c>
       <c r="B335" t="n">
         <v>79373</v>
@@ -37847,10 +37875,10 @@
         </is>
       </c>
       <c r="Q335" t="n">
-        <v>608013</v>
+        <v>608046</v>
       </c>
       <c r="R335" t="n">
-        <v>7309723</v>
+        <v>7309697</v>
       </c>
       <c r="S335" t="n">
         <v>3</v>
@@ -37882,7 +37910,7 @@
       </c>
       <c r="Z335" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA335" t="inlineStr">
@@ -37892,7 +37920,7 @@
       </c>
       <c r="AB335" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD335" t="b">
@@ -37923,7 +37951,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>135349903</v>
+        <v>135349900</v>
       </c>
       <c r="B336" t="n">
         <v>79373</v>
@@ -37958,10 +37986,10 @@
         </is>
       </c>
       <c r="Q336" t="n">
-        <v>607999</v>
+        <v>608013</v>
       </c>
       <c r="R336" t="n">
-        <v>7309728</v>
+        <v>7309723</v>
       </c>
       <c r="S336" t="n">
         <v>3</v>
@@ -37993,7 +38021,7 @@
       </c>
       <c r="Z336" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA336" t="inlineStr">
@@ -38003,7 +38031,7 @@
       </c>
       <c r="AB336" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD336" t="b">
@@ -38034,7 +38062,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>135349908</v>
+        <v>135349903</v>
       </c>
       <c r="B337" t="n">
         <v>79373</v>
@@ -38069,13 +38097,13 @@
         </is>
       </c>
       <c r="Q337" t="n">
-        <v>608018</v>
+        <v>607999</v>
       </c>
       <c r="R337" t="n">
-        <v>7309659</v>
+        <v>7309728</v>
       </c>
       <c r="S337" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T337" t="inlineStr">
         <is>
@@ -38104,7 +38132,7 @@
       </c>
       <c r="Z337" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA337" t="inlineStr">
@@ -38114,7 +38142,7 @@
       </c>
       <c r="AB337" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD337" t="b">
@@ -38145,7 +38173,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>135349917</v>
+        <v>135349908</v>
       </c>
       <c r="B338" t="n">
         <v>79373</v>
@@ -38180,10 +38208,10 @@
         </is>
       </c>
       <c r="Q338" t="n">
-        <v>607981</v>
+        <v>608018</v>
       </c>
       <c r="R338" t="n">
-        <v>7309626</v>
+        <v>7309659</v>
       </c>
       <c r="S338" t="n">
         <v>4</v>
@@ -38215,7 +38243,7 @@
       </c>
       <c r="Z338" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA338" t="inlineStr">
@@ -38225,7 +38253,7 @@
       </c>
       <c r="AB338" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD338" t="b">
@@ -38256,53 +38284,48 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>135349918</v>
+        <v>135349917</v>
       </c>
       <c r="B339" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E339" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I339" t="inlineStr"/>
-      <c r="M339" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P339" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q339" t="n">
-        <v>607960</v>
+        <v>607981</v>
       </c>
       <c r="R339" t="n">
-        <v>7309607</v>
+        <v>7309626</v>
       </c>
       <c r="S339" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T339" t="inlineStr">
         <is>
@@ -38331,7 +38354,7 @@
       </c>
       <c r="Z339" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA339" t="inlineStr">
@@ -38341,7 +38364,7 @@
       </c>
       <c r="AB339" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD339" t="b">
@@ -38372,27 +38395,27 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>135349901</v>
+        <v>135349918</v>
       </c>
       <c r="B340" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E340" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -38412,13 +38435,13 @@
         </is>
       </c>
       <c r="Q340" t="n">
-        <v>608001</v>
+        <v>607960</v>
       </c>
       <c r="R340" t="n">
-        <v>7309725</v>
+        <v>7309607</v>
       </c>
       <c r="S340" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T340" t="inlineStr">
         <is>
@@ -38447,7 +38470,7 @@
       </c>
       <c r="Z340" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA340" t="inlineStr">
@@ -38457,12 +38480,7 @@
       </c>
       <c r="AB340" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC340" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD340" t="b">
@@ -38493,7 +38511,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>135349904</v>
+        <v>135349901</v>
       </c>
       <c r="B341" t="n">
         <v>57975</v>
@@ -38533,13 +38551,13 @@
         </is>
       </c>
       <c r="Q341" t="n">
-        <v>607987</v>
+        <v>608001</v>
       </c>
       <c r="R341" t="n">
-        <v>7309708</v>
+        <v>7309725</v>
       </c>
       <c r="S341" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T341" t="inlineStr">
         <is>
@@ -38568,7 +38586,7 @@
       </c>
       <c r="Z341" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA341" t="inlineStr">
@@ -38578,19 +38596,19 @@
       </c>
       <c r="AB341" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC341" t="inlineStr">
         <is>
-          <t>skalad klen gran</t>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD341" t="b">
         <v>0</v>
       </c>
       <c r="AE341" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG341" t="b">
         <v>0</v>
@@ -38614,48 +38632,53 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>80987071</v>
+        <v>135349904</v>
       </c>
       <c r="B342" t="n">
-        <v>57141</v>
+        <v>57975</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr"/>
+      <c r="M342" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P342" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q342" t="n">
-        <v>608360</v>
+        <v>607987</v>
       </c>
       <c r="R342" t="n">
-        <v>7309498</v>
+        <v>7309708</v>
       </c>
       <c r="S342" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T342" t="inlineStr">
         <is>
@@ -38679,19 +38702,34 @@
       </c>
       <c r="Y342" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA342" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB342" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AC342" t="inlineStr">
+        <is>
+          <t>skalad klen gran</t>
         </is>
       </c>
       <c r="AD342" t="b">
         <v>0</v>
       </c>
       <c r="AE342" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG342" t="b">
         <v>0</v>
@@ -38699,44 +38737,48 @@
       <c r="AT342" t="inlineStr"/>
       <c r="AW342" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX342" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY342" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY342" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>80987075</v>
+        <v>80987071</v>
       </c>
       <c r="B343" t="n">
-        <v>58057</v>
+        <v>57141</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I343" t="inlineStr"/>
@@ -38746,10 +38788,10 @@
         </is>
       </c>
       <c r="Q343" t="n">
-        <v>608231</v>
+        <v>608360</v>
       </c>
       <c r="R343" t="n">
-        <v>7309648</v>
+        <v>7309498</v>
       </c>
       <c r="S343" t="n">
         <v>10</v>
@@ -38808,10 +38850,10 @@
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>135349897</v>
+        <v>80987075</v>
       </c>
       <c r="B344" t="n">
-        <v>58079</v>
+        <v>58057</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -38837,24 +38879,19 @@
         </is>
       </c>
       <c r="I344" t="inlineStr"/>
-      <c r="M344" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
       <c r="P344" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q344" t="n">
-        <v>608053</v>
+        <v>608231</v>
       </c>
       <c r="R344" t="n">
-        <v>7309696</v>
+        <v>7309648</v>
       </c>
       <c r="S344" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T344" t="inlineStr">
         <is>
@@ -38878,22 +38915,12 @@
       </c>
       <c r="Y344" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z344" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA344" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB344" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD344" t="b">
@@ -38908,64 +38935,65 @@
       <c r="AT344" t="inlineStr"/>
       <c r="AW344" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX344" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY344" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>135351869</v>
+        <v>135349897</v>
       </c>
       <c r="B345" t="n">
-        <v>99094</v>
+        <v>58079</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>219795</v>
+        <v>103031</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr"/>
+      <c r="M345" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P345" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q345" t="n">
-        <v>608121</v>
+        <v>608053</v>
       </c>
       <c r="R345" t="n">
-        <v>7309664</v>
+        <v>7309696</v>
       </c>
       <c r="S345" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T345" t="inlineStr">
         <is>
@@ -38994,7 +39022,7 @@
       </c>
       <c r="Z345" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA345" t="inlineStr">
@@ -39004,7 +39032,7 @@
       </c>
       <c r="AB345" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD345" t="b">
@@ -39019,12 +39047,12 @@
       <c r="AT345" t="inlineStr"/>
       <c r="AW345" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX345" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY345" t="inlineStr">
@@ -39035,10 +39063,10 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>135351871</v>
+        <v>135351869</v>
       </c>
       <c r="B346" t="n">
-        <v>99197</v>
+        <v>99094</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -39046,21 +39074,21 @@
         </is>
       </c>
       <c r="E346" t="n">
-        <v>219811</v>
+        <v>219795</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I346" t="inlineStr"/>
@@ -39070,13 +39098,13 @@
         </is>
       </c>
       <c r="Q346" t="n">
-        <v>608132</v>
+        <v>608121</v>
       </c>
       <c r="R346" t="n">
-        <v>7309645</v>
+        <v>7309664</v>
       </c>
       <c r="S346" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T346" t="inlineStr">
         <is>
@@ -39105,7 +39133,7 @@
       </c>
       <c r="Z346" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA346" t="inlineStr">
@@ -39115,7 +39143,7 @@
       </c>
       <c r="AB346" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD346" t="b">
@@ -39146,10 +39174,10 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>135351874</v>
+        <v>135351871</v>
       </c>
       <c r="B347" t="n">
-        <v>110150</v>
+        <v>99197</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -39157,21 +39185,21 @@
         </is>
       </c>
       <c r="E347" t="n">
-        <v>220294</v>
+        <v>219811</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I347" t="inlineStr"/>
@@ -39181,13 +39209,13 @@
         </is>
       </c>
       <c r="Q347" t="n">
-        <v>608136</v>
+        <v>608132</v>
       </c>
       <c r="R347" t="n">
-        <v>7309644</v>
+        <v>7309645</v>
       </c>
       <c r="S347" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T347" t="inlineStr">
         <is>
@@ -39216,7 +39244,7 @@
       </c>
       <c r="Z347" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA347" t="inlineStr">
@@ -39226,7 +39254,7 @@
       </c>
       <c r="AB347" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD347" t="b">
@@ -39257,57 +39285,48 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>135349921</v>
+        <v>135351874</v>
       </c>
       <c r="B348" t="n">
-        <v>99195</v>
+        <v>110150</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>220787</v>
+        <v>220294</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I348" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K348" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr"/>
       <c r="P348" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q348" t="n">
-        <v>607991</v>
+        <v>608136</v>
       </c>
       <c r="R348" t="n">
-        <v>7309608</v>
+        <v>7309644</v>
       </c>
       <c r="S348" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T348" t="inlineStr">
         <is>
@@ -39336,7 +39355,7 @@
       </c>
       <c r="Z348" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -39346,7 +39365,7 @@
       </c>
       <c r="AB348" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD348" t="b">
@@ -39361,12 +39380,12 @@
       <c r="AT348" t="inlineStr"/>
       <c r="AW348" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX348" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY348" t="inlineStr">
@@ -39377,49 +39396,54 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>135349909</v>
+        <v>135349921</v>
       </c>
       <c r="B349" t="n">
-        <v>106309</v>
+        <v>99195</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I349" t="inlineStr"/>
-      <c r="J349" t="inlineStr"/>
-      <c r="K349" t="inlineStr"/>
-      <c r="L349" t="inlineStr"/>
-      <c r="N349" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P349" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q349" t="n">
-        <v>608014</v>
+        <v>607991</v>
       </c>
       <c r="R349" t="n">
-        <v>7309638</v>
+        <v>7309608</v>
       </c>
       <c r="S349" t="n">
         <v>3</v>
@@ -39451,7 +39475,7 @@
       </c>
       <c r="Z349" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -39461,7 +39485,7 @@
       </c>
       <c r="AB349" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD349" t="b">
@@ -39470,7 +39494,6 @@
       <c r="AE349" t="b">
         <v>0</v>
       </c>
-      <c r="AF349" t="inlineStr"/>
       <c r="AG349" t="b">
         <v>0</v>
       </c>
@@ -39493,10 +39516,10 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>135349896</v>
+        <v>135349909</v>
       </c>
       <c r="B350" t="n">
-        <v>99217</v>
+        <v>106309</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -39504,34 +39527,38 @@
         </is>
       </c>
       <c r="E350" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I350" t="inlineStr"/>
+      <c r="J350" t="inlineStr"/>
+      <c r="K350" t="inlineStr"/>
+      <c r="L350" t="inlineStr"/>
+      <c r="N350" t="inlineStr"/>
       <c r="P350" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q350" t="n">
-        <v>608056</v>
+        <v>608014</v>
       </c>
       <c r="R350" t="n">
-        <v>7309695</v>
+        <v>7309638</v>
       </c>
       <c r="S350" t="n">
         <v>3</v>
@@ -39563,7 +39590,7 @@
       </c>
       <c r="Z350" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA350" t="inlineStr">
@@ -39573,7 +39600,7 @@
       </c>
       <c r="AB350" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD350" t="b">
@@ -39582,6 +39609,7 @@
       <c r="AE350" t="b">
         <v>0</v>
       </c>
+      <c r="AF350" t="inlineStr"/>
       <c r="AG350" t="b">
         <v>0</v>
       </c>
@@ -39604,10 +39632,10 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>135349910</v>
+        <v>135349896</v>
       </c>
       <c r="B351" t="n">
-        <v>103764</v>
+        <v>99217</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -39615,21 +39643,21 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>222004</v>
+        <v>221952</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I351" t="inlineStr"/>
@@ -39639,10 +39667,10 @@
         </is>
       </c>
       <c r="Q351" t="n">
-        <v>608014</v>
+        <v>608056</v>
       </c>
       <c r="R351" t="n">
-        <v>7309638</v>
+        <v>7309695</v>
       </c>
       <c r="S351" t="n">
         <v>3</v>
@@ -39674,7 +39702,7 @@
       </c>
       <c r="Z351" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA351" t="inlineStr">
@@ -39684,7 +39712,7 @@
       </c>
       <c r="AB351" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD351" t="b">
@@ -39715,10 +39743,10 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>135356148</v>
+        <v>135349910</v>
       </c>
       <c r="B352" t="n">
-        <v>104707</v>
+        <v>103764</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -39726,16 +39754,16 @@
         </is>
       </c>
       <c r="E352" t="n">
-        <v>222412</v>
+        <v>222004</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -39750,13 +39778,13 @@
         </is>
       </c>
       <c r="Q352" t="n">
-        <v>607978</v>
+        <v>608014</v>
       </c>
       <c r="R352" t="n">
-        <v>7309596</v>
+        <v>7309638</v>
       </c>
       <c r="S352" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T352" t="inlineStr">
         <is>
@@ -39785,7 +39813,7 @@
       </c>
       <c r="Z352" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA352" t="inlineStr">
@@ -39795,7 +39823,7 @@
       </c>
       <c r="AB352" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD352" t="b">
@@ -39810,12 +39838,12 @@
       <c r="AT352" t="inlineStr"/>
       <c r="AW352" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr">
@@ -39826,10 +39854,10 @@
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>135351867</v>
+        <v>135356148</v>
       </c>
       <c r="B353" t="n">
-        <v>99198</v>
+        <v>104707</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -39837,19 +39865,23 @@
         </is>
       </c>
       <c r="E353" t="n">
-        <v>223614</v>
+        <v>222412</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>Vanlig brudsporre</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. conopsea</t>
-        </is>
-      </c>
-      <c r="H353" t="inlineStr"/>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I353" t="inlineStr"/>
       <c r="P353" t="inlineStr">
         <is>
@@ -39857,13 +39889,13 @@
         </is>
       </c>
       <c r="Q353" t="n">
-        <v>608123</v>
+        <v>607978</v>
       </c>
       <c r="R353" t="n">
-        <v>7309661</v>
+        <v>7309596</v>
       </c>
       <c r="S353" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T353" t="inlineStr">
         <is>
@@ -39892,7 +39924,7 @@
       </c>
       <c r="Z353" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA353" t="inlineStr">
@@ -39902,7 +39934,7 @@
       </c>
       <c r="AB353" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD353" t="b">
@@ -39911,19 +39943,18 @@
       <c r="AE353" t="b">
         <v>0</v>
       </c>
-      <c r="AF353" t="inlineStr"/>
       <c r="AG353" t="b">
         <v>0</v>
       </c>
       <c r="AT353" t="inlineStr"/>
       <c r="AW353" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr">
@@ -39934,10 +39965,10 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>135349891</v>
+        <v>135351867</v>
       </c>
       <c r="B354" t="n">
-        <v>101293</v>
+        <v>99198</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -39945,23 +39976,19 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>224885</v>
+        <v>223614</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Vanlig brudsporre</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H354" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr"/>
       <c r="P354" t="inlineStr">
         <is>
@@ -39969,13 +39996,13 @@
         </is>
       </c>
       <c r="Q354" t="n">
-        <v>608082</v>
+        <v>608123</v>
       </c>
       <c r="R354" t="n">
-        <v>7309684</v>
+        <v>7309661</v>
       </c>
       <c r="S354" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T354" t="inlineStr">
         <is>
@@ -40004,7 +40031,7 @@
       </c>
       <c r="Z354" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA354" t="inlineStr">
@@ -40014,7 +40041,7 @@
       </c>
       <c r="AB354" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD354" t="b">
@@ -40023,18 +40050,19 @@
       <c r="AE354" t="b">
         <v>0</v>
       </c>
+      <c r="AF354" t="inlineStr"/>
       <c r="AG354" t="b">
         <v>0</v>
       </c>
       <c r="AT354" t="inlineStr"/>
       <c r="AW354" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX354" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY354" t="inlineStr">
@@ -40045,48 +40073,48 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>80987080</v>
+        <v>135349891</v>
       </c>
       <c r="B355" t="n">
-        <v>91905</v>
+        <v>101293</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>1108</v>
+        <v>224885</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I355" t="inlineStr"/>
       <c r="P355" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q355" t="n">
-        <v>607814</v>
+        <v>608082</v>
       </c>
       <c r="R355" t="n">
-        <v>7310183</v>
+        <v>7309684</v>
       </c>
       <c r="S355" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T355" t="inlineStr">
         <is>
@@ -40110,12 +40138,22 @@
       </c>
       <c r="Y355" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA355" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB355" t="inlineStr">
+        <is>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD355" t="b">
@@ -40130,19 +40168,23 @@
       <c r="AT355" t="inlineStr"/>
       <c r="AW355" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX355" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY355" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY355" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>80987082</v>
+        <v>80987080</v>
       </c>
       <c r="B356" t="n">
         <v>91905</v>
@@ -40177,10 +40219,10 @@
         </is>
       </c>
       <c r="Q356" t="n">
-        <v>607707</v>
+        <v>607814</v>
       </c>
       <c r="R356" t="n">
-        <v>7310262</v>
+        <v>7310183</v>
       </c>
       <c r="S356" t="n">
         <v>10</v>
@@ -40239,7 +40281,7 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>80987083</v>
+        <v>80987082</v>
       </c>
       <c r="B357" t="n">
         <v>91905</v>
@@ -40274,10 +40316,10 @@
         </is>
       </c>
       <c r="Q357" t="n">
-        <v>607709</v>
+        <v>607707</v>
       </c>
       <c r="R357" t="n">
-        <v>7310293</v>
+        <v>7310262</v>
       </c>
       <c r="S357" t="n">
         <v>10</v>
@@ -40336,10 +40378,10 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>80987064</v>
+        <v>80987083</v>
       </c>
       <c r="B358" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -40347,21 +40389,21 @@
         </is>
       </c>
       <c r="E358" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I358" t="inlineStr"/>
@@ -40371,10 +40413,10 @@
         </is>
       </c>
       <c r="Q358" t="n">
-        <v>607818</v>
+        <v>607709</v>
       </c>
       <c r="R358" t="n">
-        <v>7310228</v>
+        <v>7310293</v>
       </c>
       <c r="S358" t="n">
         <v>10</v>
@@ -40433,10 +40475,10 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>80987115</v>
+        <v>80987064</v>
       </c>
       <c r="B359" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -40444,21 +40486,21 @@
         </is>
       </c>
       <c r="E359" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I359" t="inlineStr"/>
@@ -40468,10 +40510,10 @@
         </is>
       </c>
       <c r="Q359" t="n">
-        <v>607759</v>
+        <v>607818</v>
       </c>
       <c r="R359" t="n">
-        <v>7310182</v>
+        <v>7310228</v>
       </c>
       <c r="S359" t="n">
         <v>10</v>
@@ -40530,7 +40572,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>80987117</v>
+        <v>80987115</v>
       </c>
       <c r="B360" t="n">
         <v>83173</v>
@@ -40565,10 +40607,10 @@
         </is>
       </c>
       <c r="Q360" t="n">
-        <v>607751</v>
+        <v>607759</v>
       </c>
       <c r="R360" t="n">
-        <v>7310193</v>
+        <v>7310182</v>
       </c>
       <c r="S360" t="n">
         <v>10</v>
@@ -40627,32 +40669,32 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>80987066</v>
+        <v>80987117</v>
       </c>
       <c r="B361" t="n">
-        <v>92632</v>
+        <v>83173</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I361" t="inlineStr"/>
@@ -40662,10 +40704,10 @@
         </is>
       </c>
       <c r="Q361" t="n">
-        <v>607822</v>
+        <v>607751</v>
       </c>
       <c r="R361" t="n">
-        <v>7310199</v>
+        <v>7310193</v>
       </c>
       <c r="S361" t="n">
         <v>10</v>
@@ -40724,48 +40766,48 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>135351855</v>
+        <v>80987066</v>
       </c>
       <c r="B362" t="n">
-        <v>79373</v>
+        <v>92632</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I362" t="inlineStr"/>
       <c r="P362" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q362" t="n">
-        <v>607677</v>
+        <v>607822</v>
       </c>
       <c r="R362" t="n">
-        <v>7310726</v>
+        <v>7310199</v>
       </c>
       <c r="S362" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="T362" t="inlineStr">
         <is>
@@ -40789,22 +40831,12 @@
       </c>
       <c r="Y362" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z362" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA362" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB362" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD362" t="b">
@@ -40819,64 +40851,60 @@
       <c r="AT362" t="inlineStr"/>
       <c r="AW362" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY362" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY362" t="inlineStr"/>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>80987069</v>
+        <v>135351855</v>
       </c>
       <c r="B363" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I363" t="inlineStr"/>
       <c r="P363" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q363" t="n">
-        <v>607759</v>
+        <v>607677</v>
       </c>
       <c r="R363" t="n">
-        <v>7310308</v>
+        <v>7310726</v>
       </c>
       <c r="S363" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="T363" t="inlineStr">
         <is>
@@ -40900,12 +40928,22 @@
       </c>
       <c r="Y363" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA363" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB363" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD363" t="b">
@@ -40920,22 +40958,26 @@
       <c r="AT363" t="inlineStr"/>
       <c r="AW363" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY363" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY363" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>80987072</v>
+        <v>80987069</v>
       </c>
       <c r="B364" t="n">
-        <v>92208</v>
+        <v>57953</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -40943,21 +40985,21 @@
         </is>
       </c>
       <c r="E364" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I364" t="inlineStr"/>
@@ -40967,10 +41009,10 @@
         </is>
       </c>
       <c r="Q364" t="n">
-        <v>608406</v>
+        <v>607759</v>
       </c>
       <c r="R364" t="n">
-        <v>7309441</v>
+        <v>7310308</v>
       </c>
       <c r="S364" t="n">
         <v>10</v>
@@ -41029,10 +41071,10 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>80987076</v>
+        <v>80987072</v>
       </c>
       <c r="B365" t="n">
-        <v>79406</v>
+        <v>92208</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -41040,21 +41082,21 @@
         </is>
       </c>
       <c r="E365" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I365" t="inlineStr"/>
@@ -41064,10 +41106,10 @@
         </is>
       </c>
       <c r="Q365" t="n">
-        <v>608479</v>
+        <v>608406</v>
       </c>
       <c r="R365" t="n">
-        <v>7309341</v>
+        <v>7309441</v>
       </c>
       <c r="S365" t="n">
         <v>10</v>
@@ -41126,7 +41168,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>80987077</v>
+        <v>80987076</v>
       </c>
       <c r="B366" t="n">
         <v>79406</v>
@@ -41161,10 +41203,10 @@
         </is>
       </c>
       <c r="Q366" t="n">
-        <v>608374</v>
+        <v>608479</v>
       </c>
       <c r="R366" t="n">
-        <v>7309488</v>
+        <v>7309341</v>
       </c>
       <c r="S366" t="n">
         <v>10</v>
@@ -41223,10 +41265,10 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>80987081</v>
+        <v>80987077</v>
       </c>
       <c r="B367" t="n">
-        <v>91905</v>
+        <v>79406</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -41234,21 +41276,21 @@
         </is>
       </c>
       <c r="E367" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I367" t="inlineStr"/>
@@ -41258,10 +41300,10 @@
         </is>
       </c>
       <c r="Q367" t="n">
-        <v>608446</v>
+        <v>608374</v>
       </c>
       <c r="R367" t="n">
-        <v>7309372</v>
+        <v>7309488</v>
       </c>
       <c r="S367" t="n">
         <v>10</v>
@@ -41320,10 +41362,10 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>80987060</v>
+        <v>80987081</v>
       </c>
       <c r="B368" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -41331,21 +41373,21 @@
         </is>
       </c>
       <c r="E368" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I368" t="inlineStr"/>
@@ -41355,7 +41397,7 @@
         </is>
       </c>
       <c r="Q368" t="n">
-        <v>608459</v>
+        <v>608446</v>
       </c>
       <c r="R368" t="n">
         <v>7309372</v>
@@ -41417,7 +41459,7 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>80987061</v>
+        <v>80987060</v>
       </c>
       <c r="B369" t="n">
         <v>91909</v>
@@ -41452,10 +41494,10 @@
         </is>
       </c>
       <c r="Q369" t="n">
-        <v>608386</v>
+        <v>608459</v>
       </c>
       <c r="R369" t="n">
-        <v>7309399</v>
+        <v>7309372</v>
       </c>
       <c r="S369" t="n">
         <v>10</v>
@@ -41514,7 +41556,7 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>80987062</v>
+        <v>80987061</v>
       </c>
       <c r="B370" t="n">
         <v>91909</v>
@@ -41549,10 +41591,10 @@
         </is>
       </c>
       <c r="Q370" t="n">
-        <v>608403</v>
+        <v>608386</v>
       </c>
       <c r="R370" t="n">
-        <v>7309432</v>
+        <v>7309399</v>
       </c>
       <c r="S370" t="n">
         <v>10</v>
@@ -41611,7 +41653,7 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>80987063</v>
+        <v>80987062</v>
       </c>
       <c r="B371" t="n">
         <v>91909</v>
@@ -41646,10 +41688,10 @@
         </is>
       </c>
       <c r="Q371" t="n">
-        <v>608422</v>
+        <v>608403</v>
       </c>
       <c r="R371" t="n">
-        <v>7309394</v>
+        <v>7309432</v>
       </c>
       <c r="S371" t="n">
         <v>10</v>
@@ -41708,10 +41750,10 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>80987114</v>
+        <v>80987063</v>
       </c>
       <c r="B372" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -41719,21 +41761,21 @@
         </is>
       </c>
       <c r="E372" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I372" t="inlineStr"/>
@@ -41743,10 +41785,10 @@
         </is>
       </c>
       <c r="Q372" t="n">
-        <v>608390</v>
+        <v>608422</v>
       </c>
       <c r="R372" t="n">
-        <v>7309533</v>
+        <v>7309394</v>
       </c>
       <c r="S372" t="n">
         <v>10</v>
@@ -41805,32 +41847,32 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>80987067</v>
+        <v>80987114</v>
       </c>
       <c r="B373" t="n">
-        <v>92632</v>
+        <v>83173</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I373" t="inlineStr"/>
@@ -41840,10 +41882,10 @@
         </is>
       </c>
       <c r="Q373" t="n">
-        <v>608399</v>
+        <v>608390</v>
       </c>
       <c r="R373" t="n">
-        <v>7309450</v>
+        <v>7309533</v>
       </c>
       <c r="S373" t="n">
         <v>10</v>
@@ -41899,6 +41941,103 @@
         </is>
       </c>
       <c r="AY373" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="n">
+        <v>80987067</v>
+      </c>
+      <c r="B374" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr"/>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>Veddeklinten, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q374" t="n">
+        <v>608399</v>
+      </c>
+      <c r="R374" t="n">
+        <v>7309450</v>
+      </c>
+      <c r="S374" t="n">
+        <v>10</v>
+      </c>
+      <c r="T374" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U374" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V374" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W374" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y374" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AA374" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AD374" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE374" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG374" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT374" t="inlineStr"/>
+      <c r="AW374" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX374" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY374" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -5309,11 +5309,16 @@
           <t>13:15</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Kan det vara lappmes?</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG42" t="b">
         <v>0</v>
@@ -6845,6 +6850,9 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
@@ -6905,6 +6913,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6934,7 +6943,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY56" t="inlineStr"/>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY663"/>
+  <dimension ref="A1:AY662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63780,10 +63780,10 @@
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>135388298</v>
+        <v>135349898</v>
       </c>
       <c r="B567" t="n">
-        <v>93089</v>
+        <v>79373</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -63791,34 +63791,34 @@
         </is>
       </c>
       <c r="E567" t="n">
-        <v>5906</v>
+        <v>6425</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>Olivbrun kremla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>Russula olivobrunnea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Ruots. &amp; Vauras</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I567" t="inlineStr"/>
       <c r="P567" t="inlineStr">
         <is>
-          <t>Laisdalen päronberget, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q567" t="n">
-        <v>608033</v>
+        <v>608046</v>
       </c>
       <c r="R567" t="n">
-        <v>7309659</v>
+        <v>7309697</v>
       </c>
       <c r="S567" t="n">
         <v>3</v>
@@ -63845,22 +63845,22 @@
       </c>
       <c r="Y567" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z567" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA567" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB567" t="inlineStr">
         <is>
-          <t>16:13</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD567" t="b">
@@ -63869,19 +63869,18 @@
       <c r="AE567" t="b">
         <v>0</v>
       </c>
-      <c r="AF567" t="inlineStr"/>
       <c r="AG567" t="b">
         <v>0</v>
       </c>
       <c r="AT567" t="inlineStr"/>
       <c r="AW567" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX567" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY567" t="inlineStr">
@@ -63892,7 +63891,7 @@
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>135349898</v>
+        <v>135349900</v>
       </c>
       <c r="B568" t="n">
         <v>79373</v>
@@ -63927,10 +63926,10 @@
         </is>
       </c>
       <c r="Q568" t="n">
-        <v>608046</v>
+        <v>608013</v>
       </c>
       <c r="R568" t="n">
-        <v>7309697</v>
+        <v>7309723</v>
       </c>
       <c r="S568" t="n">
         <v>3</v>
@@ -63962,7 +63961,7 @@
       </c>
       <c r="Z568" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA568" t="inlineStr">
@@ -63972,7 +63971,7 @@
       </c>
       <c r="AB568" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD568" t="b">
@@ -64003,7 +64002,7 @@
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>135349900</v>
+        <v>135349903</v>
       </c>
       <c r="B569" t="n">
         <v>79373</v>
@@ -64038,10 +64037,10 @@
         </is>
       </c>
       <c r="Q569" t="n">
-        <v>608013</v>
+        <v>607999</v>
       </c>
       <c r="R569" t="n">
-        <v>7309723</v>
+        <v>7309728</v>
       </c>
       <c r="S569" t="n">
         <v>3</v>
@@ -64073,7 +64072,7 @@
       </c>
       <c r="Z569" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA569" t="inlineStr">
@@ -64083,7 +64082,7 @@
       </c>
       <c r="AB569" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD569" t="b">
@@ -64114,7 +64113,7 @@
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>135349903</v>
+        <v>135349908</v>
       </c>
       <c r="B570" t="n">
         <v>79373</v>
@@ -64149,13 +64148,13 @@
         </is>
       </c>
       <c r="Q570" t="n">
-        <v>607999</v>
+        <v>608018</v>
       </c>
       <c r="R570" t="n">
-        <v>7309728</v>
+        <v>7309659</v>
       </c>
       <c r="S570" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T570" t="inlineStr">
         <is>
@@ -64184,7 +64183,7 @@
       </c>
       <c r="Z570" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA570" t="inlineStr">
@@ -64194,7 +64193,7 @@
       </c>
       <c r="AB570" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD570" t="b">
@@ -64225,7 +64224,7 @@
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>135349908</v>
+        <v>135349917</v>
       </c>
       <c r="B571" t="n">
         <v>79373</v>
@@ -64260,10 +64259,10 @@
         </is>
       </c>
       <c r="Q571" t="n">
-        <v>608018</v>
+        <v>607981</v>
       </c>
       <c r="R571" t="n">
-        <v>7309659</v>
+        <v>7309626</v>
       </c>
       <c r="S571" t="n">
         <v>4</v>
@@ -64295,7 +64294,7 @@
       </c>
       <c r="Z571" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA571" t="inlineStr">
@@ -64305,7 +64304,7 @@
       </c>
       <c r="AB571" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD571" t="b">
@@ -64336,7 +64335,7 @@
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>135349917</v>
+        <v>135378171</v>
       </c>
       <c r="B572" t="n">
         <v>79373</v>
@@ -64371,10 +64370,10 @@
         </is>
       </c>
       <c r="Q572" t="n">
-        <v>607981</v>
+        <v>607795</v>
       </c>
       <c r="R572" t="n">
-        <v>7309626</v>
+        <v>7310000</v>
       </c>
       <c r="S572" t="n">
         <v>4</v>
@@ -64401,22 +64400,22 @@
       </c>
       <c r="Y572" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z572" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA572" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB572" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD572" t="b">
@@ -64447,7 +64446,7 @@
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>135378171</v>
+        <v>135378177</v>
       </c>
       <c r="B573" t="n">
         <v>79373</v>
@@ -64482,10 +64481,10 @@
         </is>
       </c>
       <c r="Q573" t="n">
-        <v>607795</v>
+        <v>607747</v>
       </c>
       <c r="R573" t="n">
-        <v>7310000</v>
+        <v>7309987</v>
       </c>
       <c r="S573" t="n">
         <v>4</v>
@@ -64517,7 +64516,7 @@
       </c>
       <c r="Z573" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA573" t="inlineStr">
@@ -64527,7 +64526,7 @@
       </c>
       <c r="AB573" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD573" t="b">
@@ -64558,7 +64557,7 @@
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>135378177</v>
+        <v>135384317</v>
       </c>
       <c r="B574" t="n">
         <v>79373</v>
@@ -64589,17 +64588,17 @@
       <c r="I574" t="inlineStr"/>
       <c r="P574" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q574" t="n">
-        <v>607747</v>
+        <v>608065</v>
       </c>
       <c r="R574" t="n">
-        <v>7309987</v>
+        <v>7309664</v>
       </c>
       <c r="S574" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T574" t="inlineStr">
         <is>
@@ -64628,7 +64627,7 @@
       </c>
       <c r="Z574" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA574" t="inlineStr">
@@ -64638,7 +64637,7 @@
       </c>
       <c r="AB574" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD574" t="b">
@@ -64653,12 +64652,12 @@
       <c r="AT574" t="inlineStr"/>
       <c r="AW574" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX574" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY574" t="inlineStr">
@@ -64669,7 +64668,7 @@
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>135384317</v>
+        <v>135384321</v>
       </c>
       <c r="B575" t="n">
         <v>79373</v>
@@ -64704,10 +64703,10 @@
         </is>
       </c>
       <c r="Q575" t="n">
-        <v>608065</v>
+        <v>608050</v>
       </c>
       <c r="R575" t="n">
-        <v>7309664</v>
+        <v>7309656</v>
       </c>
       <c r="S575" t="n">
         <v>5</v>
@@ -64739,7 +64738,7 @@
       </c>
       <c r="Z575" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA575" t="inlineStr">
@@ -64749,7 +64748,7 @@
       </c>
       <c r="AB575" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD575" t="b">
@@ -64780,7 +64779,7 @@
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>135384321</v>
+        <v>135384326</v>
       </c>
       <c r="B576" t="n">
         <v>79373</v>
@@ -64815,10 +64814,10 @@
         </is>
       </c>
       <c r="Q576" t="n">
-        <v>608050</v>
+        <v>608033</v>
       </c>
       <c r="R576" t="n">
-        <v>7309656</v>
+        <v>7309664</v>
       </c>
       <c r="S576" t="n">
         <v>5</v>
@@ -64850,7 +64849,7 @@
       </c>
       <c r="Z576" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA576" t="inlineStr">
@@ -64860,7 +64859,7 @@
       </c>
       <c r="AB576" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD576" t="b">
@@ -64891,7 +64890,7 @@
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>135384326</v>
+        <v>135385234</v>
       </c>
       <c r="B577" t="n">
         <v>79373</v>
@@ -64922,17 +64921,17 @@
       <c r="I577" t="inlineStr"/>
       <c r="P577" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q577" t="n">
-        <v>608033</v>
+        <v>607787</v>
       </c>
       <c r="R577" t="n">
-        <v>7309664</v>
+        <v>7310002</v>
       </c>
       <c r="S577" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T577" t="inlineStr">
         <is>
@@ -64961,7 +64960,7 @@
       </c>
       <c r="Z577" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA577" t="inlineStr">
@@ -64971,7 +64970,7 @@
       </c>
       <c r="AB577" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD577" t="b">
@@ -64986,12 +64985,12 @@
       <c r="AT577" t="inlineStr"/>
       <c r="AW577" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX577" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY577" t="inlineStr">
@@ -65002,7 +65001,7 @@
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>135385234</v>
+        <v>135385291</v>
       </c>
       <c r="B578" t="n">
         <v>79373</v>
@@ -65037,13 +65036,13 @@
         </is>
       </c>
       <c r="Q578" t="n">
-        <v>607787</v>
+        <v>607837</v>
       </c>
       <c r="R578" t="n">
-        <v>7310002</v>
+        <v>7309959</v>
       </c>
       <c r="S578" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T578" t="inlineStr">
         <is>
@@ -65072,7 +65071,7 @@
       </c>
       <c r="Z578" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA578" t="inlineStr">
@@ -65082,7 +65081,7 @@
       </c>
       <c r="AB578" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD578" t="b">
@@ -65113,7 +65112,7 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>135385291</v>
+        <v>135385299</v>
       </c>
       <c r="B579" t="n">
         <v>79373</v>
@@ -65148,10 +65147,10 @@
         </is>
       </c>
       <c r="Q579" t="n">
-        <v>607837</v>
+        <v>607852</v>
       </c>
       <c r="R579" t="n">
-        <v>7309959</v>
+        <v>7309897</v>
       </c>
       <c r="S579" t="n">
         <v>5</v>
@@ -65183,7 +65182,7 @@
       </c>
       <c r="Z579" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA579" t="inlineStr">
@@ -65193,7 +65192,7 @@
       </c>
       <c r="AB579" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD579" t="b">
@@ -65224,7 +65223,7 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>135385299</v>
+        <v>135385304</v>
       </c>
       <c r="B580" t="n">
         <v>79373</v>
@@ -65259,13 +65258,13 @@
         </is>
       </c>
       <c r="Q580" t="n">
-        <v>607852</v>
+        <v>607802</v>
       </c>
       <c r="R580" t="n">
-        <v>7309897</v>
+        <v>7309878</v>
       </c>
       <c r="S580" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T580" t="inlineStr">
         <is>
@@ -65294,7 +65293,7 @@
       </c>
       <c r="Z580" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA580" t="inlineStr">
@@ -65304,7 +65303,7 @@
       </c>
       <c r="AB580" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD580" t="b">
@@ -65335,7 +65334,7 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>135385304</v>
+        <v>135385313</v>
       </c>
       <c r="B581" t="n">
         <v>79373</v>
@@ -65370,13 +65369,13 @@
         </is>
       </c>
       <c r="Q581" t="n">
-        <v>607802</v>
+        <v>607895</v>
       </c>
       <c r="R581" t="n">
-        <v>7309878</v>
+        <v>7309854</v>
       </c>
       <c r="S581" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T581" t="inlineStr">
         <is>
@@ -65405,7 +65404,7 @@
       </c>
       <c r="Z581" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA581" t="inlineStr">
@@ -65415,7 +65414,7 @@
       </c>
       <c r="AB581" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD581" t="b">
@@ -65446,7 +65445,7 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>135385313</v>
+        <v>135385317</v>
       </c>
       <c r="B582" t="n">
         <v>79373</v>
@@ -65481,10 +65480,10 @@
         </is>
       </c>
       <c r="Q582" t="n">
-        <v>607895</v>
+        <v>607886</v>
       </c>
       <c r="R582" t="n">
-        <v>7309854</v>
+        <v>7309931</v>
       </c>
       <c r="S582" t="n">
         <v>5</v>
@@ -65516,7 +65515,7 @@
       </c>
       <c r="Z582" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA582" t="inlineStr">
@@ -65526,7 +65525,7 @@
       </c>
       <c r="AB582" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD582" t="b">
@@ -65557,7 +65556,7 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>135385317</v>
+        <v>135385321</v>
       </c>
       <c r="B583" t="n">
         <v>79373</v>
@@ -65592,10 +65591,10 @@
         </is>
       </c>
       <c r="Q583" t="n">
-        <v>607886</v>
+        <v>608036</v>
       </c>
       <c r="R583" t="n">
-        <v>7309931</v>
+        <v>7309659</v>
       </c>
       <c r="S583" t="n">
         <v>5</v>
@@ -65627,7 +65626,7 @@
       </c>
       <c r="Z583" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA583" t="inlineStr">
@@ -65637,7 +65636,7 @@
       </c>
       <c r="AB583" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD583" t="b">
@@ -65668,7 +65667,7 @@
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>135385321</v>
+        <v>135385325</v>
       </c>
       <c r="B584" t="n">
         <v>79373</v>
@@ -65703,13 +65702,13 @@
         </is>
       </c>
       <c r="Q584" t="n">
-        <v>608036</v>
+        <v>608048</v>
       </c>
       <c r="R584" t="n">
-        <v>7309659</v>
+        <v>7309630</v>
       </c>
       <c r="S584" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T584" t="inlineStr">
         <is>
@@ -65738,7 +65737,7 @@
       </c>
       <c r="Z584" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA584" t="inlineStr">
@@ -65748,7 +65747,7 @@
       </c>
       <c r="AB584" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD584" t="b">
@@ -65779,7 +65778,7 @@
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>135385325</v>
+        <v>135393119</v>
       </c>
       <c r="B585" t="n">
         <v>79373</v>
@@ -65810,17 +65809,17 @@
       <c r="I585" t="inlineStr"/>
       <c r="P585" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q585" t="n">
-        <v>608048</v>
+        <v>608112</v>
       </c>
       <c r="R585" t="n">
-        <v>7309630</v>
+        <v>7309586</v>
       </c>
       <c r="S585" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T585" t="inlineStr">
         <is>
@@ -65849,7 +65848,7 @@
       </c>
       <c r="Z585" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA585" t="inlineStr">
@@ -65859,7 +65858,7 @@
       </c>
       <c r="AB585" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD585" t="b">
@@ -65874,23 +65873,19 @@
       <c r="AT585" t="inlineStr"/>
       <c r="AW585" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX585" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY585" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY585" t="inlineStr"/>
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>135393119</v>
+        <v>135393137</v>
       </c>
       <c r="B586" t="n">
         <v>79373</v>
@@ -65925,10 +65920,10 @@
         </is>
       </c>
       <c r="Q586" t="n">
-        <v>608112</v>
+        <v>607967</v>
       </c>
       <c r="R586" t="n">
-        <v>7309586</v>
+        <v>7309711</v>
       </c>
       <c r="S586" t="n">
         <v>5</v>
@@ -65960,7 +65955,7 @@
       </c>
       <c r="Z586" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA586" t="inlineStr">
@@ -65970,7 +65965,7 @@
       </c>
       <c r="AB586" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD586" t="b">
@@ -65997,48 +65992,48 @@
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>135393137</v>
+        <v>135378172</v>
       </c>
       <c r="B587" t="n">
-        <v>79373</v>
+        <v>83358</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E587" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I587" t="inlineStr"/>
       <c r="P587" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q587" t="n">
-        <v>607967</v>
+        <v>607794</v>
       </c>
       <c r="R587" t="n">
-        <v>7309711</v>
+        <v>7309999</v>
       </c>
       <c r="S587" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T587" t="inlineStr">
         <is>
@@ -66067,7 +66062,7 @@
       </c>
       <c r="Z587" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA587" t="inlineStr">
@@ -66077,7 +66072,7 @@
       </c>
       <c r="AB587" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD587" t="b">
@@ -66092,19 +66087,23 @@
       <c r="AT587" t="inlineStr"/>
       <c r="AW587" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX587" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY587" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY587" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>135378172</v>
+        <v>135378176</v>
       </c>
       <c r="B588" t="n">
         <v>83358</v>
@@ -66139,13 +66138,13 @@
         </is>
       </c>
       <c r="Q588" t="n">
-        <v>607794</v>
+        <v>607782</v>
       </c>
       <c r="R588" t="n">
-        <v>7309999</v>
+        <v>7310008</v>
       </c>
       <c r="S588" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T588" t="inlineStr">
         <is>
@@ -66174,7 +66173,7 @@
       </c>
       <c r="Z588" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA588" t="inlineStr">
@@ -66184,7 +66183,7 @@
       </c>
       <c r="AB588" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD588" t="b">
@@ -66215,7 +66214,7 @@
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>135378176</v>
+        <v>135385230</v>
       </c>
       <c r="B589" t="n">
         <v>83358</v>
@@ -66246,17 +66245,17 @@
       <c r="I589" t="inlineStr"/>
       <c r="P589" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q589" t="n">
-        <v>607782</v>
+        <v>607789</v>
       </c>
       <c r="R589" t="n">
-        <v>7310008</v>
+        <v>7309990</v>
       </c>
       <c r="S589" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="T589" t="inlineStr">
         <is>
@@ -66285,7 +66284,7 @@
       </c>
       <c r="Z589" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA589" t="inlineStr">
@@ -66295,7 +66294,7 @@
       </c>
       <c r="AB589" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD589" t="b">
@@ -66310,12 +66309,12 @@
       <c r="AT589" t="inlineStr"/>
       <c r="AW589" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX589" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY589" t="inlineStr">
@@ -66326,7 +66325,7 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>135385230</v>
+        <v>135385287</v>
       </c>
       <c r="B590" t="n">
         <v>83358</v>
@@ -66361,13 +66360,13 @@
         </is>
       </c>
       <c r="Q590" t="n">
-        <v>607789</v>
+        <v>607783</v>
       </c>
       <c r="R590" t="n">
-        <v>7309990</v>
+        <v>7310048</v>
       </c>
       <c r="S590" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T590" t="inlineStr">
         <is>
@@ -66396,7 +66395,7 @@
       </c>
       <c r="Z590" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA590" t="inlineStr">
@@ -66406,7 +66405,7 @@
       </c>
       <c r="AB590" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD590" t="b">
@@ -66437,7 +66436,7 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>135385287</v>
+        <v>135385295</v>
       </c>
       <c r="B591" t="n">
         <v>83358</v>
@@ -66472,10 +66471,10 @@
         </is>
       </c>
       <c r="Q591" t="n">
-        <v>607783</v>
+        <v>607872</v>
       </c>
       <c r="R591" t="n">
-        <v>7310048</v>
+        <v>7309907</v>
       </c>
       <c r="S591" t="n">
         <v>5</v>
@@ -66507,7 +66506,7 @@
       </c>
       <c r="Z591" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA591" t="inlineStr">
@@ -66517,7 +66516,7 @@
       </c>
       <c r="AB591" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD591" t="b">
@@ -66548,7 +66547,7 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>135385295</v>
+        <v>135393123</v>
       </c>
       <c r="B592" t="n">
         <v>83358</v>
@@ -66579,14 +66578,14 @@
       <c r="I592" t="inlineStr"/>
       <c r="P592" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q592" t="n">
-        <v>607872</v>
+        <v>608142</v>
       </c>
       <c r="R592" t="n">
-        <v>7309907</v>
+        <v>7309598</v>
       </c>
       <c r="S592" t="n">
         <v>5</v>
@@ -66618,7 +66617,7 @@
       </c>
       <c r="Z592" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA592" t="inlineStr">
@@ -66628,7 +66627,7 @@
       </c>
       <c r="AB592" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD592" t="b">
@@ -66643,48 +66642,44 @@
       <c r="AT592" t="inlineStr"/>
       <c r="AW592" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX592" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY592" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY592" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>135393123</v>
+        <v>135385194</v>
       </c>
       <c r="B593" t="n">
-        <v>83358</v>
+        <v>80493</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I593" t="inlineStr"/>
@@ -66694,10 +66689,10 @@
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>608142</v>
+        <v>608065</v>
       </c>
       <c r="R593" t="n">
-        <v>7309598</v>
+        <v>7309659</v>
       </c>
       <c r="S593" t="n">
         <v>5</v>
@@ -66729,7 +66724,7 @@
       </c>
       <c r="Z593" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA593" t="inlineStr">
@@ -66739,7 +66734,7 @@
       </c>
       <c r="AB593" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD593" t="b">
@@ -66754,22 +66749,26 @@
       <c r="AT593" t="inlineStr"/>
       <c r="AW593" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX593" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY593" t="inlineStr"/>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY593" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>135385194</v>
+        <v>135349918</v>
       </c>
       <c r="B594" t="n">
-        <v>80493</v>
+        <v>57972</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -66777,37 +66776,42 @@
         </is>
       </c>
       <c r="E594" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I594" t="inlineStr"/>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P594" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>608065</v>
+        <v>607960</v>
       </c>
       <c r="R594" t="n">
-        <v>7309659</v>
+        <v>7309607</v>
       </c>
       <c r="S594" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
@@ -66831,22 +66835,22 @@
       </c>
       <c r="Y594" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z594" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA594" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB594" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD594" t="b">
@@ -66861,12 +66865,12 @@
       <c r="AT594" t="inlineStr"/>
       <c r="AW594" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX594" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY594" t="inlineStr">
@@ -66877,27 +66881,27 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>135349918</v>
+        <v>135349901</v>
       </c>
       <c r="B595" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -66917,13 +66921,13 @@
         </is>
       </c>
       <c r="Q595" t="n">
-        <v>607960</v>
+        <v>608001</v>
       </c>
       <c r="R595" t="n">
-        <v>7309607</v>
+        <v>7309725</v>
       </c>
       <c r="S595" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T595" t="inlineStr">
         <is>
@@ -66952,7 +66956,7 @@
       </c>
       <c r="Z595" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA595" t="inlineStr">
@@ -66962,7 +66966,12 @@
       </c>
       <c r="AB595" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AC595" t="inlineStr">
+        <is>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD595" t="b">
@@ -66993,7 +67002,7 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>135349901</v>
+        <v>135349904</v>
       </c>
       <c r="B596" t="n">
         <v>57975</v>
@@ -67033,13 +67042,13 @@
         </is>
       </c>
       <c r="Q596" t="n">
-        <v>608001</v>
+        <v>607987</v>
       </c>
       <c r="R596" t="n">
-        <v>7309725</v>
+        <v>7309708</v>
       </c>
       <c r="S596" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T596" t="inlineStr">
         <is>
@@ -67068,7 +67077,7 @@
       </c>
       <c r="Z596" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA596" t="inlineStr">
@@ -67078,19 +67087,19 @@
       </c>
       <c r="AB596" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC596" t="inlineStr">
         <is>
-          <t>äldre ringhack</t>
+          <t>skalad klen gran</t>
         </is>
       </c>
       <c r="AD596" t="b">
         <v>0</v>
       </c>
       <c r="AE596" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG596" t="b">
         <v>0</v>
@@ -67114,7 +67123,7 @@
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>135349904</v>
+        <v>135378174</v>
       </c>
       <c r="B597" t="n">
         <v>57975</v>
@@ -67145,7 +67154,7 @@
       <c r="I597" t="inlineStr"/>
       <c r="M597" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P597" t="inlineStr">
@@ -67154,13 +67163,13 @@
         </is>
       </c>
       <c r="Q597" t="n">
-        <v>607987</v>
+        <v>607782</v>
       </c>
       <c r="R597" t="n">
-        <v>7309708</v>
+        <v>7310010</v>
       </c>
       <c r="S597" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T597" t="inlineStr">
         <is>
@@ -67184,34 +67193,34 @@
       </c>
       <c r="Y597" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z597" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA597" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB597" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC597" t="inlineStr">
         <is>
-          <t>skalad klen gran</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD597" t="b">
         <v>0</v>
       </c>
       <c r="AE597" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG597" t="b">
         <v>0</v>
@@ -67235,7 +67244,7 @@
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>135378174</v>
+        <v>135378178</v>
       </c>
       <c r="B598" t="n">
         <v>57975</v>
@@ -67266,7 +67275,7 @@
       <c r="I598" t="inlineStr"/>
       <c r="M598" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P598" t="inlineStr">
@@ -67275,10 +67284,10 @@
         </is>
       </c>
       <c r="Q598" t="n">
-        <v>607782</v>
+        <v>607697</v>
       </c>
       <c r="R598" t="n">
-        <v>7310010</v>
+        <v>7309979</v>
       </c>
       <c r="S598" t="n">
         <v>4</v>
@@ -67310,7 +67319,7 @@
       </c>
       <c r="Z598" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA598" t="inlineStr">
@@ -67320,19 +67329,19 @@
       </c>
       <c r="AB598" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC598" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>skalad klen gran</t>
         </is>
       </c>
       <c r="AD598" t="b">
         <v>0</v>
       </c>
       <c r="AE598" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG598" t="b">
         <v>0</v>
@@ -67356,7 +67365,7 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>135378178</v>
+        <v>135378180</v>
       </c>
       <c r="B599" t="n">
         <v>57975</v>
@@ -67396,13 +67405,13 @@
         </is>
       </c>
       <c r="Q599" t="n">
-        <v>607697</v>
+        <v>607701</v>
       </c>
       <c r="R599" t="n">
         <v>7309979</v>
       </c>
       <c r="S599" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T599" t="inlineStr">
         <is>
@@ -67431,7 +67440,7 @@
       </c>
       <c r="Z599" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA599" t="inlineStr">
@@ -67441,19 +67450,19 @@
       </c>
       <c r="AB599" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC599" t="inlineStr">
         <is>
-          <t>skalad klen gran</t>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD599" t="b">
         <v>0</v>
       </c>
       <c r="AE599" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG599" t="b">
         <v>0</v>
@@ -67477,7 +67486,7 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>135378180</v>
+        <v>135382861</v>
       </c>
       <c r="B600" t="n">
         <v>57975</v>
@@ -67506,24 +67515,19 @@
         </is>
       </c>
       <c r="I600" t="inlineStr"/>
-      <c r="M600" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P600" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q600" t="n">
-        <v>607701</v>
+        <v>607775</v>
       </c>
       <c r="R600" t="n">
-        <v>7309979</v>
+        <v>7309978</v>
       </c>
       <c r="S600" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T600" t="inlineStr">
         <is>
@@ -67552,7 +67556,7 @@
       </c>
       <c r="Z600" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA600" t="inlineStr">
@@ -67562,12 +67566,12 @@
       </c>
       <c r="AB600" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC600" t="inlineStr">
         <is>
-          <t>äldre ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD600" t="b">
@@ -67582,12 +67586,12 @@
       <c r="AT600" t="inlineStr"/>
       <c r="AW600" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX600" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY600" t="inlineStr">
@@ -67598,48 +67602,48 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>135382861</v>
+        <v>80987071</v>
       </c>
       <c r="B601" t="n">
-        <v>57975</v>
+        <v>57141</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E601" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I601" t="inlineStr"/>
       <c r="P601" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q601" t="n">
-        <v>607775</v>
+        <v>608360</v>
       </c>
       <c r="R601" t="n">
-        <v>7309978</v>
+        <v>7309498</v>
       </c>
       <c r="S601" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T601" t="inlineStr">
         <is>
@@ -67663,27 +67667,12 @@
       </c>
       <c r="Y601" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z601" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA601" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB601" t="inlineStr">
-        <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC601" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD601" t="b">
@@ -67698,26 +67687,22 @@
       <c r="AT601" t="inlineStr"/>
       <c r="AW601" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX601" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
-        </is>
-      </c>
-      <c r="AY601" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY601" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>80987071</v>
+        <v>135385293</v>
       </c>
       <c r="B602" t="n">
-        <v>57141</v>
+        <v>57162</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -67745,17 +67730,17 @@
       <c r="I602" t="inlineStr"/>
       <c r="P602" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q602" t="n">
-        <v>608360</v>
+        <v>607844</v>
       </c>
       <c r="R602" t="n">
-        <v>7309498</v>
+        <v>7309941</v>
       </c>
       <c r="S602" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T602" t="inlineStr">
         <is>
@@ -67779,12 +67764,27 @@
       </c>
       <c r="Y602" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z602" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA602" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB602" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC602" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD602" t="b">
@@ -67799,60 +67799,64 @@
       <c r="AT602" t="inlineStr"/>
       <c r="AW602" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX602" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY602" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY602" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>135385293</v>
+        <v>80987075</v>
       </c>
       <c r="B603" t="n">
-        <v>57162</v>
+        <v>58057</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E603" t="n">
-        <v>100138</v>
+        <v>103031</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I603" t="inlineStr"/>
       <c r="P603" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q603" t="n">
-        <v>607844</v>
+        <v>608231</v>
       </c>
       <c r="R603" t="n">
-        <v>7309941</v>
+        <v>7309648</v>
       </c>
       <c r="S603" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T603" t="inlineStr">
         <is>
@@ -67876,27 +67880,12 @@
       </c>
       <c r="Y603" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z603" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA603" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB603" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC603" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD603" t="b">
@@ -67911,26 +67900,22 @@
       <c r="AT603" t="inlineStr"/>
       <c r="AW603" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX603" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY603" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY603" t="inlineStr"/>
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>80987075</v>
+        <v>135349897</v>
       </c>
       <c r="B604" t="n">
-        <v>58057</v>
+        <v>58079</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -67956,19 +67941,24 @@
         </is>
       </c>
       <c r="I604" t="inlineStr"/>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P604" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q604" t="n">
-        <v>608231</v>
+        <v>608053</v>
       </c>
       <c r="R604" t="n">
-        <v>7309648</v>
+        <v>7309696</v>
       </c>
       <c r="S604" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T604" t="inlineStr">
         <is>
@@ -67992,12 +67982,22 @@
       </c>
       <c r="Y604" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z604" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA604" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB604" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD604" t="b">
@@ -68012,65 +68012,64 @@
       <c r="AT604" t="inlineStr"/>
       <c r="AW604" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX604" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY604" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY604" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>135349897</v>
+        <v>135388293</v>
       </c>
       <c r="B605" t="n">
-        <v>58079</v>
+        <v>58839</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E605" t="n">
-        <v>103031</v>
+        <v>208249</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I605" t="inlineStr"/>
-      <c r="M605" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
       <c r="P605" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Laisdalen päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q605" t="n">
-        <v>608053</v>
+        <v>608068</v>
       </c>
       <c r="R605" t="n">
-        <v>7309696</v>
+        <v>7309658</v>
       </c>
       <c r="S605" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="T605" t="inlineStr">
         <is>
@@ -68094,22 +68093,22 @@
       </c>
       <c r="Y605" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z605" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA605" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB605" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD605" t="b">
@@ -68124,12 +68123,12 @@
       <c r="AT605" t="inlineStr"/>
       <c r="AW605" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX605" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY605" t="inlineStr">
@@ -68140,10 +68139,10 @@
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>135388293</v>
+        <v>135351869</v>
       </c>
       <c r="B606" t="n">
-        <v>58839</v>
+        <v>99094</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -68151,37 +68150,37 @@
         </is>
       </c>
       <c r="E606" t="n">
-        <v>208249</v>
+        <v>219795</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I606" t="inlineStr"/>
       <c r="P606" t="inlineStr">
         <is>
-          <t>Laisdalen päronberget, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q606" t="n">
-        <v>608068</v>
+        <v>608121</v>
       </c>
       <c r="R606" t="n">
-        <v>7309658</v>
+        <v>7309664</v>
       </c>
       <c r="S606" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T606" t="inlineStr">
         <is>
@@ -68205,22 +68204,22 @@
       </c>
       <c r="Y606" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z606" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA606" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB606" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD606" t="b">
@@ -68235,12 +68234,12 @@
       <c r="AT606" t="inlineStr"/>
       <c r="AW606" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX606" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY606" t="inlineStr">
@@ -68251,10 +68250,10 @@
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>135351869</v>
+        <v>135351871</v>
       </c>
       <c r="B607" t="n">
-        <v>99094</v>
+        <v>99197</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -68262,21 +68261,21 @@
         </is>
       </c>
       <c r="E607" t="n">
-        <v>219795</v>
+        <v>219811</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I607" t="inlineStr"/>
@@ -68286,13 +68285,13 @@
         </is>
       </c>
       <c r="Q607" t="n">
-        <v>608121</v>
+        <v>608132</v>
       </c>
       <c r="R607" t="n">
-        <v>7309664</v>
+        <v>7309645</v>
       </c>
       <c r="S607" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T607" t="inlineStr">
         <is>
@@ -68321,7 +68320,7 @@
       </c>
       <c r="Z607" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA607" t="inlineStr">
@@ -68331,7 +68330,7 @@
       </c>
       <c r="AB607" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD607" t="b">
@@ -68362,7 +68361,7 @@
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>135351871</v>
+        <v>135385327</v>
       </c>
       <c r="B608" t="n">
         <v>99197</v>
@@ -68393,17 +68392,17 @@
       <c r="I608" t="inlineStr"/>
       <c r="P608" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q608" t="n">
-        <v>608132</v>
+        <v>608066</v>
       </c>
       <c r="R608" t="n">
-        <v>7309645</v>
+        <v>7309643</v>
       </c>
       <c r="S608" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="T608" t="inlineStr">
         <is>
@@ -68427,22 +68426,22 @@
       </c>
       <c r="Y608" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z608" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA608" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB608" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD608" t="b">
@@ -68457,12 +68456,12 @@
       <c r="AT608" t="inlineStr"/>
       <c r="AW608" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX608" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY608" t="inlineStr">
@@ -68473,7 +68472,7 @@
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>135385327</v>
+        <v>135393145</v>
       </c>
       <c r="B609" t="n">
         <v>99197</v>
@@ -68504,17 +68503,17 @@
       <c r="I609" t="inlineStr"/>
       <c r="P609" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q609" t="n">
-        <v>608066</v>
+        <v>608084</v>
       </c>
       <c r="R609" t="n">
-        <v>7309643</v>
+        <v>7309695</v>
       </c>
       <c r="S609" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T609" t="inlineStr">
         <is>
@@ -68543,7 +68542,7 @@
       </c>
       <c r="Z609" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA609" t="inlineStr">
@@ -68553,7 +68552,7 @@
       </c>
       <c r="AB609" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD609" t="b">
@@ -68568,26 +68567,22 @@
       <c r="AT609" t="inlineStr"/>
       <c r="AW609" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX609" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY609" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY609" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>135393145</v>
+        <v>135393157</v>
       </c>
       <c r="B610" t="n">
-        <v>99197</v>
+        <v>108274</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -68595,21 +68590,21 @@
         </is>
       </c>
       <c r="E610" t="n">
-        <v>219811</v>
+        <v>220102</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I610" t="inlineStr"/>
@@ -68619,10 +68614,10 @@
         </is>
       </c>
       <c r="Q610" t="n">
-        <v>608084</v>
+        <v>608135</v>
       </c>
       <c r="R610" t="n">
-        <v>7309695</v>
+        <v>7309645</v>
       </c>
       <c r="S610" t="n">
         <v>5</v>
@@ -68654,7 +68649,7 @@
       </c>
       <c r="Z610" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA610" t="inlineStr">
@@ -68664,7 +68659,7 @@
       </c>
       <c r="AB610" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD610" t="b">
@@ -68691,10 +68686,10 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>135393157</v>
+        <v>135393151</v>
       </c>
       <c r="B611" t="n">
-        <v>108274</v>
+        <v>110023</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -68702,21 +68697,21 @@
         </is>
       </c>
       <c r="E611" t="n">
-        <v>220102</v>
+        <v>220263</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Fjällskråp</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Petasites frigidus</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I611" t="inlineStr"/>
@@ -68726,10 +68721,10 @@
         </is>
       </c>
       <c r="Q611" t="n">
-        <v>608135</v>
+        <v>608151</v>
       </c>
       <c r="R611" t="n">
-        <v>7309645</v>
+        <v>7309729</v>
       </c>
       <c r="S611" t="n">
         <v>5</v>
@@ -68761,7 +68756,7 @@
       </c>
       <c r="Z611" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA611" t="inlineStr">
@@ -68771,7 +68766,7 @@
       </c>
       <c r="AB611" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD611" t="b">
@@ -68798,10 +68793,10 @@
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>135393151</v>
+        <v>135351874</v>
       </c>
       <c r="B612" t="n">
-        <v>110023</v>
+        <v>110150</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -68809,34 +68804,34 @@
         </is>
       </c>
       <c r="E612" t="n">
-        <v>220263</v>
+        <v>220294</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>Fjällskråp</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Petasites frigidus</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I612" t="inlineStr"/>
       <c r="P612" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q612" t="n">
-        <v>608151</v>
+        <v>608136</v>
       </c>
       <c r="R612" t="n">
-        <v>7309729</v>
+        <v>7309644</v>
       </c>
       <c r="S612" t="n">
         <v>5</v>
@@ -68863,22 +68858,22 @@
       </c>
       <c r="Y612" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z612" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA612" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB612" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD612" t="b">
@@ -68893,60 +68888,73 @@
       <c r="AT612" t="inlineStr"/>
       <c r="AW612" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX612" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY612" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY612" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>135351874</v>
+        <v>135349921</v>
       </c>
       <c r="B613" t="n">
-        <v>110150</v>
+        <v>99195</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E613" t="n">
-        <v>220294</v>
+        <v>220787</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
-        </is>
-      </c>
-      <c r="I613" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P613" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q613" t="n">
-        <v>608136</v>
+        <v>607991</v>
       </c>
       <c r="R613" t="n">
-        <v>7309644</v>
+        <v>7309608</v>
       </c>
       <c r="S613" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T613" t="inlineStr">
         <is>
@@ -68975,7 +68983,7 @@
       </c>
       <c r="Z613" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA613" t="inlineStr">
@@ -68985,7 +68993,7 @@
       </c>
       <c r="AB613" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD613" t="b">
@@ -69000,12 +69008,12 @@
       <c r="AT613" t="inlineStr"/>
       <c r="AW613" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX613" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY613" t="inlineStr">
@@ -69016,54 +69024,49 @@
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>135349921</v>
+        <v>135349909</v>
       </c>
       <c r="B614" t="n">
-        <v>99195</v>
+        <v>106309</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E614" t="n">
-        <v>220787</v>
+        <v>221725</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I614" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K614" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr"/>
+      <c r="J614" t="inlineStr"/>
+      <c r="K614" t="inlineStr"/>
+      <c r="L614" t="inlineStr"/>
+      <c r="N614" t="inlineStr"/>
       <c r="P614" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q614" t="n">
-        <v>607991</v>
+        <v>608014</v>
       </c>
       <c r="R614" t="n">
-        <v>7309608</v>
+        <v>7309639</v>
       </c>
       <c r="S614" t="n">
         <v>3</v>
@@ -69095,7 +69098,7 @@
       </c>
       <c r="Z614" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA614" t="inlineStr">
@@ -69105,7 +69108,7 @@
       </c>
       <c r="AB614" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD614" t="b">
@@ -69114,6 +69117,7 @@
       <c r="AE614" t="b">
         <v>0</v>
       </c>
+      <c r="AF614" t="inlineStr"/>
       <c r="AG614" t="b">
         <v>0</v>
       </c>
@@ -69136,7 +69140,7 @@
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>135349909</v>
+        <v>135384319</v>
       </c>
       <c r="B615" t="n">
         <v>106309</v>
@@ -69165,23 +69169,19 @@
         </is>
       </c>
       <c r="I615" t="inlineStr"/>
-      <c r="J615" t="inlineStr"/>
-      <c r="K615" t="inlineStr"/>
-      <c r="L615" t="inlineStr"/>
-      <c r="N615" t="inlineStr"/>
       <c r="P615" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q615" t="n">
-        <v>608014</v>
+        <v>608048</v>
       </c>
       <c r="R615" t="n">
-        <v>7309639</v>
+        <v>7309656</v>
       </c>
       <c r="S615" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T615" t="inlineStr">
         <is>
@@ -69205,22 +69205,22 @@
       </c>
       <c r="Y615" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z615" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA615" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB615" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD615" t="b">
@@ -69229,19 +69229,18 @@
       <c r="AE615" t="b">
         <v>0</v>
       </c>
-      <c r="AF615" t="inlineStr"/>
       <c r="AG615" t="b">
         <v>0</v>
       </c>
       <c r="AT615" t="inlineStr"/>
       <c r="AW615" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX615" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY615" t="inlineStr">
@@ -69252,7 +69251,7 @@
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>135384319</v>
+        <v>135384324</v>
       </c>
       <c r="B616" t="n">
         <v>106309</v>
@@ -69287,10 +69286,10 @@
         </is>
       </c>
       <c r="Q616" t="n">
-        <v>608048</v>
+        <v>608042</v>
       </c>
       <c r="R616" t="n">
-        <v>7309656</v>
+        <v>7309653</v>
       </c>
       <c r="S616" t="n">
         <v>5</v>
@@ -69322,7 +69321,7 @@
       </c>
       <c r="Z616" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA616" t="inlineStr">
@@ -69332,7 +69331,7 @@
       </c>
       <c r="AB616" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD616" t="b">
@@ -69363,7 +69362,7 @@
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>135384324</v>
+        <v>135388296</v>
       </c>
       <c r="B617" t="n">
         <v>106309</v>
@@ -69394,17 +69393,17 @@
       <c r="I617" t="inlineStr"/>
       <c r="P617" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Laisdalen päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q617" t="n">
-        <v>608042</v>
+        <v>608057</v>
       </c>
       <c r="R617" t="n">
-        <v>7309653</v>
+        <v>7309661</v>
       </c>
       <c r="S617" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T617" t="inlineStr">
         <is>
@@ -69433,7 +69432,7 @@
       </c>
       <c r="Z617" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA617" t="inlineStr">
@@ -69443,7 +69442,7 @@
       </c>
       <c r="AB617" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD617" t="b">
@@ -69458,12 +69457,12 @@
       <c r="AT617" t="inlineStr"/>
       <c r="AW617" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX617" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY617" t="inlineStr">
@@ -69474,7 +69473,7 @@
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>135388296</v>
+        <v>135393149</v>
       </c>
       <c r="B618" t="n">
         <v>106309</v>
@@ -69505,17 +69504,17 @@
       <c r="I618" t="inlineStr"/>
       <c r="P618" t="inlineStr">
         <is>
-          <t>Laisdalen päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q618" t="n">
-        <v>608057</v>
+        <v>608109</v>
       </c>
       <c r="R618" t="n">
-        <v>7309661</v>
+        <v>7309705</v>
       </c>
       <c r="S618" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T618" t="inlineStr">
         <is>
@@ -69544,7 +69543,7 @@
       </c>
       <c r="Z618" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA618" t="inlineStr">
@@ -69554,7 +69553,7 @@
       </c>
       <c r="AB618" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD618" t="b">
@@ -69569,26 +69568,22 @@
       <c r="AT618" t="inlineStr"/>
       <c r="AW618" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX618" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY618" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>135393149</v>
+        <v>135385157</v>
       </c>
       <c r="B619" t="n">
-        <v>106309</v>
+        <v>98063</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -69596,21 +69591,21 @@
         </is>
       </c>
       <c r="E619" t="n">
-        <v>221725</v>
+        <v>221946</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I619" t="inlineStr"/>
@@ -69620,10 +69615,10 @@
         </is>
       </c>
       <c r="Q619" t="n">
-        <v>608109</v>
+        <v>607832</v>
       </c>
       <c r="R619" t="n">
-        <v>7309705</v>
+        <v>7310013</v>
       </c>
       <c r="S619" t="n">
         <v>5</v>
@@ -69655,7 +69650,7 @@
       </c>
       <c r="Z619" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA619" t="inlineStr">
@@ -69665,7 +69660,7 @@
       </c>
       <c r="AB619" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD619" t="b">
@@ -69680,22 +69675,26 @@
       <c r="AT619" t="inlineStr"/>
       <c r="AW619" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX619" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY619" t="inlineStr"/>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY619" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>135385157</v>
+        <v>135349896</v>
       </c>
       <c r="B620" t="n">
-        <v>98063</v>
+        <v>99217</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -69703,37 +69702,37 @@
         </is>
       </c>
       <c r="E620" t="n">
-        <v>221946</v>
+        <v>221952</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I620" t="inlineStr"/>
       <c r="P620" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q620" t="n">
-        <v>607832</v>
+        <v>608056</v>
       </c>
       <c r="R620" t="n">
-        <v>7310013</v>
+        <v>7309695</v>
       </c>
       <c r="S620" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T620" t="inlineStr">
         <is>
@@ -69757,22 +69756,22 @@
       </c>
       <c r="Y620" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z620" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA620" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB620" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD620" t="b">
@@ -69787,12 +69786,12 @@
       <c r="AT620" t="inlineStr"/>
       <c r="AW620" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX620" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY620" t="inlineStr">
@@ -69803,10 +69802,10 @@
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>135349896</v>
+        <v>135349910</v>
       </c>
       <c r="B621" t="n">
-        <v>99217</v>
+        <v>103764</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -69814,21 +69813,21 @@
         </is>
       </c>
       <c r="E621" t="n">
-        <v>221952</v>
+        <v>222004</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I621" t="inlineStr"/>
@@ -69838,10 +69837,10 @@
         </is>
       </c>
       <c r="Q621" t="n">
-        <v>608056</v>
+        <v>608014</v>
       </c>
       <c r="R621" t="n">
-        <v>7309695</v>
+        <v>7309639</v>
       </c>
       <c r="S621" t="n">
         <v>3</v>
@@ -69873,7 +69872,7 @@
       </c>
       <c r="Z621" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA621" t="inlineStr">
@@ -69883,7 +69882,7 @@
       </c>
       <c r="AB621" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD621" t="b">
@@ -69914,10 +69913,10 @@
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>135349910</v>
+        <v>135356148</v>
       </c>
       <c r="B622" t="n">
-        <v>103764</v>
+        <v>104707</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -69925,16 +69924,16 @@
         </is>
       </c>
       <c r="E622" t="n">
-        <v>222004</v>
+        <v>222412</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -69949,13 +69948,13 @@
         </is>
       </c>
       <c r="Q622" t="n">
-        <v>608014</v>
+        <v>607978</v>
       </c>
       <c r="R622" t="n">
-        <v>7309639</v>
+        <v>7309596</v>
       </c>
       <c r="S622" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="T622" t="inlineStr">
         <is>
@@ -69984,7 +69983,7 @@
       </c>
       <c r="Z622" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA622" t="inlineStr">
@@ -69994,7 +69993,7 @@
       </c>
       <c r="AB622" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD622" t="b">
@@ -70009,12 +70008,12 @@
       <c r="AT622" t="inlineStr"/>
       <c r="AW622" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX622" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY622" t="inlineStr">
@@ -70025,7 +70024,7 @@
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>135356148</v>
+        <v>135393154</v>
       </c>
       <c r="B623" t="n">
         <v>104707</v>
@@ -70056,17 +70055,17 @@
       <c r="I623" t="inlineStr"/>
       <c r="P623" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q623" t="n">
-        <v>607978</v>
+        <v>608171</v>
       </c>
       <c r="R623" t="n">
-        <v>7309596</v>
+        <v>7309720</v>
       </c>
       <c r="S623" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T623" t="inlineStr">
         <is>
@@ -70090,22 +70089,22 @@
       </c>
       <c r="Y623" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z623" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA623" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB623" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD623" t="b">
@@ -70120,26 +70119,22 @@
       <c r="AT623" t="inlineStr"/>
       <c r="AW623" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX623" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
-        </is>
-      </c>
-      <c r="AY623" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>135393154</v>
+        <v>135393126</v>
       </c>
       <c r="B624" t="n">
-        <v>104707</v>
+        <v>100806</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -70147,16 +70142,16 @@
         </is>
       </c>
       <c r="E624" t="n">
-        <v>222412</v>
+        <v>222584</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -70171,10 +70166,10 @@
         </is>
       </c>
       <c r="Q624" t="n">
-        <v>608171</v>
+        <v>608021</v>
       </c>
       <c r="R624" t="n">
-        <v>7309720</v>
+        <v>7309604</v>
       </c>
       <c r="S624" t="n">
         <v>5</v>
@@ -70206,7 +70201,7 @@
       </c>
       <c r="Z624" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA624" t="inlineStr">
@@ -70216,7 +70211,7 @@
       </c>
       <c r="AB624" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD624" t="b">
@@ -70243,10 +70238,10 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>135393126</v>
+        <v>135388299</v>
       </c>
       <c r="B625" t="n">
-        <v>100806</v>
+        <v>102871</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -70254,16 +70249,16 @@
         </is>
       </c>
       <c r="E625" t="n">
-        <v>222584</v>
+        <v>223037</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -70274,17 +70269,17 @@
       <c r="I625" t="inlineStr"/>
       <c r="P625" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q625" t="n">
-        <v>608021</v>
+        <v>608030</v>
       </c>
       <c r="R625" t="n">
-        <v>7309604</v>
+        <v>7309591</v>
       </c>
       <c r="S625" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="T625" t="inlineStr">
         <is>
@@ -70313,7 +70308,7 @@
       </c>
       <c r="Z625" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA625" t="inlineStr">
@@ -70323,7 +70318,7 @@
       </c>
       <c r="AB625" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD625" t="b">
@@ -70338,22 +70333,26 @@
       <c r="AT625" t="inlineStr"/>
       <c r="AW625" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX625" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY625" t="inlineStr"/>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY625" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>135388299</v>
+        <v>135351867</v>
       </c>
       <c r="B626" t="n">
-        <v>102871</v>
+        <v>99198</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -70361,37 +70360,33 @@
         </is>
       </c>
       <c r="E626" t="n">
-        <v>223037</v>
+        <v>223614</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Vanlig brudsporre</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
-        </is>
-      </c>
-      <c r="H626" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr"/>
       <c r="I626" t="inlineStr"/>
       <c r="P626" t="inlineStr">
         <is>
-          <t>Laisdalen päronberget, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q626" t="n">
-        <v>608030</v>
+        <v>608123</v>
       </c>
       <c r="R626" t="n">
-        <v>7309591</v>
+        <v>7309661</v>
       </c>
       <c r="S626" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="T626" t="inlineStr">
         <is>
@@ -70415,22 +70410,22 @@
       </c>
       <c r="Y626" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z626" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA626" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB626" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD626" t="b">
@@ -70439,18 +70434,19 @@
       <c r="AE626" t="b">
         <v>0</v>
       </c>
+      <c r="AF626" t="inlineStr"/>
       <c r="AG626" t="b">
         <v>0</v>
       </c>
       <c r="AT626" t="inlineStr"/>
       <c r="AW626" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX626" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY626" t="inlineStr">
@@ -70461,10 +70457,10 @@
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>135351867</v>
+        <v>135349891</v>
       </c>
       <c r="B627" t="n">
-        <v>99198</v>
+        <v>101293</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -70472,19 +70468,23 @@
         </is>
       </c>
       <c r="E627" t="n">
-        <v>223614</v>
+        <v>224885</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>Vanlig brudsporre</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. conopsea</t>
-        </is>
-      </c>
-      <c r="H627" t="inlineStr"/>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
       <c r="I627" t="inlineStr"/>
       <c r="P627" t="inlineStr">
         <is>
@@ -70492,13 +70492,13 @@
         </is>
       </c>
       <c r="Q627" t="n">
-        <v>608123</v>
+        <v>608082</v>
       </c>
       <c r="R627" t="n">
-        <v>7309661</v>
+        <v>7309684</v>
       </c>
       <c r="S627" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T627" t="inlineStr">
         <is>
@@ -70527,7 +70527,7 @@
       </c>
       <c r="Z627" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA627" t="inlineStr">
@@ -70537,7 +70537,7 @@
       </c>
       <c r="AB627" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD627" t="b">
@@ -70546,19 +70546,18 @@
       <c r="AE627" t="b">
         <v>0</v>
       </c>
-      <c r="AF627" t="inlineStr"/>
       <c r="AG627" t="b">
         <v>0</v>
       </c>
       <c r="AT627" t="inlineStr"/>
       <c r="AW627" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX627" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY627" t="inlineStr">
@@ -70569,7 +70568,7 @@
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>135349891</v>
+        <v>135393129</v>
       </c>
       <c r="B628" t="n">
         <v>101293</v>
@@ -70600,17 +70599,17 @@
       <c r="I628" t="inlineStr"/>
       <c r="P628" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q628" t="n">
-        <v>608082</v>
+        <v>608021</v>
       </c>
       <c r="R628" t="n">
-        <v>7309684</v>
+        <v>7309619</v>
       </c>
       <c r="S628" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T628" t="inlineStr">
         <is>
@@ -70634,22 +70633,22 @@
       </c>
       <c r="Y628" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z628" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA628" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB628" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD628" t="b">
@@ -70664,23 +70663,19 @@
       <c r="AT628" t="inlineStr"/>
       <c r="AW628" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX628" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY628" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY628" t="inlineStr"/>
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>135393129</v>
+        <v>135393131</v>
       </c>
       <c r="B629" t="n">
         <v>101293</v>
@@ -70715,10 +70710,10 @@
         </is>
       </c>
       <c r="Q629" t="n">
-        <v>608021</v>
+        <v>608014</v>
       </c>
       <c r="R629" t="n">
-        <v>7309619</v>
+        <v>7309625</v>
       </c>
       <c r="S629" t="n">
         <v>5</v>
@@ -70750,7 +70745,7 @@
       </c>
       <c r="Z629" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA629" t="inlineStr">
@@ -70760,7 +70755,7 @@
       </c>
       <c r="AB629" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD629" t="b">
@@ -70787,7 +70782,7 @@
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>135393131</v>
+        <v>135393150</v>
       </c>
       <c r="B630" t="n">
         <v>101293</v>
@@ -70822,10 +70817,10 @@
         </is>
       </c>
       <c r="Q630" t="n">
-        <v>608014</v>
+        <v>608136</v>
       </c>
       <c r="R630" t="n">
-        <v>7309625</v>
+        <v>7309706</v>
       </c>
       <c r="S630" t="n">
         <v>5</v>
@@ -70857,7 +70852,7 @@
       </c>
       <c r="Z630" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA630" t="inlineStr">
@@ -70867,7 +70862,7 @@
       </c>
       <c r="AB630" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD630" t="b">
@@ -70894,48 +70889,48 @@
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>135393150</v>
+        <v>135378173</v>
       </c>
       <c r="B631" t="n">
-        <v>101293</v>
+        <v>78382</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E631" t="n">
-        <v>224885</v>
+        <v>228579</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I631" t="inlineStr"/>
       <c r="P631" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q631" t="n">
-        <v>608136</v>
+        <v>607794</v>
       </c>
       <c r="R631" t="n">
-        <v>7309706</v>
+        <v>7309999</v>
       </c>
       <c r="S631" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T631" t="inlineStr">
         <is>
@@ -70964,7 +70959,7 @@
       </c>
       <c r="Z631" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA631" t="inlineStr">
@@ -70974,7 +70969,7 @@
       </c>
       <c r="AB631" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD631" t="b">
@@ -70989,19 +70984,23 @@
       <c r="AT631" t="inlineStr"/>
       <c r="AW631" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX631" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY631" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY631" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>135378173</v>
+        <v>135378175</v>
       </c>
       <c r="B632" t="n">
         <v>78382</v>
@@ -71036,10 +71035,10 @@
         </is>
       </c>
       <c r="Q632" t="n">
-        <v>607794</v>
+        <v>607781</v>
       </c>
       <c r="R632" t="n">
-        <v>7309999</v>
+        <v>7310006</v>
       </c>
       <c r="S632" t="n">
         <v>4</v>
@@ -71071,7 +71070,7 @@
       </c>
       <c r="Z632" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA632" t="inlineStr">
@@ -71081,7 +71080,7 @@
       </c>
       <c r="AB632" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD632" t="b">
@@ -71112,7 +71111,7 @@
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>135378175</v>
+        <v>135378179</v>
       </c>
       <c r="B633" t="n">
         <v>78382</v>
@@ -71147,10 +71146,10 @@
         </is>
       </c>
       <c r="Q633" t="n">
-        <v>607781</v>
+        <v>607702</v>
       </c>
       <c r="R633" t="n">
-        <v>7310006</v>
+        <v>7309979</v>
       </c>
       <c r="S633" t="n">
         <v>4</v>
@@ -71182,7 +71181,7 @@
       </c>
       <c r="Z633" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA633" t="inlineStr">
@@ -71192,7 +71191,7 @@
       </c>
       <c r="AB633" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD633" t="b">
@@ -71223,7 +71222,7 @@
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>135378179</v>
+        <v>135378181</v>
       </c>
       <c r="B634" t="n">
         <v>78382</v>
@@ -71258,10 +71257,10 @@
         </is>
       </c>
       <c r="Q634" t="n">
-        <v>607702</v>
+        <v>607671</v>
       </c>
       <c r="R634" t="n">
-        <v>7309979</v>
+        <v>7309990</v>
       </c>
       <c r="S634" t="n">
         <v>4</v>
@@ -71293,7 +71292,7 @@
       </c>
       <c r="Z634" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA634" t="inlineStr">
@@ -71303,7 +71302,7 @@
       </c>
       <c r="AB634" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD634" t="b">
@@ -71334,7 +71333,7 @@
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>135378181</v>
+        <v>135385232</v>
       </c>
       <c r="B635" t="n">
         <v>78382</v>
@@ -71365,17 +71364,17 @@
       <c r="I635" t="inlineStr"/>
       <c r="P635" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q635" t="n">
-        <v>607671</v>
+        <v>607787</v>
       </c>
       <c r="R635" t="n">
-        <v>7309990</v>
+        <v>7310002</v>
       </c>
       <c r="S635" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T635" t="inlineStr">
         <is>
@@ -71404,7 +71403,7 @@
       </c>
       <c r="Z635" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA635" t="inlineStr">
@@ -71414,7 +71413,7 @@
       </c>
       <c r="AB635" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD635" t="b">
@@ -71429,12 +71428,12 @@
       <c r="AT635" t="inlineStr"/>
       <c r="AW635" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX635" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY635" t="inlineStr">
@@ -71445,7 +71444,7 @@
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>135385232</v>
+        <v>135385289</v>
       </c>
       <c r="B636" t="n">
         <v>78382</v>
@@ -71480,10 +71479,10 @@
         </is>
       </c>
       <c r="Q636" t="n">
-        <v>607787</v>
+        <v>607788</v>
       </c>
       <c r="R636" t="n">
-        <v>7310002</v>
+        <v>7310050</v>
       </c>
       <c r="S636" t="n">
         <v>5</v>
@@ -71515,7 +71514,7 @@
       </c>
       <c r="Z636" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA636" t="inlineStr">
@@ -71525,7 +71524,7 @@
       </c>
       <c r="AB636" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD636" t="b">
@@ -71556,7 +71555,7 @@
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>135385289</v>
+        <v>135385297</v>
       </c>
       <c r="B637" t="n">
         <v>78382</v>
@@ -71591,10 +71590,10 @@
         </is>
       </c>
       <c r="Q637" t="n">
-        <v>607788</v>
+        <v>607872</v>
       </c>
       <c r="R637" t="n">
-        <v>7310050</v>
+        <v>7309907</v>
       </c>
       <c r="S637" t="n">
         <v>5</v>
@@ -71626,7 +71625,7 @@
       </c>
       <c r="Z637" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA637" t="inlineStr">
@@ -71636,7 +71635,7 @@
       </c>
       <c r="AB637" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD637" t="b">
@@ -71667,10 +71666,10 @@
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>135385297</v>
+        <v>135385236</v>
       </c>
       <c r="B638" t="n">
-        <v>78382</v>
+        <v>79396</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -71678,21 +71677,21 @@
         </is>
       </c>
       <c r="E638" t="n">
-        <v>228579</v>
+        <v>260591</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I638" t="inlineStr"/>
@@ -71702,10 +71701,10 @@
         </is>
       </c>
       <c r="Q638" t="n">
-        <v>607872</v>
+        <v>607717</v>
       </c>
       <c r="R638" t="n">
-        <v>7309907</v>
+        <v>7309995</v>
       </c>
       <c r="S638" t="n">
         <v>5</v>
@@ -71737,7 +71736,7 @@
       </c>
       <c r="Z638" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA638" t="inlineStr">
@@ -71747,7 +71746,7 @@
       </c>
       <c r="AB638" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD638" t="b">
@@ -71778,7 +71777,7 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>135385236</v>
+        <v>135385311</v>
       </c>
       <c r="B639" t="n">
         <v>79396</v>
@@ -71813,10 +71812,10 @@
         </is>
       </c>
       <c r="Q639" t="n">
-        <v>607717</v>
+        <v>607861</v>
       </c>
       <c r="R639" t="n">
-        <v>7309995</v>
+        <v>7309816</v>
       </c>
       <c r="S639" t="n">
         <v>5</v>
@@ -71848,7 +71847,7 @@
       </c>
       <c r="Z639" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA639" t="inlineStr">
@@ -71858,7 +71857,7 @@
       </c>
       <c r="AB639" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD639" t="b">
@@ -71889,10 +71888,10 @@
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>135385311</v>
+        <v>80987080</v>
       </c>
       <c r="B640" t="n">
-        <v>79396</v>
+        <v>91905</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -71900,37 +71899,37 @@
         </is>
       </c>
       <c r="E640" t="n">
-        <v>260591</v>
+        <v>1108</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I640" t="inlineStr"/>
       <c r="P640" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q640" t="n">
-        <v>607861</v>
+        <v>607814</v>
       </c>
       <c r="R640" t="n">
-        <v>7309816</v>
+        <v>7310183</v>
       </c>
       <c r="S640" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T640" t="inlineStr">
         <is>
@@ -71954,22 +71953,12 @@
       </c>
       <c r="Y640" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z640" t="inlineStr">
-        <is>
-          <t>15:46</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA640" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB640" t="inlineStr">
-        <is>
-          <t>15:46</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD640" t="b">
@@ -71984,23 +71973,19 @@
       <c r="AT640" t="inlineStr"/>
       <c r="AW640" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX640" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY640" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY640" t="inlineStr"/>
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>80987080</v>
+        <v>80987082</v>
       </c>
       <c r="B641" t="n">
         <v>91905</v>
@@ -72035,10 +72020,10 @@
         </is>
       </c>
       <c r="Q641" t="n">
-        <v>607814</v>
+        <v>607707</v>
       </c>
       <c r="R641" t="n">
-        <v>7310183</v>
+        <v>7310262</v>
       </c>
       <c r="S641" t="n">
         <v>10</v>
@@ -72097,7 +72082,7 @@
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>80987082</v>
+        <v>80987083</v>
       </c>
       <c r="B642" t="n">
         <v>91905</v>
@@ -72132,10 +72117,10 @@
         </is>
       </c>
       <c r="Q642" t="n">
-        <v>607707</v>
+        <v>607709</v>
       </c>
       <c r="R642" t="n">
-        <v>7310262</v>
+        <v>7310293</v>
       </c>
       <c r="S642" t="n">
         <v>10</v>
@@ -72194,10 +72179,10 @@
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>80987083</v>
+        <v>80987064</v>
       </c>
       <c r="B643" t="n">
-        <v>91905</v>
+        <v>91909</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -72205,21 +72190,21 @@
         </is>
       </c>
       <c r="E643" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I643" t="inlineStr"/>
@@ -72229,10 +72214,10 @@
         </is>
       </c>
       <c r="Q643" t="n">
-        <v>607709</v>
+        <v>607818</v>
       </c>
       <c r="R643" t="n">
-        <v>7310293</v>
+        <v>7310228</v>
       </c>
       <c r="S643" t="n">
         <v>10</v>
@@ -72291,10 +72276,10 @@
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>80987064</v>
+        <v>80987115</v>
       </c>
       <c r="B644" t="n">
-        <v>91909</v>
+        <v>83173</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -72302,21 +72287,21 @@
         </is>
       </c>
       <c r="E644" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I644" t="inlineStr"/>
@@ -72326,10 +72311,10 @@
         </is>
       </c>
       <c r="Q644" t="n">
-        <v>607818</v>
+        <v>607759</v>
       </c>
       <c r="R644" t="n">
-        <v>7310228</v>
+        <v>7310182</v>
       </c>
       <c r="S644" t="n">
         <v>10</v>
@@ -72388,7 +72373,7 @@
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>80987115</v>
+        <v>80987117</v>
       </c>
       <c r="B645" t="n">
         <v>83173</v>
@@ -72423,10 +72408,10 @@
         </is>
       </c>
       <c r="Q645" t="n">
-        <v>607759</v>
+        <v>607751</v>
       </c>
       <c r="R645" t="n">
-        <v>7310182</v>
+        <v>7310193</v>
       </c>
       <c r="S645" t="n">
         <v>10</v>
@@ -72485,32 +72470,32 @@
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>80987117</v>
+        <v>80987066</v>
       </c>
       <c r="B646" t="n">
-        <v>83173</v>
+        <v>92632</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E646" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I646" t="inlineStr"/>
@@ -72520,10 +72505,10 @@
         </is>
       </c>
       <c r="Q646" t="n">
-        <v>607751</v>
+        <v>607822</v>
       </c>
       <c r="R646" t="n">
-        <v>7310193</v>
+        <v>7310199</v>
       </c>
       <c r="S646" t="n">
         <v>10</v>
@@ -72582,48 +72567,48 @@
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>80987066</v>
+        <v>135351855</v>
       </c>
       <c r="B647" t="n">
-        <v>92632</v>
+        <v>79373</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E647" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I647" t="inlineStr"/>
       <c r="P647" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q647" t="n">
-        <v>607822</v>
+        <v>607677</v>
       </c>
       <c r="R647" t="n">
-        <v>7310199</v>
+        <v>7310726</v>
       </c>
       <c r="S647" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="T647" t="inlineStr">
         <is>
@@ -72647,12 +72632,22 @@
       </c>
       <c r="Y647" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z647" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA647" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB647" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD647" t="b">
@@ -72667,19 +72662,23 @@
       <c r="AT647" t="inlineStr"/>
       <c r="AW647" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX647" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY647" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY647" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>135351855</v>
+        <v>135382864</v>
       </c>
       <c r="B648" t="n">
         <v>79373</v>
@@ -72714,13 +72713,13 @@
         </is>
       </c>
       <c r="Q648" t="n">
-        <v>607677</v>
+        <v>607670</v>
       </c>
       <c r="R648" t="n">
-        <v>7310726</v>
+        <v>7310121</v>
       </c>
       <c r="S648" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="T648" t="inlineStr">
         <is>
@@ -72744,22 +72743,22 @@
       </c>
       <c r="Y648" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z648" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA648" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB648" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD648" t="b">
@@ -72774,12 +72773,12 @@
       <c r="AT648" t="inlineStr"/>
       <c r="AW648" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX648" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY648" t="inlineStr">
@@ -72790,7 +72789,7 @@
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>135382864</v>
+        <v>135385285</v>
       </c>
       <c r="B649" t="n">
         <v>79373</v>
@@ -72821,17 +72820,17 @@
       <c r="I649" t="inlineStr"/>
       <c r="P649" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q649" t="n">
-        <v>607670</v>
+        <v>607756</v>
       </c>
       <c r="R649" t="n">
-        <v>7310121</v>
+        <v>7310082</v>
       </c>
       <c r="S649" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T649" t="inlineStr">
         <is>
@@ -72860,7 +72859,7 @@
       </c>
       <c r="Z649" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA649" t="inlineStr">
@@ -72870,7 +72869,7 @@
       </c>
       <c r="AB649" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD649" t="b">
@@ -72885,12 +72884,12 @@
       <c r="AT649" t="inlineStr"/>
       <c r="AW649" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX649" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY649" t="inlineStr">
@@ -72901,48 +72900,48 @@
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>135385285</v>
+        <v>80987069</v>
       </c>
       <c r="B650" t="n">
-        <v>79373</v>
+        <v>57953</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E650" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I650" t="inlineStr"/>
       <c r="P650" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q650" t="n">
-        <v>607756</v>
+        <v>607759</v>
       </c>
       <c r="R650" t="n">
-        <v>7310082</v>
+        <v>7310308</v>
       </c>
       <c r="S650" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T650" t="inlineStr">
         <is>
@@ -72966,22 +72965,12 @@
       </c>
       <c r="Y650" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z650" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA650" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB650" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD650" t="b">
@@ -72996,64 +72985,69 @@
       <c r="AT650" t="inlineStr"/>
       <c r="AW650" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX650" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY650" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY650" t="inlineStr"/>
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>80987069</v>
+        <v>135382865</v>
       </c>
       <c r="B651" t="n">
-        <v>57953</v>
+        <v>5181</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E651" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I651" t="inlineStr"/>
+      <c r="J651" t="inlineStr"/>
+      <c r="K651" t="inlineStr"/>
+      <c r="L651" t="inlineStr"/>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N651" t="inlineStr"/>
       <c r="P651" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q651" t="n">
-        <v>607759</v>
+        <v>607674</v>
       </c>
       <c r="R651" t="n">
-        <v>7310308</v>
+        <v>7310117</v>
       </c>
       <c r="S651" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T651" t="inlineStr">
         <is>
@@ -73077,12 +73071,22 @@
       </c>
       <c r="Y651" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z651" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA651" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB651" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD651" t="b">
@@ -73091,72 +73095,76 @@
       <c r="AE651" t="b">
         <v>0</v>
       </c>
+      <c r="AF651" t="inlineStr"/>
       <c r="AG651" t="b">
         <v>0</v>
       </c>
       <c r="AT651" t="inlineStr"/>
       <c r="AW651" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX651" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY651" t="inlineStr"/>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY651" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>135382865</v>
+        <v>135385195</v>
       </c>
       <c r="B652" t="n">
-        <v>5181</v>
+        <v>57975</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E652" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I652" t="inlineStr"/>
-      <c r="J652" t="inlineStr"/>
       <c r="K652" t="inlineStr"/>
       <c r="L652" t="inlineStr"/>
       <c r="M652" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N652" t="inlineStr"/>
       <c r="P652" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q652" t="n">
-        <v>607674</v>
+        <v>608400</v>
       </c>
       <c r="R652" t="n">
-        <v>7310117</v>
+        <v>7309309</v>
       </c>
       <c r="S652" t="n">
         <v>5</v>
@@ -73188,7 +73196,7 @@
       </c>
       <c r="Z652" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA652" t="inlineStr">
@@ -73198,7 +73206,7 @@
       </c>
       <c r="AB652" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD652" t="b">
@@ -73207,19 +73215,18 @@
       <c r="AE652" t="b">
         <v>0</v>
       </c>
-      <c r="AF652" t="inlineStr"/>
       <c r="AG652" t="b">
         <v>0</v>
       </c>
       <c r="AT652" t="inlineStr"/>
       <c r="AW652" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX652" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY652" t="inlineStr">
@@ -73230,10 +73237,10 @@
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>135385195</v>
+        <v>80987072</v>
       </c>
       <c r="B653" t="n">
-        <v>57975</v>
+        <v>92208</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -73241,45 +73248,37 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I653" t="inlineStr"/>
-      <c r="K653" t="inlineStr"/>
-      <c r="L653" t="inlineStr"/>
-      <c r="M653" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N653" t="inlineStr"/>
       <c r="P653" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q653" t="n">
-        <v>608400</v>
+        <v>608406</v>
       </c>
       <c r="R653" t="n">
-        <v>7309309</v>
+        <v>7309441</v>
       </c>
       <c r="S653" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T653" t="inlineStr">
         <is>
@@ -73303,22 +73302,12 @@
       </c>
       <c r="Y653" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z653" t="inlineStr">
-        <is>
-          <t>16:37</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA653" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB653" t="inlineStr">
-        <is>
-          <t>16:37</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD653" t="b">
@@ -73333,26 +73322,22 @@
       <c r="AT653" t="inlineStr"/>
       <c r="AW653" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX653" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY653" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>80987072</v>
+        <v>80987076</v>
       </c>
       <c r="B654" t="n">
-        <v>92208</v>
+        <v>79406</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -73360,21 +73345,21 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>658</v>
+        <v>864</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I654" t="inlineStr"/>
@@ -73384,10 +73369,10 @@
         </is>
       </c>
       <c r="Q654" t="n">
-        <v>608406</v>
+        <v>608479</v>
       </c>
       <c r="R654" t="n">
-        <v>7309441</v>
+        <v>7309341</v>
       </c>
       <c r="S654" t="n">
         <v>10</v>
@@ -73446,7 +73431,7 @@
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>80987076</v>
+        <v>80987077</v>
       </c>
       <c r="B655" t="n">
         <v>79406</v>
@@ -73481,10 +73466,10 @@
         </is>
       </c>
       <c r="Q655" t="n">
-        <v>608479</v>
+        <v>608374</v>
       </c>
       <c r="R655" t="n">
-        <v>7309341</v>
+        <v>7309488</v>
       </c>
       <c r="S655" t="n">
         <v>10</v>
@@ -73543,10 +73528,10 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>80987077</v>
+        <v>80987081</v>
       </c>
       <c r="B656" t="n">
-        <v>79406</v>
+        <v>91905</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -73554,21 +73539,21 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>864</v>
+        <v>1108</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I656" t="inlineStr"/>
@@ -73578,10 +73563,10 @@
         </is>
       </c>
       <c r="Q656" t="n">
-        <v>608374</v>
+        <v>608446</v>
       </c>
       <c r="R656" t="n">
-        <v>7309488</v>
+        <v>7309372</v>
       </c>
       <c r="S656" t="n">
         <v>10</v>
@@ -73640,10 +73625,10 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>80987081</v>
+        <v>80987060</v>
       </c>
       <c r="B657" t="n">
-        <v>91905</v>
+        <v>91909</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -73651,21 +73636,21 @@
         </is>
       </c>
       <c r="E657" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I657" t="inlineStr"/>
@@ -73675,7 +73660,7 @@
         </is>
       </c>
       <c r="Q657" t="n">
-        <v>608446</v>
+        <v>608459</v>
       </c>
       <c r="R657" t="n">
         <v>7309372</v>
@@ -73737,7 +73722,7 @@
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>80987060</v>
+        <v>80987061</v>
       </c>
       <c r="B658" t="n">
         <v>91909</v>
@@ -73772,10 +73757,10 @@
         </is>
       </c>
       <c r="Q658" t="n">
-        <v>608459</v>
+        <v>608386</v>
       </c>
       <c r="R658" t="n">
-        <v>7309372</v>
+        <v>7309399</v>
       </c>
       <c r="S658" t="n">
         <v>10</v>
@@ -73834,7 +73819,7 @@
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>80987061</v>
+        <v>80987062</v>
       </c>
       <c r="B659" t="n">
         <v>91909</v>
@@ -73869,10 +73854,10 @@
         </is>
       </c>
       <c r="Q659" t="n">
-        <v>608386</v>
+        <v>608403</v>
       </c>
       <c r="R659" t="n">
-        <v>7309399</v>
+        <v>7309432</v>
       </c>
       <c r="S659" t="n">
         <v>10</v>
@@ -73931,7 +73916,7 @@
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>80987062</v>
+        <v>80987063</v>
       </c>
       <c r="B660" t="n">
         <v>91909</v>
@@ -73966,10 +73951,10 @@
         </is>
       </c>
       <c r="Q660" t="n">
-        <v>608403</v>
+        <v>608422</v>
       </c>
       <c r="R660" t="n">
-        <v>7309432</v>
+        <v>7309394</v>
       </c>
       <c r="S660" t="n">
         <v>10</v>
@@ -74028,10 +74013,10 @@
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>80987063</v>
+        <v>80987114</v>
       </c>
       <c r="B661" t="n">
-        <v>91909</v>
+        <v>83173</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -74039,21 +74024,21 @@
         </is>
       </c>
       <c r="E661" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I661" t="inlineStr"/>
@@ -74063,10 +74048,10 @@
         </is>
       </c>
       <c r="Q661" t="n">
-        <v>608422</v>
+        <v>608390</v>
       </c>
       <c r="R661" t="n">
-        <v>7309394</v>
+        <v>7309533</v>
       </c>
       <c r="S661" t="n">
         <v>10</v>
@@ -74125,32 +74110,32 @@
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>80987114</v>
+        <v>80987067</v>
       </c>
       <c r="B662" t="n">
-        <v>83173</v>
+        <v>92632</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E662" t="n">
-        <v>1312</v>
+        <v>3298</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I662" t="inlineStr"/>
@@ -74160,10 +74145,10 @@
         </is>
       </c>
       <c r="Q662" t="n">
-        <v>608390</v>
+        <v>608399</v>
       </c>
       <c r="R662" t="n">
-        <v>7309533</v>
+        <v>7309450</v>
       </c>
       <c r="S662" t="n">
         <v>10</v>
@@ -74219,103 +74204,6 @@
         </is>
       </c>
       <c r="AY662" t="inlineStr"/>
-    </row>
-    <row r="663">
-      <c r="A663" t="n">
-        <v>80987067</v>
-      </c>
-      <c r="B663" t="n">
-        <v>92632</v>
-      </c>
-      <c r="D663" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E663" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F663" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
-      </c>
-      <c r="G663" t="inlineStr">
-        <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H663" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I663" t="inlineStr"/>
-      <c r="P663" t="inlineStr">
-        <is>
-          <t>Veddeklinten, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q663" t="n">
-        <v>608399</v>
-      </c>
-      <c r="R663" t="n">
-        <v>7309450</v>
-      </c>
-      <c r="S663" t="n">
-        <v>10</v>
-      </c>
-      <c r="T663" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U663" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="V663" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W663" t="inlineStr">
-        <is>
-          <t>Arjeplog</t>
-        </is>
-      </c>
-      <c r="Y663" t="inlineStr">
-        <is>
-          <t>2019-08-19</t>
-        </is>
-      </c>
-      <c r="AA663" t="inlineStr">
-        <is>
-          <t>2019-08-19</t>
-        </is>
-      </c>
-      <c r="AD663" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE663" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG663" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT663" t="inlineStr"/>
-      <c r="AW663" t="inlineStr">
-        <is>
-          <t>Sture Westerberg</t>
-        </is>
-      </c>
-      <c r="AX663" t="inlineStr">
-        <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY663" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY662"/>
+  <dimension ref="A1:AY663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63780,10 +63780,10 @@
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>135349898</v>
+        <v>135388298</v>
       </c>
       <c r="B567" t="n">
-        <v>79373</v>
+        <v>93089</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -63791,34 +63791,37 @@
         </is>
       </c>
       <c r="E567" t="n">
-        <v>6425</v>
+        <v>5906</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Olivbrun kremla</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Russula olivobrunnea</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Ruots. &amp; Vauras</t>
         </is>
       </c>
       <c r="I567" t="inlineStr"/>
+      <c r="J567" t="inlineStr"/>
+      <c r="K567" t="inlineStr"/>
+      <c r="N567" t="inlineStr"/>
       <c r="P567" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Laisdalen päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q567" t="n">
-        <v>608046</v>
+        <v>608033</v>
       </c>
       <c r="R567" t="n">
-        <v>7309697</v>
+        <v>7309659</v>
       </c>
       <c r="S567" t="n">
         <v>3</v>
@@ -63845,22 +63848,27 @@
       </c>
       <c r="Y567" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z567" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="AA567" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB567" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:13</t>
+        </is>
+      </c>
+      <c r="AC567" t="inlineStr">
+        <is>
+          <t>dna sekvenseras</t>
         </is>
       </c>
       <c r="AD567" t="b">
@@ -63869,18 +63877,19 @@
       <c r="AE567" t="b">
         <v>0</v>
       </c>
+      <c r="AF567" t="inlineStr"/>
       <c r="AG567" t="b">
         <v>0</v>
       </c>
       <c r="AT567" t="inlineStr"/>
       <c r="AW567" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX567" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY567" t="inlineStr">
@@ -63891,7 +63900,7 @@
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>135349900</v>
+        <v>135349898</v>
       </c>
       <c r="B568" t="n">
         <v>79373</v>
@@ -63926,10 +63935,10 @@
         </is>
       </c>
       <c r="Q568" t="n">
-        <v>608013</v>
+        <v>608046</v>
       </c>
       <c r="R568" t="n">
-        <v>7309723</v>
+        <v>7309697</v>
       </c>
       <c r="S568" t="n">
         <v>3</v>
@@ -63961,7 +63970,7 @@
       </c>
       <c r="Z568" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA568" t="inlineStr">
@@ -63971,7 +63980,7 @@
       </c>
       <c r="AB568" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD568" t="b">
@@ -64002,7 +64011,7 @@
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>135349903</v>
+        <v>135349900</v>
       </c>
       <c r="B569" t="n">
         <v>79373</v>
@@ -64037,10 +64046,10 @@
         </is>
       </c>
       <c r="Q569" t="n">
-        <v>607999</v>
+        <v>608013</v>
       </c>
       <c r="R569" t="n">
-        <v>7309728</v>
+        <v>7309723</v>
       </c>
       <c r="S569" t="n">
         <v>3</v>
@@ -64072,7 +64081,7 @@
       </c>
       <c r="Z569" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA569" t="inlineStr">
@@ -64082,7 +64091,7 @@
       </c>
       <c r="AB569" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD569" t="b">
@@ -64113,7 +64122,7 @@
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>135349908</v>
+        <v>135349903</v>
       </c>
       <c r="B570" t="n">
         <v>79373</v>
@@ -64148,13 +64157,13 @@
         </is>
       </c>
       <c r="Q570" t="n">
-        <v>608018</v>
+        <v>607999</v>
       </c>
       <c r="R570" t="n">
-        <v>7309659</v>
+        <v>7309728</v>
       </c>
       <c r="S570" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T570" t="inlineStr">
         <is>
@@ -64183,7 +64192,7 @@
       </c>
       <c r="Z570" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA570" t="inlineStr">
@@ -64193,7 +64202,7 @@
       </c>
       <c r="AB570" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD570" t="b">
@@ -64224,7 +64233,7 @@
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>135349917</v>
+        <v>135349908</v>
       </c>
       <c r="B571" t="n">
         <v>79373</v>
@@ -64259,10 +64268,10 @@
         </is>
       </c>
       <c r="Q571" t="n">
-        <v>607981</v>
+        <v>608018</v>
       </c>
       <c r="R571" t="n">
-        <v>7309626</v>
+        <v>7309659</v>
       </c>
       <c r="S571" t="n">
         <v>4</v>
@@ -64294,7 +64303,7 @@
       </c>
       <c r="Z571" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA571" t="inlineStr">
@@ -64304,7 +64313,7 @@
       </c>
       <c r="AB571" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD571" t="b">
@@ -64335,7 +64344,7 @@
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>135378171</v>
+        <v>135349917</v>
       </c>
       <c r="B572" t="n">
         <v>79373</v>
@@ -64370,10 +64379,10 @@
         </is>
       </c>
       <c r="Q572" t="n">
-        <v>607795</v>
+        <v>607981</v>
       </c>
       <c r="R572" t="n">
-        <v>7310000</v>
+        <v>7309626</v>
       </c>
       <c r="S572" t="n">
         <v>4</v>
@@ -64400,22 +64409,22 @@
       </c>
       <c r="Y572" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z572" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA572" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB572" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD572" t="b">
@@ -64446,7 +64455,7 @@
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>135378177</v>
+        <v>135378171</v>
       </c>
       <c r="B573" t="n">
         <v>79373</v>
@@ -64481,10 +64490,10 @@
         </is>
       </c>
       <c r="Q573" t="n">
-        <v>607747</v>
+        <v>607795</v>
       </c>
       <c r="R573" t="n">
-        <v>7309987</v>
+        <v>7310000</v>
       </c>
       <c r="S573" t="n">
         <v>4</v>
@@ -64516,7 +64525,7 @@
       </c>
       <c r="Z573" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA573" t="inlineStr">
@@ -64526,7 +64535,7 @@
       </c>
       <c r="AB573" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD573" t="b">
@@ -64557,7 +64566,7 @@
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>135384317</v>
+        <v>135378177</v>
       </c>
       <c r="B574" t="n">
         <v>79373</v>
@@ -64588,17 +64597,17 @@
       <c r="I574" t="inlineStr"/>
       <c r="P574" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q574" t="n">
-        <v>608065</v>
+        <v>607747</v>
       </c>
       <c r="R574" t="n">
-        <v>7309664</v>
+        <v>7309987</v>
       </c>
       <c r="S574" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T574" t="inlineStr">
         <is>
@@ -64627,7 +64636,7 @@
       </c>
       <c r="Z574" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA574" t="inlineStr">
@@ -64637,7 +64646,7 @@
       </c>
       <c r="AB574" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD574" t="b">
@@ -64652,12 +64661,12 @@
       <c r="AT574" t="inlineStr"/>
       <c r="AW574" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX574" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY574" t="inlineStr">
@@ -64668,7 +64677,7 @@
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>135384321</v>
+        <v>135384317</v>
       </c>
       <c r="B575" t="n">
         <v>79373</v>
@@ -64703,10 +64712,10 @@
         </is>
       </c>
       <c r="Q575" t="n">
-        <v>608050</v>
+        <v>608065</v>
       </c>
       <c r="R575" t="n">
-        <v>7309656</v>
+        <v>7309664</v>
       </c>
       <c r="S575" t="n">
         <v>5</v>
@@ -64738,7 +64747,7 @@
       </c>
       <c r="Z575" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA575" t="inlineStr">
@@ -64748,7 +64757,7 @@
       </c>
       <c r="AB575" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD575" t="b">
@@ -64779,7 +64788,7 @@
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>135384326</v>
+        <v>135384321</v>
       </c>
       <c r="B576" t="n">
         <v>79373</v>
@@ -64814,10 +64823,10 @@
         </is>
       </c>
       <c r="Q576" t="n">
-        <v>608033</v>
+        <v>608050</v>
       </c>
       <c r="R576" t="n">
-        <v>7309664</v>
+        <v>7309656</v>
       </c>
       <c r="S576" t="n">
         <v>5</v>
@@ -64849,7 +64858,7 @@
       </c>
       <c r="Z576" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA576" t="inlineStr">
@@ -64859,7 +64868,7 @@
       </c>
       <c r="AB576" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD576" t="b">
@@ -64890,7 +64899,7 @@
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>135385234</v>
+        <v>135384326</v>
       </c>
       <c r="B577" t="n">
         <v>79373</v>
@@ -64921,17 +64930,17 @@
       <c r="I577" t="inlineStr"/>
       <c r="P577" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q577" t="n">
-        <v>607787</v>
+        <v>608033</v>
       </c>
       <c r="R577" t="n">
-        <v>7310002</v>
+        <v>7309664</v>
       </c>
       <c r="S577" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T577" t="inlineStr">
         <is>
@@ -64960,7 +64969,7 @@
       </c>
       <c r="Z577" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA577" t="inlineStr">
@@ -64970,7 +64979,7 @@
       </c>
       <c r="AB577" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD577" t="b">
@@ -64985,12 +64994,12 @@
       <c r="AT577" t="inlineStr"/>
       <c r="AW577" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX577" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY577" t="inlineStr">
@@ -65001,7 +65010,7 @@
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>135385291</v>
+        <v>135385234</v>
       </c>
       <c r="B578" t="n">
         <v>79373</v>
@@ -65036,13 +65045,13 @@
         </is>
       </c>
       <c r="Q578" t="n">
-        <v>607837</v>
+        <v>607787</v>
       </c>
       <c r="R578" t="n">
-        <v>7309959</v>
+        <v>7310002</v>
       </c>
       <c r="S578" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T578" t="inlineStr">
         <is>
@@ -65071,7 +65080,7 @@
       </c>
       <c r="Z578" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA578" t="inlineStr">
@@ -65081,7 +65090,7 @@
       </c>
       <c r="AB578" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD578" t="b">
@@ -65112,7 +65121,7 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>135385299</v>
+        <v>135385291</v>
       </c>
       <c r="B579" t="n">
         <v>79373</v>
@@ -65147,10 +65156,10 @@
         </is>
       </c>
       <c r="Q579" t="n">
-        <v>607852</v>
+        <v>607837</v>
       </c>
       <c r="R579" t="n">
-        <v>7309897</v>
+        <v>7309959</v>
       </c>
       <c r="S579" t="n">
         <v>5</v>
@@ -65182,7 +65191,7 @@
       </c>
       <c r="Z579" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA579" t="inlineStr">
@@ -65192,7 +65201,7 @@
       </c>
       <c r="AB579" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD579" t="b">
@@ -65223,7 +65232,7 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>135385304</v>
+        <v>135385299</v>
       </c>
       <c r="B580" t="n">
         <v>79373</v>
@@ -65258,13 +65267,13 @@
         </is>
       </c>
       <c r="Q580" t="n">
-        <v>607802</v>
+        <v>607852</v>
       </c>
       <c r="R580" t="n">
-        <v>7309878</v>
+        <v>7309897</v>
       </c>
       <c r="S580" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T580" t="inlineStr">
         <is>
@@ -65293,7 +65302,7 @@
       </c>
       <c r="Z580" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA580" t="inlineStr">
@@ -65303,7 +65312,7 @@
       </c>
       <c r="AB580" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD580" t="b">
@@ -65334,7 +65343,7 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>135385313</v>
+        <v>135385304</v>
       </c>
       <c r="B581" t="n">
         <v>79373</v>
@@ -65369,13 +65378,13 @@
         </is>
       </c>
       <c r="Q581" t="n">
-        <v>607895</v>
+        <v>607802</v>
       </c>
       <c r="R581" t="n">
-        <v>7309854</v>
+        <v>7309878</v>
       </c>
       <c r="S581" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T581" t="inlineStr">
         <is>
@@ -65404,7 +65413,7 @@
       </c>
       <c r="Z581" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA581" t="inlineStr">
@@ -65414,7 +65423,7 @@
       </c>
       <c r="AB581" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD581" t="b">
@@ -65445,7 +65454,7 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>135385317</v>
+        <v>135385313</v>
       </c>
       <c r="B582" t="n">
         <v>79373</v>
@@ -65480,10 +65489,10 @@
         </is>
       </c>
       <c r="Q582" t="n">
-        <v>607886</v>
+        <v>607895</v>
       </c>
       <c r="R582" t="n">
-        <v>7309931</v>
+        <v>7309854</v>
       </c>
       <c r="S582" t="n">
         <v>5</v>
@@ -65515,7 +65524,7 @@
       </c>
       <c r="Z582" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA582" t="inlineStr">
@@ -65525,7 +65534,7 @@
       </c>
       <c r="AB582" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD582" t="b">
@@ -65556,7 +65565,7 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>135385321</v>
+        <v>135385317</v>
       </c>
       <c r="B583" t="n">
         <v>79373</v>
@@ -65591,10 +65600,10 @@
         </is>
       </c>
       <c r="Q583" t="n">
-        <v>608036</v>
+        <v>607886</v>
       </c>
       <c r="R583" t="n">
-        <v>7309659</v>
+        <v>7309931</v>
       </c>
       <c r="S583" t="n">
         <v>5</v>
@@ -65626,7 +65635,7 @@
       </c>
       <c r="Z583" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA583" t="inlineStr">
@@ -65636,7 +65645,7 @@
       </c>
       <c r="AB583" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD583" t="b">
@@ -65667,7 +65676,7 @@
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>135385325</v>
+        <v>135385321</v>
       </c>
       <c r="B584" t="n">
         <v>79373</v>
@@ -65702,13 +65711,13 @@
         </is>
       </c>
       <c r="Q584" t="n">
-        <v>608048</v>
+        <v>608036</v>
       </c>
       <c r="R584" t="n">
-        <v>7309630</v>
+        <v>7309659</v>
       </c>
       <c r="S584" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T584" t="inlineStr">
         <is>
@@ -65737,7 +65746,7 @@
       </c>
       <c r="Z584" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA584" t="inlineStr">
@@ -65747,7 +65756,7 @@
       </c>
       <c r="AB584" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD584" t="b">
@@ -65778,7 +65787,7 @@
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>135393119</v>
+        <v>135385325</v>
       </c>
       <c r="B585" t="n">
         <v>79373</v>
@@ -65809,17 +65818,17 @@
       <c r="I585" t="inlineStr"/>
       <c r="P585" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q585" t="n">
-        <v>608112</v>
+        <v>608048</v>
       </c>
       <c r="R585" t="n">
-        <v>7309586</v>
+        <v>7309630</v>
       </c>
       <c r="S585" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="T585" t="inlineStr">
         <is>
@@ -65848,7 +65857,7 @@
       </c>
       <c r="Z585" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA585" t="inlineStr">
@@ -65858,7 +65867,7 @@
       </c>
       <c r="AB585" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD585" t="b">
@@ -65873,19 +65882,23 @@
       <c r="AT585" t="inlineStr"/>
       <c r="AW585" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX585" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY585" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY585" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>135393137</v>
+        <v>135393119</v>
       </c>
       <c r="B586" t="n">
         <v>79373</v>
@@ -65920,10 +65933,10 @@
         </is>
       </c>
       <c r="Q586" t="n">
-        <v>607967</v>
+        <v>608112</v>
       </c>
       <c r="R586" t="n">
-        <v>7309711</v>
+        <v>7309586</v>
       </c>
       <c r="S586" t="n">
         <v>5</v>
@@ -65955,7 +65968,7 @@
       </c>
       <c r="Z586" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA586" t="inlineStr">
@@ -65965,7 +65978,7 @@
       </c>
       <c r="AB586" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD586" t="b">
@@ -65992,48 +66005,48 @@
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>135378172</v>
+        <v>135393137</v>
       </c>
       <c r="B587" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E587" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I587" t="inlineStr"/>
       <c r="P587" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q587" t="n">
-        <v>607794</v>
+        <v>607967</v>
       </c>
       <c r="R587" t="n">
-        <v>7309999</v>
+        <v>7309711</v>
       </c>
       <c r="S587" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T587" t="inlineStr">
         <is>
@@ -66062,7 +66075,7 @@
       </c>
       <c r="Z587" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA587" t="inlineStr">
@@ -66072,7 +66085,7 @@
       </c>
       <c r="AB587" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD587" t="b">
@@ -66087,23 +66100,19 @@
       <c r="AT587" t="inlineStr"/>
       <c r="AW587" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX587" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY587" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>135378176</v>
+        <v>135378172</v>
       </c>
       <c r="B588" t="n">
         <v>83358</v>
@@ -66138,13 +66147,13 @@
         </is>
       </c>
       <c r="Q588" t="n">
-        <v>607782</v>
+        <v>607794</v>
       </c>
       <c r="R588" t="n">
-        <v>7310008</v>
+        <v>7309999</v>
       </c>
       <c r="S588" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T588" t="inlineStr">
         <is>
@@ -66173,7 +66182,7 @@
       </c>
       <c r="Z588" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA588" t="inlineStr">
@@ -66183,7 +66192,7 @@
       </c>
       <c r="AB588" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD588" t="b">
@@ -66214,7 +66223,7 @@
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>135385230</v>
+        <v>135378176</v>
       </c>
       <c r="B589" t="n">
         <v>83358</v>
@@ -66245,17 +66254,17 @@
       <c r="I589" t="inlineStr"/>
       <c r="P589" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q589" t="n">
-        <v>607789</v>
+        <v>607782</v>
       </c>
       <c r="R589" t="n">
-        <v>7309990</v>
+        <v>7310008</v>
       </c>
       <c r="S589" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="T589" t="inlineStr">
         <is>
@@ -66284,7 +66293,7 @@
       </c>
       <c r="Z589" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA589" t="inlineStr">
@@ -66294,7 +66303,7 @@
       </c>
       <c r="AB589" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD589" t="b">
@@ -66309,12 +66318,12 @@
       <c r="AT589" t="inlineStr"/>
       <c r="AW589" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX589" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY589" t="inlineStr">
@@ -66325,7 +66334,7 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>135385287</v>
+        <v>135385230</v>
       </c>
       <c r="B590" t="n">
         <v>83358</v>
@@ -66360,13 +66369,13 @@
         </is>
       </c>
       <c r="Q590" t="n">
-        <v>607783</v>
+        <v>607789</v>
       </c>
       <c r="R590" t="n">
-        <v>7310048</v>
+        <v>7309990</v>
       </c>
       <c r="S590" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T590" t="inlineStr">
         <is>
@@ -66395,7 +66404,7 @@
       </c>
       <c r="Z590" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA590" t="inlineStr">
@@ -66405,7 +66414,7 @@
       </c>
       <c r="AB590" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD590" t="b">
@@ -66436,7 +66445,7 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>135385295</v>
+        <v>135385287</v>
       </c>
       <c r="B591" t="n">
         <v>83358</v>
@@ -66471,10 +66480,10 @@
         </is>
       </c>
       <c r="Q591" t="n">
-        <v>607872</v>
+        <v>607783</v>
       </c>
       <c r="R591" t="n">
-        <v>7309907</v>
+        <v>7310048</v>
       </c>
       <c r="S591" t="n">
         <v>5</v>
@@ -66506,7 +66515,7 @@
       </c>
       <c r="Z591" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA591" t="inlineStr">
@@ -66516,7 +66525,7 @@
       </c>
       <c r="AB591" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AD591" t="b">
@@ -66547,7 +66556,7 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>135393123</v>
+        <v>135385295</v>
       </c>
       <c r="B592" t="n">
         <v>83358</v>
@@ -66578,14 +66587,14 @@
       <c r="I592" t="inlineStr"/>
       <c r="P592" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q592" t="n">
-        <v>608142</v>
+        <v>607872</v>
       </c>
       <c r="R592" t="n">
-        <v>7309598</v>
+        <v>7309907</v>
       </c>
       <c r="S592" t="n">
         <v>5</v>
@@ -66617,7 +66626,7 @@
       </c>
       <c r="Z592" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA592" t="inlineStr">
@@ -66627,7 +66636,7 @@
       </c>
       <c r="AB592" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD592" t="b">
@@ -66642,44 +66651,48 @@
       <c r="AT592" t="inlineStr"/>
       <c r="AW592" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX592" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY592" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY592" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>135385194</v>
+        <v>135393123</v>
       </c>
       <c r="B593" t="n">
-        <v>80493</v>
+        <v>83358</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I593" t="inlineStr"/>
@@ -66689,10 +66702,10 @@
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>608065</v>
+        <v>608142</v>
       </c>
       <c r="R593" t="n">
-        <v>7309659</v>
+        <v>7309598</v>
       </c>
       <c r="S593" t="n">
         <v>5</v>
@@ -66724,7 +66737,7 @@
       </c>
       <c r="Z593" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA593" t="inlineStr">
@@ -66734,7 +66747,7 @@
       </c>
       <c r="AB593" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD593" t="b">
@@ -66749,26 +66762,22 @@
       <c r="AT593" t="inlineStr"/>
       <c r="AW593" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX593" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY593" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>135349918</v>
+        <v>135385194</v>
       </c>
       <c r="B594" t="n">
-        <v>57972</v>
+        <v>80493</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -66776,42 +66785,37 @@
         </is>
       </c>
       <c r="E594" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I594" t="inlineStr"/>
-      <c r="M594" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P594" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>607960</v>
+        <v>608065</v>
       </c>
       <c r="R594" t="n">
-        <v>7309607</v>
+        <v>7309659</v>
       </c>
       <c r="S594" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
@@ -66835,22 +66839,22 @@
       </c>
       <c r="Y594" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z594" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA594" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB594" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD594" t="b">
@@ -66865,12 +66869,12 @@
       <c r="AT594" t="inlineStr"/>
       <c r="AW594" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX594" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY594" t="inlineStr">
@@ -66881,27 +66885,27 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>135349901</v>
+        <v>135349918</v>
       </c>
       <c r="B595" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -66921,13 +66925,13 @@
         </is>
       </c>
       <c r="Q595" t="n">
-        <v>608001</v>
+        <v>607960</v>
       </c>
       <c r="R595" t="n">
-        <v>7309725</v>
+        <v>7309607</v>
       </c>
       <c r="S595" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T595" t="inlineStr">
         <is>
@@ -66956,7 +66960,7 @@
       </c>
       <c r="Z595" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA595" t="inlineStr">
@@ -66966,12 +66970,7 @@
       </c>
       <c r="AB595" t="inlineStr">
         <is>
-          <t>15:37</t>
-        </is>
-      </c>
-      <c r="AC595" t="inlineStr">
-        <is>
-          <t>äldre ringhack</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD595" t="b">
@@ -67002,7 +67001,7 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>135349904</v>
+        <v>135349901</v>
       </c>
       <c r="B596" t="n">
         <v>57975</v>
@@ -67042,13 +67041,13 @@
         </is>
       </c>
       <c r="Q596" t="n">
-        <v>607987</v>
+        <v>608001</v>
       </c>
       <c r="R596" t="n">
-        <v>7309708</v>
+        <v>7309725</v>
       </c>
       <c r="S596" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T596" t="inlineStr">
         <is>
@@ -67077,7 +67076,7 @@
       </c>
       <c r="Z596" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA596" t="inlineStr">
@@ -67087,19 +67086,19 @@
       </c>
       <c r="AB596" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AC596" t="inlineStr">
         <is>
-          <t>skalad klen gran</t>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD596" t="b">
         <v>0</v>
       </c>
       <c r="AE596" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG596" t="b">
         <v>0</v>
@@ -67123,7 +67122,7 @@
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>135378174</v>
+        <v>135349904</v>
       </c>
       <c r="B597" t="n">
         <v>57975</v>
@@ -67154,7 +67153,7 @@
       <c r="I597" t="inlineStr"/>
       <c r="M597" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P597" t="inlineStr">
@@ -67163,13 +67162,13 @@
         </is>
       </c>
       <c r="Q597" t="n">
-        <v>607782</v>
+        <v>607987</v>
       </c>
       <c r="R597" t="n">
-        <v>7310010</v>
+        <v>7309708</v>
       </c>
       <c r="S597" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="T597" t="inlineStr">
         <is>
@@ -67193,34 +67192,34 @@
       </c>
       <c r="Y597" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z597" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA597" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB597" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AC597" t="inlineStr">
         <is>
-          <t>färska ringhack</t>
+          <t>skalad klen gran</t>
         </is>
       </c>
       <c r="AD597" t="b">
         <v>0</v>
       </c>
       <c r="AE597" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG597" t="b">
         <v>0</v>
@@ -67244,7 +67243,7 @@
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>135378178</v>
+        <v>135378174</v>
       </c>
       <c r="B598" t="n">
         <v>57975</v>
@@ -67275,7 +67274,7 @@
       <c r="I598" t="inlineStr"/>
       <c r="M598" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P598" t="inlineStr">
@@ -67284,10 +67283,10 @@
         </is>
       </c>
       <c r="Q598" t="n">
-        <v>607697</v>
+        <v>607782</v>
       </c>
       <c r="R598" t="n">
-        <v>7309979</v>
+        <v>7310010</v>
       </c>
       <c r="S598" t="n">
         <v>4</v>
@@ -67319,7 +67318,7 @@
       </c>
       <c r="Z598" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA598" t="inlineStr">
@@ -67329,19 +67328,19 @@
       </c>
       <c r="AB598" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC598" t="inlineStr">
         <is>
-          <t>skalad klen gran</t>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD598" t="b">
         <v>0</v>
       </c>
       <c r="AE598" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG598" t="b">
         <v>0</v>
@@ -67365,7 +67364,7 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>135378180</v>
+        <v>135378178</v>
       </c>
       <c r="B599" t="n">
         <v>57975</v>
@@ -67405,13 +67404,13 @@
         </is>
       </c>
       <c r="Q599" t="n">
-        <v>607701</v>
+        <v>607697</v>
       </c>
       <c r="R599" t="n">
         <v>7309979</v>
       </c>
       <c r="S599" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T599" t="inlineStr">
         <is>
@@ -67440,7 +67439,7 @@
       </c>
       <c r="Z599" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA599" t="inlineStr">
@@ -67450,19 +67449,19 @@
       </c>
       <c r="AB599" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AC599" t="inlineStr">
         <is>
-          <t>äldre ringhack</t>
+          <t>skalad klen gran</t>
         </is>
       </c>
       <c r="AD599" t="b">
         <v>0</v>
       </c>
       <c r="AE599" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG599" t="b">
         <v>0</v>
@@ -67486,7 +67485,7 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>135382861</v>
+        <v>135378180</v>
       </c>
       <c r="B600" t="n">
         <v>57975</v>
@@ -67515,19 +67514,24 @@
         </is>
       </c>
       <c r="I600" t="inlineStr"/>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P600" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q600" t="n">
-        <v>607775</v>
+        <v>607701</v>
       </c>
       <c r="R600" t="n">
-        <v>7309978</v>
+        <v>7309979</v>
       </c>
       <c r="S600" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T600" t="inlineStr">
         <is>
@@ -67556,7 +67560,7 @@
       </c>
       <c r="Z600" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA600" t="inlineStr">
@@ -67566,12 +67570,12 @@
       </c>
       <c r="AB600" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AC600" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>äldre ringhack</t>
         </is>
       </c>
       <c r="AD600" t="b">
@@ -67586,12 +67590,12 @@
       <c r="AT600" t="inlineStr"/>
       <c r="AW600" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX600" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY600" t="inlineStr">
@@ -67602,48 +67606,48 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>80987071</v>
+        <v>135382861</v>
       </c>
       <c r="B601" t="n">
-        <v>57141</v>
+        <v>57975</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E601" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I601" t="inlineStr"/>
       <c r="P601" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q601" t="n">
-        <v>608360</v>
+        <v>607775</v>
       </c>
       <c r="R601" t="n">
-        <v>7309498</v>
+        <v>7309978</v>
       </c>
       <c r="S601" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T601" t="inlineStr">
         <is>
@@ -67667,12 +67671,27 @@
       </c>
       <c r="Y601" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z601" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA601" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB601" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC601" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD601" t="b">
@@ -67687,22 +67706,26 @@
       <c r="AT601" t="inlineStr"/>
       <c r="AW601" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX601" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY601" t="inlineStr"/>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY601" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>135385293</v>
+        <v>80987071</v>
       </c>
       <c r="B602" t="n">
-        <v>57162</v>
+        <v>57141</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -67730,17 +67753,17 @@
       <c r="I602" t="inlineStr"/>
       <c r="P602" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q602" t="n">
-        <v>607844</v>
+        <v>608360</v>
       </c>
       <c r="R602" t="n">
-        <v>7309941</v>
+        <v>7309498</v>
       </c>
       <c r="S602" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T602" t="inlineStr">
         <is>
@@ -67764,27 +67787,12 @@
       </c>
       <c r="Y602" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z602" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA602" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB602" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC602" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD602" t="b">
@@ -67799,64 +67807,60 @@
       <c r="AT602" t="inlineStr"/>
       <c r="AW602" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX602" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY602" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY602" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>80987075</v>
+        <v>135385293</v>
       </c>
       <c r="B603" t="n">
-        <v>58057</v>
+        <v>57162</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E603" t="n">
-        <v>103031</v>
+        <v>100138</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G603" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I603" t="inlineStr"/>
       <c r="P603" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q603" t="n">
-        <v>608231</v>
+        <v>607844</v>
       </c>
       <c r="R603" t="n">
-        <v>7309648</v>
+        <v>7309941</v>
       </c>
       <c r="S603" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T603" t="inlineStr">
         <is>
@@ -67880,12 +67884,27 @@
       </c>
       <c r="Y603" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z603" t="inlineStr">
+        <is>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA603" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB603" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC603" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD603" t="b">
@@ -67900,22 +67919,26 @@
       <c r="AT603" t="inlineStr"/>
       <c r="AW603" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX603" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY603" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY603" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>135349897</v>
+        <v>80987075</v>
       </c>
       <c r="B604" t="n">
-        <v>58079</v>
+        <v>58057</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -67941,24 +67964,19 @@
         </is>
       </c>
       <c r="I604" t="inlineStr"/>
-      <c r="M604" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
       <c r="P604" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q604" t="n">
-        <v>608053</v>
+        <v>608231</v>
       </c>
       <c r="R604" t="n">
-        <v>7309696</v>
+        <v>7309648</v>
       </c>
       <c r="S604" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T604" t="inlineStr">
         <is>
@@ -67982,22 +68000,12 @@
       </c>
       <c r="Y604" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z604" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA604" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB604" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD604" t="b">
@@ -68012,64 +68020,65 @@
       <c r="AT604" t="inlineStr"/>
       <c r="AW604" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX604" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY604" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY604" t="inlineStr"/>
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>135388293</v>
+        <v>135349897</v>
       </c>
       <c r="B605" t="n">
-        <v>58839</v>
+        <v>58079</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E605" t="n">
-        <v>208249</v>
+        <v>103031</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I605" t="inlineStr"/>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P605" t="inlineStr">
         <is>
-          <t>Laisdalen päronberget, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q605" t="n">
-        <v>608068</v>
+        <v>608053</v>
       </c>
       <c r="R605" t="n">
-        <v>7309658</v>
+        <v>7309696</v>
       </c>
       <c r="S605" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="T605" t="inlineStr">
         <is>
@@ -68093,22 +68102,22 @@
       </c>
       <c r="Y605" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z605" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA605" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB605" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD605" t="b">
@@ -68123,12 +68132,12 @@
       <c r="AT605" t="inlineStr"/>
       <c r="AW605" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX605" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY605" t="inlineStr">
@@ -68139,10 +68148,10 @@
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>135351869</v>
+        <v>135388293</v>
       </c>
       <c r="B606" t="n">
-        <v>99094</v>
+        <v>58839</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -68150,37 +68159,37 @@
         </is>
       </c>
       <c r="E606" t="n">
-        <v>219795</v>
+        <v>208249</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I606" t="inlineStr"/>
       <c r="P606" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Laisdalen päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q606" t="n">
-        <v>608121</v>
+        <v>608068</v>
       </c>
       <c r="R606" t="n">
-        <v>7309664</v>
+        <v>7309658</v>
       </c>
       <c r="S606" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T606" t="inlineStr">
         <is>
@@ -68204,22 +68213,22 @@
       </c>
       <c r="Y606" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z606" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA606" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB606" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD606" t="b">
@@ -68234,12 +68243,12 @@
       <c r="AT606" t="inlineStr"/>
       <c r="AW606" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX606" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY606" t="inlineStr">
@@ -68250,10 +68259,10 @@
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>135351871</v>
+        <v>135351869</v>
       </c>
       <c r="B607" t="n">
-        <v>99197</v>
+        <v>99094</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -68261,21 +68270,21 @@
         </is>
       </c>
       <c r="E607" t="n">
-        <v>219811</v>
+        <v>219795</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I607" t="inlineStr"/>
@@ -68285,13 +68294,13 @@
         </is>
       </c>
       <c r="Q607" t="n">
-        <v>608132</v>
+        <v>608121</v>
       </c>
       <c r="R607" t="n">
-        <v>7309645</v>
+        <v>7309664</v>
       </c>
       <c r="S607" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T607" t="inlineStr">
         <is>
@@ -68320,7 +68329,7 @@
       </c>
       <c r="Z607" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA607" t="inlineStr">
@@ -68330,7 +68339,7 @@
       </c>
       <c r="AB607" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD607" t="b">
@@ -68361,7 +68370,7 @@
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>135385327</v>
+        <v>135351871</v>
       </c>
       <c r="B608" t="n">
         <v>99197</v>
@@ -68392,17 +68401,17 @@
       <c r="I608" t="inlineStr"/>
       <c r="P608" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q608" t="n">
-        <v>608066</v>
+        <v>608132</v>
       </c>
       <c r="R608" t="n">
-        <v>7309643</v>
+        <v>7309645</v>
       </c>
       <c r="S608" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="T608" t="inlineStr">
         <is>
@@ -68426,22 +68435,22 @@
       </c>
       <c r="Y608" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z608" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA608" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB608" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD608" t="b">
@@ -68456,12 +68465,12 @@
       <c r="AT608" t="inlineStr"/>
       <c r="AW608" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX608" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY608" t="inlineStr">
@@ -68472,7 +68481,7 @@
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>135393145</v>
+        <v>135385327</v>
       </c>
       <c r="B609" t="n">
         <v>99197</v>
@@ -68503,17 +68512,17 @@
       <c r="I609" t="inlineStr"/>
       <c r="P609" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q609" t="n">
-        <v>608084</v>
+        <v>608066</v>
       </c>
       <c r="R609" t="n">
-        <v>7309695</v>
+        <v>7309643</v>
       </c>
       <c r="S609" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T609" t="inlineStr">
         <is>
@@ -68542,7 +68551,7 @@
       </c>
       <c r="Z609" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA609" t="inlineStr">
@@ -68552,7 +68561,7 @@
       </c>
       <c r="AB609" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD609" t="b">
@@ -68567,22 +68576,26 @@
       <c r="AT609" t="inlineStr"/>
       <c r="AW609" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX609" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY609" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY609" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>135393157</v>
+        <v>135393145</v>
       </c>
       <c r="B610" t="n">
-        <v>108274</v>
+        <v>99197</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -68590,21 +68603,21 @@
         </is>
       </c>
       <c r="E610" t="n">
-        <v>220102</v>
+        <v>219811</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I610" t="inlineStr"/>
@@ -68614,10 +68627,10 @@
         </is>
       </c>
       <c r="Q610" t="n">
-        <v>608135</v>
+        <v>608084</v>
       </c>
       <c r="R610" t="n">
-        <v>7309645</v>
+        <v>7309695</v>
       </c>
       <c r="S610" t="n">
         <v>5</v>
@@ -68649,7 +68662,7 @@
       </c>
       <c r="Z610" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA610" t="inlineStr">
@@ -68659,7 +68672,7 @@
       </c>
       <c r="AB610" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD610" t="b">
@@ -68686,10 +68699,10 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>135393151</v>
+        <v>135393157</v>
       </c>
       <c r="B611" t="n">
-        <v>110023</v>
+        <v>108274</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -68697,21 +68710,21 @@
         </is>
       </c>
       <c r="E611" t="n">
-        <v>220263</v>
+        <v>220102</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>Fjällskråp</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>Petasites frigidus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I611" t="inlineStr"/>
@@ -68721,10 +68734,10 @@
         </is>
       </c>
       <c r="Q611" t="n">
-        <v>608151</v>
+        <v>608135</v>
       </c>
       <c r="R611" t="n">
-        <v>7309729</v>
+        <v>7309645</v>
       </c>
       <c r="S611" t="n">
         <v>5</v>
@@ -68756,7 +68769,7 @@
       </c>
       <c r="Z611" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA611" t="inlineStr">
@@ -68766,7 +68779,7 @@
       </c>
       <c r="AB611" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD611" t="b">
@@ -68793,10 +68806,10 @@
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>135351874</v>
+        <v>135393151</v>
       </c>
       <c r="B612" t="n">
-        <v>110150</v>
+        <v>110023</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -68804,34 +68817,34 @@
         </is>
       </c>
       <c r="E612" t="n">
-        <v>220294</v>
+        <v>220263</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Fjällskråp</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Petasites frigidus</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
+          <t>(L.) Fr.</t>
         </is>
       </c>
       <c r="I612" t="inlineStr"/>
       <c r="P612" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q612" t="n">
-        <v>608136</v>
+        <v>608151</v>
       </c>
       <c r="R612" t="n">
-        <v>7309644</v>
+        <v>7309729</v>
       </c>
       <c r="S612" t="n">
         <v>5</v>
@@ -68858,22 +68871,22 @@
       </c>
       <c r="Y612" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z612" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA612" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB612" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD612" t="b">
@@ -68888,73 +68901,60 @@
       <c r="AT612" t="inlineStr"/>
       <c r="AW612" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX612" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY612" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>135349921</v>
+        <v>135351874</v>
       </c>
       <c r="B613" t="n">
-        <v>99195</v>
+        <v>110150</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E613" t="n">
-        <v>220787</v>
+        <v>220294</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I613" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K613" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr"/>
       <c r="P613" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q613" t="n">
-        <v>607991</v>
+        <v>608136</v>
       </c>
       <c r="R613" t="n">
-        <v>7309608</v>
+        <v>7309644</v>
       </c>
       <c r="S613" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T613" t="inlineStr">
         <is>
@@ -68983,7 +68983,7 @@
       </c>
       <c r="Z613" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA613" t="inlineStr">
@@ -68993,7 +68993,7 @@
       </c>
       <c r="AB613" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD613" t="b">
@@ -69008,12 +69008,12 @@
       <c r="AT613" t="inlineStr"/>
       <c r="AW613" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX613" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY613" t="inlineStr">
@@ -69024,49 +69024,54 @@
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>135349909</v>
+        <v>135349921</v>
       </c>
       <c r="B614" t="n">
-        <v>106309</v>
+        <v>99195</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E614" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I614" t="inlineStr"/>
-      <c r="J614" t="inlineStr"/>
-      <c r="K614" t="inlineStr"/>
-      <c r="L614" t="inlineStr"/>
-      <c r="N614" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P614" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q614" t="n">
-        <v>608014</v>
+        <v>607991</v>
       </c>
       <c r="R614" t="n">
-        <v>7309639</v>
+        <v>7309608</v>
       </c>
       <c r="S614" t="n">
         <v>3</v>
@@ -69098,7 +69103,7 @@
       </c>
       <c r="Z614" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA614" t="inlineStr">
@@ -69108,7 +69113,7 @@
       </c>
       <c r="AB614" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD614" t="b">
@@ -69117,7 +69122,6 @@
       <c r="AE614" t="b">
         <v>0</v>
       </c>
-      <c r="AF614" t="inlineStr"/>
       <c r="AG614" t="b">
         <v>0</v>
       </c>
@@ -69140,7 +69144,7 @@
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>135384319</v>
+        <v>135349909</v>
       </c>
       <c r="B615" t="n">
         <v>106309</v>
@@ -69169,19 +69173,23 @@
         </is>
       </c>
       <c r="I615" t="inlineStr"/>
+      <c r="J615" t="inlineStr"/>
+      <c r="K615" t="inlineStr"/>
+      <c r="L615" t="inlineStr"/>
+      <c r="N615" t="inlineStr"/>
       <c r="P615" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q615" t="n">
-        <v>608048</v>
+        <v>608014</v>
       </c>
       <c r="R615" t="n">
-        <v>7309656</v>
+        <v>7309639</v>
       </c>
       <c r="S615" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T615" t="inlineStr">
         <is>
@@ -69205,22 +69213,22 @@
       </c>
       <c r="Y615" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z615" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA615" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB615" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD615" t="b">
@@ -69229,18 +69237,19 @@
       <c r="AE615" t="b">
         <v>0</v>
       </c>
+      <c r="AF615" t="inlineStr"/>
       <c r="AG615" t="b">
         <v>0</v>
       </c>
       <c r="AT615" t="inlineStr"/>
       <c r="AW615" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX615" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY615" t="inlineStr">
@@ -69251,7 +69260,7 @@
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>135384324</v>
+        <v>135384319</v>
       </c>
       <c r="B616" t="n">
         <v>106309</v>
@@ -69286,10 +69295,10 @@
         </is>
       </c>
       <c r="Q616" t="n">
-        <v>608042</v>
+        <v>608048</v>
       </c>
       <c r="R616" t="n">
-        <v>7309653</v>
+        <v>7309656</v>
       </c>
       <c r="S616" t="n">
         <v>5</v>
@@ -69321,7 +69330,7 @@
       </c>
       <c r="Z616" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA616" t="inlineStr">
@@ -69331,7 +69340,7 @@
       </c>
       <c r="AB616" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD616" t="b">
@@ -69362,7 +69371,7 @@
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>135388296</v>
+        <v>135384324</v>
       </c>
       <c r="B617" t="n">
         <v>106309</v>
@@ -69393,17 +69402,17 @@
       <c r="I617" t="inlineStr"/>
       <c r="P617" t="inlineStr">
         <is>
-          <t>Laisdalen päronberget, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q617" t="n">
-        <v>608057</v>
+        <v>608042</v>
       </c>
       <c r="R617" t="n">
-        <v>7309661</v>
+        <v>7309653</v>
       </c>
       <c r="S617" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T617" t="inlineStr">
         <is>
@@ -69432,7 +69441,7 @@
       </c>
       <c r="Z617" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA617" t="inlineStr">
@@ -69442,7 +69451,7 @@
       </c>
       <c r="AB617" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD617" t="b">
@@ -69457,12 +69466,12 @@
       <c r="AT617" t="inlineStr"/>
       <c r="AW617" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX617" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY617" t="inlineStr">
@@ -69473,7 +69482,7 @@
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>135393149</v>
+        <v>135388296</v>
       </c>
       <c r="B618" t="n">
         <v>106309</v>
@@ -69504,17 +69513,17 @@
       <c r="I618" t="inlineStr"/>
       <c r="P618" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q618" t="n">
-        <v>608109</v>
+        <v>608057</v>
       </c>
       <c r="R618" t="n">
-        <v>7309705</v>
+        <v>7309661</v>
       </c>
       <c r="S618" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T618" t="inlineStr">
         <is>
@@ -69543,7 +69552,7 @@
       </c>
       <c r="Z618" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA618" t="inlineStr">
@@ -69553,7 +69562,7 @@
       </c>
       <c r="AB618" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD618" t="b">
@@ -69568,22 +69577,26 @@
       <c r="AT618" t="inlineStr"/>
       <c r="AW618" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX618" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY618" t="inlineStr"/>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY618" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>135385157</v>
+        <v>135393149</v>
       </c>
       <c r="B619" t="n">
-        <v>98063</v>
+        <v>106309</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -69591,21 +69604,21 @@
         </is>
       </c>
       <c r="E619" t="n">
-        <v>221946</v>
+        <v>221725</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I619" t="inlineStr"/>
@@ -69615,10 +69628,10 @@
         </is>
       </c>
       <c r="Q619" t="n">
-        <v>607832</v>
+        <v>608109</v>
       </c>
       <c r="R619" t="n">
-        <v>7310013</v>
+        <v>7309705</v>
       </c>
       <c r="S619" t="n">
         <v>5</v>
@@ -69650,7 +69663,7 @@
       </c>
       <c r="Z619" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA619" t="inlineStr">
@@ -69660,7 +69673,7 @@
       </c>
       <c r="AB619" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD619" t="b">
@@ -69675,26 +69688,22 @@
       <c r="AT619" t="inlineStr"/>
       <c r="AW619" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX619" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY619" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>135349896</v>
+        <v>135385157</v>
       </c>
       <c r="B620" t="n">
-        <v>99217</v>
+        <v>98063</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -69702,37 +69711,37 @@
         </is>
       </c>
       <c r="E620" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I620" t="inlineStr"/>
       <c r="P620" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q620" t="n">
-        <v>608056</v>
+        <v>607832</v>
       </c>
       <c r="R620" t="n">
-        <v>7309695</v>
+        <v>7310013</v>
       </c>
       <c r="S620" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T620" t="inlineStr">
         <is>
@@ -69756,22 +69765,22 @@
       </c>
       <c r="Y620" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z620" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA620" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB620" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD620" t="b">
@@ -69786,12 +69795,12 @@
       <c r="AT620" t="inlineStr"/>
       <c r="AW620" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX620" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY620" t="inlineStr">
@@ -69802,10 +69811,10 @@
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>135349910</v>
+        <v>135349896</v>
       </c>
       <c r="B621" t="n">
-        <v>103764</v>
+        <v>99217</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -69813,21 +69822,21 @@
         </is>
       </c>
       <c r="E621" t="n">
-        <v>222004</v>
+        <v>221952</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I621" t="inlineStr"/>
@@ -69837,10 +69846,10 @@
         </is>
       </c>
       <c r="Q621" t="n">
-        <v>608014</v>
+        <v>608056</v>
       </c>
       <c r="R621" t="n">
-        <v>7309639</v>
+        <v>7309695</v>
       </c>
       <c r="S621" t="n">
         <v>3</v>
@@ -69872,7 +69881,7 @@
       </c>
       <c r="Z621" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA621" t="inlineStr">
@@ -69882,7 +69891,7 @@
       </c>
       <c r="AB621" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD621" t="b">
@@ -69913,10 +69922,10 @@
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>135356148</v>
+        <v>135349910</v>
       </c>
       <c r="B622" t="n">
-        <v>104707</v>
+        <v>103764</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -69924,16 +69933,16 @@
         </is>
       </c>
       <c r="E622" t="n">
-        <v>222412</v>
+        <v>222004</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H622" t="inlineStr">
@@ -69948,13 +69957,13 @@
         </is>
       </c>
       <c r="Q622" t="n">
-        <v>607978</v>
+        <v>608014</v>
       </c>
       <c r="R622" t="n">
-        <v>7309596</v>
+        <v>7309639</v>
       </c>
       <c r="S622" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="T622" t="inlineStr">
         <is>
@@ -69983,7 +69992,7 @@
       </c>
       <c r="Z622" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA622" t="inlineStr">
@@ -69993,7 +70002,7 @@
       </c>
       <c r="AB622" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD622" t="b">
@@ -70008,12 +70017,12 @@
       <c r="AT622" t="inlineStr"/>
       <c r="AW622" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX622" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY622" t="inlineStr">
@@ -70024,7 +70033,7 @@
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>135393154</v>
+        <v>135356148</v>
       </c>
       <c r="B623" t="n">
         <v>104707</v>
@@ -70055,17 +70064,17 @@
       <c r="I623" t="inlineStr"/>
       <c r="P623" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q623" t="n">
-        <v>608171</v>
+        <v>607978</v>
       </c>
       <c r="R623" t="n">
-        <v>7309720</v>
+        <v>7309596</v>
       </c>
       <c r="S623" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T623" t="inlineStr">
         <is>
@@ -70089,22 +70098,22 @@
       </c>
       <c r="Y623" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z623" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA623" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB623" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD623" t="b">
@@ -70119,22 +70128,26 @@
       <c r="AT623" t="inlineStr"/>
       <c r="AW623" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX623" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY623" t="inlineStr"/>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY623" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>135393126</v>
+        <v>135393154</v>
       </c>
       <c r="B624" t="n">
-        <v>100806</v>
+        <v>104707</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -70142,16 +70155,16 @@
         </is>
       </c>
       <c r="E624" t="n">
-        <v>222584</v>
+        <v>222412</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -70166,10 +70179,10 @@
         </is>
       </c>
       <c r="Q624" t="n">
-        <v>608021</v>
+        <v>608171</v>
       </c>
       <c r="R624" t="n">
-        <v>7309604</v>
+        <v>7309720</v>
       </c>
       <c r="S624" t="n">
         <v>5</v>
@@ -70201,7 +70214,7 @@
       </c>
       <c r="Z624" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA624" t="inlineStr">
@@ -70211,7 +70224,7 @@
       </c>
       <c r="AB624" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD624" t="b">
@@ -70238,10 +70251,10 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>135388299</v>
+        <v>135393126</v>
       </c>
       <c r="B625" t="n">
-        <v>102871</v>
+        <v>100806</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -70249,16 +70262,16 @@
         </is>
       </c>
       <c r="E625" t="n">
-        <v>223037</v>
+        <v>222584</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Melica nutans</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -70269,17 +70282,17 @@
       <c r="I625" t="inlineStr"/>
       <c r="P625" t="inlineStr">
         <is>
-          <t>Laisdalen päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q625" t="n">
-        <v>608030</v>
+        <v>608021</v>
       </c>
       <c r="R625" t="n">
-        <v>7309591</v>
+        <v>7309604</v>
       </c>
       <c r="S625" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="T625" t="inlineStr">
         <is>
@@ -70308,7 +70321,7 @@
       </c>
       <c r="Z625" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA625" t="inlineStr">
@@ -70318,7 +70331,7 @@
       </c>
       <c r="AB625" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD625" t="b">
@@ -70333,26 +70346,22 @@
       <c r="AT625" t="inlineStr"/>
       <c r="AW625" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX625" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
-        </is>
-      </c>
-      <c r="AY625" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>135351867</v>
+        <v>135388299</v>
       </c>
       <c r="B626" t="n">
-        <v>99198</v>
+        <v>102871</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -70360,33 +70369,37 @@
         </is>
       </c>
       <c r="E626" t="n">
-        <v>223614</v>
+        <v>223037</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>Vanlig brudsporre</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. conopsea</t>
-        </is>
-      </c>
-      <c r="H626" t="inlineStr"/>
+          <t>Geum rivale</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I626" t="inlineStr"/>
       <c r="P626" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Laisdalen päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q626" t="n">
-        <v>608123</v>
+        <v>608030</v>
       </c>
       <c r="R626" t="n">
-        <v>7309661</v>
+        <v>7309591</v>
       </c>
       <c r="S626" t="n">
-        <v>5</v>
+        <v>61</v>
       </c>
       <c r="T626" t="inlineStr">
         <is>
@@ -70410,22 +70423,22 @@
       </c>
       <c r="Y626" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z626" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA626" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB626" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD626" t="b">
@@ -70434,19 +70447,18 @@
       <c r="AE626" t="b">
         <v>0</v>
       </c>
-      <c r="AF626" t="inlineStr"/>
       <c r="AG626" t="b">
         <v>0</v>
       </c>
       <c r="AT626" t="inlineStr"/>
       <c r="AW626" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX626" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY626" t="inlineStr">
@@ -70457,10 +70469,10 @@
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>135349891</v>
+        <v>135351867</v>
       </c>
       <c r="B627" t="n">
-        <v>101293</v>
+        <v>99198</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -70468,23 +70480,19 @@
         </is>
       </c>
       <c r="E627" t="n">
-        <v>224885</v>
+        <v>223614</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Vanlig brudsporre</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H627" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr"/>
       <c r="I627" t="inlineStr"/>
       <c r="P627" t="inlineStr">
         <is>
@@ -70492,13 +70500,13 @@
         </is>
       </c>
       <c r="Q627" t="n">
-        <v>608082</v>
+        <v>608123</v>
       </c>
       <c r="R627" t="n">
-        <v>7309684</v>
+        <v>7309661</v>
       </c>
       <c r="S627" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T627" t="inlineStr">
         <is>
@@ -70527,7 +70535,7 @@
       </c>
       <c r="Z627" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA627" t="inlineStr">
@@ -70537,7 +70545,7 @@
       </c>
       <c r="AB627" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD627" t="b">
@@ -70546,18 +70554,19 @@
       <c r="AE627" t="b">
         <v>0</v>
       </c>
+      <c r="AF627" t="inlineStr"/>
       <c r="AG627" t="b">
         <v>0</v>
       </c>
       <c r="AT627" t="inlineStr"/>
       <c r="AW627" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX627" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY627" t="inlineStr">
@@ -70568,7 +70577,7 @@
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>135393129</v>
+        <v>135349891</v>
       </c>
       <c r="B628" t="n">
         <v>101293</v>
@@ -70599,17 +70608,17 @@
       <c r="I628" t="inlineStr"/>
       <c r="P628" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q628" t="n">
-        <v>608021</v>
+        <v>608082</v>
       </c>
       <c r="R628" t="n">
-        <v>7309619</v>
+        <v>7309684</v>
       </c>
       <c r="S628" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T628" t="inlineStr">
         <is>
@@ -70633,22 +70642,22 @@
       </c>
       <c r="Y628" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z628" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA628" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB628" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD628" t="b">
@@ -70663,19 +70672,23 @@
       <c r="AT628" t="inlineStr"/>
       <c r="AW628" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX628" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY628" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY628" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>135393131</v>
+        <v>135393129</v>
       </c>
       <c r="B629" t="n">
         <v>101293</v>
@@ -70710,10 +70723,10 @@
         </is>
       </c>
       <c r="Q629" t="n">
-        <v>608014</v>
+        <v>608021</v>
       </c>
       <c r="R629" t="n">
-        <v>7309625</v>
+        <v>7309619</v>
       </c>
       <c r="S629" t="n">
         <v>5</v>
@@ -70745,7 +70758,7 @@
       </c>
       <c r="Z629" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA629" t="inlineStr">
@@ -70755,7 +70768,7 @@
       </c>
       <c r="AB629" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD629" t="b">
@@ -70782,7 +70795,7 @@
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>135393150</v>
+        <v>135393131</v>
       </c>
       <c r="B630" t="n">
         <v>101293</v>
@@ -70817,10 +70830,10 @@
         </is>
       </c>
       <c r="Q630" t="n">
-        <v>608136</v>
+        <v>608014</v>
       </c>
       <c r="R630" t="n">
-        <v>7309706</v>
+        <v>7309625</v>
       </c>
       <c r="S630" t="n">
         <v>5</v>
@@ -70852,7 +70865,7 @@
       </c>
       <c r="Z630" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA630" t="inlineStr">
@@ -70862,7 +70875,7 @@
       </c>
       <c r="AB630" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD630" t="b">
@@ -70889,48 +70902,48 @@
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>135378173</v>
+        <v>135393150</v>
       </c>
       <c r="B631" t="n">
-        <v>78382</v>
+        <v>101293</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E631" t="n">
-        <v>228579</v>
+        <v>224885</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H631" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I631" t="inlineStr"/>
       <c r="P631" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q631" t="n">
-        <v>607794</v>
+        <v>608136</v>
       </c>
       <c r="R631" t="n">
-        <v>7309999</v>
+        <v>7309706</v>
       </c>
       <c r="S631" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T631" t="inlineStr">
         <is>
@@ -70959,7 +70972,7 @@
       </c>
       <c r="Z631" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA631" t="inlineStr">
@@ -70969,7 +70982,7 @@
       </c>
       <c r="AB631" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD631" t="b">
@@ -70984,23 +70997,19 @@
       <c r="AT631" t="inlineStr"/>
       <c r="AW631" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX631" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY631" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>135378175</v>
+        <v>135378173</v>
       </c>
       <c r="B632" t="n">
         <v>78382</v>
@@ -71035,10 +71044,10 @@
         </is>
       </c>
       <c r="Q632" t="n">
-        <v>607781</v>
+        <v>607794</v>
       </c>
       <c r="R632" t="n">
-        <v>7310006</v>
+        <v>7309999</v>
       </c>
       <c r="S632" t="n">
         <v>4</v>
@@ -71070,7 +71079,7 @@
       </c>
       <c r="Z632" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA632" t="inlineStr">
@@ -71080,7 +71089,7 @@
       </c>
       <c r="AB632" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD632" t="b">
@@ -71111,7 +71120,7 @@
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>135378179</v>
+        <v>135378175</v>
       </c>
       <c r="B633" t="n">
         <v>78382</v>
@@ -71146,10 +71155,10 @@
         </is>
       </c>
       <c r="Q633" t="n">
-        <v>607702</v>
+        <v>607781</v>
       </c>
       <c r="R633" t="n">
-        <v>7309979</v>
+        <v>7310006</v>
       </c>
       <c r="S633" t="n">
         <v>4</v>
@@ -71181,7 +71190,7 @@
       </c>
       <c r="Z633" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA633" t="inlineStr">
@@ -71191,7 +71200,7 @@
       </c>
       <c r="AB633" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD633" t="b">
@@ -71222,7 +71231,7 @@
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>135378181</v>
+        <v>135378179</v>
       </c>
       <c r="B634" t="n">
         <v>78382</v>
@@ -71257,10 +71266,10 @@
         </is>
       </c>
       <c r="Q634" t="n">
-        <v>607671</v>
+        <v>607702</v>
       </c>
       <c r="R634" t="n">
-        <v>7309990</v>
+        <v>7309979</v>
       </c>
       <c r="S634" t="n">
         <v>4</v>
@@ -71292,7 +71301,7 @@
       </c>
       <c r="Z634" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA634" t="inlineStr">
@@ -71302,7 +71311,7 @@
       </c>
       <c r="AB634" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD634" t="b">
@@ -71333,7 +71342,7 @@
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>135385232</v>
+        <v>135378181</v>
       </c>
       <c r="B635" t="n">
         <v>78382</v>
@@ -71364,17 +71373,17 @@
       <c r="I635" t="inlineStr"/>
       <c r="P635" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q635" t="n">
-        <v>607787</v>
+        <v>607671</v>
       </c>
       <c r="R635" t="n">
-        <v>7310002</v>
+        <v>7309990</v>
       </c>
       <c r="S635" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T635" t="inlineStr">
         <is>
@@ -71403,7 +71412,7 @@
       </c>
       <c r="Z635" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA635" t="inlineStr">
@@ -71413,7 +71422,7 @@
       </c>
       <c r="AB635" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD635" t="b">
@@ -71428,12 +71437,12 @@
       <c r="AT635" t="inlineStr"/>
       <c r="AW635" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX635" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY635" t="inlineStr">
@@ -71444,7 +71453,7 @@
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>135385289</v>
+        <v>135385232</v>
       </c>
       <c r="B636" t="n">
         <v>78382</v>
@@ -71479,10 +71488,10 @@
         </is>
       </c>
       <c r="Q636" t="n">
-        <v>607788</v>
+        <v>607787</v>
       </c>
       <c r="R636" t="n">
-        <v>7310050</v>
+        <v>7310002</v>
       </c>
       <c r="S636" t="n">
         <v>5</v>
@@ -71514,7 +71523,7 @@
       </c>
       <c r="Z636" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA636" t="inlineStr">
@@ -71524,7 +71533,7 @@
       </c>
       <c r="AB636" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD636" t="b">
@@ -71555,7 +71564,7 @@
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>135385297</v>
+        <v>135385289</v>
       </c>
       <c r="B637" t="n">
         <v>78382</v>
@@ -71590,10 +71599,10 @@
         </is>
       </c>
       <c r="Q637" t="n">
-        <v>607872</v>
+        <v>607788</v>
       </c>
       <c r="R637" t="n">
-        <v>7309907</v>
+        <v>7310050</v>
       </c>
       <c r="S637" t="n">
         <v>5</v>
@@ -71625,7 +71634,7 @@
       </c>
       <c r="Z637" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA637" t="inlineStr">
@@ -71635,7 +71644,7 @@
       </c>
       <c r="AB637" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD637" t="b">
@@ -71666,10 +71675,10 @@
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>135385236</v>
+        <v>135385297</v>
       </c>
       <c r="B638" t="n">
-        <v>79396</v>
+        <v>78382</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -71677,21 +71686,21 @@
         </is>
       </c>
       <c r="E638" t="n">
-        <v>260591</v>
+        <v>228579</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I638" t="inlineStr"/>
@@ -71701,10 +71710,10 @@
         </is>
       </c>
       <c r="Q638" t="n">
-        <v>607717</v>
+        <v>607872</v>
       </c>
       <c r="R638" t="n">
-        <v>7309995</v>
+        <v>7309907</v>
       </c>
       <c r="S638" t="n">
         <v>5</v>
@@ -71736,7 +71745,7 @@
       </c>
       <c r="Z638" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA638" t="inlineStr">
@@ -71746,7 +71755,7 @@
       </c>
       <c r="AB638" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD638" t="b">
@@ -71777,7 +71786,7 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>135385311</v>
+        <v>135385236</v>
       </c>
       <c r="B639" t="n">
         <v>79396</v>
@@ -71812,10 +71821,10 @@
         </is>
       </c>
       <c r="Q639" t="n">
-        <v>607861</v>
+        <v>607717</v>
       </c>
       <c r="R639" t="n">
-        <v>7309816</v>
+        <v>7309995</v>
       </c>
       <c r="S639" t="n">
         <v>5</v>
@@ -71847,7 +71856,7 @@
       </c>
       <c r="Z639" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA639" t="inlineStr">
@@ -71857,7 +71866,7 @@
       </c>
       <c r="AB639" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD639" t="b">
@@ -71888,10 +71897,10 @@
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>80987080</v>
+        <v>135385311</v>
       </c>
       <c r="B640" t="n">
-        <v>91905</v>
+        <v>79396</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -71899,37 +71908,37 @@
         </is>
       </c>
       <c r="E640" t="n">
-        <v>1108</v>
+        <v>260591</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I640" t="inlineStr"/>
       <c r="P640" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q640" t="n">
-        <v>607814</v>
+        <v>607861</v>
       </c>
       <c r="R640" t="n">
-        <v>7310183</v>
+        <v>7309816</v>
       </c>
       <c r="S640" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T640" t="inlineStr">
         <is>
@@ -71953,12 +71962,22 @@
       </c>
       <c r="Y640" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z640" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA640" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB640" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD640" t="b">
@@ -71973,19 +71992,23 @@
       <c r="AT640" t="inlineStr"/>
       <c r="AW640" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX640" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY640" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY640" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>80987082</v>
+        <v>80987080</v>
       </c>
       <c r="B641" t="n">
         <v>91905</v>
@@ -72020,10 +72043,10 @@
         </is>
       </c>
       <c r="Q641" t="n">
-        <v>607707</v>
+        <v>607814</v>
       </c>
       <c r="R641" t="n">
-        <v>7310262</v>
+        <v>7310183</v>
       </c>
       <c r="S641" t="n">
         <v>10</v>
@@ -72082,7 +72105,7 @@
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>80987083</v>
+        <v>80987082</v>
       </c>
       <c r="B642" t="n">
         <v>91905</v>
@@ -72117,10 +72140,10 @@
         </is>
       </c>
       <c r="Q642" t="n">
-        <v>607709</v>
+        <v>607707</v>
       </c>
       <c r="R642" t="n">
-        <v>7310293</v>
+        <v>7310262</v>
       </c>
       <c r="S642" t="n">
         <v>10</v>
@@ -72179,10 +72202,10 @@
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>80987064</v>
+        <v>80987083</v>
       </c>
       <c r="B643" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -72190,21 +72213,21 @@
         </is>
       </c>
       <c r="E643" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I643" t="inlineStr"/>
@@ -72214,10 +72237,10 @@
         </is>
       </c>
       <c r="Q643" t="n">
-        <v>607818</v>
+        <v>607709</v>
       </c>
       <c r="R643" t="n">
-        <v>7310228</v>
+        <v>7310293</v>
       </c>
       <c r="S643" t="n">
         <v>10</v>
@@ -72276,10 +72299,10 @@
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>80987115</v>
+        <v>80987064</v>
       </c>
       <c r="B644" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -72287,21 +72310,21 @@
         </is>
       </c>
       <c r="E644" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I644" t="inlineStr"/>
@@ -72311,10 +72334,10 @@
         </is>
       </c>
       <c r="Q644" t="n">
-        <v>607759</v>
+        <v>607818</v>
       </c>
       <c r="R644" t="n">
-        <v>7310182</v>
+        <v>7310228</v>
       </c>
       <c r="S644" t="n">
         <v>10</v>
@@ -72373,7 +72396,7 @@
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>80987117</v>
+        <v>80987115</v>
       </c>
       <c r="B645" t="n">
         <v>83173</v>
@@ -72408,10 +72431,10 @@
         </is>
       </c>
       <c r="Q645" t="n">
-        <v>607751</v>
+        <v>607759</v>
       </c>
       <c r="R645" t="n">
-        <v>7310193</v>
+        <v>7310182</v>
       </c>
       <c r="S645" t="n">
         <v>10</v>
@@ -72470,32 +72493,32 @@
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>80987066</v>
+        <v>80987117</v>
       </c>
       <c r="B646" t="n">
-        <v>92632</v>
+        <v>83173</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E646" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I646" t="inlineStr"/>
@@ -72505,10 +72528,10 @@
         </is>
       </c>
       <c r="Q646" t="n">
-        <v>607822</v>
+        <v>607751</v>
       </c>
       <c r="R646" t="n">
-        <v>7310199</v>
+        <v>7310193</v>
       </c>
       <c r="S646" t="n">
         <v>10</v>
@@ -72567,48 +72590,48 @@
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>135351855</v>
+        <v>80987066</v>
       </c>
       <c r="B647" t="n">
-        <v>79373</v>
+        <v>92632</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E647" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I647" t="inlineStr"/>
       <c r="P647" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q647" t="n">
-        <v>607677</v>
+        <v>607822</v>
       </c>
       <c r="R647" t="n">
-        <v>7310726</v>
+        <v>7310199</v>
       </c>
       <c r="S647" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="T647" t="inlineStr">
         <is>
@@ -72632,22 +72655,12 @@
       </c>
       <c r="Y647" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z647" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA647" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB647" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD647" t="b">
@@ -72662,23 +72675,19 @@
       <c r="AT647" t="inlineStr"/>
       <c r="AW647" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX647" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY647" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY647" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>135382864</v>
+        <v>135351855</v>
       </c>
       <c r="B648" t="n">
         <v>79373</v>
@@ -72713,13 +72722,13 @@
         </is>
       </c>
       <c r="Q648" t="n">
-        <v>607670</v>
+        <v>607677</v>
       </c>
       <c r="R648" t="n">
-        <v>7310121</v>
+        <v>7310726</v>
       </c>
       <c r="S648" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="T648" t="inlineStr">
         <is>
@@ -72743,22 +72752,22 @@
       </c>
       <c r="Y648" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z648" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA648" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB648" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD648" t="b">
@@ -72773,12 +72782,12 @@
       <c r="AT648" t="inlineStr"/>
       <c r="AW648" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX648" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY648" t="inlineStr">
@@ -72789,7 +72798,7 @@
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>135385285</v>
+        <v>135382864</v>
       </c>
       <c r="B649" t="n">
         <v>79373</v>
@@ -72820,17 +72829,17 @@
       <c r="I649" t="inlineStr"/>
       <c r="P649" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q649" t="n">
-        <v>607756</v>
+        <v>607670</v>
       </c>
       <c r="R649" t="n">
-        <v>7310082</v>
+        <v>7310121</v>
       </c>
       <c r="S649" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T649" t="inlineStr">
         <is>
@@ -72859,7 +72868,7 @@
       </c>
       <c r="Z649" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA649" t="inlineStr">
@@ -72869,7 +72878,7 @@
       </c>
       <c r="AB649" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD649" t="b">
@@ -72884,12 +72893,12 @@
       <c r="AT649" t="inlineStr"/>
       <c r="AW649" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX649" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY649" t="inlineStr">
@@ -72900,48 +72909,48 @@
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>80987069</v>
+        <v>135385285</v>
       </c>
       <c r="B650" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E650" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I650" t="inlineStr"/>
       <c r="P650" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q650" t="n">
-        <v>607759</v>
+        <v>607756</v>
       </c>
       <c r="R650" t="n">
-        <v>7310308</v>
+        <v>7310082</v>
       </c>
       <c r="S650" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T650" t="inlineStr">
         <is>
@@ -72965,12 +72974,22 @@
       </c>
       <c r="Y650" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z650" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA650" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB650" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD650" t="b">
@@ -72985,69 +73004,64 @@
       <c r="AT650" t="inlineStr"/>
       <c r="AW650" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX650" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY650" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY650" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>135382865</v>
+        <v>80987069</v>
       </c>
       <c r="B651" t="n">
-        <v>5181</v>
+        <v>57953</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E651" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I651" t="inlineStr"/>
-      <c r="J651" t="inlineStr"/>
-      <c r="K651" t="inlineStr"/>
-      <c r="L651" t="inlineStr"/>
-      <c r="M651" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N651" t="inlineStr"/>
       <c r="P651" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q651" t="n">
-        <v>607674</v>
+        <v>607759</v>
       </c>
       <c r="R651" t="n">
-        <v>7310117</v>
+        <v>7310308</v>
       </c>
       <c r="S651" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T651" t="inlineStr">
         <is>
@@ -73071,22 +73085,12 @@
       </c>
       <c r="Y651" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z651" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA651" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB651" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD651" t="b">
@@ -73095,76 +73099,72 @@
       <c r="AE651" t="b">
         <v>0</v>
       </c>
-      <c r="AF651" t="inlineStr"/>
       <c r="AG651" t="b">
         <v>0</v>
       </c>
       <c r="AT651" t="inlineStr"/>
       <c r="AW651" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX651" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
-        </is>
-      </c>
-      <c r="AY651" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>135385195</v>
+        <v>135382865</v>
       </c>
       <c r="B652" t="n">
-        <v>57975</v>
+        <v>5181</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E652" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I652" t="inlineStr"/>
+      <c r="J652" t="inlineStr"/>
       <c r="K652" t="inlineStr"/>
       <c r="L652" t="inlineStr"/>
       <c r="M652" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N652" t="inlineStr"/>
       <c r="P652" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q652" t="n">
-        <v>608400</v>
+        <v>607674</v>
       </c>
       <c r="R652" t="n">
-        <v>7309309</v>
+        <v>7310117</v>
       </c>
       <c r="S652" t="n">
         <v>5</v>
@@ -73196,7 +73196,7 @@
       </c>
       <c r="Z652" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA652" t="inlineStr">
@@ -73206,7 +73206,7 @@
       </c>
       <c r="AB652" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD652" t="b">
@@ -73215,18 +73215,19 @@
       <c r="AE652" t="b">
         <v>0</v>
       </c>
+      <c r="AF652" t="inlineStr"/>
       <c r="AG652" t="b">
         <v>0</v>
       </c>
       <c r="AT652" t="inlineStr"/>
       <c r="AW652" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX652" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY652" t="inlineStr">
@@ -73237,10 +73238,10 @@
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>80987072</v>
+        <v>135385195</v>
       </c>
       <c r="B653" t="n">
-        <v>92208</v>
+        <v>57975</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -73248,37 +73249,45 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I653" t="inlineStr"/>
+      <c r="K653" t="inlineStr"/>
+      <c r="L653" t="inlineStr"/>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N653" t="inlineStr"/>
       <c r="P653" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q653" t="n">
-        <v>608406</v>
+        <v>608400</v>
       </c>
       <c r="R653" t="n">
-        <v>7309441</v>
+        <v>7309309</v>
       </c>
       <c r="S653" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T653" t="inlineStr">
         <is>
@@ -73302,12 +73311,22 @@
       </c>
       <c r="Y653" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z653" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA653" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB653" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD653" t="b">
@@ -73322,22 +73341,26 @@
       <c r="AT653" t="inlineStr"/>
       <c r="AW653" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX653" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY653" t="inlineStr"/>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY653" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>80987076</v>
+        <v>80987072</v>
       </c>
       <c r="B654" t="n">
-        <v>79406</v>
+        <v>92208</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -73345,21 +73368,21 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I654" t="inlineStr"/>
@@ -73369,10 +73392,10 @@
         </is>
       </c>
       <c r="Q654" t="n">
-        <v>608479</v>
+        <v>608406</v>
       </c>
       <c r="R654" t="n">
-        <v>7309341</v>
+        <v>7309441</v>
       </c>
       <c r="S654" t="n">
         <v>10</v>
@@ -73431,7 +73454,7 @@
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>80987077</v>
+        <v>80987076</v>
       </c>
       <c r="B655" t="n">
         <v>79406</v>
@@ -73466,10 +73489,10 @@
         </is>
       </c>
       <c r="Q655" t="n">
-        <v>608374</v>
+        <v>608479</v>
       </c>
       <c r="R655" t="n">
-        <v>7309488</v>
+        <v>7309341</v>
       </c>
       <c r="S655" t="n">
         <v>10</v>
@@ -73528,10 +73551,10 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>80987081</v>
+        <v>80987077</v>
       </c>
       <c r="B656" t="n">
-        <v>91905</v>
+        <v>79406</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -73539,21 +73562,21 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I656" t="inlineStr"/>
@@ -73563,10 +73586,10 @@
         </is>
       </c>
       <c r="Q656" t="n">
-        <v>608446</v>
+        <v>608374</v>
       </c>
       <c r="R656" t="n">
-        <v>7309372</v>
+        <v>7309488</v>
       </c>
       <c r="S656" t="n">
         <v>10</v>
@@ -73625,10 +73648,10 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>80987060</v>
+        <v>80987081</v>
       </c>
       <c r="B657" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -73636,21 +73659,21 @@
         </is>
       </c>
       <c r="E657" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I657" t="inlineStr"/>
@@ -73660,7 +73683,7 @@
         </is>
       </c>
       <c r="Q657" t="n">
-        <v>608459</v>
+        <v>608446</v>
       </c>
       <c r="R657" t="n">
         <v>7309372</v>
@@ -73722,7 +73745,7 @@
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>80987061</v>
+        <v>80987060</v>
       </c>
       <c r="B658" t="n">
         <v>91909</v>
@@ -73757,10 +73780,10 @@
         </is>
       </c>
       <c r="Q658" t="n">
-        <v>608386</v>
+        <v>608459</v>
       </c>
       <c r="R658" t="n">
-        <v>7309399</v>
+        <v>7309372</v>
       </c>
       <c r="S658" t="n">
         <v>10</v>
@@ -73819,7 +73842,7 @@
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>80987062</v>
+        <v>80987061</v>
       </c>
       <c r="B659" t="n">
         <v>91909</v>
@@ -73854,10 +73877,10 @@
         </is>
       </c>
       <c r="Q659" t="n">
-        <v>608403</v>
+        <v>608386</v>
       </c>
       <c r="R659" t="n">
-        <v>7309432</v>
+        <v>7309399</v>
       </c>
       <c r="S659" t="n">
         <v>10</v>
@@ -73916,7 +73939,7 @@
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>80987063</v>
+        <v>80987062</v>
       </c>
       <c r="B660" t="n">
         <v>91909</v>
@@ -73951,10 +73974,10 @@
         </is>
       </c>
       <c r="Q660" t="n">
-        <v>608422</v>
+        <v>608403</v>
       </c>
       <c r="R660" t="n">
-        <v>7309394</v>
+        <v>7309432</v>
       </c>
       <c r="S660" t="n">
         <v>10</v>
@@ -74013,10 +74036,10 @@
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>80987114</v>
+        <v>80987063</v>
       </c>
       <c r="B661" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -74024,21 +74047,21 @@
         </is>
       </c>
       <c r="E661" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I661" t="inlineStr"/>
@@ -74048,10 +74071,10 @@
         </is>
       </c>
       <c r="Q661" t="n">
-        <v>608390</v>
+        <v>608422</v>
       </c>
       <c r="R661" t="n">
-        <v>7309533</v>
+        <v>7309394</v>
       </c>
       <c r="S661" t="n">
         <v>10</v>
@@ -74110,32 +74133,32 @@
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>80987067</v>
+        <v>80987114</v>
       </c>
       <c r="B662" t="n">
-        <v>92632</v>
+        <v>83173</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E662" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I662" t="inlineStr"/>
@@ -74145,10 +74168,10 @@
         </is>
       </c>
       <c r="Q662" t="n">
-        <v>608399</v>
+        <v>608390</v>
       </c>
       <c r="R662" t="n">
-        <v>7309450</v>
+        <v>7309533</v>
       </c>
       <c r="S662" t="n">
         <v>10</v>
@@ -74204,6 +74227,103 @@
         </is>
       </c>
       <c r="AY662" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" t="n">
+        <v>80987067</v>
+      </c>
+      <c r="B663" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E663" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr"/>
+      <c r="P663" t="inlineStr">
+        <is>
+          <t>Veddeklinten, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q663" t="n">
+        <v>608399</v>
+      </c>
+      <c r="R663" t="n">
+        <v>7309450</v>
+      </c>
+      <c r="S663" t="n">
+        <v>10</v>
+      </c>
+      <c r="T663" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U663" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V663" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W663" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y663" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AA663" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AD663" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE663" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG663" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT663" t="inlineStr"/>
+      <c r="AW663" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX663" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY663" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -12721,7 +12721,7 @@
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
@@ -12943,7 +12943,7 @@
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
@@ -19388,7 +19388,7 @@
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
@@ -23820,7 +23820,7 @@
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
@@ -44006,7 +44006,7 @@
       </c>
       <c r="AX389" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY389" t="inlineStr">
@@ -44233,7 +44233,7 @@
       </c>
       <c r="AX391" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY391" t="inlineStr">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -66843,6 +66843,9 @@
         </is>
       </c>
       <c r="I593" t="inlineStr"/>
+      <c r="J593" t="inlineStr"/>
+      <c r="K593" t="inlineStr"/>
+      <c r="N593" t="inlineStr"/>
       <c r="P593" t="inlineStr">
         <is>
           <t>Laisdalen päronberget, Pi lm</t>
@@ -66899,7 +66902,7 @@
       </c>
       <c r="AC593" t="inlineStr">
         <is>
-          <t>dna sekvenseras</t>
+          <t>dna sekvenseras Den smakade något syrligt med en lätt hetta efter några sekunder som snabbt avtog. Platsen var en naturskog med framförallt gran, vid ett uttorkat källflöde med högörtskarkatär. Fältskikt med gräs, fukt &amp;  friskmossor, pyrola, fräken, stormhatt och tibast.</t>
         </is>
       </c>
       <c r="AD593" t="b">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -8211,11 +8211,14 @@
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
@@ -8292,7 +8295,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -74096,7 +74096,7 @@
         <v>608014</v>
       </c>
       <c r="R657" t="n">
-        <v>7309639</v>
+        <v>7309638</v>
       </c>
       <c r="S657" t="n">
         <v>3</v>
@@ -75552,7 +75552,7 @@
         <v>608014</v>
       </c>
       <c r="R670" t="n">
-        <v>7309639</v>
+        <v>7309638</v>
       </c>
       <c r="S670" t="n">
         <v>3</v>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY723"/>
+  <dimension ref="A1:AY724"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77674,48 +77674,48 @@
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>135378173</v>
+        <v>135523597</v>
       </c>
       <c r="B689" t="n">
-        <v>78382</v>
+        <v>101293</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E689" t="n">
-        <v>228579</v>
+        <v>224885</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I689" t="inlineStr"/>
       <c r="P689" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q689" t="n">
-        <v>607794</v>
+        <v>608073</v>
       </c>
       <c r="R689" t="n">
-        <v>7309999</v>
+        <v>7309660</v>
       </c>
       <c r="S689" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T689" t="inlineStr">
         <is>
@@ -77744,7 +77744,7 @@
       </c>
       <c r="Z689" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA689" t="inlineStr">
@@ -77754,7 +77754,7 @@
       </c>
       <c r="AB689" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD689" t="b">
@@ -77769,23 +77769,19 @@
       <c r="AT689" t="inlineStr"/>
       <c r="AW689" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX689" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY689" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY689" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>135378175</v>
+        <v>135378173</v>
       </c>
       <c r="B690" t="n">
         <v>78382</v>
@@ -77820,10 +77816,10 @@
         </is>
       </c>
       <c r="Q690" t="n">
-        <v>607781</v>
+        <v>607794</v>
       </c>
       <c r="R690" t="n">
-        <v>7310006</v>
+        <v>7309999</v>
       </c>
       <c r="S690" t="n">
         <v>4</v>
@@ -77855,7 +77851,7 @@
       </c>
       <c r="Z690" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA690" t="inlineStr">
@@ -77865,7 +77861,7 @@
       </c>
       <c r="AB690" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD690" t="b">
@@ -77896,7 +77892,7 @@
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>135378179</v>
+        <v>135378175</v>
       </c>
       <c r="B691" t="n">
         <v>78382</v>
@@ -77931,10 +77927,10 @@
         </is>
       </c>
       <c r="Q691" t="n">
-        <v>607702</v>
+        <v>607781</v>
       </c>
       <c r="R691" t="n">
-        <v>7309979</v>
+        <v>7310006</v>
       </c>
       <c r="S691" t="n">
         <v>4</v>
@@ -77966,7 +77962,7 @@
       </c>
       <c r="Z691" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA691" t="inlineStr">
@@ -77976,7 +77972,7 @@
       </c>
       <c r="AB691" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD691" t="b">
@@ -78007,7 +78003,7 @@
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>135378181</v>
+        <v>135378179</v>
       </c>
       <c r="B692" t="n">
         <v>78382</v>
@@ -78042,10 +78038,10 @@
         </is>
       </c>
       <c r="Q692" t="n">
-        <v>607671</v>
+        <v>607702</v>
       </c>
       <c r="R692" t="n">
-        <v>7309990</v>
+        <v>7309979</v>
       </c>
       <c r="S692" t="n">
         <v>4</v>
@@ -78077,7 +78073,7 @@
       </c>
       <c r="Z692" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA692" t="inlineStr">
@@ -78087,7 +78083,7 @@
       </c>
       <c r="AB692" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD692" t="b">
@@ -78118,7 +78114,7 @@
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>135385232</v>
+        <v>135378181</v>
       </c>
       <c r="B693" t="n">
         <v>78382</v>
@@ -78149,17 +78145,17 @@
       <c r="I693" t="inlineStr"/>
       <c r="P693" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q693" t="n">
-        <v>607787</v>
+        <v>607671</v>
       </c>
       <c r="R693" t="n">
-        <v>7310002</v>
+        <v>7309990</v>
       </c>
       <c r="S693" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T693" t="inlineStr">
         <is>
@@ -78188,7 +78184,7 @@
       </c>
       <c r="Z693" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA693" t="inlineStr">
@@ -78198,7 +78194,7 @@
       </c>
       <c r="AB693" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD693" t="b">
@@ -78213,12 +78209,12 @@
       <c r="AT693" t="inlineStr"/>
       <c r="AW693" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX693" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY693" t="inlineStr">
@@ -78229,7 +78225,7 @@
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>135385289</v>
+        <v>135385232</v>
       </c>
       <c r="B694" t="n">
         <v>78382</v>
@@ -78264,10 +78260,10 @@
         </is>
       </c>
       <c r="Q694" t="n">
-        <v>607788</v>
+        <v>607787</v>
       </c>
       <c r="R694" t="n">
-        <v>7310050</v>
+        <v>7310002</v>
       </c>
       <c r="S694" t="n">
         <v>5</v>
@@ -78299,7 +78295,7 @@
       </c>
       <c r="Z694" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA694" t="inlineStr">
@@ -78309,7 +78305,7 @@
       </c>
       <c r="AB694" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD694" t="b">
@@ -78340,7 +78336,7 @@
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>135385297</v>
+        <v>135385289</v>
       </c>
       <c r="B695" t="n">
         <v>78382</v>
@@ -78375,10 +78371,10 @@
         </is>
       </c>
       <c r="Q695" t="n">
-        <v>607872</v>
+        <v>607788</v>
       </c>
       <c r="R695" t="n">
-        <v>7309907</v>
+        <v>7310050</v>
       </c>
       <c r="S695" t="n">
         <v>5</v>
@@ -78410,7 +78406,7 @@
       </c>
       <c r="Z695" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA695" t="inlineStr">
@@ -78420,7 +78416,7 @@
       </c>
       <c r="AB695" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD695" t="b">
@@ -78451,7 +78447,7 @@
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>135422134</v>
+        <v>135385297</v>
       </c>
       <c r="B696" t="n">
         <v>78382</v>
@@ -78482,17 +78478,17 @@
       <c r="I696" t="inlineStr"/>
       <c r="P696" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q696" t="n">
-        <v>608091</v>
+        <v>607872</v>
       </c>
       <c r="R696" t="n">
-        <v>7309583</v>
+        <v>7309907</v>
       </c>
       <c r="S696" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T696" t="inlineStr">
         <is>
@@ -78521,7 +78517,7 @@
       </c>
       <c r="Z696" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA696" t="inlineStr">
@@ -78531,7 +78527,7 @@
       </c>
       <c r="AB696" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD696" t="b">
@@ -78542,31 +78538,16 @@
       </c>
       <c r="AG696" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ696" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK696" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO696" t="inlineStr">
-        <is>
-          <t>På barken av äldre levande gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT696" t="inlineStr"/>
       <c r="AW696" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX696" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY696" t="inlineStr">
@@ -78577,32 +78558,32 @@
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>135422148</v>
+        <v>135422134</v>
       </c>
       <c r="B697" t="n">
-        <v>80444</v>
+        <v>78382</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E697" t="n">
-        <v>229748</v>
+        <v>228579</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I697" t="inlineStr"/>
@@ -78612,13 +78593,13 @@
         </is>
       </c>
       <c r="Q697" t="n">
-        <v>607928</v>
+        <v>608091</v>
       </c>
       <c r="R697" t="n">
-        <v>7309603</v>
+        <v>7309583</v>
       </c>
       <c r="S697" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T697" t="inlineStr">
         <is>
@@ -78647,7 +78628,7 @@
       </c>
       <c r="Z697" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA697" t="inlineStr">
@@ -78657,7 +78638,7 @@
       </c>
       <c r="AB697" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD697" t="b">
@@ -78669,24 +78650,19 @@
       <c r="AG697" t="b">
         <v>0</v>
       </c>
-      <c r="AI697" t="inlineStr">
-        <is>
-          <t>Uttorkad bäckfåra i örtrik granskog</t>
-        </is>
-      </c>
       <c r="AJ697" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK697" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO697" t="inlineStr">
         <is>
-          <t>Björklåga i uttorkad bäckfåra # Betula</t>
+          <t>På barken av äldre levande gran # Picea abies</t>
         </is>
       </c>
       <c r="AT697" t="inlineStr"/>
@@ -78708,32 +78684,32 @@
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>135422151</v>
+        <v>135422148</v>
       </c>
       <c r="B698" t="n">
-        <v>87161</v>
+        <v>80444</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E698" t="n">
-        <v>249278</v>
+        <v>229748</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I698" t="inlineStr"/>
@@ -78743,13 +78719,13 @@
         </is>
       </c>
       <c r="Q698" t="n">
-        <v>607924</v>
+        <v>607928</v>
       </c>
       <c r="R698" t="n">
-        <v>7309606</v>
+        <v>7309603</v>
       </c>
       <c r="S698" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T698" t="inlineStr">
         <is>
@@ -78778,7 +78754,7 @@
       </c>
       <c r="Z698" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA698" t="inlineStr">
@@ -78788,7 +78764,7 @@
       </c>
       <c r="AB698" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD698" t="b">
@@ -78802,7 +78778,22 @@
       </c>
       <c r="AI698" t="inlineStr">
         <is>
-          <t>Örtrik granskog</t>
+          <t>Uttorkad bäckfåra i örtrik granskog</t>
+        </is>
+      </c>
+      <c r="AJ698" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK698" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO698" t="inlineStr">
+        <is>
+          <t>Björklåga i uttorkad bäckfåra # Betula</t>
         </is>
       </c>
       <c r="AT698" t="inlineStr"/>
@@ -78824,10 +78815,10 @@
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>135385236</v>
+        <v>135422151</v>
       </c>
       <c r="B699" t="n">
-        <v>79396</v>
+        <v>87161</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -78835,34 +78826,34 @@
         </is>
       </c>
       <c r="E699" t="n">
-        <v>260591</v>
+        <v>249278</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I699" t="inlineStr"/>
       <c r="P699" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q699" t="n">
-        <v>607717</v>
+        <v>607924</v>
       </c>
       <c r="R699" t="n">
-        <v>7309995</v>
+        <v>7309606</v>
       </c>
       <c r="S699" t="n">
         <v>5</v>
@@ -78894,7 +78885,7 @@
       </c>
       <c r="Z699" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA699" t="inlineStr">
@@ -78904,7 +78895,7 @@
       </c>
       <c r="AB699" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD699" t="b">
@@ -78915,16 +78906,21 @@
       </c>
       <c r="AG699" t="b">
         <v>0</v>
+      </c>
+      <c r="AI699" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT699" t="inlineStr"/>
       <c r="AW699" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX699" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY699" t="inlineStr">
@@ -78935,7 +78931,7 @@
     </row>
     <row r="700">
       <c r="A700" t="n">
-        <v>135385311</v>
+        <v>135385236</v>
       </c>
       <c r="B700" t="n">
         <v>79396</v>
@@ -78970,10 +78966,10 @@
         </is>
       </c>
       <c r="Q700" t="n">
-        <v>607861</v>
+        <v>607717</v>
       </c>
       <c r="R700" t="n">
-        <v>7309816</v>
+        <v>7309995</v>
       </c>
       <c r="S700" t="n">
         <v>5</v>
@@ -79005,7 +79001,7 @@
       </c>
       <c r="Z700" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA700" t="inlineStr">
@@ -79015,7 +79011,7 @@
       </c>
       <c r="AB700" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD700" t="b">
@@ -79046,10 +79042,10 @@
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>80987080</v>
+        <v>135385311</v>
       </c>
       <c r="B701" t="n">
-        <v>91905</v>
+        <v>79396</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -79057,37 +79053,37 @@
         </is>
       </c>
       <c r="E701" t="n">
-        <v>1108</v>
+        <v>260591</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I701" t="inlineStr"/>
       <c r="P701" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q701" t="n">
-        <v>607814</v>
+        <v>607861</v>
       </c>
       <c r="R701" t="n">
-        <v>7310183</v>
+        <v>7309816</v>
       </c>
       <c r="S701" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T701" t="inlineStr">
         <is>
@@ -79111,12 +79107,22 @@
       </c>
       <c r="Y701" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z701" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA701" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB701" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD701" t="b">
@@ -79131,19 +79137,23 @@
       <c r="AT701" t="inlineStr"/>
       <c r="AW701" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX701" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY701" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY701" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>80987082</v>
+        <v>80987080</v>
       </c>
       <c r="B702" t="n">
         <v>91905</v>
@@ -79178,10 +79188,10 @@
         </is>
       </c>
       <c r="Q702" t="n">
-        <v>607707</v>
+        <v>607814</v>
       </c>
       <c r="R702" t="n">
-        <v>7310262</v>
+        <v>7310183</v>
       </c>
       <c r="S702" t="n">
         <v>10</v>
@@ -79240,7 +79250,7 @@
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>80987083</v>
+        <v>80987082</v>
       </c>
       <c r="B703" t="n">
         <v>91905</v>
@@ -79275,10 +79285,10 @@
         </is>
       </c>
       <c r="Q703" t="n">
-        <v>607709</v>
+        <v>607707</v>
       </c>
       <c r="R703" t="n">
-        <v>7310293</v>
+        <v>7310262</v>
       </c>
       <c r="S703" t="n">
         <v>10</v>
@@ -79337,10 +79347,10 @@
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>80987064</v>
+        <v>80987083</v>
       </c>
       <c r="B704" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -79348,21 +79358,21 @@
         </is>
       </c>
       <c r="E704" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I704" t="inlineStr"/>
@@ -79372,10 +79382,10 @@
         </is>
       </c>
       <c r="Q704" t="n">
-        <v>607818</v>
+        <v>607709</v>
       </c>
       <c r="R704" t="n">
-        <v>7310228</v>
+        <v>7310293</v>
       </c>
       <c r="S704" t="n">
         <v>10</v>
@@ -79434,10 +79444,10 @@
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>80987115</v>
+        <v>80987064</v>
       </c>
       <c r="B705" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -79445,21 +79455,21 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I705" t="inlineStr"/>
@@ -79469,10 +79479,10 @@
         </is>
       </c>
       <c r="Q705" t="n">
-        <v>607759</v>
+        <v>607818</v>
       </c>
       <c r="R705" t="n">
-        <v>7310182</v>
+        <v>7310228</v>
       </c>
       <c r="S705" t="n">
         <v>10</v>
@@ -79531,7 +79541,7 @@
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>80987117</v>
+        <v>80987115</v>
       </c>
       <c r="B706" t="n">
         <v>83173</v>
@@ -79566,10 +79576,10 @@
         </is>
       </c>
       <c r="Q706" t="n">
-        <v>607751</v>
+        <v>607759</v>
       </c>
       <c r="R706" t="n">
-        <v>7310193</v>
+        <v>7310182</v>
       </c>
       <c r="S706" t="n">
         <v>10</v>
@@ -79628,32 +79638,32 @@
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>80987066</v>
+        <v>80987117</v>
       </c>
       <c r="B707" t="n">
-        <v>92632</v>
+        <v>83173</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E707" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I707" t="inlineStr"/>
@@ -79663,10 +79673,10 @@
         </is>
       </c>
       <c r="Q707" t="n">
-        <v>607822</v>
+        <v>607751</v>
       </c>
       <c r="R707" t="n">
-        <v>7310199</v>
+        <v>7310193</v>
       </c>
       <c r="S707" t="n">
         <v>10</v>
@@ -79725,48 +79735,48 @@
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>135351855</v>
+        <v>80987066</v>
       </c>
       <c r="B708" t="n">
-        <v>79373</v>
+        <v>92632</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E708" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I708" t="inlineStr"/>
       <c r="P708" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q708" t="n">
-        <v>607677</v>
+        <v>607822</v>
       </c>
       <c r="R708" t="n">
-        <v>7310726</v>
+        <v>7310199</v>
       </c>
       <c r="S708" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="T708" t="inlineStr">
         <is>
@@ -79790,22 +79800,12 @@
       </c>
       <c r="Y708" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z708" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA708" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB708" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD708" t="b">
@@ -79820,23 +79820,19 @@
       <c r="AT708" t="inlineStr"/>
       <c r="AW708" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX708" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY708" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>135382864</v>
+        <v>135351855</v>
       </c>
       <c r="B709" t="n">
         <v>79373</v>
@@ -79871,13 +79867,13 @@
         </is>
       </c>
       <c r="Q709" t="n">
-        <v>607670</v>
+        <v>607677</v>
       </c>
       <c r="R709" t="n">
-        <v>7310121</v>
+        <v>7310726</v>
       </c>
       <c r="S709" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="T709" t="inlineStr">
         <is>
@@ -79901,22 +79897,22 @@
       </c>
       <c r="Y709" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z709" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA709" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB709" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD709" t="b">
@@ -79931,12 +79927,12 @@
       <c r="AT709" t="inlineStr"/>
       <c r="AW709" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX709" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY709" t="inlineStr">
@@ -79947,7 +79943,7 @@
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>135385285</v>
+        <v>135382864</v>
       </c>
       <c r="B710" t="n">
         <v>79373</v>
@@ -79978,17 +79974,17 @@
       <c r="I710" t="inlineStr"/>
       <c r="P710" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q710" t="n">
-        <v>607756</v>
+        <v>607670</v>
       </c>
       <c r="R710" t="n">
-        <v>7310082</v>
+        <v>7310121</v>
       </c>
       <c r="S710" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T710" t="inlineStr">
         <is>
@@ -80017,7 +80013,7 @@
       </c>
       <c r="Z710" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA710" t="inlineStr">
@@ -80027,7 +80023,7 @@
       </c>
       <c r="AB710" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD710" t="b">
@@ -80042,12 +80038,12 @@
       <c r="AT710" t="inlineStr"/>
       <c r="AW710" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX710" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY710" t="inlineStr">
@@ -80058,48 +80054,48 @@
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>80987069</v>
+        <v>135385285</v>
       </c>
       <c r="B711" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E711" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I711" t="inlineStr"/>
       <c r="P711" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q711" t="n">
-        <v>607759</v>
+        <v>607756</v>
       </c>
       <c r="R711" t="n">
-        <v>7310308</v>
+        <v>7310082</v>
       </c>
       <c r="S711" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T711" t="inlineStr">
         <is>
@@ -80123,12 +80119,22 @@
       </c>
       <c r="Y711" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z711" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA711" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB711" t="inlineStr">
+        <is>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD711" t="b">
@@ -80143,69 +80149,64 @@
       <c r="AT711" t="inlineStr"/>
       <c r="AW711" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX711" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY711" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY711" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>135382865</v>
+        <v>80987069</v>
       </c>
       <c r="B712" t="n">
-        <v>5181</v>
+        <v>57953</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E712" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I712" t="inlineStr"/>
-      <c r="J712" t="inlineStr"/>
-      <c r="K712" t="inlineStr"/>
-      <c r="L712" t="inlineStr"/>
-      <c r="M712" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N712" t="inlineStr"/>
       <c r="P712" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q712" t="n">
-        <v>607674</v>
+        <v>607759</v>
       </c>
       <c r="R712" t="n">
-        <v>7310117</v>
+        <v>7310308</v>
       </c>
       <c r="S712" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T712" t="inlineStr">
         <is>
@@ -80229,22 +80230,12 @@
       </c>
       <c r="Y712" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z712" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA712" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB712" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD712" t="b">
@@ -80253,76 +80244,72 @@
       <c r="AE712" t="b">
         <v>0</v>
       </c>
-      <c r="AF712" t="inlineStr"/>
       <c r="AG712" t="b">
         <v>0</v>
       </c>
       <c r="AT712" t="inlineStr"/>
       <c r="AW712" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX712" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
-        </is>
-      </c>
-      <c r="AY712" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>135385195</v>
+        <v>135382865</v>
       </c>
       <c r="B713" t="n">
-        <v>57975</v>
+        <v>5181</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E713" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I713" t="inlineStr"/>
+      <c r="J713" t="inlineStr"/>
       <c r="K713" t="inlineStr"/>
       <c r="L713" t="inlineStr"/>
       <c r="M713" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N713" t="inlineStr"/>
       <c r="P713" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q713" t="n">
-        <v>608400</v>
+        <v>607674</v>
       </c>
       <c r="R713" t="n">
-        <v>7309309</v>
+        <v>7310117</v>
       </c>
       <c r="S713" t="n">
         <v>5</v>
@@ -80354,7 +80341,7 @@
       </c>
       <c r="Z713" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA713" t="inlineStr">
@@ -80364,7 +80351,7 @@
       </c>
       <c r="AB713" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD713" t="b">
@@ -80373,18 +80360,19 @@
       <c r="AE713" t="b">
         <v>0</v>
       </c>
+      <c r="AF713" t="inlineStr"/>
       <c r="AG713" t="b">
         <v>0</v>
       </c>
       <c r="AT713" t="inlineStr"/>
       <c r="AW713" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX713" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY713" t="inlineStr">
@@ -80395,10 +80383,10 @@
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>80987072</v>
+        <v>135385195</v>
       </c>
       <c r="B714" t="n">
-        <v>92208</v>
+        <v>57975</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -80406,37 +80394,45 @@
         </is>
       </c>
       <c r="E714" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I714" t="inlineStr"/>
+      <c r="K714" t="inlineStr"/>
+      <c r="L714" t="inlineStr"/>
+      <c r="M714" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N714" t="inlineStr"/>
       <c r="P714" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q714" t="n">
-        <v>608406</v>
+        <v>608400</v>
       </c>
       <c r="R714" t="n">
-        <v>7309441</v>
+        <v>7309309</v>
       </c>
       <c r="S714" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T714" t="inlineStr">
         <is>
@@ -80460,12 +80456,22 @@
       </c>
       <c r="Y714" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z714" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA714" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB714" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD714" t="b">
@@ -80480,22 +80486,26 @@
       <c r="AT714" t="inlineStr"/>
       <c r="AW714" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX714" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY714" t="inlineStr"/>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY714" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>80987076</v>
+        <v>80987072</v>
       </c>
       <c r="B715" t="n">
-        <v>79406</v>
+        <v>92208</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -80503,21 +80513,21 @@
         </is>
       </c>
       <c r="E715" t="n">
-        <v>864</v>
+        <v>658</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I715" t="inlineStr"/>
@@ -80527,10 +80537,10 @@
         </is>
       </c>
       <c r="Q715" t="n">
-        <v>608479</v>
+        <v>608406</v>
       </c>
       <c r="R715" t="n">
-        <v>7309341</v>
+        <v>7309441</v>
       </c>
       <c r="S715" t="n">
         <v>10</v>
@@ -80589,7 +80599,7 @@
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>80987077</v>
+        <v>80987076</v>
       </c>
       <c r="B716" t="n">
         <v>79406</v>
@@ -80624,10 +80634,10 @@
         </is>
       </c>
       <c r="Q716" t="n">
-        <v>608374</v>
+        <v>608479</v>
       </c>
       <c r="R716" t="n">
-        <v>7309488</v>
+        <v>7309341</v>
       </c>
       <c r="S716" t="n">
         <v>10</v>
@@ -80686,10 +80696,10 @@
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>80987081</v>
+        <v>80987077</v>
       </c>
       <c r="B717" t="n">
-        <v>91905</v>
+        <v>79406</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -80697,21 +80707,21 @@
         </is>
       </c>
       <c r="E717" t="n">
-        <v>1108</v>
+        <v>864</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I717" t="inlineStr"/>
@@ -80721,10 +80731,10 @@
         </is>
       </c>
       <c r="Q717" t="n">
-        <v>608446</v>
+        <v>608374</v>
       </c>
       <c r="R717" t="n">
-        <v>7309372</v>
+        <v>7309488</v>
       </c>
       <c r="S717" t="n">
         <v>10</v>
@@ -80783,10 +80793,10 @@
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>80987060</v>
+        <v>80987081</v>
       </c>
       <c r="B718" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -80794,21 +80804,21 @@
         </is>
       </c>
       <c r="E718" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I718" t="inlineStr"/>
@@ -80818,7 +80828,7 @@
         </is>
       </c>
       <c r="Q718" t="n">
-        <v>608459</v>
+        <v>608446</v>
       </c>
       <c r="R718" t="n">
         <v>7309372</v>
@@ -80880,7 +80890,7 @@
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>80987061</v>
+        <v>80987060</v>
       </c>
       <c r="B719" t="n">
         <v>91909</v>
@@ -80915,10 +80925,10 @@
         </is>
       </c>
       <c r="Q719" t="n">
-        <v>608386</v>
+        <v>608459</v>
       </c>
       <c r="R719" t="n">
-        <v>7309399</v>
+        <v>7309372</v>
       </c>
       <c r="S719" t="n">
         <v>10</v>
@@ -80977,7 +80987,7 @@
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>80987062</v>
+        <v>80987061</v>
       </c>
       <c r="B720" t="n">
         <v>91909</v>
@@ -81012,10 +81022,10 @@
         </is>
       </c>
       <c r="Q720" t="n">
-        <v>608403</v>
+        <v>608386</v>
       </c>
       <c r="R720" t="n">
-        <v>7309432</v>
+        <v>7309399</v>
       </c>
       <c r="S720" t="n">
         <v>10</v>
@@ -81074,7 +81084,7 @@
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>80987063</v>
+        <v>80987062</v>
       </c>
       <c r="B721" t="n">
         <v>91909</v>
@@ -81109,10 +81119,10 @@
         </is>
       </c>
       <c r="Q721" t="n">
-        <v>608422</v>
+        <v>608403</v>
       </c>
       <c r="R721" t="n">
-        <v>7309394</v>
+        <v>7309432</v>
       </c>
       <c r="S721" t="n">
         <v>10</v>
@@ -81171,10 +81181,10 @@
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>80987114</v>
+        <v>80987063</v>
       </c>
       <c r="B722" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -81182,21 +81192,21 @@
         </is>
       </c>
       <c r="E722" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I722" t="inlineStr"/>
@@ -81206,10 +81216,10 @@
         </is>
       </c>
       <c r="Q722" t="n">
-        <v>608390</v>
+        <v>608422</v>
       </c>
       <c r="R722" t="n">
-        <v>7309533</v>
+        <v>7309394</v>
       </c>
       <c r="S722" t="n">
         <v>10</v>
@@ -81268,32 +81278,32 @@
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>80987067</v>
+        <v>80987114</v>
       </c>
       <c r="B723" t="n">
-        <v>92632</v>
+        <v>83173</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E723" t="n">
-        <v>3298</v>
+        <v>1312</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I723" t="inlineStr"/>
@@ -81303,10 +81313,10 @@
         </is>
       </c>
       <c r="Q723" t="n">
-        <v>608399</v>
+        <v>608390</v>
       </c>
       <c r="R723" t="n">
-        <v>7309450</v>
+        <v>7309533</v>
       </c>
       <c r="S723" t="n">
         <v>10</v>
@@ -81362,6 +81372,103 @@
         </is>
       </c>
       <c r="AY723" t="inlineStr"/>
+    </row>
+    <row r="724">
+      <c r="A724" t="n">
+        <v>80987067</v>
+      </c>
+      <c r="B724" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E724" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr"/>
+      <c r="P724" t="inlineStr">
+        <is>
+          <t>Veddeklinten, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q724" t="n">
+        <v>608399</v>
+      </c>
+      <c r="R724" t="n">
+        <v>7309450</v>
+      </c>
+      <c r="S724" t="n">
+        <v>10</v>
+      </c>
+      <c r="T724" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U724" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V724" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W724" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y724" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AA724" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AD724" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE724" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG724" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT724" t="inlineStr"/>
+      <c r="AW724" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX724" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY724" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY724"/>
+  <dimension ref="A1:AY727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -73359,10 +73359,10 @@
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>135422166</v>
+        <v>135523737</v>
       </c>
       <c r="B651" t="n">
-        <v>107943</v>
+        <v>99197</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -73370,42 +73370,37 @@
         </is>
       </c>
       <c r="E651" t="n">
-        <v>219933</v>
+        <v>219811</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I651" t="inlineStr"/>
-      <c r="K651" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
       <c r="P651" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q651" t="n">
-        <v>608038</v>
+        <v>608111</v>
       </c>
       <c r="R651" t="n">
-        <v>7309623</v>
+        <v>7309661</v>
       </c>
       <c r="S651" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T651" t="inlineStr">
         <is>
@@ -73434,7 +73429,7 @@
       </c>
       <c r="Z651" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA651" t="inlineStr">
@@ -73444,7 +73439,7 @@
       </c>
       <c r="AB651" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD651" t="b">
@@ -73455,35 +73450,26 @@
       </c>
       <c r="AG651" t="b">
         <v>0</v>
-      </c>
-      <c r="AI651" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
-        </is>
       </c>
       <c r="AT651" t="inlineStr"/>
       <c r="AW651" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX651" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY651" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY651" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>135422142</v>
+        <v>135422166</v>
       </c>
       <c r="B652" t="n">
-        <v>108205</v>
+        <v>107943</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -73491,34 +73477,39 @@
         </is>
       </c>
       <c r="E652" t="n">
-        <v>220083</v>
+        <v>219933</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H652" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P652" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q652" t="n">
-        <v>607980</v>
+        <v>608038</v>
       </c>
       <c r="R652" t="n">
-        <v>7309608</v>
+        <v>7309623</v>
       </c>
       <c r="S652" t="n">
         <v>5</v>
@@ -73550,7 +73541,7 @@
       </c>
       <c r="Z652" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA652" t="inlineStr">
@@ -73560,7 +73551,7 @@
       </c>
       <c r="AB652" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD652" t="b">
@@ -73596,10 +73587,10 @@
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>135393157</v>
+        <v>135523654</v>
       </c>
       <c r="B653" t="n">
-        <v>108274</v>
+        <v>107943</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -73607,21 +73598,21 @@
         </is>
       </c>
       <c r="E653" t="n">
-        <v>220102</v>
+        <v>219933</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I653" t="inlineStr"/>
@@ -73631,13 +73622,13 @@
         </is>
       </c>
       <c r="Q653" t="n">
-        <v>608135</v>
+        <v>608037</v>
       </c>
       <c r="R653" t="n">
-        <v>7309645</v>
+        <v>7309597</v>
       </c>
       <c r="S653" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T653" t="inlineStr">
         <is>
@@ -73666,7 +73657,7 @@
       </c>
       <c r="Z653" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA653" t="inlineStr">
@@ -73676,7 +73667,7 @@
       </c>
       <c r="AB653" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD653" t="b">
@@ -73691,22 +73682,22 @@
       <c r="AT653" t="inlineStr"/>
       <c r="AW653" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX653" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY653" t="inlineStr"/>
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>135422154</v>
+        <v>135422142</v>
       </c>
       <c r="B654" t="n">
-        <v>108274</v>
+        <v>108205</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -73714,21 +73705,21 @@
         </is>
       </c>
       <c r="E654" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I654" t="inlineStr"/>
@@ -73738,10 +73729,10 @@
         </is>
       </c>
       <c r="Q654" t="n">
-        <v>608022</v>
+        <v>607980</v>
       </c>
       <c r="R654" t="n">
-        <v>7309641</v>
+        <v>7309608</v>
       </c>
       <c r="S654" t="n">
         <v>5</v>
@@ -73773,7 +73764,7 @@
       </c>
       <c r="Z654" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA654" t="inlineStr">
@@ -73783,7 +73774,7 @@
       </c>
       <c r="AB654" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD654" t="b">
@@ -73819,7 +73810,7 @@
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>135422169</v>
+        <v>135393157</v>
       </c>
       <c r="B655" t="n">
         <v>108274</v>
@@ -73850,17 +73841,17 @@
       <c r="I655" t="inlineStr"/>
       <c r="P655" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q655" t="n">
-        <v>608036</v>
+        <v>608135</v>
       </c>
       <c r="R655" t="n">
-        <v>7309643</v>
+        <v>7309645</v>
       </c>
       <c r="S655" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T655" t="inlineStr">
         <is>
@@ -73889,7 +73880,7 @@
       </c>
       <c r="Z655" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA655" t="inlineStr">
@@ -73899,7 +73890,7 @@
       </c>
       <c r="AB655" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD655" t="b">
@@ -73910,35 +73901,26 @@
       </c>
       <c r="AG655" t="b">
         <v>0</v>
-      </c>
-      <c r="AI655" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
-        </is>
       </c>
       <c r="AT655" t="inlineStr"/>
       <c r="AW655" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX655" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY655" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY655" t="inlineStr"/>
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>135393151</v>
+        <v>135422154</v>
       </c>
       <c r="B656" t="n">
-        <v>110023</v>
+        <v>108274</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -73946,34 +73928,34 @@
         </is>
       </c>
       <c r="E656" t="n">
-        <v>220263</v>
+        <v>220102</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>Fjällskråp</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>Petasites frigidus</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>(L.) Fr.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I656" t="inlineStr"/>
       <c r="P656" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q656" t="n">
-        <v>608151</v>
+        <v>608022</v>
       </c>
       <c r="R656" t="n">
-        <v>7309729</v>
+        <v>7309641</v>
       </c>
       <c r="S656" t="n">
         <v>5</v>
@@ -74005,7 +73987,7 @@
       </c>
       <c r="Z656" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA656" t="inlineStr">
@@ -74015,7 +73997,7 @@
       </c>
       <c r="AB656" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD656" t="b">
@@ -74026,26 +74008,35 @@
       </c>
       <c r="AG656" t="b">
         <v>0</v>
+      </c>
+      <c r="AI656" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT656" t="inlineStr"/>
       <c r="AW656" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX656" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY656" t="inlineStr"/>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY656" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>135351874</v>
+        <v>135422169</v>
       </c>
       <c r="B657" t="n">
-        <v>110150</v>
+        <v>108274</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -74053,21 +74044,21 @@
         </is>
       </c>
       <c r="E657" t="n">
-        <v>220294</v>
+        <v>220102</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I657" t="inlineStr"/>
@@ -74077,13 +74068,13 @@
         </is>
       </c>
       <c r="Q657" t="n">
-        <v>608136</v>
+        <v>608036</v>
       </c>
       <c r="R657" t="n">
-        <v>7309644</v>
+        <v>7309643</v>
       </c>
       <c r="S657" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T657" t="inlineStr">
         <is>
@@ -74107,22 +74098,22 @@
       </c>
       <c r="Y657" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z657" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA657" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB657" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD657" t="b">
@@ -74133,16 +74124,21 @@
       </c>
       <c r="AG657" t="b">
         <v>0</v>
+      </c>
+      <c r="AI657" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT657" t="inlineStr"/>
       <c r="AW657" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX657" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY657" t="inlineStr">
@@ -74153,57 +74149,48 @@
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>135349921</v>
+        <v>135393151</v>
       </c>
       <c r="B658" t="n">
-        <v>99195</v>
+        <v>110023</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E658" t="n">
-        <v>220787</v>
+        <v>220263</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fjällskråp</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Petasites frigidus</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I658" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K658" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Fr.</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr"/>
       <c r="P658" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q658" t="n">
-        <v>607991</v>
+        <v>608151</v>
       </c>
       <c r="R658" t="n">
-        <v>7309608</v>
+        <v>7309729</v>
       </c>
       <c r="S658" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T658" t="inlineStr">
         <is>
@@ -74227,22 +74214,22 @@
       </c>
       <c r="Y658" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z658" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA658" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB658" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD658" t="b">
@@ -74257,26 +74244,22 @@
       <c r="AT658" t="inlineStr"/>
       <c r="AW658" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX658" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY658" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY658" t="inlineStr"/>
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>135349909</v>
+        <v>135351874</v>
       </c>
       <c r="B659" t="n">
-        <v>106309</v>
+        <v>110150</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -74284,41 +74267,37 @@
         </is>
       </c>
       <c r="E659" t="n">
-        <v>221725</v>
+        <v>220294</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fjällskära</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Saussurea alpina</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) DC.</t>
         </is>
       </c>
       <c r="I659" t="inlineStr"/>
-      <c r="J659" t="inlineStr"/>
-      <c r="K659" t="inlineStr"/>
-      <c r="L659" t="inlineStr"/>
-      <c r="N659" t="inlineStr"/>
       <c r="P659" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q659" t="n">
-        <v>608014</v>
+        <v>608136</v>
       </c>
       <c r="R659" t="n">
-        <v>7309638</v>
+        <v>7309644</v>
       </c>
       <c r="S659" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T659" t="inlineStr">
         <is>
@@ -74347,7 +74326,7 @@
       </c>
       <c r="Z659" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA659" t="inlineStr">
@@ -74357,7 +74336,7 @@
       </c>
       <c r="AB659" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD659" t="b">
@@ -74366,19 +74345,18 @@
       <c r="AE659" t="b">
         <v>0</v>
       </c>
-      <c r="AF659" t="inlineStr"/>
       <c r="AG659" t="b">
         <v>0</v>
       </c>
       <c r="AT659" t="inlineStr"/>
       <c r="AW659" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX659" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY659" t="inlineStr">
@@ -74389,48 +74367,57 @@
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>135384319</v>
+        <v>135349921</v>
       </c>
       <c r="B660" t="n">
-        <v>106309</v>
+        <v>99195</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E660" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I660" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P660" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q660" t="n">
-        <v>608048</v>
+        <v>607991</v>
       </c>
       <c r="R660" t="n">
-        <v>7309656</v>
+        <v>7309608</v>
       </c>
       <c r="S660" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T660" t="inlineStr">
         <is>
@@ -74454,22 +74441,22 @@
       </c>
       <c r="Y660" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z660" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA660" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB660" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD660" t="b">
@@ -74484,12 +74471,12 @@
       <c r="AT660" t="inlineStr"/>
       <c r="AW660" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX660" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY660" t="inlineStr">
@@ -74500,7 +74487,7 @@
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>135384324</v>
+        <v>135349909</v>
       </c>
       <c r="B661" t="n">
         <v>106309</v>
@@ -74529,19 +74516,23 @@
         </is>
       </c>
       <c r="I661" t="inlineStr"/>
+      <c r="J661" t="inlineStr"/>
+      <c r="K661" t="inlineStr"/>
+      <c r="L661" t="inlineStr"/>
+      <c r="N661" t="inlineStr"/>
       <c r="P661" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q661" t="n">
-        <v>608042</v>
+        <v>608014</v>
       </c>
       <c r="R661" t="n">
-        <v>7309653</v>
+        <v>7309638</v>
       </c>
       <c r="S661" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T661" t="inlineStr">
         <is>
@@ -74565,22 +74556,22 @@
       </c>
       <c r="Y661" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z661" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA661" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB661" t="inlineStr">
         <is>
-          <t>16:09</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD661" t="b">
@@ -74589,18 +74580,19 @@
       <c r="AE661" t="b">
         <v>0</v>
       </c>
+      <c r="AF661" t="inlineStr"/>
       <c r="AG661" t="b">
         <v>0</v>
       </c>
       <c r="AT661" t="inlineStr"/>
       <c r="AW661" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX661" t="inlineStr">
         <is>
-          <t>Paulina Delin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY661" t="inlineStr">
@@ -74611,7 +74603,7 @@
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>135388296</v>
+        <v>135384319</v>
       </c>
       <c r="B662" t="n">
         <v>106309</v>
@@ -74642,17 +74634,17 @@
       <c r="I662" t="inlineStr"/>
       <c r="P662" t="inlineStr">
         <is>
-          <t>Laisdalen päronberget, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q662" t="n">
-        <v>608057</v>
+        <v>608048</v>
       </c>
       <c r="R662" t="n">
-        <v>7309661</v>
+        <v>7309656</v>
       </c>
       <c r="S662" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T662" t="inlineStr">
         <is>
@@ -74681,7 +74673,7 @@
       </c>
       <c r="Z662" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA662" t="inlineStr">
@@ -74691,7 +74683,7 @@
       </c>
       <c r="AB662" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD662" t="b">
@@ -74706,12 +74698,12 @@
       <c r="AT662" t="inlineStr"/>
       <c r="AW662" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX662" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AY662" t="inlineStr">
@@ -74722,7 +74714,7 @@
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>135393149</v>
+        <v>135384324</v>
       </c>
       <c r="B663" t="n">
         <v>106309</v>
@@ -74753,14 +74745,14 @@
       <c r="I663" t="inlineStr"/>
       <c r="P663" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q663" t="n">
-        <v>608109</v>
+        <v>608042</v>
       </c>
       <c r="R663" t="n">
-        <v>7309705</v>
+        <v>7309653</v>
       </c>
       <c r="S663" t="n">
         <v>5</v>
@@ -74792,7 +74784,7 @@
       </c>
       <c r="Z663" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AA663" t="inlineStr">
@@ -74802,7 +74794,7 @@
       </c>
       <c r="AB663" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="AD663" t="b">
@@ -74817,19 +74809,23 @@
       <c r="AT663" t="inlineStr"/>
       <c r="AW663" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Paulina Delin</t>
         </is>
       </c>
       <c r="AX663" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY663" t="inlineStr"/>
+          <t>Paulina Delin</t>
+        </is>
+      </c>
+      <c r="AY663" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>135422137</v>
+        <v>135388296</v>
       </c>
       <c r="B664" t="n">
         <v>106309</v>
@@ -74860,17 +74856,17 @@
       <c r="I664" t="inlineStr"/>
       <c r="P664" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Laisdalen päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q664" t="n">
-        <v>608098</v>
+        <v>608057</v>
       </c>
       <c r="R664" t="n">
-        <v>7309537</v>
+        <v>7309661</v>
       </c>
       <c r="S664" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T664" t="inlineStr">
         <is>
@@ -74899,7 +74895,7 @@
       </c>
       <c r="Z664" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA664" t="inlineStr">
@@ -74909,7 +74905,7 @@
       </c>
       <c r="AB664" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD664" t="b">
@@ -74924,12 +74920,12 @@
       <c r="AT664" t="inlineStr"/>
       <c r="AW664" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX664" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY664" t="inlineStr">
@@ -74940,7 +74936,7 @@
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>135422150</v>
+        <v>135393149</v>
       </c>
       <c r="B665" t="n">
         <v>106309</v>
@@ -74971,14 +74967,14 @@
       <c r="I665" t="inlineStr"/>
       <c r="P665" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q665" t="n">
-        <v>607932</v>
+        <v>608109</v>
       </c>
       <c r="R665" t="n">
-        <v>7309600</v>
+        <v>7309705</v>
       </c>
       <c r="S665" t="n">
         <v>5</v>
@@ -75010,7 +75006,7 @@
       </c>
       <c r="Z665" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA665" t="inlineStr">
@@ -75020,7 +75016,7 @@
       </c>
       <c r="AB665" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD665" t="b">
@@ -75031,32 +75027,23 @@
       </c>
       <c r="AG665" t="b">
         <v>0</v>
-      </c>
-      <c r="AI665" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
-        </is>
       </c>
       <c r="AT665" t="inlineStr"/>
       <c r="AW665" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX665" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY665" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY665" t="inlineStr"/>
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>135422155</v>
+        <v>135422137</v>
       </c>
       <c r="B666" t="n">
         <v>106309</v>
@@ -75091,10 +75078,10 @@
         </is>
       </c>
       <c r="Q666" t="n">
-        <v>608051</v>
+        <v>608098</v>
       </c>
       <c r="R666" t="n">
-        <v>7309668</v>
+        <v>7309537</v>
       </c>
       <c r="S666" t="n">
         <v>5</v>
@@ -75126,7 +75113,7 @@
       </c>
       <c r="Z666" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA666" t="inlineStr">
@@ -75136,7 +75123,7 @@
       </c>
       <c r="AB666" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD666" t="b">
@@ -75147,11 +75134,6 @@
       </c>
       <c r="AG666" t="b">
         <v>0</v>
-      </c>
-      <c r="AI666" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
-        </is>
       </c>
       <c r="AT666" t="inlineStr"/>
       <c r="AW666" t="inlineStr">
@@ -75172,7 +75154,7 @@
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>135422159</v>
+        <v>135422150</v>
       </c>
       <c r="B667" t="n">
         <v>106309</v>
@@ -75207,10 +75189,10 @@
         </is>
       </c>
       <c r="Q667" t="n">
-        <v>608073</v>
+        <v>607932</v>
       </c>
       <c r="R667" t="n">
-        <v>7309640</v>
+        <v>7309600</v>
       </c>
       <c r="S667" t="n">
         <v>5</v>
@@ -75242,7 +75224,7 @@
       </c>
       <c r="Z667" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA667" t="inlineStr">
@@ -75252,7 +75234,7 @@
       </c>
       <c r="AB667" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD667" t="b">
@@ -75288,7 +75270,7 @@
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>135440319</v>
+        <v>135422155</v>
       </c>
       <c r="B668" t="n">
         <v>106309</v>
@@ -75319,14 +75301,14 @@
       <c r="I668" t="inlineStr"/>
       <c r="P668" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q668" t="n">
-        <v>608072</v>
+        <v>608051</v>
       </c>
       <c r="R668" t="n">
-        <v>7309649</v>
+        <v>7309668</v>
       </c>
       <c r="S668" t="n">
         <v>5</v>
@@ -75358,7 +75340,7 @@
       </c>
       <c r="Z668" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA668" t="inlineStr">
@@ -75368,7 +75350,7 @@
       </c>
       <c r="AB668" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD668" t="b">
@@ -75379,16 +75361,21 @@
       </c>
       <c r="AG668" t="b">
         <v>0</v>
+      </c>
+      <c r="AI668" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT668" t="inlineStr"/>
       <c r="AW668" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX668" t="inlineStr">
         <is>
-          <t>Linnea Ingelsbo</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY668" t="inlineStr">
@@ -75399,10 +75386,10 @@
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>135422167</v>
+        <v>135422159</v>
       </c>
       <c r="B669" t="n">
-        <v>98054</v>
+        <v>106309</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -75410,19 +75397,23 @@
         </is>
       </c>
       <c r="E669" t="n">
-        <v>221944</v>
+        <v>221725</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H669" t="inlineStr"/>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
       <c r="I669" t="inlineStr"/>
       <c r="P669" t="inlineStr">
         <is>
@@ -75430,10 +75421,10 @@
         </is>
       </c>
       <c r="Q669" t="n">
-        <v>608038</v>
+        <v>608073</v>
       </c>
       <c r="R669" t="n">
-        <v>7309623</v>
+        <v>7309640</v>
       </c>
       <c r="S669" t="n">
         <v>5</v>
@@ -75465,7 +75456,7 @@
       </c>
       <c r="Z669" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA669" t="inlineStr">
@@ -75475,7 +75466,7 @@
       </c>
       <c r="AB669" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD669" t="b">
@@ -75511,10 +75502,10 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>135385157</v>
+        <v>135440319</v>
       </c>
       <c r="B670" t="n">
-        <v>98063</v>
+        <v>106309</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -75522,34 +75513,34 @@
         </is>
       </c>
       <c r="E670" t="n">
-        <v>221946</v>
+        <v>221725</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I670" t="inlineStr"/>
       <c r="P670" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q670" t="n">
-        <v>607832</v>
+        <v>608072</v>
       </c>
       <c r="R670" t="n">
-        <v>7310013</v>
+        <v>7309649</v>
       </c>
       <c r="S670" t="n">
         <v>5</v>
@@ -75581,7 +75572,7 @@
       </c>
       <c r="Z670" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA670" t="inlineStr">
@@ -75591,7 +75582,7 @@
       </c>
       <c r="AB670" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD670" t="b">
@@ -75606,12 +75597,12 @@
       <c r="AT670" t="inlineStr"/>
       <c r="AW670" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AX670" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Linnea Ingelsbo</t>
         </is>
       </c>
       <c r="AY670" t="inlineStr">
@@ -75622,10 +75613,10 @@
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>135349896</v>
+        <v>135422167</v>
       </c>
       <c r="B671" t="n">
-        <v>99217</v>
+        <v>98054</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -75633,23 +75624,19 @@
         </is>
       </c>
       <c r="E671" t="n">
-        <v>221952</v>
+        <v>221944</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
-        </is>
-      </c>
-      <c r="H671" t="inlineStr">
-        <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr"/>
       <c r="I671" t="inlineStr"/>
       <c r="P671" t="inlineStr">
         <is>
@@ -75657,13 +75644,13 @@
         </is>
       </c>
       <c r="Q671" t="n">
-        <v>608056</v>
+        <v>608038</v>
       </c>
       <c r="R671" t="n">
-        <v>7309695</v>
+        <v>7309623</v>
       </c>
       <c r="S671" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T671" t="inlineStr">
         <is>
@@ -75687,22 +75674,22 @@
       </c>
       <c r="Y671" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z671" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA671" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB671" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD671" t="b">
@@ -75713,16 +75700,21 @@
       </c>
       <c r="AG671" t="b">
         <v>0</v>
+      </c>
+      <c r="AI671" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT671" t="inlineStr"/>
       <c r="AW671" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX671" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY671" t="inlineStr">
@@ -75733,10 +75725,10 @@
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>135349910</v>
+        <v>135523644</v>
       </c>
       <c r="B672" t="n">
-        <v>103764</v>
+        <v>98054</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -75744,37 +75736,33 @@
         </is>
       </c>
       <c r="E672" t="n">
-        <v>222004</v>
+        <v>221944</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>Kärrviol</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>Viola palustris</t>
-        </is>
-      </c>
-      <c r="H672" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr"/>
       <c r="I672" t="inlineStr"/>
       <c r="P672" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q672" t="n">
-        <v>608014</v>
+        <v>608037</v>
       </c>
       <c r="R672" t="n">
-        <v>7309638</v>
+        <v>7309597</v>
       </c>
       <c r="S672" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T672" t="inlineStr">
         <is>
@@ -75798,22 +75786,22 @@
       </c>
       <c r="Y672" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z672" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA672" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB672" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD672" t="b">
@@ -75828,26 +75816,22 @@
       <c r="AT672" t="inlineStr"/>
       <c r="AW672" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX672" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY672" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY672" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>135356148</v>
+        <v>135385157</v>
       </c>
       <c r="B673" t="n">
-        <v>104707</v>
+        <v>98063</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -75855,16 +75839,16 @@
         </is>
       </c>
       <c r="E673" t="n">
-        <v>222412</v>
+        <v>221946</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
@@ -75875,17 +75859,17 @@
       <c r="I673" t="inlineStr"/>
       <c r="P673" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q673" t="n">
-        <v>607978</v>
+        <v>607832</v>
       </c>
       <c r="R673" t="n">
-        <v>7309596</v>
+        <v>7310013</v>
       </c>
       <c r="S673" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T673" t="inlineStr">
         <is>
@@ -75909,22 +75893,22 @@
       </c>
       <c r="Y673" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z673" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA673" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB673" t="inlineStr">
         <is>
-          <t>15:56</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD673" t="b">
@@ -75939,12 +75923,12 @@
       <c r="AT673" t="inlineStr"/>
       <c r="AW673" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX673" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AY673" t="inlineStr">
@@ -75955,10 +75939,10 @@
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>135393154</v>
+        <v>135349896</v>
       </c>
       <c r="B674" t="n">
-        <v>104707</v>
+        <v>99217</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -75966,37 +75950,37 @@
         </is>
       </c>
       <c r="E674" t="n">
-        <v>222412</v>
+        <v>221952</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I674" t="inlineStr"/>
       <c r="P674" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q674" t="n">
-        <v>608171</v>
+        <v>608056</v>
       </c>
       <c r="R674" t="n">
-        <v>7309720</v>
+        <v>7309695</v>
       </c>
       <c r="S674" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T674" t="inlineStr">
         <is>
@@ -76020,22 +76004,22 @@
       </c>
       <c r="Y674" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z674" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA674" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB674" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD674" t="b">
@@ -76050,22 +76034,26 @@
       <c r="AT674" t="inlineStr"/>
       <c r="AW674" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX674" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY674" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY674" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>135422138</v>
+        <v>135349910</v>
       </c>
       <c r="B675" t="n">
-        <v>104707</v>
+        <v>103764</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -76073,16 +76061,16 @@
         </is>
       </c>
       <c r="E675" t="n">
-        <v>222412</v>
+        <v>222004</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kärrviol</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Viola palustris</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
@@ -76090,34 +76078,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I675" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J675" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K675" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I675" t="inlineStr"/>
       <c r="P675" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q675" t="n">
-        <v>608116</v>
+        <v>608014</v>
       </c>
       <c r="R675" t="n">
-        <v>7309530</v>
+        <v>7309638</v>
       </c>
       <c r="S675" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T675" t="inlineStr">
         <is>
@@ -76141,22 +76115,22 @@
       </c>
       <c r="Y675" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z675" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA675" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB675" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD675" t="b">
@@ -76167,21 +76141,16 @@
       </c>
       <c r="AG675" t="b">
         <v>0</v>
-      </c>
-      <c r="AI675" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
-        </is>
       </c>
       <c r="AT675" t="inlineStr"/>
       <c r="AW675" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX675" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY675" t="inlineStr">
@@ -76192,7 +76161,7 @@
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>135422163</v>
+        <v>135356148</v>
       </c>
       <c r="B676" t="n">
         <v>104707</v>
@@ -76220,34 +76189,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I676" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J676" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K676" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I676" t="inlineStr"/>
       <c r="P676" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q676" t="n">
-        <v>607983</v>
+        <v>607978</v>
       </c>
       <c r="R676" t="n">
-        <v>7309618</v>
+        <v>7309596</v>
       </c>
       <c r="S676" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T676" t="inlineStr">
         <is>
@@ -76271,22 +76226,22 @@
       </c>
       <c r="Y676" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z676" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AA676" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB676" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="AD676" t="b">
@@ -76297,21 +76252,16 @@
       </c>
       <c r="AG676" t="b">
         <v>0</v>
-      </c>
-      <c r="AI676" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
-        </is>
       </c>
       <c r="AT676" t="inlineStr"/>
       <c r="AW676" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX676" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY676" t="inlineStr">
@@ -76322,7 +76272,7 @@
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>135422168</v>
+        <v>135393154</v>
       </c>
       <c r="B677" t="n">
         <v>104707</v>
@@ -76350,34 +76300,20 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I677" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J677" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K677" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I677" t="inlineStr"/>
       <c r="P677" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q677" t="n">
-        <v>608036</v>
+        <v>608171</v>
       </c>
       <c r="R677" t="n">
-        <v>7309638</v>
+        <v>7309720</v>
       </c>
       <c r="S677" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T677" t="inlineStr">
         <is>
@@ -76406,7 +76342,7 @@
       </c>
       <c r="Z677" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA677" t="inlineStr">
@@ -76416,7 +76352,7 @@
       </c>
       <c r="AB677" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD677" t="b">
@@ -76427,35 +76363,26 @@
       </c>
       <c r="AG677" t="b">
         <v>0</v>
-      </c>
-      <c r="AI677" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
-        </is>
       </c>
       <c r="AT677" t="inlineStr"/>
       <c r="AW677" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX677" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY677" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY677" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>135393126</v>
+        <v>135422138</v>
       </c>
       <c r="B678" t="n">
-        <v>100806</v>
+        <v>104707</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -76463,16 +76390,16 @@
         </is>
       </c>
       <c r="E678" t="n">
-        <v>222584</v>
+        <v>222412</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>Bergsslok</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>Melica nutans</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
@@ -76480,17 +76407,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I678" t="inlineStr"/>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P678" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q678" t="n">
-        <v>608021</v>
+        <v>608116</v>
       </c>
       <c r="R678" t="n">
-        <v>7309604</v>
+        <v>7309530</v>
       </c>
       <c r="S678" t="n">
         <v>5</v>
@@ -76522,7 +76463,7 @@
       </c>
       <c r="Z678" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA678" t="inlineStr">
@@ -76532,7 +76473,7 @@
       </c>
       <c r="AB678" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD678" t="b">
@@ -76543,26 +76484,35 @@
       </c>
       <c r="AG678" t="b">
         <v>0</v>
+      </c>
+      <c r="AI678" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT678" t="inlineStr"/>
       <c r="AW678" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX678" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY678" t="inlineStr"/>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY678" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>135388299</v>
+        <v>135422163</v>
       </c>
       <c r="B679" t="n">
-        <v>102871</v>
+        <v>104707</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -76570,16 +76520,16 @@
         </is>
       </c>
       <c r="E679" t="n">
-        <v>223037</v>
+        <v>222412</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>Humleblomster</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>Geum rivale</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
@@ -76587,20 +76537,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I679" t="inlineStr"/>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P679" t="inlineStr">
         <is>
-          <t>Laisdalen päronberget, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q679" t="n">
-        <v>608030</v>
+        <v>607983</v>
       </c>
       <c r="R679" t="n">
-        <v>7309591</v>
+        <v>7309618</v>
       </c>
       <c r="S679" t="n">
-        <v>61</v>
+        <v>5</v>
       </c>
       <c r="T679" t="inlineStr">
         <is>
@@ -76629,7 +76593,7 @@
       </c>
       <c r="Z679" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA679" t="inlineStr">
@@ -76639,7 +76603,7 @@
       </c>
       <c r="AB679" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD679" t="b">
@@ -76650,16 +76614,21 @@
       </c>
       <c r="AG679" t="b">
         <v>0</v>
+      </c>
+      <c r="AI679" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT679" t="inlineStr"/>
       <c r="AW679" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX679" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY679" t="inlineStr">
@@ -76670,10 +76639,10 @@
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>135422143</v>
+        <v>135422168</v>
       </c>
       <c r="B680" t="n">
-        <v>99001</v>
+        <v>104707</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -76681,16 +76650,16 @@
         </is>
       </c>
       <c r="E680" t="n">
-        <v>223049</v>
+        <v>222412</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
@@ -76698,20 +76667,34 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I680" t="inlineStr"/>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P680" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q680" t="n">
-        <v>607980</v>
+        <v>608036</v>
       </c>
       <c r="R680" t="n">
-        <v>7309608</v>
+        <v>7309638</v>
       </c>
       <c r="S680" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T680" t="inlineStr">
         <is>
@@ -76740,7 +76723,7 @@
       </c>
       <c r="Z680" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA680" t="inlineStr">
@@ -76750,7 +76733,7 @@
       </c>
       <c r="AB680" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AD680" t="b">
@@ -76786,10 +76769,10 @@
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>135351867</v>
+        <v>135393126</v>
       </c>
       <c r="B681" t="n">
-        <v>99198</v>
+        <v>100806</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -76797,30 +76780,34 @@
         </is>
       </c>
       <c r="E681" t="n">
-        <v>223614</v>
+        <v>222584</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>Vanlig brudsporre</t>
+          <t>Bergsslok</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea subsp. conopsea</t>
-        </is>
-      </c>
-      <c r="H681" t="inlineStr"/>
+          <t>Melica nutans</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I681" t="inlineStr"/>
       <c r="P681" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q681" t="n">
-        <v>608123</v>
+        <v>608021</v>
       </c>
       <c r="R681" t="n">
-        <v>7309661</v>
+        <v>7309604</v>
       </c>
       <c r="S681" t="n">
         <v>5</v>
@@ -76847,22 +76834,22 @@
       </c>
       <c r="Y681" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z681" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA681" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB681" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD681" t="b">
@@ -76871,33 +76858,28 @@
       <c r="AE681" t="b">
         <v>0</v>
       </c>
-      <c r="AF681" t="inlineStr"/>
       <c r="AG681" t="b">
         <v>0</v>
       </c>
       <c r="AT681" t="inlineStr"/>
       <c r="AW681" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX681" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY681" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY681" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>135349891</v>
+        <v>135388299</v>
       </c>
       <c r="B682" t="n">
-        <v>101293</v>
+        <v>102871</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -76905,37 +76887,37 @@
         </is>
       </c>
       <c r="E682" t="n">
-        <v>224885</v>
+        <v>223037</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Humleblomster</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Geum rivale</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I682" t="inlineStr"/>
       <c r="P682" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Laisdalen päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q682" t="n">
-        <v>608082</v>
+        <v>608030</v>
       </c>
       <c r="R682" t="n">
-        <v>7309684</v>
+        <v>7309591</v>
       </c>
       <c r="S682" t="n">
-        <v>3</v>
+        <v>61</v>
       </c>
       <c r="T682" t="inlineStr">
         <is>
@@ -76959,22 +76941,22 @@
       </c>
       <c r="Y682" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z682" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA682" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB682" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD682" t="b">
@@ -76989,12 +76971,12 @@
       <c r="AT682" t="inlineStr"/>
       <c r="AW682" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AX682" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl</t>
         </is>
       </c>
       <c r="AY682" t="inlineStr">
@@ -77005,10 +76987,10 @@
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>135393129</v>
+        <v>135422143</v>
       </c>
       <c r="B683" t="n">
-        <v>101293</v>
+        <v>99001</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -77016,34 +76998,34 @@
         </is>
       </c>
       <c r="E683" t="n">
-        <v>224885</v>
+        <v>223049</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I683" t="inlineStr"/>
       <c r="P683" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q683" t="n">
-        <v>608021</v>
+        <v>607980</v>
       </c>
       <c r="R683" t="n">
-        <v>7309619</v>
+        <v>7309608</v>
       </c>
       <c r="S683" t="n">
         <v>5</v>
@@ -77075,7 +77057,7 @@
       </c>
       <c r="Z683" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA683" t="inlineStr">
@@ -77085,7 +77067,7 @@
       </c>
       <c r="AB683" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD683" t="b">
@@ -77096,26 +77078,35 @@
       </c>
       <c r="AG683" t="b">
         <v>0</v>
+      </c>
+      <c r="AI683" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT683" t="inlineStr"/>
       <c r="AW683" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX683" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY683" t="inlineStr"/>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY683" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
-        <v>135393131</v>
+        <v>135351867</v>
       </c>
       <c r="B684" t="n">
-        <v>101293</v>
+        <v>99198</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -77123,34 +77114,30 @@
         </is>
       </c>
       <c r="E684" t="n">
-        <v>224885</v>
+        <v>223614</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Vanlig brudsporre</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H684" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
+          <t>Gymnadenia conopsea subsp. conopsea</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr"/>
       <c r="I684" t="inlineStr"/>
       <c r="P684" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q684" t="n">
-        <v>608014</v>
+        <v>608123</v>
       </c>
       <c r="R684" t="n">
-        <v>7309625</v>
+        <v>7309661</v>
       </c>
       <c r="S684" t="n">
         <v>5</v>
@@ -77177,22 +77164,22 @@
       </c>
       <c r="Y684" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z684" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA684" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB684" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD684" t="b">
@@ -77201,25 +77188,30 @@
       <c r="AE684" t="b">
         <v>0</v>
       </c>
+      <c r="AF684" t="inlineStr"/>
       <c r="AG684" t="b">
         <v>0</v>
       </c>
       <c r="AT684" t="inlineStr"/>
       <c r="AW684" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX684" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY684" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY684" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
-        <v>135393150</v>
+        <v>135349891</v>
       </c>
       <c r="B685" t="n">
         <v>101293</v>
@@ -77250,17 +77242,17 @@
       <c r="I685" t="inlineStr"/>
       <c r="P685" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q685" t="n">
-        <v>608136</v>
+        <v>608082</v>
       </c>
       <c r="R685" t="n">
-        <v>7309706</v>
+        <v>7309684</v>
       </c>
       <c r="S685" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T685" t="inlineStr">
         <is>
@@ -77284,22 +77276,22 @@
       </c>
       <c r="Y685" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z685" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA685" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB685" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD685" t="b">
@@ -77314,19 +77306,23 @@
       <c r="AT685" t="inlineStr"/>
       <c r="AW685" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX685" t="inlineStr">
         <is>
-          <t>Ann Normark</t>
-        </is>
-      </c>
-      <c r="AY685" t="inlineStr"/>
+          <t>Mattias Dalkvist</t>
+        </is>
+      </c>
+      <c r="AY685" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
-        <v>135422139</v>
+        <v>135393129</v>
       </c>
       <c r="B686" t="n">
         <v>101293</v>
@@ -77357,14 +77353,14 @@
       <c r="I686" t="inlineStr"/>
       <c r="P686" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q686" t="n">
-        <v>608113</v>
+        <v>608021</v>
       </c>
       <c r="R686" t="n">
-        <v>7309528</v>
+        <v>7309619</v>
       </c>
       <c r="S686" t="n">
         <v>5</v>
@@ -77396,7 +77392,7 @@
       </c>
       <c r="Z686" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA686" t="inlineStr">
@@ -77406,7 +77402,7 @@
       </c>
       <c r="AB686" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD686" t="b">
@@ -77417,32 +77413,23 @@
       </c>
       <c r="AG686" t="b">
         <v>0</v>
-      </c>
-      <c r="AI686" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
-        </is>
       </c>
       <c r="AT686" t="inlineStr"/>
       <c r="AW686" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX686" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY686" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY686" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" t="n">
-        <v>135422140</v>
+        <v>135393131</v>
       </c>
       <c r="B687" t="n">
         <v>101293</v>
@@ -77473,14 +77460,14 @@
       <c r="I687" t="inlineStr"/>
       <c r="P687" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q687" t="n">
-        <v>607989</v>
+        <v>608014</v>
       </c>
       <c r="R687" t="n">
-        <v>7309602</v>
+        <v>7309625</v>
       </c>
       <c r="S687" t="n">
         <v>5</v>
@@ -77512,7 +77499,7 @@
       </c>
       <c r="Z687" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA687" t="inlineStr">
@@ -77522,7 +77509,7 @@
       </c>
       <c r="AB687" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD687" t="b">
@@ -77533,32 +77520,23 @@
       </c>
       <c r="AG687" t="b">
         <v>0</v>
-      </c>
-      <c r="AI687" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
-        </is>
       </c>
       <c r="AT687" t="inlineStr"/>
       <c r="AW687" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX687" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY687" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY687" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" t="n">
-        <v>135422152</v>
+        <v>135393150</v>
       </c>
       <c r="B688" t="n">
         <v>101293</v>
@@ -77589,14 +77567,14 @@
       <c r="I688" t="inlineStr"/>
       <c r="P688" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q688" t="n">
-        <v>608010</v>
+        <v>608136</v>
       </c>
       <c r="R688" t="n">
-        <v>7309640</v>
+        <v>7309706</v>
       </c>
       <c r="S688" t="n">
         <v>5</v>
@@ -77628,7 +77606,7 @@
       </c>
       <c r="Z688" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA688" t="inlineStr">
@@ -77638,7 +77616,7 @@
       </c>
       <c r="AB688" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD688" t="b">
@@ -77649,32 +77627,23 @@
       </c>
       <c r="AG688" t="b">
         <v>0</v>
-      </c>
-      <c r="AI688" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
-        </is>
       </c>
       <c r="AT688" t="inlineStr"/>
       <c r="AW688" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ann Normark</t>
         </is>
       </c>
       <c r="AX688" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
-        </is>
-      </c>
-      <c r="AY688" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Ann Normark</t>
+        </is>
+      </c>
+      <c r="AY688" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" t="n">
-        <v>135523597</v>
+        <v>135422139</v>
       </c>
       <c r="B689" t="n">
         <v>101293</v>
@@ -77705,17 +77674,17 @@
       <c r="I689" t="inlineStr"/>
       <c r="P689" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q689" t="n">
-        <v>608073</v>
+        <v>608113</v>
       </c>
       <c r="R689" t="n">
-        <v>7309660</v>
+        <v>7309528</v>
       </c>
       <c r="S689" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T689" t="inlineStr">
         <is>
@@ -77744,7 +77713,7 @@
       </c>
       <c r="Z689" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA689" t="inlineStr">
@@ -77754,7 +77723,7 @@
       </c>
       <c r="AB689" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD689" t="b">
@@ -77765,48 +77734,57 @@
       </c>
       <c r="AG689" t="b">
         <v>0</v>
+      </c>
+      <c r="AI689" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT689" t="inlineStr"/>
       <c r="AW689" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX689" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
-        </is>
-      </c>
-      <c r="AY689" t="inlineStr"/>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY689" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
-        <v>135378173</v>
+        <v>135422140</v>
       </c>
       <c r="B690" t="n">
-        <v>78382</v>
+        <v>101293</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E690" t="n">
-        <v>228579</v>
+        <v>224885</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I690" t="inlineStr"/>
@@ -77816,13 +77794,13 @@
         </is>
       </c>
       <c r="Q690" t="n">
-        <v>607794</v>
+        <v>607989</v>
       </c>
       <c r="R690" t="n">
-        <v>7309999</v>
+        <v>7309602</v>
       </c>
       <c r="S690" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T690" t="inlineStr">
         <is>
@@ -77851,7 +77829,7 @@
       </c>
       <c r="Z690" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA690" t="inlineStr">
@@ -77861,7 +77839,7 @@
       </c>
       <c r="AB690" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD690" t="b">
@@ -77872,16 +77850,21 @@
       </c>
       <c r="AG690" t="b">
         <v>0</v>
+      </c>
+      <c r="AI690" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT690" t="inlineStr"/>
       <c r="AW690" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX690" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY690" t="inlineStr">
@@ -77892,32 +77875,32 @@
     </row>
     <row r="691">
       <c r="A691" t="n">
-        <v>135378175</v>
+        <v>135422152</v>
       </c>
       <c r="B691" t="n">
-        <v>78382</v>
+        <v>101293</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E691" t="n">
-        <v>228579</v>
+        <v>224885</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I691" t="inlineStr"/>
@@ -77927,13 +77910,13 @@
         </is>
       </c>
       <c r="Q691" t="n">
-        <v>607781</v>
+        <v>608010</v>
       </c>
       <c r="R691" t="n">
-        <v>7310006</v>
+        <v>7309640</v>
       </c>
       <c r="S691" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T691" t="inlineStr">
         <is>
@@ -77962,7 +77945,7 @@
       </c>
       <c r="Z691" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA691" t="inlineStr">
@@ -77972,7 +77955,7 @@
       </c>
       <c r="AB691" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD691" t="b">
@@ -77983,16 +77966,21 @@
       </c>
       <c r="AG691" t="b">
         <v>0</v>
+      </c>
+      <c r="AI691" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT691" t="inlineStr"/>
       <c r="AW691" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX691" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY691" t="inlineStr">
@@ -78003,48 +77991,48 @@
     </row>
     <row r="692">
       <c r="A692" t="n">
-        <v>135378179</v>
+        <v>135523597</v>
       </c>
       <c r="B692" t="n">
-        <v>78382</v>
+        <v>101293</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E692" t="n">
-        <v>228579</v>
+        <v>224885</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I692" t="inlineStr"/>
       <c r="P692" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q692" t="n">
-        <v>607702</v>
+        <v>608073</v>
       </c>
       <c r="R692" t="n">
-        <v>7309979</v>
+        <v>7309660</v>
       </c>
       <c r="S692" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T692" t="inlineStr">
         <is>
@@ -78073,7 +78061,7 @@
       </c>
       <c r="Z692" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA692" t="inlineStr">
@@ -78083,7 +78071,7 @@
       </c>
       <c r="AB692" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD692" t="b">
@@ -78098,23 +78086,19 @@
       <c r="AT692" t="inlineStr"/>
       <c r="AW692" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX692" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
-        </is>
-      </c>
-      <c r="AY692" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY692" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" t="n">
-        <v>135378181</v>
+        <v>135378173</v>
       </c>
       <c r="B693" t="n">
         <v>78382</v>
@@ -78149,10 +78133,10 @@
         </is>
       </c>
       <c r="Q693" t="n">
-        <v>607671</v>
+        <v>607794</v>
       </c>
       <c r="R693" t="n">
-        <v>7309990</v>
+        <v>7309999</v>
       </c>
       <c r="S693" t="n">
         <v>4</v>
@@ -78184,7 +78168,7 @@
       </c>
       <c r="Z693" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA693" t="inlineStr">
@@ -78194,7 +78178,7 @@
       </c>
       <c r="AB693" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD693" t="b">
@@ -78225,7 +78209,7 @@
     </row>
     <row r="694">
       <c r="A694" t="n">
-        <v>135385232</v>
+        <v>135378175</v>
       </c>
       <c r="B694" t="n">
         <v>78382</v>
@@ -78256,17 +78240,17 @@
       <c r="I694" t="inlineStr"/>
       <c r="P694" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q694" t="n">
-        <v>607787</v>
+        <v>607781</v>
       </c>
       <c r="R694" t="n">
-        <v>7310002</v>
+        <v>7310006</v>
       </c>
       <c r="S694" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T694" t="inlineStr">
         <is>
@@ -78295,7 +78279,7 @@
       </c>
       <c r="Z694" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA694" t="inlineStr">
@@ -78305,7 +78289,7 @@
       </c>
       <c r="AB694" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD694" t="b">
@@ -78320,12 +78304,12 @@
       <c r="AT694" t="inlineStr"/>
       <c r="AW694" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX694" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY694" t="inlineStr">
@@ -78336,7 +78320,7 @@
     </row>
     <row r="695">
       <c r="A695" t="n">
-        <v>135385289</v>
+        <v>135378179</v>
       </c>
       <c r="B695" t="n">
         <v>78382</v>
@@ -78367,17 +78351,17 @@
       <c r="I695" t="inlineStr"/>
       <c r="P695" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q695" t="n">
-        <v>607788</v>
+        <v>607702</v>
       </c>
       <c r="R695" t="n">
-        <v>7310050</v>
+        <v>7309979</v>
       </c>
       <c r="S695" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T695" t="inlineStr">
         <is>
@@ -78406,7 +78390,7 @@
       </c>
       <c r="Z695" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA695" t="inlineStr">
@@ -78416,7 +78400,7 @@
       </c>
       <c r="AB695" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD695" t="b">
@@ -78431,12 +78415,12 @@
       <c r="AT695" t="inlineStr"/>
       <c r="AW695" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX695" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY695" t="inlineStr">
@@ -78447,7 +78431,7 @@
     </row>
     <row r="696">
       <c r="A696" t="n">
-        <v>135385297</v>
+        <v>135378181</v>
       </c>
       <c r="B696" t="n">
         <v>78382</v>
@@ -78478,17 +78462,17 @@
       <c r="I696" t="inlineStr"/>
       <c r="P696" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q696" t="n">
-        <v>607872</v>
+        <v>607671</v>
       </c>
       <c r="R696" t="n">
-        <v>7309907</v>
+        <v>7309990</v>
       </c>
       <c r="S696" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T696" t="inlineStr">
         <is>
@@ -78517,7 +78501,7 @@
       </c>
       <c r="Z696" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA696" t="inlineStr">
@@ -78527,7 +78511,7 @@
       </c>
       <c r="AB696" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD696" t="b">
@@ -78542,12 +78526,12 @@
       <c r="AT696" t="inlineStr"/>
       <c r="AW696" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX696" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY696" t="inlineStr">
@@ -78558,7 +78542,7 @@
     </row>
     <row r="697">
       <c r="A697" t="n">
-        <v>135422134</v>
+        <v>135385232</v>
       </c>
       <c r="B697" t="n">
         <v>78382</v>
@@ -78589,17 +78573,17 @@
       <c r="I697" t="inlineStr"/>
       <c r="P697" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q697" t="n">
-        <v>608091</v>
+        <v>607787</v>
       </c>
       <c r="R697" t="n">
-        <v>7309583</v>
+        <v>7310002</v>
       </c>
       <c r="S697" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T697" t="inlineStr">
         <is>
@@ -78628,7 +78612,7 @@
       </c>
       <c r="Z697" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA697" t="inlineStr">
@@ -78638,7 +78622,7 @@
       </c>
       <c r="AB697" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD697" t="b">
@@ -78649,31 +78633,16 @@
       </c>
       <c r="AG697" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ697" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK697" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO697" t="inlineStr">
-        <is>
-          <t>På barken av äldre levande gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT697" t="inlineStr"/>
       <c r="AW697" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX697" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY697" t="inlineStr">
@@ -78684,48 +78653,48 @@
     </row>
     <row r="698">
       <c r="A698" t="n">
-        <v>135422148</v>
+        <v>135385289</v>
       </c>
       <c r="B698" t="n">
-        <v>80444</v>
+        <v>78382</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E698" t="n">
-        <v>229748</v>
+        <v>228579</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I698" t="inlineStr"/>
       <c r="P698" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q698" t="n">
-        <v>607928</v>
+        <v>607788</v>
       </c>
       <c r="R698" t="n">
-        <v>7309603</v>
+        <v>7310050</v>
       </c>
       <c r="S698" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T698" t="inlineStr">
         <is>
@@ -78754,7 +78723,7 @@
       </c>
       <c r="Z698" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA698" t="inlineStr">
@@ -78764,7 +78733,7 @@
       </c>
       <c r="AB698" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD698" t="b">
@@ -78775,36 +78744,16 @@
       </c>
       <c r="AG698" t="b">
         <v>0</v>
-      </c>
-      <c r="AI698" t="inlineStr">
-        <is>
-          <t>Uttorkad bäckfåra i örtrik granskog</t>
-        </is>
-      </c>
-      <c r="AJ698" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK698" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO698" t="inlineStr">
-        <is>
-          <t>Björklåga i uttorkad bäckfåra # Betula</t>
-        </is>
       </c>
       <c r="AT698" t="inlineStr"/>
       <c r="AW698" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX698" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY698" t="inlineStr">
@@ -78815,10 +78764,10 @@
     </row>
     <row r="699">
       <c r="A699" t="n">
-        <v>135422151</v>
+        <v>135385297</v>
       </c>
       <c r="B699" t="n">
-        <v>87161</v>
+        <v>78382</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -78826,34 +78775,34 @@
         </is>
       </c>
       <c r="E699" t="n">
-        <v>249278</v>
+        <v>228579</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>Barrviolspindling</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>Cortinarius harcynicus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>(Pers.) M.M.Moser</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I699" t="inlineStr"/>
       <c r="P699" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q699" t="n">
-        <v>607924</v>
+        <v>607872</v>
       </c>
       <c r="R699" t="n">
-        <v>7309606</v>
+        <v>7309907</v>
       </c>
       <c r="S699" t="n">
         <v>5</v>
@@ -78885,7 +78834,7 @@
       </c>
       <c r="Z699" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA699" t="inlineStr">
@@ -78895,7 +78844,7 @@
       </c>
       <c r="AB699" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD699" t="b">
@@ -78906,21 +78855,16 @@
       </c>
       <c r="AG699" t="b">
         <v>0</v>
-      </c>
-      <c r="AI699" t="inlineStr">
-        <is>
-          <t>Örtrik granskog</t>
-        </is>
       </c>
       <c r="AT699" t="inlineStr"/>
       <c r="AW699" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX699" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY699" t="inlineStr">
@@ -78931,10 +78875,10 @@
     </row>
     <row r="700">
       <c r="A700" t="n">
-        <v>135385236</v>
+        <v>135422134</v>
       </c>
       <c r="B700" t="n">
-        <v>79396</v>
+        <v>78382</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -78942,37 +78886,37 @@
         </is>
       </c>
       <c r="E700" t="n">
-        <v>260591</v>
+        <v>228579</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I700" t="inlineStr"/>
       <c r="P700" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q700" t="n">
-        <v>607717</v>
+        <v>608091</v>
       </c>
       <c r="R700" t="n">
-        <v>7309995</v>
+        <v>7309583</v>
       </c>
       <c r="S700" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T700" t="inlineStr">
         <is>
@@ -79001,7 +78945,7 @@
       </c>
       <c r="Z700" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA700" t="inlineStr">
@@ -79011,7 +78955,7 @@
       </c>
       <c r="AB700" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD700" t="b">
@@ -79022,16 +78966,31 @@
       </c>
       <c r="AG700" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ700" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK700" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO700" t="inlineStr">
+        <is>
+          <t>På barken av äldre levande gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT700" t="inlineStr"/>
       <c r="AW700" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX700" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY700" t="inlineStr">
@@ -79042,48 +79001,48 @@
     </row>
     <row r="701">
       <c r="A701" t="n">
-        <v>135385311</v>
+        <v>135422148</v>
       </c>
       <c r="B701" t="n">
-        <v>79396</v>
+        <v>80444</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E701" t="n">
-        <v>260591</v>
+        <v>229748</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I701" t="inlineStr"/>
       <c r="P701" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q701" t="n">
-        <v>607861</v>
+        <v>607928</v>
       </c>
       <c r="R701" t="n">
-        <v>7309816</v>
+        <v>7309603</v>
       </c>
       <c r="S701" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T701" t="inlineStr">
         <is>
@@ -79112,7 +79071,7 @@
       </c>
       <c r="Z701" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA701" t="inlineStr">
@@ -79122,7 +79081,7 @@
       </c>
       <c r="AB701" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AD701" t="b">
@@ -79133,16 +79092,36 @@
       </c>
       <c r="AG701" t="b">
         <v>0</v>
+      </c>
+      <c r="AI701" t="inlineStr">
+        <is>
+          <t>Uttorkad bäckfåra i örtrik granskog</t>
+        </is>
+      </c>
+      <c r="AJ701" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK701" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO701" t="inlineStr">
+        <is>
+          <t>Björklåga i uttorkad bäckfåra # Betula</t>
+        </is>
       </c>
       <c r="AT701" t="inlineStr"/>
       <c r="AW701" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX701" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY701" t="inlineStr">
@@ -79153,10 +79132,10 @@
     </row>
     <row r="702">
       <c r="A702" t="n">
-        <v>80987080</v>
+        <v>135422151</v>
       </c>
       <c r="B702" t="n">
-        <v>91905</v>
+        <v>87161</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -79164,37 +79143,37 @@
         </is>
       </c>
       <c r="E702" t="n">
-        <v>1108</v>
+        <v>249278</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Barrviolspindling</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Cortinarius harcynicus</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Pers.) M.M.Moser</t>
         </is>
       </c>
       <c r="I702" t="inlineStr"/>
       <c r="P702" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q702" t="n">
-        <v>607814</v>
+        <v>607924</v>
       </c>
       <c r="R702" t="n">
-        <v>7310183</v>
+        <v>7309606</v>
       </c>
       <c r="S702" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T702" t="inlineStr">
         <is>
@@ -79218,12 +79197,22 @@
       </c>
       <c r="Y702" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z702" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA702" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB702" t="inlineStr">
+        <is>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD702" t="b">
@@ -79234,26 +79223,35 @@
       </c>
       <c r="AG702" t="b">
         <v>0</v>
+      </c>
+      <c r="AI702" t="inlineStr">
+        <is>
+          <t>Örtrik granskog</t>
+        </is>
       </c>
       <c r="AT702" t="inlineStr"/>
       <c r="AW702" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX702" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY702" t="inlineStr"/>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY702" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="n">
-        <v>80987082</v>
+        <v>135385236</v>
       </c>
       <c r="B703" t="n">
-        <v>91905</v>
+        <v>79396</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -79261,37 +79259,37 @@
         </is>
       </c>
       <c r="E703" t="n">
-        <v>1108</v>
+        <v>260591</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I703" t="inlineStr"/>
       <c r="P703" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q703" t="n">
-        <v>607707</v>
+        <v>607717</v>
       </c>
       <c r="R703" t="n">
-        <v>7310262</v>
+        <v>7309995</v>
       </c>
       <c r="S703" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T703" t="inlineStr">
         <is>
@@ -79315,12 +79313,22 @@
       </c>
       <c r="Y703" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z703" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA703" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB703" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD703" t="b">
@@ -79335,22 +79343,26 @@
       <c r="AT703" t="inlineStr"/>
       <c r="AW703" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX703" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY703" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY703" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
-        <v>80987083</v>
+        <v>135385311</v>
       </c>
       <c r="B704" t="n">
-        <v>91905</v>
+        <v>79396</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -79358,37 +79370,37 @@
         </is>
       </c>
       <c r="E704" t="n">
-        <v>1108</v>
+        <v>260591</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I704" t="inlineStr"/>
       <c r="P704" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q704" t="n">
-        <v>607709</v>
+        <v>607861</v>
       </c>
       <c r="R704" t="n">
-        <v>7310293</v>
+        <v>7309816</v>
       </c>
       <c r="S704" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T704" t="inlineStr">
         <is>
@@ -79412,12 +79424,22 @@
       </c>
       <c r="Y704" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z704" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA704" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB704" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD704" t="b">
@@ -79432,22 +79454,26 @@
       <c r="AT704" t="inlineStr"/>
       <c r="AW704" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX704" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY704" t="inlineStr"/>
+          <t>Lina Hällström</t>
+        </is>
+      </c>
+      <c r="AY704" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="n">
-        <v>80987064</v>
+        <v>80987080</v>
       </c>
       <c r="B705" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -79455,21 +79481,21 @@
         </is>
       </c>
       <c r="E705" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I705" t="inlineStr"/>
@@ -79479,10 +79505,10 @@
         </is>
       </c>
       <c r="Q705" t="n">
-        <v>607818</v>
+        <v>607814</v>
       </c>
       <c r="R705" t="n">
-        <v>7310228</v>
+        <v>7310183</v>
       </c>
       <c r="S705" t="n">
         <v>10</v>
@@ -79541,10 +79567,10 @@
     </row>
     <row r="706">
       <c r="A706" t="n">
-        <v>80987115</v>
+        <v>80987082</v>
       </c>
       <c r="B706" t="n">
-        <v>83173</v>
+        <v>91905</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -79552,21 +79578,21 @@
         </is>
       </c>
       <c r="E706" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I706" t="inlineStr"/>
@@ -79576,10 +79602,10 @@
         </is>
       </c>
       <c r="Q706" t="n">
-        <v>607759</v>
+        <v>607707</v>
       </c>
       <c r="R706" t="n">
-        <v>7310182</v>
+        <v>7310262</v>
       </c>
       <c r="S706" t="n">
         <v>10</v>
@@ -79638,10 +79664,10 @@
     </row>
     <row r="707">
       <c r="A707" t="n">
-        <v>80987117</v>
+        <v>80987083</v>
       </c>
       <c r="B707" t="n">
-        <v>83173</v>
+        <v>91905</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -79649,21 +79675,21 @@
         </is>
       </c>
       <c r="E707" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I707" t="inlineStr"/>
@@ -79673,10 +79699,10 @@
         </is>
       </c>
       <c r="Q707" t="n">
-        <v>607751</v>
+        <v>607709</v>
       </c>
       <c r="R707" t="n">
-        <v>7310193</v>
+        <v>7310293</v>
       </c>
       <c r="S707" t="n">
         <v>10</v>
@@ -79735,32 +79761,32 @@
     </row>
     <row r="708">
       <c r="A708" t="n">
-        <v>80987066</v>
+        <v>80987064</v>
       </c>
       <c r="B708" t="n">
-        <v>92632</v>
+        <v>91909</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E708" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I708" t="inlineStr"/>
@@ -79770,10 +79796,10 @@
         </is>
       </c>
       <c r="Q708" t="n">
-        <v>607822</v>
+        <v>607818</v>
       </c>
       <c r="R708" t="n">
-        <v>7310199</v>
+        <v>7310228</v>
       </c>
       <c r="S708" t="n">
         <v>10</v>
@@ -79832,48 +79858,48 @@
     </row>
     <row r="709">
       <c r="A709" t="n">
-        <v>135351855</v>
+        <v>80987115</v>
       </c>
       <c r="B709" t="n">
-        <v>79373</v>
+        <v>83173</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E709" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G709" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I709" t="inlineStr"/>
       <c r="P709" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q709" t="n">
-        <v>607677</v>
+        <v>607759</v>
       </c>
       <c r="R709" t="n">
-        <v>7310726</v>
+        <v>7310182</v>
       </c>
       <c r="S709" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="T709" t="inlineStr">
         <is>
@@ -79897,22 +79923,12 @@
       </c>
       <c r="Y709" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="Z709" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA709" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="AB709" t="inlineStr">
-        <is>
-          <t>15:20</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD709" t="b">
@@ -79927,64 +79943,60 @@
       <c r="AT709" t="inlineStr"/>
       <c r="AW709" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX709" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY709" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="n">
-        <v>135382864</v>
+        <v>80987117</v>
       </c>
       <c r="B710" t="n">
-        <v>79373</v>
+        <v>83173</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E710" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I710" t="inlineStr"/>
       <c r="P710" t="inlineStr">
         <is>
-          <t>Laisdalen Päronberget, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q710" t="n">
-        <v>607670</v>
+        <v>607751</v>
       </c>
       <c r="R710" t="n">
-        <v>7310121</v>
+        <v>7310193</v>
       </c>
       <c r="S710" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T710" t="inlineStr">
         <is>
@@ -80008,22 +80020,12 @@
       </c>
       <c r="Y710" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z710" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA710" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB710" t="inlineStr">
-        <is>
-          <t>13:07</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD710" t="b">
@@ -80038,64 +80040,60 @@
       <c r="AT710" t="inlineStr"/>
       <c r="AW710" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX710" t="inlineStr">
         <is>
-          <t>Linda-Marie Grahn</t>
-        </is>
-      </c>
-      <c r="AY710" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="n">
-        <v>135385285</v>
+        <v>80987066</v>
       </c>
       <c r="B711" t="n">
-        <v>79373</v>
+        <v>92632</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E711" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I711" t="inlineStr"/>
       <c r="P711" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
+          <t>Veddeklinten, Pi lm</t>
         </is>
       </c>
       <c r="Q711" t="n">
-        <v>607756</v>
+        <v>607822</v>
       </c>
       <c r="R711" t="n">
-        <v>7310082</v>
+        <v>7310199</v>
       </c>
       <c r="S711" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T711" t="inlineStr">
         <is>
@@ -80119,22 +80117,12 @@
       </c>
       <c r="Y711" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="Z711" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AA711" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AB711" t="inlineStr">
-        <is>
-          <t>15:16</t>
+          <t>2019-08-19</t>
         </is>
       </c>
       <c r="AD711" t="b">
@@ -80149,64 +80137,60 @@
       <c r="AT711" t="inlineStr"/>
       <c r="AW711" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
+          <t>Sture Westerberg</t>
         </is>
       </c>
       <c r="AX711" t="inlineStr">
         <is>
-          <t>Lina Hällström</t>
-        </is>
-      </c>
-      <c r="AY711" t="inlineStr">
-        <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
-        </is>
-      </c>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="n">
-        <v>80987069</v>
+        <v>135351855</v>
       </c>
       <c r="B712" t="n">
-        <v>57953</v>
+        <v>79373</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E712" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I712" t="inlineStr"/>
       <c r="P712" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q712" t="n">
-        <v>607759</v>
+        <v>607677</v>
       </c>
       <c r="R712" t="n">
-        <v>7310308</v>
+        <v>7310726</v>
       </c>
       <c r="S712" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="T712" t="inlineStr">
         <is>
@@ -80230,12 +80214,22 @@
       </c>
       <c r="Y712" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="Z712" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA712" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AB712" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD712" t="b">
@@ -80250,66 +80244,61 @@
       <c r="AT712" t="inlineStr"/>
       <c r="AW712" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX712" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY712" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY712" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
-        <v>135382865</v>
+        <v>135382864</v>
       </c>
       <c r="B713" t="n">
-        <v>5181</v>
+        <v>79373</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E713" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G713" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I713" t="inlineStr"/>
-      <c r="J713" t="inlineStr"/>
-      <c r="K713" t="inlineStr"/>
-      <c r="L713" t="inlineStr"/>
-      <c r="M713" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N713" t="inlineStr"/>
       <c r="P713" t="inlineStr">
         <is>
           <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q713" t="n">
-        <v>607674</v>
+        <v>607670</v>
       </c>
       <c r="R713" t="n">
-        <v>7310117</v>
+        <v>7310121</v>
       </c>
       <c r="S713" t="n">
         <v>5</v>
@@ -80341,7 +80330,7 @@
       </c>
       <c r="Z713" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA713" t="inlineStr">
@@ -80351,7 +80340,7 @@
       </c>
       <c r="AB713" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD713" t="b">
@@ -80360,7 +80349,6 @@
       <c r="AE713" t="b">
         <v>0</v>
       </c>
-      <c r="AF713" t="inlineStr"/>
       <c r="AG713" t="b">
         <v>0</v>
       </c>
@@ -80383,56 +80371,48 @@
     </row>
     <row r="714">
       <c r="A714" t="n">
-        <v>135385195</v>
+        <v>135385285</v>
       </c>
       <c r="B714" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E714" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I714" t="inlineStr"/>
-      <c r="K714" t="inlineStr"/>
-      <c r="L714" t="inlineStr"/>
-      <c r="M714" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N714" t="inlineStr"/>
       <c r="P714" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_orto, Pi lm</t>
         </is>
       </c>
       <c r="Q714" t="n">
-        <v>608400</v>
+        <v>607756</v>
       </c>
       <c r="R714" t="n">
-        <v>7309309</v>
+        <v>7310082</v>
       </c>
       <c r="S714" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T714" t="inlineStr">
         <is>
@@ -80461,7 +80441,7 @@
       </c>
       <c r="Z714" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA714" t="inlineStr">
@@ -80471,7 +80451,7 @@
       </c>
       <c r="AB714" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD714" t="b">
@@ -80486,12 +80466,12 @@
       <c r="AT714" t="inlineStr"/>
       <c r="AW714" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AX714" t="inlineStr">
         <is>
-          <t>Isak Falk Eliasson</t>
+          <t>Lina Hällström</t>
         </is>
       </c>
       <c r="AY714" t="inlineStr">
@@ -80502,10 +80482,10 @@
     </row>
     <row r="715">
       <c r="A715" t="n">
-        <v>80987072</v>
+        <v>80987069</v>
       </c>
       <c r="B715" t="n">
-        <v>92208</v>
+        <v>57953</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -80513,21 +80493,21 @@
         </is>
       </c>
       <c r="E715" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I715" t="inlineStr"/>
@@ -80537,10 +80517,10 @@
         </is>
       </c>
       <c r="Q715" t="n">
-        <v>608406</v>
+        <v>607759</v>
       </c>
       <c r="R715" t="n">
-        <v>7309441</v>
+        <v>7310308</v>
       </c>
       <c r="S715" t="n">
         <v>10</v>
@@ -80599,48 +80579,57 @@
     </row>
     <row r="716">
       <c r="A716" t="n">
-        <v>80987076</v>
+        <v>135382865</v>
       </c>
       <c r="B716" t="n">
-        <v>79406</v>
+        <v>5181</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E716" t="n">
-        <v>864</v>
+        <v>100526</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I716" t="inlineStr"/>
+      <c r="J716" t="inlineStr"/>
+      <c r="K716" t="inlineStr"/>
+      <c r="L716" t="inlineStr"/>
+      <c r="M716" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N716" t="inlineStr"/>
       <c r="P716" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q716" t="n">
-        <v>608479</v>
+        <v>607674</v>
       </c>
       <c r="R716" t="n">
-        <v>7309341</v>
+        <v>7310117</v>
       </c>
       <c r="S716" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T716" t="inlineStr">
         <is>
@@ -80664,12 +80653,22 @@
       </c>
       <c r="Y716" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z716" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA716" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB716" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD716" t="b">
@@ -80678,28 +80677,33 @@
       <c r="AE716" t="b">
         <v>0</v>
       </c>
+      <c r="AF716" t="inlineStr"/>
       <c r="AG716" t="b">
         <v>0</v>
       </c>
       <c r="AT716" t="inlineStr"/>
       <c r="AW716" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AX716" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY716" t="inlineStr"/>
+          <t>Linda-Marie Grahn</t>
+        </is>
+      </c>
+      <c r="AY716" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="n">
-        <v>80987077</v>
+        <v>135385195</v>
       </c>
       <c r="B717" t="n">
-        <v>79406</v>
+        <v>57975</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -80707,37 +80711,45 @@
         </is>
       </c>
       <c r="E717" t="n">
-        <v>864</v>
+        <v>100109</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I717" t="inlineStr"/>
+      <c r="K717" t="inlineStr"/>
+      <c r="L717" t="inlineStr"/>
+      <c r="M717" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N717" t="inlineStr"/>
       <c r="P717" t="inlineStr">
         <is>
-          <t>Veddeklinten, Pi lm</t>
+          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
         </is>
       </c>
       <c r="Q717" t="n">
-        <v>608374</v>
+        <v>608400</v>
       </c>
       <c r="R717" t="n">
-        <v>7309488</v>
+        <v>7309309</v>
       </c>
       <c r="S717" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T717" t="inlineStr">
         <is>
@@ -80761,12 +80773,22 @@
       </c>
       <c r="Y717" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="Z717" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA717" t="inlineStr">
         <is>
-          <t>2019-08-19</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AB717" t="inlineStr">
+        <is>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD717" t="b">
@@ -80781,22 +80803,26 @@
       <c r="AT717" t="inlineStr"/>
       <c r="AW717" t="inlineStr">
         <is>
-          <t>Sture Westerberg</t>
+          <t>Isak Falk Eliasson</t>
         </is>
       </c>
       <c r="AX717" t="inlineStr">
         <is>
-          <t>Steve Daurer</t>
-        </is>
-      </c>
-      <c r="AY717" t="inlineStr"/>
+          <t>Isak Falk Eliasson</t>
+        </is>
+      </c>
+      <c r="AY717" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
-        <v>80987081</v>
+        <v>80987072</v>
       </c>
       <c r="B718" t="n">
-        <v>91905</v>
+        <v>92208</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -80804,21 +80830,21 @@
         </is>
       </c>
       <c r="E718" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I718" t="inlineStr"/>
@@ -80828,10 +80854,10 @@
         </is>
       </c>
       <c r="Q718" t="n">
-        <v>608446</v>
+        <v>608406</v>
       </c>
       <c r="R718" t="n">
-        <v>7309372</v>
+        <v>7309441</v>
       </c>
       <c r="S718" t="n">
         <v>10</v>
@@ -80890,10 +80916,10 @@
     </row>
     <row r="719">
       <c r="A719" t="n">
-        <v>80987060</v>
+        <v>80987076</v>
       </c>
       <c r="B719" t="n">
-        <v>91909</v>
+        <v>79406</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -80901,21 +80927,21 @@
         </is>
       </c>
       <c r="E719" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G719" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I719" t="inlineStr"/>
@@ -80925,10 +80951,10 @@
         </is>
       </c>
       <c r="Q719" t="n">
-        <v>608459</v>
+        <v>608479</v>
       </c>
       <c r="R719" t="n">
-        <v>7309372</v>
+        <v>7309341</v>
       </c>
       <c r="S719" t="n">
         <v>10</v>
@@ -80987,10 +81013,10 @@
     </row>
     <row r="720">
       <c r="A720" t="n">
-        <v>80987061</v>
+        <v>80987077</v>
       </c>
       <c r="B720" t="n">
-        <v>91909</v>
+        <v>79406</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -80998,21 +81024,21 @@
         </is>
       </c>
       <c r="E720" t="n">
-        <v>1202</v>
+        <v>864</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I720" t="inlineStr"/>
@@ -81022,10 +81048,10 @@
         </is>
       </c>
       <c r="Q720" t="n">
-        <v>608386</v>
+        <v>608374</v>
       </c>
       <c r="R720" t="n">
-        <v>7309399</v>
+        <v>7309488</v>
       </c>
       <c r="S720" t="n">
         <v>10</v>
@@ -81084,10 +81110,10 @@
     </row>
     <row r="721">
       <c r="A721" t="n">
-        <v>80987062</v>
+        <v>80987081</v>
       </c>
       <c r="B721" t="n">
-        <v>91909</v>
+        <v>91905</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -81095,21 +81121,21 @@
         </is>
       </c>
       <c r="E721" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I721" t="inlineStr"/>
@@ -81119,10 +81145,10 @@
         </is>
       </c>
       <c r="Q721" t="n">
-        <v>608403</v>
+        <v>608446</v>
       </c>
       <c r="R721" t="n">
-        <v>7309432</v>
+        <v>7309372</v>
       </c>
       <c r="S721" t="n">
         <v>10</v>
@@ -81181,7 +81207,7 @@
     </row>
     <row r="722">
       <c r="A722" t="n">
-        <v>80987063</v>
+        <v>80987060</v>
       </c>
       <c r="B722" t="n">
         <v>91909</v>
@@ -81216,10 +81242,10 @@
         </is>
       </c>
       <c r="Q722" t="n">
-        <v>608422</v>
+        <v>608459</v>
       </c>
       <c r="R722" t="n">
-        <v>7309394</v>
+        <v>7309372</v>
       </c>
       <c r="S722" t="n">
         <v>10</v>
@@ -81278,10 +81304,10 @@
     </row>
     <row r="723">
       <c r="A723" t="n">
-        <v>80987114</v>
+        <v>80987061</v>
       </c>
       <c r="B723" t="n">
-        <v>83173</v>
+        <v>91909</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -81289,21 +81315,21 @@
         </is>
       </c>
       <c r="E723" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I723" t="inlineStr"/>
@@ -81313,10 +81339,10 @@
         </is>
       </c>
       <c r="Q723" t="n">
-        <v>608390</v>
+        <v>608386</v>
       </c>
       <c r="R723" t="n">
-        <v>7309533</v>
+        <v>7309399</v>
       </c>
       <c r="S723" t="n">
         <v>10</v>
@@ -81375,32 +81401,32 @@
     </row>
     <row r="724">
       <c r="A724" t="n">
-        <v>80987067</v>
+        <v>80987062</v>
       </c>
       <c r="B724" t="n">
-        <v>92632</v>
+        <v>91909</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E724" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I724" t="inlineStr"/>
@@ -81410,10 +81436,10 @@
         </is>
       </c>
       <c r="Q724" t="n">
-        <v>608399</v>
+        <v>608403</v>
       </c>
       <c r="R724" t="n">
-        <v>7309450</v>
+        <v>7309432</v>
       </c>
       <c r="S724" t="n">
         <v>10</v>
@@ -81469,6 +81495,297 @@
         </is>
       </c>
       <c r="AY724" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" t="n">
+        <v>80987063</v>
+      </c>
+      <c r="B725" t="n">
+        <v>91909</v>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E725" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr"/>
+      <c r="P725" t="inlineStr">
+        <is>
+          <t>Veddeklinten, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q725" t="n">
+        <v>608422</v>
+      </c>
+      <c r="R725" t="n">
+        <v>7309394</v>
+      </c>
+      <c r="S725" t="n">
+        <v>10</v>
+      </c>
+      <c r="T725" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U725" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V725" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W725" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y725" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AA725" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AD725" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE725" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG725" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT725" t="inlineStr"/>
+      <c r="AW725" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX725" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY725" t="inlineStr"/>
+    </row>
+    <row r="726">
+      <c r="A726" t="n">
+        <v>80987114</v>
+      </c>
+      <c r="B726" t="n">
+        <v>83173</v>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E726" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr"/>
+      <c r="P726" t="inlineStr">
+        <is>
+          <t>Veddeklinten, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q726" t="n">
+        <v>608390</v>
+      </c>
+      <c r="R726" t="n">
+        <v>7309533</v>
+      </c>
+      <c r="S726" t="n">
+        <v>10</v>
+      </c>
+      <c r="T726" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U726" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V726" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W726" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y726" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AA726" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AD726" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE726" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG726" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT726" t="inlineStr"/>
+      <c r="AW726" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX726" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY726" t="inlineStr"/>
+    </row>
+    <row r="727">
+      <c r="A727" t="n">
+        <v>80987067</v>
+      </c>
+      <c r="B727" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E727" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr"/>
+      <c r="P727" t="inlineStr">
+        <is>
+          <t>Veddeklinten, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q727" t="n">
+        <v>608399</v>
+      </c>
+      <c r="R727" t="n">
+        <v>7309450</v>
+      </c>
+      <c r="S727" t="n">
+        <v>10</v>
+      </c>
+      <c r="T727" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U727" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="V727" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W727" t="inlineStr">
+        <is>
+          <t>Arjeplog</t>
+        </is>
+      </c>
+      <c r="Y727" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AA727" t="inlineStr">
+        <is>
+          <t>2019-08-19</t>
+        </is>
+      </c>
+      <c r="AD727" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE727" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG727" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT727" t="inlineStr"/>
+      <c r="AW727" t="inlineStr">
+        <is>
+          <t>Sture Westerberg</t>
+        </is>
+      </c>
+      <c r="AX727" t="inlineStr">
+        <is>
+          <t>Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY727" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -6874,9 +6874,12 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q58" t="n">
@@ -6934,6 +6937,7 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
+      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6948,7 +6952,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY58" t="inlineStr"/>
+      <c r="AY58" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8442,14 +8450,17 @@
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q71" t="n">
@@ -8521,7 +8532,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY71" t="inlineStr"/>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -73277,9 +73292,13 @@
         </is>
       </c>
       <c r="I650" t="inlineStr"/>
+      <c r="J650" t="inlineStr"/>
+      <c r="K650" t="inlineStr"/>
+      <c r="L650" t="inlineStr"/>
+      <c r="N650" t="inlineStr"/>
       <c r="P650" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q650" t="n">
@@ -73337,6 +73356,7 @@
       <c r="AE650" t="b">
         <v>0</v>
       </c>
+      <c r="AF650" t="inlineStr"/>
       <c r="AG650" t="b">
         <v>0</v>
       </c>
@@ -73351,7 +73371,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY650" t="inlineStr"/>
+      <c r="AY650" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -73505,9 +73529,13 @@
         </is>
       </c>
       <c r="I652" t="inlineStr"/>
+      <c r="J652" t="inlineStr"/>
+      <c r="K652" t="inlineStr"/>
+      <c r="L652" t="inlineStr"/>
+      <c r="N652" t="inlineStr"/>
       <c r="P652" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q652" t="n">
@@ -73565,6 +73593,7 @@
       <c r="AE652" t="b">
         <v>0</v>
       </c>
+      <c r="AF652" t="inlineStr"/>
       <c r="AG652" t="b">
         <v>0</v>
       </c>
@@ -73579,7 +73608,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY652" t="inlineStr"/>
+      <c r="AY652" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -75639,9 +75672,13 @@
       </c>
       <c r="H671" t="inlineStr"/>
       <c r="I671" t="inlineStr"/>
+      <c r="J671" t="inlineStr"/>
+      <c r="K671" t="inlineStr"/>
+      <c r="L671" t="inlineStr"/>
+      <c r="N671" t="inlineStr"/>
       <c r="P671" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q671" t="n">
@@ -75699,6 +75736,7 @@
       <c r="AE671" t="b">
         <v>0</v>
       </c>
+      <c r="AF671" t="inlineStr"/>
       <c r="AG671" t="b">
         <v>0</v>
       </c>
@@ -75713,7 +75751,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY671" t="inlineStr"/>
+      <c r="AY671" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
@@ -77909,9 +77951,13 @@
         </is>
       </c>
       <c r="I691" t="inlineStr"/>
+      <c r="J691" t="inlineStr"/>
+      <c r="K691" t="inlineStr"/>
+      <c r="L691" t="inlineStr"/>
+      <c r="N691" t="inlineStr"/>
       <c r="P691" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q691" t="n">
@@ -77969,6 +78015,7 @@
       <c r="AE691" t="b">
         <v>0</v>
       </c>
+      <c r="AF691" t="inlineStr"/>
       <c r="AG691" t="b">
         <v>0</v>
       </c>
@@ -77983,7 +78030,11 @@
           <t>Isak Falk Eliasson</t>
         </is>
       </c>
-      <c r="AY691" t="inlineStr"/>
+      <c r="AY691" t="inlineStr">
+        <is>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="n">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -18704,7 +18704,7 @@
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson , Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
@@ -34345,7 +34345,7 @@
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
@@ -37987,7 +37987,7 @@
       </c>
       <c r="AX334" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY334" t="inlineStr">
@@ -38320,7 +38320,7 @@
       </c>
       <c r="AX337" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY337" t="inlineStr">
@@ -46103,7 +46103,7 @@
       </c>
       <c r="AX407" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY407" t="inlineStr">
@@ -46214,7 +46214,7 @@
       </c>
       <c r="AX408" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY408" t="inlineStr">
@@ -49993,7 +49993,7 @@
       </c>
       <c r="AX442" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY442" t="inlineStr">
@@ -50104,7 +50104,7 @@
       </c>
       <c r="AX443" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY443" t="inlineStr">
@@ -50215,7 +50215,7 @@
       </c>
       <c r="AX444" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY444" t="inlineStr">
@@ -51263,7 +51263,7 @@
       </c>
       <c r="AX453" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY453" t="inlineStr">
@@ -52262,7 +52262,7 @@
       </c>
       <c r="AX462" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva, Maja Rancic, Torun Ingrid Maria Jacobsson, Mattias Dalkvist, Cecilia Goldkuhl, Linda-Marie Grahn</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY462" t="inlineStr">
@@ -54850,7 +54850,7 @@
       </c>
       <c r="AX484" t="inlineStr">
         <is>
-          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Linda  Hansson , Johan Råghall, Martin Axegård, Petya Valcheva</t>
+          <t>Tyr Nilsson, Linda-Marie Grahn, Cecilia Goldkuhl, Mattias Dalkvist, Torun Ingrid Maria Jacobsson, Maja Rancic, Petya Valcheva, Martin Axegård, Johan Råghall, Linda  Hansson</t>
         </is>
       </c>
       <c r="AY484" t="inlineStr">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY726"/>
+  <dimension ref="A1:AZ726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382792</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382849</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382856</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382857</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384234</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384235</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385147</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385148</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385226</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388256</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1893,6 +1948,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388260</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2004,6 +2064,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385153</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2115,6 +2180,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388254</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2212,6 +2282,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987065</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2324,6 +2399,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384225</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2431,6 +2511,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393109</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2542,6 +2627,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440290</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2653,6 +2743,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382845</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2750,6 +2845,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987122</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2861,6 +2961,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356136</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2972,6 +3077,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382843</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3083,6 +3193,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388250</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3194,6 +3309,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378144</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3305,6 +3425,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378147</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3416,6 +3541,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378156</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3527,6 +3657,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378158</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3638,6 +3773,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378162</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3749,6 +3889,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378168</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3860,6 +4005,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382839</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3971,6 +4121,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382853</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4082,6 +4237,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382858</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4193,6 +4353,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384223</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4304,6 +4469,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384230</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4415,6 +4585,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384236</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4526,6 +4701,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384237</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4637,6 +4817,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385151</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4748,6 +4933,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385156</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4855,6 +5045,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393097</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4962,6 +5157,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393098</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5069,6 +5269,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393101</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5176,6 +5381,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393102</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5287,6 +5497,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440288</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5403,6 +5618,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356134</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5514,6 +5734,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378145</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5625,6 +5850,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378149</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5736,6 +5966,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382793</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5847,6 +6082,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382794</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5958,6 +6198,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382795</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6069,6 +6314,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384227</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6180,6 +6430,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384232</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6291,6 +6546,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384238</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6402,6 +6662,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388255</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6513,6 +6778,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388257</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6620,6 +6890,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393105</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6731,6 +7006,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440284</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6840,6 +7120,11 @@
       <c r="AY57" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440285</t>
         </is>
       </c>
     </row>
@@ -6957,6 +7242,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135521526</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7068,6 +7358,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385154</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7184,6 +7479,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422122</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7305,6 +7605,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422125</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7426,6 +7731,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378148</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7547,6 +7857,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378152</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7668,6 +7983,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378155</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7804,6 +8124,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378167</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7940,6 +8265,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378169</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8056,6 +8386,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384239</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8175,6 +8510,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385152</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8294,6 +8634,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385155</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8418,6 +8763,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422128</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8537,6 +8887,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135521659</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8661,6 +9016,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382852</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8785,6 +9145,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382859</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8901,6 +9266,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388253</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9017,6 +9387,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422126</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9133,6 +9508,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388249</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9261,6 +9641,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356132</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9385,6 +9770,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356141</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9506,6 +9896,11 @@
       <c r="AY79" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382854</t>
         </is>
       </c>
     </row>
@@ -9625,6 +10020,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382851</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9732,6 +10132,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393108</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9848,6 +10253,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422123</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9959,6 +10369,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356130</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10070,6 +10485,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382846</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10181,6 +10601,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356131</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10297,6 +10722,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356139</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10408,6 +10838,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382842</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10519,6 +10954,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422127</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10630,6 +11070,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378151</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10741,6 +11186,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378157</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10852,6 +11302,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378159</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10963,6 +11418,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378164</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11072,6 +11532,11 @@
       <c r="AY93" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378166</t>
         </is>
       </c>
     </row>
@@ -11204,6 +11669,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388089</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11315,6 +11785,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385246</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11426,6 +11901,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385253</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11537,6 +12017,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378182</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11648,6 +12133,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378183</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11759,6 +12249,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378194</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11870,6 +12365,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385250</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11981,6 +12481,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440301</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12092,6 +12597,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440302</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12203,6 +12713,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378184</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12314,6 +12829,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378188</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12425,6 +12945,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378195</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12536,6 +13061,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385242</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12647,6 +13177,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385255</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12768,6 +13303,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378193</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12879,6 +13419,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378185</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12990,6 +13535,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378190</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13101,6 +13651,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378191</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13212,6 +13767,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378196</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13323,6 +13883,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385244</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13434,6 +13999,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385257</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13552,6 +14122,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135441451</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13661,6 +14236,11 @@
       <c r="AY116" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356147</t>
         </is>
       </c>
     </row>
@@ -13783,6 +14363,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351866</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13900,6 +14485,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388280</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14011,6 +14601,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385183</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14122,6 +14717,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385263</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14233,6 +14833,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388278</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14340,6 +14945,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393121</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14451,6 +15061,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440316</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14604,6 +15219,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440315</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14715,6 +15335,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356001</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14826,6 +15451,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356004</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14937,6 +15567,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356007</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15048,6 +15683,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382797</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15159,6 +15799,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382799</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15270,6 +15915,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382863</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15381,6 +16031,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382869</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15492,6 +16147,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382871</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15603,6 +16263,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384240</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15714,6 +16379,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384242</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15825,6 +16495,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384247</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15936,6 +16611,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384250</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16047,6 +16727,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384259</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16163,6 +16848,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384271</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16274,6 +16964,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384289</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16385,6 +17080,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384292</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16496,6 +17196,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384301</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16607,6 +17312,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384306</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16718,6 +17428,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385159</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16829,6 +17544,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385160</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16940,6 +17660,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385174</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -17051,6 +17776,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385179</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -17162,6 +17892,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385181</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -17273,6 +18008,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385186</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -17384,6 +18124,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385187</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -17495,6 +18240,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385274</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -17606,6 +18356,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388266</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17717,6 +18472,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388271</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17828,6 +18588,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388277</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17939,6 +18704,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388286</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -18050,6 +18820,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378203</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -18161,6 +18936,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385170</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -18272,6 +19052,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385278</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -18383,6 +19168,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385281</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -18494,6 +19284,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388265</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -18601,6 +19396,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393106</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18712,6 +19512,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355999</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18823,6 +19628,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385260</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18934,6 +19744,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385265</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -19045,6 +19860,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385271</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -19156,6 +19976,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388289</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -19267,6 +20092,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440306</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -19378,6 +20208,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440310</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -19489,6 +20324,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440313</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -19600,6 +20440,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388275</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19711,6 +20556,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351494</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19822,6 +20672,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382872</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19933,6 +20788,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382873</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -20044,6 +20904,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388268</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -20160,6 +21025,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385269</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -20271,6 +21141,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388288</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -20381,6 +21256,11 @@
       <c r="AY176" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385164</t>
         </is>
       </c>
     </row>
@@ -20498,6 +21378,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388281</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -20605,6 +21490,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393116</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20716,6 +21606,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382805</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20827,6 +21722,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382800</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20938,6 +21838,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382809</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -21049,6 +21954,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388276</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -21160,6 +22070,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349889</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -21271,6 +22186,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351847</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -21382,6 +22302,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351849</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -21493,6 +22418,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351856</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -21604,6 +22534,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351859</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21715,6 +22650,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356002</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21826,6 +22766,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357671</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21937,6 +22882,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357673</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -22048,6 +22998,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378201</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -22159,6 +23114,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378202</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -22270,6 +23230,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378211</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -22381,6 +23346,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378215</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -22492,6 +23462,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378216</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -22603,6 +23578,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378217</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22714,6 +23694,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378218</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22825,6 +23810,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384241</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22936,6 +23926,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384243</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -23047,6 +24042,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384244</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -23158,6 +24158,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384253</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -23269,6 +24274,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384255</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -23380,6 +24390,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384262</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -23491,6 +24506,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384274</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -23602,6 +24622,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384277</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -23713,6 +24738,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384282</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -23824,6 +24854,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384287</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23935,6 +24970,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384294</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -24046,6 +25086,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384296</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -24157,6 +25202,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384310</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -24268,6 +25318,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384313</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -24379,6 +25434,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385158</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -24490,6 +25550,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385175</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -24601,6 +25666,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385182</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -24712,6 +25782,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385192</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -24823,6 +25898,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385267</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24934,6 +26014,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385276</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -25045,6 +26130,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385283</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -25156,6 +26246,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388270</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -25267,6 +26362,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388274</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -25378,6 +26478,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388279</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -25489,6 +26594,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388282</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -25600,6 +26710,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388285</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -25711,6 +26826,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388292</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -25818,6 +26938,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393096</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25929,6 +27054,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440317</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -26036,6 +27166,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393099</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -26147,6 +27282,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356000</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -26258,6 +27398,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356003</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -26369,6 +27514,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356005</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -26480,6 +27630,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378198</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -26591,6 +27746,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378208</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -26702,6 +27862,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382796</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -26813,6 +27978,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382801</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -26924,6 +28094,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382802</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -27035,6 +28210,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382804</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -27146,6 +28326,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382807</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -27257,6 +28442,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382808</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -27368,6 +28558,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382810</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -27479,6 +28674,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384280</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -27590,6 +28790,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384308</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -27701,6 +28906,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385189</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -27812,6 +29022,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440308</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -27923,6 +29138,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385259</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -28044,6 +29264,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349888</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -28160,6 +29385,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351846</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -28279,6 +29509,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351854</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -28395,6 +29630,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356143</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -28511,6 +29751,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356144</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -28627,6 +29872,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358103</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -28746,6 +29996,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385178</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -28865,6 +30120,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385185</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -28986,6 +30246,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388284</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -29114,6 +30379,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354042</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -29237,6 +30507,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382867</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -29348,6 +30623,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385188</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -29464,6 +30744,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358108</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -29575,6 +30860,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440314</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -29686,6 +30976,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351853</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -29797,6 +31092,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358105</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -29908,6 +31208,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358106</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -30019,6 +31324,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358107</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -30126,6 +31436,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393104</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -30233,6 +31548,11 @@
         </is>
       </c>
       <c r="AY264" t="inlineStr"/>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393117</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -30344,6 +31664,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351858</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -30455,6 +31780,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351865</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -30566,6 +31896,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378197</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -30677,6 +32012,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ268" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378199</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -30788,6 +32128,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378204</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -30899,6 +32244,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378206</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -31010,6 +32360,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ271" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378209</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -31121,6 +32476,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ272" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378210</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -31232,6 +32592,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378214</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -31343,6 +32708,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385167</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -31454,6 +32824,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385168</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -31565,6 +32940,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385169</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -31674,6 +33054,11 @@
       <c r="AY277" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351803</t>
         </is>
       </c>
     </row>
@@ -31791,6 +33176,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355993</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -31911,6 +33301,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355968</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -32022,6 +33417,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ280" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358086</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -32133,6 +33533,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351469</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -32244,6 +33649,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351780</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -32355,6 +33765,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351789</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -32466,6 +33881,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ284" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351806</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -32577,6 +33997,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354060</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -32688,6 +34113,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388262</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -32799,6 +34229,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349819</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -32910,6 +34345,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351450</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -33021,6 +34461,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351463</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -33132,6 +34577,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351811</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -33243,6 +34693,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354052</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -33354,6 +34809,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354057</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -33465,6 +34925,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354065</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -33576,6 +35041,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354068</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -33687,6 +35157,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354076</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -33798,6 +35273,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354085</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -33909,6 +35389,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354104</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -34020,6 +35505,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355971</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -34131,6 +35621,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355973</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -34242,6 +35737,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355982</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -34353,6 +35853,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355998</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -34450,6 +35955,11 @@
         </is>
       </c>
       <c r="AY302" t="inlineStr"/>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987079</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -34561,6 +36071,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354091</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -34672,6 +36187,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349862</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -34783,6 +36303,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351749</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -34894,6 +36419,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ306" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351755</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -35005,6 +36535,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351760</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -35116,6 +36651,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351781</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -35227,6 +36767,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351788</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -35338,6 +36883,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ310" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351809</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -35449,6 +36999,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ311" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351831</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -35560,6 +37115,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354073</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -35671,6 +37231,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356831</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -35782,6 +37347,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ314" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351466</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -35893,6 +37463,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351807</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -35990,6 +37565,11 @@
         </is>
       </c>
       <c r="AY316" t="inlineStr"/>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987120</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -36101,6 +37681,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349818</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -36212,6 +37797,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349820</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -36323,6 +37913,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351455</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -36434,6 +38029,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354059</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -36545,6 +38145,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ321" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354063</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -36656,6 +38261,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354106</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -36767,6 +38377,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349834</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -36879,6 +38494,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351791</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -36990,6 +38610,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355992</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -37087,6 +38712,11 @@
         </is>
       </c>
       <c r="AY326" t="inlineStr"/>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987074</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -37198,6 +38828,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351464</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -37309,6 +38944,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351748</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -37420,6 +39060,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351490</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -37536,6 +39181,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351491</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -37662,6 +39312,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354094</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -37773,6 +39428,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354098</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -37884,6 +39544,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354100</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -37995,6 +39660,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355991</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -38106,6 +39776,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357665</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -38217,6 +39892,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ336" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351473</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -38328,6 +40008,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ337" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355983</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -38439,6 +40124,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ338" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358094</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -38550,6 +40240,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ339" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351457</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -38661,6 +40356,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ340" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351471</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -38772,6 +40472,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ341" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358076</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -38883,6 +40588,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ342" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388263</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -38994,6 +40704,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ343" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349829</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -39105,6 +40820,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ344" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349837</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -39216,6 +40936,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ345" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349838</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -39327,6 +41052,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ346" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349843</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -39438,6 +41168,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ347" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349844</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -39549,6 +41284,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ348" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349846</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -39660,6 +41400,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ349" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349848</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -39771,6 +41516,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ350" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349849</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -39882,6 +41632,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ351" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349853</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -39993,6 +41748,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ352" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349855</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -40104,6 +41864,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ353" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349858</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -40215,6 +41980,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ354" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349864</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -40326,6 +42096,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349865</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -40437,6 +42212,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349868</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -40548,6 +42328,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349870</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -40659,6 +42444,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349877</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -40770,6 +42560,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ359" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349882</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
@@ -40881,6 +42676,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351447</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -40992,6 +42792,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351448</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -41103,6 +42908,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351452</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -41214,6 +43024,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ363" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351453</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -41325,6 +43140,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ364" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351456</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -41436,6 +43256,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ365" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351458</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -41547,6 +43372,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ366" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351461</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -41658,6 +43488,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ367" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351465</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -41769,6 +43604,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ368" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351468</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -41880,6 +43720,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ369" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351741</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -41991,6 +43836,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ370" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351744</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -42102,6 +43952,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ371" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351747</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -42213,6 +44068,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ372" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351759</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -42324,6 +44184,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ373" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351765</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -42435,6 +44300,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ374" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351767</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -42546,6 +44416,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ375" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351769</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -42657,6 +44532,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ376" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351777</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -42768,6 +44648,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ377" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351783</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -42879,6 +44764,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ378" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351787</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -43003,6 +44893,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ379" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351790</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -43114,6 +45009,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ380" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351792</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -43225,6 +45125,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ381" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351794</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -43336,6 +45241,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ382" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351801</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
@@ -43447,6 +45357,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ383" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351802</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
@@ -43558,6 +45473,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ384" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351804</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -43669,6 +45589,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ385" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351808</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -43780,6 +45705,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ386" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351812</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -43891,6 +45821,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ387" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351824</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
@@ -44002,6 +45937,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ388" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351825</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -44113,6 +46053,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ389" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351826</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
@@ -44224,6 +46169,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ390" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351827</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
@@ -44335,6 +46285,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ391" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351828</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -44446,6 +46401,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ392" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351837</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -44557,6 +46517,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ393" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351839</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
@@ -44668,6 +46633,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ394" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351845</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
@@ -44779,6 +46749,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ395" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354048</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
@@ -44890,6 +46865,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ396" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354054</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -45001,6 +46981,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ397" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354056</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -45112,6 +47097,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ398" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354062</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -45223,6 +47213,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ399" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354064</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -45334,6 +47329,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ400" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354067</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
@@ -45445,6 +47445,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ401" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354070</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -45556,6 +47561,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ402" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354074</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
@@ -45667,6 +47677,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ403" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354077</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
@@ -45778,6 +47793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ404" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354079</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
@@ -45889,6 +47909,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ405" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354082</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
@@ -46000,6 +48025,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ406" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354103</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
@@ -46111,6 +48141,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ407" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355975</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
@@ -46222,6 +48257,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ408" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355978</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
@@ -46333,6 +48373,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ409" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355979</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
@@ -46444,6 +48489,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ410" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355980</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
@@ -46555,6 +48605,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ411" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355981</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
@@ -46666,6 +48721,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ412" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355984</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
@@ -46782,6 +48842,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ413" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355985</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
@@ -46893,6 +48958,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ414" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355995</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
@@ -47004,6 +49074,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ415" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356827</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
@@ -47115,6 +49190,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ416" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356828</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
@@ -47226,6 +49306,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ417" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357661</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
@@ -47337,6 +49422,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ418" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358079</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
@@ -47448,6 +49538,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ419" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358092</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
@@ -47559,6 +49654,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ420" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358098</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
@@ -47670,6 +49770,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ421" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388259</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
@@ -47781,6 +49886,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ422" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388261</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
@@ -47892,6 +50002,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ423" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355996</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
@@ -48003,6 +50118,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ424" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349814</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
@@ -48114,6 +50234,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ425" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349815</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
@@ -48225,6 +50350,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ426" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349823</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
@@ -48336,6 +50466,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ427" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349824</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
@@ -48447,6 +50582,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ428" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349831</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
@@ -48558,6 +50698,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ429" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349840</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
@@ -48669,6 +50814,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ430" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349850</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
@@ -48780,6 +50930,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ431" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349883</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
@@ -48891,6 +51046,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ432" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351460</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
@@ -49002,6 +51162,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ433" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351462</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
@@ -49113,6 +51278,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ434" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351751</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
@@ -49224,6 +51394,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ435" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351758</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
@@ -49335,6 +51510,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ436" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351770</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
@@ -49446,6 +51626,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ437" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351797</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
@@ -49557,6 +51742,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ438" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351842</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
@@ -49668,6 +51858,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ439" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354084</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
@@ -49779,6 +51974,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ440" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354105</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
@@ -49890,6 +52090,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ441" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355969</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
@@ -50001,6 +52206,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ442" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355976</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
@@ -50112,6 +52322,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ443" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355977</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
@@ -50223,6 +52438,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ444" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355986</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
@@ -50339,6 +52559,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ445" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351492</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
@@ -50465,6 +52690,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ446" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354096</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
@@ -50576,6 +52806,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ447" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354099</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
@@ -50692,6 +52927,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ448" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349875</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
@@ -50823,6 +53063,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351482</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
@@ -50934,6 +53179,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351483</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
@@ -51043,6 +53293,11 @@
       <c r="AY451" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ451" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351486</t>
         </is>
       </c>
     </row>
@@ -51160,6 +53415,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ452" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351774</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
@@ -51271,6 +53531,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ453" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355988</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
@@ -51382,6 +53647,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ454" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355994</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
@@ -51493,6 +53763,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ455" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351481</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
@@ -51604,6 +53879,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ456" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351487</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
@@ -51715,6 +53995,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ457" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354097</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
@@ -51826,6 +54111,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ458" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355990</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
@@ -51937,6 +54227,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ459" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351484</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
@@ -52048,6 +54343,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ460" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351485</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
@@ -52159,6 +54459,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ461" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354081</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
@@ -52270,6 +54575,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ462" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355987</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
@@ -52381,6 +54691,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ463" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358090</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
@@ -52492,6 +54807,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ464" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358091</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
@@ -52606,6 +54926,11 @@
       <c r="AY465" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ465" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349860</t>
         </is>
       </c>
     </row>
@@ -52728,6 +55053,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ466" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351754</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
@@ -52842,6 +55172,11 @@
       <c r="AY467" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+        </is>
+      </c>
+      <c r="AZ467" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354089</t>
         </is>
       </c>
     </row>
@@ -52959,6 +55294,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ468" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356818</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
@@ -53056,6 +55396,11 @@
         </is>
       </c>
       <c r="AY469" t="inlineStr"/>
+      <c r="AZ469" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987068</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
@@ -53177,6 +55522,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ470" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349833</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
@@ -53298,6 +55648,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ471" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349839</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
@@ -53419,6 +55774,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ472" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349847</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
@@ -53540,6 +55900,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ473" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349861</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
@@ -53661,6 +56026,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ474" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351480</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
@@ -53785,6 +56155,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ475" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351750</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
@@ -53909,6 +56284,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ476" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351762</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
@@ -54025,6 +56405,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ477" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351772</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
@@ -54149,6 +56534,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ478" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351778</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
@@ -54260,6 +56650,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ479" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351796</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
@@ -54371,6 +56766,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ480" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351799</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
@@ -54492,6 +56892,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ481" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354087</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
@@ -54613,6 +57018,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ482" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354088</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -54734,6 +57144,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ483" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354093</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
@@ -54858,6 +57273,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ484" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135355972</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
@@ -54955,6 +57375,11 @@
         </is>
       </c>
       <c r="AY485" t="inlineStr"/>
+      <c r="AZ485" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987070</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
@@ -55079,6 +57504,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ486" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351795</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -55195,6 +57625,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ487" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349836</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -55311,6 +57746,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ488" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351472</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -55422,6 +57862,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ489" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351446</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -55533,6 +57978,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ490" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351479</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -55649,6 +58099,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ491" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349830</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -55760,6 +58215,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ492" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351476</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -55871,6 +58331,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ493" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351752</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -55982,6 +58447,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ494" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358077</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -56093,6 +58563,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ495" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358087</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -56204,6 +58679,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ496" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351449</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -56315,6 +58795,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ497" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351477</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -56426,6 +58911,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ498" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357666</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -56537,6 +59027,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ499" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135357670</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -56648,6 +59143,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ500" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358081</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -56759,6 +59259,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ501" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358082</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -56870,6 +59375,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ502" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358085</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -56981,6 +59491,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ503" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358089</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -57097,6 +59612,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ504" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349874</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -57208,6 +59728,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ505" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351489</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -57319,6 +59844,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ506" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351743</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -57430,6 +59960,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ507" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351773</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -57541,6 +60076,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ508" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354090</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -57657,6 +60197,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ509" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356125</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -57768,6 +60313,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ510" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356126</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -57879,6 +60429,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ511" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358093</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -57990,6 +60545,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ512" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358096</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -58101,6 +60661,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ513" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358099</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -58212,6 +60777,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ514" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358100</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" t="n">
@@ -58323,6 +60893,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ515" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358101</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -58434,6 +61009,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ516" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358102</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -58545,6 +61125,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ517" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351475</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -58656,6 +61241,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ518" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349813</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -58767,6 +61357,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ519" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349816</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -58878,6 +61473,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ520" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349821</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -58989,6 +61589,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ521" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349826</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -59100,6 +61705,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ522" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349827</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -59211,6 +61821,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ523" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349832</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -59322,6 +61937,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ524" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349841</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" t="n">
@@ -59433,6 +62053,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ525" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349845</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -59544,6 +62169,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ526" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349851</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -59655,6 +62285,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ527" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349854</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -59766,6 +62401,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ528" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349856</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -59877,6 +62517,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ529" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349859</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -59988,6 +62633,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ530" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349869</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" t="n">
@@ -60099,6 +62749,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ531" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349873</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="n">
@@ -60210,6 +62865,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ532" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349876</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" t="n">
@@ -60321,6 +62981,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ533" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349878</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" t="n">
@@ -60432,6 +63097,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ534" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349880</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" t="n">
@@ -60543,6 +63213,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ535" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349884</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="n">
@@ -60654,6 +63329,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ536" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349885</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" t="n">
@@ -60765,6 +63445,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ537" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349886</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
@@ -60876,6 +63561,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ538" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349887</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="n">
@@ -60987,6 +63677,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ539" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351451</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="n">
@@ -61098,6 +63793,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ540" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351745</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="n">
@@ -61209,6 +63909,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ541" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351757</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" t="n">
@@ -61320,6 +64025,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ542" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351763</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" t="n">
@@ -61431,6 +64141,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ543" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351768</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" t="n">
@@ -61542,6 +64257,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ544" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351771</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" t="n">
@@ -61653,6 +64373,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ545" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351776</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
@@ -61764,6 +64489,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ546" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351784</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" t="n">
@@ -61875,6 +64605,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ547" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351798</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="n">
@@ -61986,6 +64721,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ548" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351800</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
@@ -62097,6 +64837,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ549" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351840</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="n">
@@ -62208,6 +64953,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ550" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354046</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="n">
@@ -62319,6 +65069,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ551" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354061</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" t="n">
@@ -62430,6 +65185,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ552" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354078</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" t="n">
@@ -62541,6 +65301,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ553" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354083</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" t="n">
@@ -62652,6 +65417,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ554" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358078</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" t="n">
@@ -62761,6 +65531,11 @@
       <c r="AY555" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ555" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351742</t>
         </is>
       </c>
     </row>
@@ -62902,6 +65677,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
         </is>
       </c>
+      <c r="AZ556" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135354071</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
@@ -63033,6 +65813,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ557" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422147</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" t="n">
@@ -63162,6 +65947,11 @@
       <c r="AY558" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ558" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422165</t>
         </is>
       </c>
     </row>
@@ -63279,6 +66069,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ559" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349920</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" t="n">
@@ -63390,6 +66185,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ560" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440323</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" t="n">
@@ -63487,6 +66287,11 @@
         </is>
       </c>
       <c r="AY561" t="inlineStr"/>
+      <c r="AZ561" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987073</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" t="n">
@@ -63598,6 +66403,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ562" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349899</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" t="n">
@@ -63705,6 +66515,11 @@
         </is>
       </c>
       <c r="AY563" t="inlineStr"/>
+      <c r="AZ563" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393122</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
@@ -63816,6 +66631,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ564" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385302</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="n">
@@ -63927,6 +66747,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ565" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385308</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" t="n">
@@ -64038,6 +66863,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ566" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385315</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" t="n">
@@ -64149,6 +66979,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ567" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385319</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
@@ -64246,6 +67081,11 @@
         </is>
       </c>
       <c r="AY568" t="inlineStr"/>
+      <c r="AZ568" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987078</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
@@ -64343,6 +67183,11 @@
         </is>
       </c>
       <c r="AY569" t="inlineStr"/>
+      <c r="AZ569" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987084</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
@@ -64454,6 +67299,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ570" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349895</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="n">
@@ -64565,6 +67415,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ571" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349906</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" t="n">
@@ -64676,6 +67531,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ572" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385306</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="n">
@@ -64787,6 +67647,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ573" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385240</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
@@ -64894,6 +67759,11 @@
         </is>
       </c>
       <c r="AY574" t="inlineStr"/>
+      <c r="AZ574" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393114</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
@@ -65005,6 +67875,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ575" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440300</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" t="n">
@@ -65112,6 +67987,11 @@
         </is>
       </c>
       <c r="AY576" t="inlineStr"/>
+      <c r="AZ576" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393138</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="n">
@@ -65219,6 +68099,11 @@
         </is>
       </c>
       <c r="AY577" t="inlineStr"/>
+      <c r="AZ577" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393158</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="n">
@@ -65316,6 +68201,11 @@
         </is>
       </c>
       <c r="AY578" t="inlineStr"/>
+      <c r="AZ578" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987116</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="n">
@@ -65413,6 +68303,11 @@
         </is>
       </c>
       <c r="AY579" t="inlineStr"/>
+      <c r="AZ579" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987118</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
@@ -65510,6 +68405,11 @@
         </is>
       </c>
       <c r="AY580" t="inlineStr"/>
+      <c r="AZ580" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987119</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" t="n">
@@ -65607,6 +68507,11 @@
         </is>
       </c>
       <c r="AY581" t="inlineStr"/>
+      <c r="AZ581" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987121</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" t="n">
@@ -65704,6 +68609,11 @@
         </is>
       </c>
       <c r="AY582" t="inlineStr"/>
+      <c r="AZ582" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987123</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" t="n">
@@ -65815,6 +68725,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ583" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382862</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
@@ -65926,6 +68841,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ584" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385323</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" t="n">
@@ -66052,6 +68972,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ585" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422133</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" t="n">
@@ -66178,6 +69103,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ586" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422136</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
@@ -66275,6 +69205,11 @@
         </is>
       </c>
       <c r="AY587" t="inlineStr"/>
+      <c r="AZ587" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987085</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" t="n">
@@ -66386,6 +69321,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ588" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349911</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" t="n">
@@ -66493,6 +69433,11 @@
         </is>
       </c>
       <c r="AY589" t="inlineStr"/>
+      <c r="AZ589" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393155</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
@@ -66604,6 +69549,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ590" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349919</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="n">
@@ -66715,6 +69665,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ591" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349892</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" t="n">
@@ -66826,6 +69781,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ592" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349905</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="n">
@@ -66935,6 +69895,11 @@
       <c r="AY593" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ593" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385238</t>
         </is>
       </c>
     </row>
@@ -67057,6 +70022,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ594" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388294</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="n">
@@ -67177,6 +70147,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ595" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388298</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" t="n">
@@ -67288,6 +70263,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ596" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349898</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" t="n">
@@ -67399,6 +70379,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ597" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349900</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="n">
@@ -67510,6 +70495,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ598" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349903</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" t="n">
@@ -67621,6 +70611,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ599" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349908</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
@@ -67732,6 +70727,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ600" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349917</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" t="n">
@@ -67843,6 +70843,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ601" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378171</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
@@ -67954,6 +70959,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ602" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378177</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
@@ -68065,6 +71075,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ603" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384317</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" t="n">
@@ -68176,6 +71191,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ604" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384321</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" t="n">
@@ -68287,6 +71307,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ605" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384326</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" t="n">
@@ -68398,6 +71423,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ606" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385234</t>
+        </is>
+      </c>
     </row>
     <row r="607">
       <c r="A607" t="n">
@@ -68509,6 +71539,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ607" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385291</t>
+        </is>
+      </c>
     </row>
     <row r="608">
       <c r="A608" t="n">
@@ -68620,6 +71655,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ608" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385299</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
@@ -68731,6 +71771,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ609" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385304</t>
+        </is>
+      </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
@@ -68842,6 +71887,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ610" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385313</t>
+        </is>
+      </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
@@ -68953,6 +72003,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ611" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385317</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="n">
@@ -69064,6 +72119,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ612" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385321</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -69175,6 +72235,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ613" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385325</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -69282,6 +72347,11 @@
         </is>
       </c>
       <c r="AY614" t="inlineStr"/>
+      <c r="AZ614" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393119</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -69389,6 +72459,11 @@
         </is>
       </c>
       <c r="AY615" t="inlineStr"/>
+      <c r="AZ615" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393137</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -69500,6 +72575,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ616" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422129</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -69611,6 +72691,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ617" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440298</t>
+        </is>
+      </c>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -69722,6 +72807,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ618" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378172</t>
+        </is>
+      </c>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -69833,6 +72923,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ619" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378176</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -69944,6 +73039,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ620" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385230</t>
+        </is>
+      </c>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -70055,6 +73155,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ621" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385287</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -70166,6 +73271,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ622" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385295</t>
+        </is>
+      </c>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -70273,6 +73383,11 @@
         </is>
       </c>
       <c r="AY623" t="inlineStr"/>
+      <c r="AZ623" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393123</t>
+        </is>
+      </c>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -70399,6 +73514,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ624" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422132</t>
+        </is>
+      </c>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -70510,6 +73630,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ625" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440297</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -70621,6 +73746,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ626" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385194</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -70737,6 +73867,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ627" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349918</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -70858,6 +73993,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ628" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349901</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
@@ -70979,6 +74119,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ629" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349904</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -71100,6 +74245,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ630" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378174</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -71221,6 +74371,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ631" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378178</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -71342,6 +74497,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ632" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378180</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -71458,6 +74618,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ633" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382861</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -71584,6 +74749,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ634" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422144</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -71681,6 +74851,11 @@
         </is>
       </c>
       <c r="AY635" t="inlineStr"/>
+      <c r="AZ635" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987071</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -71797,6 +74972,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ636" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385293</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -71908,6 +75088,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ637" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440320</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -72005,6 +75190,11 @@
         </is>
       </c>
       <c r="AY638" t="inlineStr"/>
+      <c r="AZ638" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987075</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -72121,6 +75311,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ639" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349897</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -72236,6 +75431,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ640" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422135</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
@@ -72347,6 +75547,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ641" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388293</t>
+        </is>
+      </c>
     </row>
     <row r="642">
       <c r="A642" t="n">
@@ -72463,6 +75668,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ642" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422161</t>
+        </is>
+      </c>
     </row>
     <row r="643">
       <c r="A643" t="n">
@@ -72574,6 +75784,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ643" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351869</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" t="n">
@@ -72699,6 +75914,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ644" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422162</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="n">
@@ -72810,6 +76030,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ645" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351871</t>
+        </is>
+      </c>
     </row>
     <row r="646">
       <c r="A646" t="n">
@@ -72921,6 +76146,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ646" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385327</t>
+        </is>
+      </c>
     </row>
     <row r="647">
       <c r="A647" t="n">
@@ -73028,6 +76258,11 @@
         </is>
       </c>
       <c r="AY647" t="inlineStr"/>
+      <c r="AZ647" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393145</t>
+        </is>
+      </c>
     </row>
     <row r="648">
       <c r="A648" t="n">
@@ -73144,6 +76379,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ648" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422156</t>
+        </is>
+      </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
@@ -73258,6 +76498,11 @@
       <c r="AY649" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ649" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422160</t>
         </is>
       </c>
     </row>
@@ -73376,6 +76621,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ650" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135523737</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" t="n">
@@ -73495,6 +76745,11 @@
       <c r="AY651" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ651" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422166</t>
         </is>
       </c>
     </row>
@@ -73613,6 +76868,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ652" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135523654</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
@@ -73729,6 +76989,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ653" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422142</t>
+        </is>
+      </c>
     </row>
     <row r="654">
       <c r="A654" t="n">
@@ -73836,6 +77101,11 @@
         </is>
       </c>
       <c r="AY654" t="inlineStr"/>
+      <c r="AZ654" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393157</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" t="n">
@@ -73952,6 +77222,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ655" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422154</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" t="n">
@@ -74068,6 +77343,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ656" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422169</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" t="n">
@@ -74175,6 +77455,11 @@
         </is>
       </c>
       <c r="AY657" t="inlineStr"/>
+      <c r="AZ657" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393151</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
@@ -74286,6 +77571,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ658" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351874</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
@@ -74404,6 +77694,11 @@
       <c r="AY659" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ659" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349921</t>
         </is>
       </c>
     </row>
@@ -74522,6 +77817,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ660" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349909</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
@@ -74633,6 +77933,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ661" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384319</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
@@ -74744,6 +78049,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ662" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135384324</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
@@ -74855,6 +78165,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ663" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388296</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" t="n">
@@ -74962,6 +78277,11 @@
         </is>
       </c>
       <c r="AY664" t="inlineStr"/>
+      <c r="AZ664" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393149</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
@@ -75073,6 +78393,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ665" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422137</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
@@ -75189,6 +78514,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ666" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422150</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" t="n">
@@ -75305,6 +78635,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ667" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422155</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" t="n">
@@ -75421,6 +78756,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ668" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422159</t>
+        </is>
+      </c>
     </row>
     <row r="669">
       <c r="A669" t="n">
@@ -75532,6 +78872,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ669" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135440319</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" t="n">
@@ -75642,6 +78987,11 @@
       <c r="AY670" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ670" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422167</t>
         </is>
       </c>
     </row>
@@ -75756,6 +79106,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ671" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135523644</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
@@ -75867,6 +79222,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ672" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385157</t>
+        </is>
+      </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
@@ -75978,6 +79338,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ673" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349896</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="n">
@@ -76089,6 +79454,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ674" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349910</t>
+        </is>
+      </c>
     </row>
     <row r="675">
       <c r="A675" t="n">
@@ -76200,6 +79570,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ675" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135356148</t>
+        </is>
+      </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
@@ -76307,6 +79682,11 @@
         </is>
       </c>
       <c r="AY676" t="inlineStr"/>
+      <c r="AZ676" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393154</t>
+        </is>
+      </c>
     </row>
     <row r="677">
       <c r="A677" t="n">
@@ -76437,6 +79817,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ677" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422138</t>
+        </is>
+      </c>
     </row>
     <row r="678">
       <c r="A678" t="n">
@@ -76567,6 +79952,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ678" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422163</t>
+        </is>
+      </c>
     </row>
     <row r="679">
       <c r="A679" t="n">
@@ -76697,6 +80087,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ679" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422168</t>
+        </is>
+      </c>
     </row>
     <row r="680">
       <c r="A680" t="n">
@@ -76804,6 +80199,11 @@
         </is>
       </c>
       <c r="AY680" t="inlineStr"/>
+      <c r="AZ680" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393126</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="n">
@@ -76915,6 +80315,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ681" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135388299</t>
+        </is>
+      </c>
     </row>
     <row r="682">
       <c r="A682" t="n">
@@ -77031,6 +80436,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ682" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422143</t>
+        </is>
+      </c>
     </row>
     <row r="683">
       <c r="A683" t="n">
@@ -77139,6 +80549,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ683" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351867</t>
+        </is>
+      </c>
     </row>
     <row r="684">
       <c r="A684" t="n">
@@ -77250,6 +80665,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ684" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135349891</t>
+        </is>
+      </c>
     </row>
     <row r="685">
       <c r="A685" t="n">
@@ -77357,6 +80777,11 @@
         </is>
       </c>
       <c r="AY685" t="inlineStr"/>
+      <c r="AZ685" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393129</t>
+        </is>
+      </c>
     </row>
     <row r="686">
       <c r="A686" t="n">
@@ -77464,6 +80889,11 @@
         </is>
       </c>
       <c r="AY686" t="inlineStr"/>
+      <c r="AZ686" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393131</t>
+        </is>
+      </c>
     </row>
     <row r="687">
       <c r="A687" t="n">
@@ -77571,6 +81001,11 @@
         </is>
       </c>
       <c r="AY687" t="inlineStr"/>
+      <c r="AZ687" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135393150</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="n">
@@ -77687,6 +81122,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ688" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422139</t>
+        </is>
+      </c>
     </row>
     <row r="689">
       <c r="A689" t="n">
@@ -77803,6 +81243,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ689" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422140</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="n">
@@ -77917,6 +81362,11 @@
       <c r="AY690" t="inlineStr">
         <is>
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
+        </is>
+      </c>
+      <c r="AZ690" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422152</t>
         </is>
       </c>
     </row>
@@ -78035,6 +81485,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ691" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135523597</t>
+        </is>
+      </c>
     </row>
     <row r="692">
       <c r="A692" t="n">
@@ -78146,6 +81601,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ692" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378173</t>
+        </is>
+      </c>
     </row>
     <row r="693">
       <c r="A693" t="n">
@@ -78257,6 +81717,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ693" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378175</t>
+        </is>
+      </c>
     </row>
     <row r="694">
       <c r="A694" t="n">
@@ -78368,6 +81833,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ694" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378179</t>
+        </is>
+      </c>
     </row>
     <row r="695">
       <c r="A695" t="n">
@@ -78479,6 +81949,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ695" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135378181</t>
+        </is>
+      </c>
     </row>
     <row r="696">
       <c r="A696" t="n">
@@ -78590,6 +82065,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ696" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385232</t>
+        </is>
+      </c>
     </row>
     <row r="697">
       <c r="A697" t="n">
@@ -78701,6 +82181,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ697" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385289</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="n">
@@ -78812,6 +82297,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ698" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385297</t>
+        </is>
+      </c>
     </row>
     <row r="699">
       <c r="A699" t="n">
@@ -78938,6 +82428,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ699" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422134</t>
+        </is>
+      </c>
     </row>
     <row r="700">
       <c r="A700" t="n">
@@ -79069,6 +82564,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ700" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422148</t>
+        </is>
+      </c>
     </row>
     <row r="701">
       <c r="A701" t="n">
@@ -79185,6 +82685,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ701" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135422151</t>
+        </is>
+      </c>
     </row>
     <row r="702">
       <c r="A702" t="n">
@@ -79296,6 +82801,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ702" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385236</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" t="n">
@@ -79407,6 +82917,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ703" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385311</t>
+        </is>
+      </c>
     </row>
     <row r="704">
       <c r="A704" t="n">
@@ -79504,6 +83019,11 @@
         </is>
       </c>
       <c r="AY704" t="inlineStr"/>
+      <c r="AZ704" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987080</t>
+        </is>
+      </c>
     </row>
     <row r="705">
       <c r="A705" t="n">
@@ -79601,6 +83121,11 @@
         </is>
       </c>
       <c r="AY705" t="inlineStr"/>
+      <c r="AZ705" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987082</t>
+        </is>
+      </c>
     </row>
     <row r="706">
       <c r="A706" t="n">
@@ -79698,6 +83223,11 @@
         </is>
       </c>
       <c r="AY706" t="inlineStr"/>
+      <c r="AZ706" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987083</t>
+        </is>
+      </c>
     </row>
     <row r="707">
       <c r="A707" t="n">
@@ -79795,6 +83325,11 @@
         </is>
       </c>
       <c r="AY707" t="inlineStr"/>
+      <c r="AZ707" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987064</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="n">
@@ -79892,6 +83427,11 @@
         </is>
       </c>
       <c r="AY708" t="inlineStr"/>
+      <c r="AZ708" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987115</t>
+        </is>
+      </c>
     </row>
     <row r="709">
       <c r="A709" t="n">
@@ -79989,6 +83529,11 @@
         </is>
       </c>
       <c r="AY709" t="inlineStr"/>
+      <c r="AZ709" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987117</t>
+        </is>
+      </c>
     </row>
     <row r="710">
       <c r="A710" t="n">
@@ -80086,6 +83631,11 @@
         </is>
       </c>
       <c r="AY710" t="inlineStr"/>
+      <c r="AZ710" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987066</t>
+        </is>
+      </c>
     </row>
     <row r="711">
       <c r="A711" t="n">
@@ -80197,6 +83747,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ711" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135351855</t>
+        </is>
+      </c>
     </row>
     <row r="712">
       <c r="A712" t="n">
@@ -80308,6 +83863,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ712" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382864</t>
+        </is>
+      </c>
     </row>
     <row r="713">
       <c r="A713" t="n">
@@ -80419,6 +83979,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ713" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385285</t>
+        </is>
+      </c>
     </row>
     <row r="714">
       <c r="A714" t="n">
@@ -80516,6 +84081,11 @@
         </is>
       </c>
       <c r="AY714" t="inlineStr"/>
+      <c r="AZ714" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987069</t>
+        </is>
+      </c>
     </row>
     <row r="715">
       <c r="A715" t="n">
@@ -80637,6 +84207,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ715" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135382865</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" t="n">
@@ -80756,6 +84331,11 @@
           <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
+      <c r="AZ716" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135385195</t>
+        </is>
+      </c>
     </row>
     <row r="717">
       <c r="A717" t="n">
@@ -80853,6 +84433,11 @@
         </is>
       </c>
       <c r="AY717" t="inlineStr"/>
+      <c r="AZ717" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987072</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" t="n">
@@ -80950,6 +84535,11 @@
         </is>
       </c>
       <c r="AY718" t="inlineStr"/>
+      <c r="AZ718" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987076</t>
+        </is>
+      </c>
     </row>
     <row r="719">
       <c r="A719" t="n">
@@ -81047,6 +84637,11 @@
         </is>
       </c>
       <c r="AY719" t="inlineStr"/>
+      <c r="AZ719" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987077</t>
+        </is>
+      </c>
     </row>
     <row r="720">
       <c r="A720" t="n">
@@ -81144,6 +84739,11 @@
         </is>
       </c>
       <c r="AY720" t="inlineStr"/>
+      <c r="AZ720" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987081</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="n">
@@ -81241,6 +84841,11 @@
         </is>
       </c>
       <c r="AY721" t="inlineStr"/>
+      <c r="AZ721" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987060</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="n">
@@ -81338,6 +84943,11 @@
         </is>
       </c>
       <c r="AY722" t="inlineStr"/>
+      <c r="AZ722" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987061</t>
+        </is>
+      </c>
     </row>
     <row r="723">
       <c r="A723" t="n">
@@ -81435,6 +85045,11 @@
         </is>
       </c>
       <c r="AY723" t="inlineStr"/>
+      <c r="AZ723" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987062</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" t="n">
@@ -81532,6 +85147,11 @@
         </is>
       </c>
       <c r="AY724" t="inlineStr"/>
+      <c r="AZ724" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987063</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" t="n">
@@ -81629,6 +85249,11 @@
         </is>
       </c>
       <c r="AY725" t="inlineStr"/>
+      <c r="AZ725" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987114</t>
+        </is>
+      </c>
     </row>
     <row r="726">
       <c r="A726" t="n">
@@ -81726,8 +85351,740 @@
         </is>
       </c>
       <c r="AY726" t="inlineStr"/>
+      <c r="AZ726" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80987067</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ268" r:id="rId267"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ269" r:id="rId268"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ270" r:id="rId269"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ271" r:id="rId270"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ272" r:id="rId271"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ273" r:id="rId272"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ274" r:id="rId273"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ275" r:id="rId274"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ276" r:id="rId275"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ277" r:id="rId276"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ278" r:id="rId277"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ279" r:id="rId278"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ280" r:id="rId279"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ281" r:id="rId280"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ282" r:id="rId281"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ283" r:id="rId282"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ284" r:id="rId283"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ285" r:id="rId284"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ286" r:id="rId285"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ287" r:id="rId286"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ288" r:id="rId287"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ289" r:id="rId288"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ290" r:id="rId289"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ291" r:id="rId290"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ292" r:id="rId291"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ293" r:id="rId292"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ294" r:id="rId293"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ295" r:id="rId294"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ296" r:id="rId295"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ297" r:id="rId296"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ298" r:id="rId297"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ299" r:id="rId298"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ300" r:id="rId299"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ301" r:id="rId300"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ302" r:id="rId301"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ303" r:id="rId302"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ304" r:id="rId303"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ305" r:id="rId304"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ306" r:id="rId305"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ307" r:id="rId306"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ308" r:id="rId307"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ309" r:id="rId308"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ310" r:id="rId309"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ311" r:id="rId310"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ312" r:id="rId311"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ313" r:id="rId312"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ314" r:id="rId313"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ315" r:id="rId314"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ316" r:id="rId315"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ317" r:id="rId316"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ318" r:id="rId317"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ319" r:id="rId318"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ320" r:id="rId319"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ321" r:id="rId320"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ322" r:id="rId321"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ323" r:id="rId322"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ324" r:id="rId323"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ325" r:id="rId324"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ326" r:id="rId325"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ327" r:id="rId326"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ328" r:id="rId327"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ329" r:id="rId328"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ330" r:id="rId329"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ331" r:id="rId330"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ332" r:id="rId331"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ333" r:id="rId332"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ334" r:id="rId333"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ335" r:id="rId334"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ336" r:id="rId335"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ337" r:id="rId336"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ338" r:id="rId337"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ339" r:id="rId338"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ340" r:id="rId339"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ341" r:id="rId340"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ342" r:id="rId341"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ343" r:id="rId342"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ344" r:id="rId343"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ345" r:id="rId344"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ346" r:id="rId345"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ347" r:id="rId346"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ348" r:id="rId347"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ349" r:id="rId348"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ350" r:id="rId349"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ351" r:id="rId350"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ352" r:id="rId351"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ353" r:id="rId352"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ354" r:id="rId353"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ355" r:id="rId354"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ356" r:id="rId355"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ357" r:id="rId356"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ358" r:id="rId357"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ359" r:id="rId358"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ360" r:id="rId359"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ361" r:id="rId360"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ362" r:id="rId361"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ363" r:id="rId362"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ364" r:id="rId363"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ365" r:id="rId364"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ366" r:id="rId365"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ367" r:id="rId366"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ368" r:id="rId367"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ369" r:id="rId368"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ370" r:id="rId369"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ371" r:id="rId370"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ372" r:id="rId371"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ373" r:id="rId372"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ374" r:id="rId373"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ375" r:id="rId374"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ376" r:id="rId375"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ377" r:id="rId376"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ378" r:id="rId377"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ379" r:id="rId378"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ380" r:id="rId379"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ381" r:id="rId380"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ382" r:id="rId381"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ383" r:id="rId382"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ384" r:id="rId383"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ385" r:id="rId384"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ386" r:id="rId385"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ387" r:id="rId386"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ388" r:id="rId387"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ389" r:id="rId388"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ390" r:id="rId389"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ391" r:id="rId390"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ392" r:id="rId391"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ393" r:id="rId392"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ394" r:id="rId393"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ395" r:id="rId394"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ396" r:id="rId395"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ397" r:id="rId396"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ398" r:id="rId397"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ399" r:id="rId398"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ400" r:id="rId399"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ401" r:id="rId400"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ402" r:id="rId401"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ403" r:id="rId402"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ404" r:id="rId403"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ405" r:id="rId404"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ406" r:id="rId405"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ407" r:id="rId406"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ408" r:id="rId407"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ409" r:id="rId408"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ410" r:id="rId409"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ411" r:id="rId410"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ412" r:id="rId411"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ413" r:id="rId412"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ414" r:id="rId413"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ415" r:id="rId414"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ416" r:id="rId415"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ417" r:id="rId416"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ418" r:id="rId417"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ419" r:id="rId418"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ420" r:id="rId419"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ421" r:id="rId420"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ422" r:id="rId421"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ423" r:id="rId422"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ424" r:id="rId423"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ425" r:id="rId424"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ426" r:id="rId425"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ427" r:id="rId426"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ428" r:id="rId427"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ429" r:id="rId428"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ430" r:id="rId429"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ431" r:id="rId430"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ432" r:id="rId431"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ433" r:id="rId432"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ434" r:id="rId433"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ435" r:id="rId434"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ436" r:id="rId435"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ437" r:id="rId436"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ438" r:id="rId437"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ439" r:id="rId438"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ440" r:id="rId439"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ441" r:id="rId440"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ442" r:id="rId441"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ443" r:id="rId442"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ444" r:id="rId443"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ445" r:id="rId444"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ446" r:id="rId445"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ447" r:id="rId446"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ448" r:id="rId447"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ449" r:id="rId448"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ450" r:id="rId449"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ451" r:id="rId450"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ452" r:id="rId451"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ453" r:id="rId452"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ454" r:id="rId453"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ455" r:id="rId454"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ456" r:id="rId455"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ457" r:id="rId456"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ458" r:id="rId457"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ459" r:id="rId458"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ460" r:id="rId459"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ461" r:id="rId460"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ462" r:id="rId461"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ463" r:id="rId462"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ464" r:id="rId463"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ465" r:id="rId464"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ466" r:id="rId465"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ467" r:id="rId466"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ468" r:id="rId467"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ469" r:id="rId468"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ470" r:id="rId469"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ471" r:id="rId470"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ472" r:id="rId471"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ473" r:id="rId472"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ474" r:id="rId473"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ475" r:id="rId474"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ476" r:id="rId475"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ477" r:id="rId476"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ478" r:id="rId477"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ479" r:id="rId478"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ480" r:id="rId479"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ481" r:id="rId480"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ482" r:id="rId481"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ483" r:id="rId482"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ484" r:id="rId483"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ485" r:id="rId484"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ486" r:id="rId485"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ487" r:id="rId486"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ488" r:id="rId487"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ489" r:id="rId488"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ490" r:id="rId489"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ491" r:id="rId490"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ492" r:id="rId491"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ493" r:id="rId492"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ494" r:id="rId493"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ495" r:id="rId494"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ496" r:id="rId495"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ497" r:id="rId496"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ498" r:id="rId497"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ499" r:id="rId498"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ500" r:id="rId499"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ501" r:id="rId500"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ502" r:id="rId501"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ503" r:id="rId502"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ504" r:id="rId503"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ505" r:id="rId504"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ506" r:id="rId505"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ507" r:id="rId506"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ508" r:id="rId507"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ509" r:id="rId508"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ510" r:id="rId509"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ511" r:id="rId510"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ512" r:id="rId511"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ513" r:id="rId512"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ514" r:id="rId513"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ515" r:id="rId514"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ516" r:id="rId515"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ517" r:id="rId516"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ518" r:id="rId517"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ519" r:id="rId518"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ520" r:id="rId519"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ521" r:id="rId520"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ522" r:id="rId521"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ523" r:id="rId522"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ524" r:id="rId523"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ525" r:id="rId524"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ526" r:id="rId525"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ527" r:id="rId526"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ528" r:id="rId527"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ529" r:id="rId528"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ530" r:id="rId529"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ531" r:id="rId530"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ532" r:id="rId531"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ533" r:id="rId532"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ534" r:id="rId533"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ535" r:id="rId534"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ536" r:id="rId535"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ537" r:id="rId536"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ538" r:id="rId537"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ539" r:id="rId538"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ540" r:id="rId539"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ541" r:id="rId540"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ542" r:id="rId541"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ543" r:id="rId542"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ544" r:id="rId543"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ545" r:id="rId544"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ546" r:id="rId545"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ547" r:id="rId546"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ548" r:id="rId547"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ549" r:id="rId548"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ550" r:id="rId549"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ551" r:id="rId550"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ552" r:id="rId551"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ553" r:id="rId552"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ554" r:id="rId553"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ555" r:id="rId554"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ556" r:id="rId555"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ557" r:id="rId556"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ558" r:id="rId557"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ559" r:id="rId558"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ560" r:id="rId559"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ561" r:id="rId560"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ562" r:id="rId561"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ563" r:id="rId562"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ564" r:id="rId563"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ565" r:id="rId564"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ566" r:id="rId565"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ567" r:id="rId566"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ568" r:id="rId567"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ569" r:id="rId568"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ570" r:id="rId569"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ571" r:id="rId570"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ572" r:id="rId571"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ573" r:id="rId572"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ574" r:id="rId573"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ575" r:id="rId574"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ576" r:id="rId575"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ577" r:id="rId576"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ578" r:id="rId577"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ579" r:id="rId578"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ580" r:id="rId579"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ581" r:id="rId580"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ582" r:id="rId581"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ583" r:id="rId582"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ584" r:id="rId583"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ585" r:id="rId584"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ586" r:id="rId585"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ587" r:id="rId586"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ588" r:id="rId587"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ589" r:id="rId588"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ590" r:id="rId589"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ591" r:id="rId590"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ592" r:id="rId591"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ593" r:id="rId592"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ594" r:id="rId593"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ595" r:id="rId594"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ596" r:id="rId595"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ597" r:id="rId596"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ598" r:id="rId597"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ599" r:id="rId598"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ600" r:id="rId599"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ601" r:id="rId600"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ602" r:id="rId601"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ603" r:id="rId602"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ604" r:id="rId603"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ605" r:id="rId604"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ606" r:id="rId605"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ607" r:id="rId606"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ608" r:id="rId607"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ609" r:id="rId608"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ610" r:id="rId609"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ611" r:id="rId610"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ612" r:id="rId611"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ613" r:id="rId612"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ614" r:id="rId613"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ615" r:id="rId614"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ616" r:id="rId615"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ617" r:id="rId616"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ618" r:id="rId617"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ619" r:id="rId618"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ620" r:id="rId619"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ621" r:id="rId620"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ622" r:id="rId621"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ623" r:id="rId622"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ624" r:id="rId623"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ625" r:id="rId624"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ626" r:id="rId625"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ627" r:id="rId626"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ628" r:id="rId627"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ629" r:id="rId628"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ630" r:id="rId629"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ631" r:id="rId630"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ632" r:id="rId631"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ633" r:id="rId632"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ634" r:id="rId633"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ635" r:id="rId634"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ636" r:id="rId635"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ637" r:id="rId636"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ638" r:id="rId637"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ639" r:id="rId638"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ640" r:id="rId639"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ641" r:id="rId640"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ642" r:id="rId641"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ643" r:id="rId642"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ644" r:id="rId643"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ645" r:id="rId644"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ646" r:id="rId645"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ647" r:id="rId646"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ648" r:id="rId647"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ649" r:id="rId648"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ650" r:id="rId649"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ651" r:id="rId650"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ652" r:id="rId651"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ653" r:id="rId652"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ654" r:id="rId653"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ655" r:id="rId654"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ656" r:id="rId655"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ657" r:id="rId656"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ658" r:id="rId657"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ659" r:id="rId658"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ660" r:id="rId659"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ661" r:id="rId660"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ662" r:id="rId661"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ663" r:id="rId662"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ664" r:id="rId663"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ665" r:id="rId664"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ666" r:id="rId665"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ667" r:id="rId666"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ668" r:id="rId667"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ669" r:id="rId668"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ670" r:id="rId669"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ671" r:id="rId670"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ672" r:id="rId671"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ673" r:id="rId672"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ674" r:id="rId673"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ675" r:id="rId674"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ676" r:id="rId675"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ677" r:id="rId676"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ678" r:id="rId677"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ679" r:id="rId678"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ680" r:id="rId679"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ681" r:id="rId680"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ682" r:id="rId681"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ683" r:id="rId682"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ684" r:id="rId683"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ685" r:id="rId684"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ686" r:id="rId685"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ687" r:id="rId686"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ688" r:id="rId687"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ689" r:id="rId688"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ690" r:id="rId689"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ691" r:id="rId690"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ692" r:id="rId691"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ693" r:id="rId692"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ694" r:id="rId693"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ695" r:id="rId694"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ696" r:id="rId695"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ697" r:id="rId696"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ698" r:id="rId697"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ699" r:id="rId698"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ700" r:id="rId699"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ701" r:id="rId700"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ702" r:id="rId701"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ703" r:id="rId702"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ704" r:id="rId703"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ705" r:id="rId704"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ706" r:id="rId705"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ707" r:id="rId706"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ708" r:id="rId707"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ709" r:id="rId708"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ710" r:id="rId709"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ711" r:id="rId710"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ712" r:id="rId711"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ713" r:id="rId712"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ714" r:id="rId713"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ715" r:id="rId714"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ716" r:id="rId715"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ717" r:id="rId716"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ718" r:id="rId717"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ719" r:id="rId718"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ720" r:id="rId719"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ721" r:id="rId720"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ722" r:id="rId721"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ723" r:id="rId722"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ724" r:id="rId723"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ725" r:id="rId724"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ726" r:id="rId725"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -30376,7 +30376,7 @@
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
@@ -33994,7 +33994,7 @@
       </c>
       <c r="AY285" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ285" t="inlineStr">
@@ -34690,7 +34690,7 @@
       </c>
       <c r="AY291" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ291" t="inlineStr">
@@ -34806,7 +34806,7 @@
       </c>
       <c r="AY292" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ292" t="inlineStr">
@@ -34922,7 +34922,7 @@
       </c>
       <c r="AY293" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ293" t="inlineStr">
@@ -35038,7 +35038,7 @@
       </c>
       <c r="AY294" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ294" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="AY295" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ295" t="inlineStr">
@@ -35270,7 +35270,7 @@
       </c>
       <c r="AY296" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ296" t="inlineStr">
@@ -35386,7 +35386,7 @@
       </c>
       <c r="AY297" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ297" t="inlineStr">
@@ -36068,7 +36068,7 @@
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
@@ -37112,7 +37112,7 @@
       </c>
       <c r="AY312" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ312" t="inlineStr">
@@ -38026,7 +38026,7 @@
       </c>
       <c r="AY320" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ320" t="inlineStr">
@@ -38142,7 +38142,7 @@
       </c>
       <c r="AY321" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ321" t="inlineStr">
@@ -38258,7 +38258,7 @@
       </c>
       <c r="AY322" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ322" t="inlineStr">
@@ -39309,7 +39309,7 @@
       </c>
       <c r="AY331" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ331" t="inlineStr">
@@ -39425,7 +39425,7 @@
       </c>
       <c r="AY332" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ332" t="inlineStr">
@@ -39541,7 +39541,7 @@
       </c>
       <c r="AY333" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ333" t="inlineStr">
@@ -46746,7 +46746,7 @@
       </c>
       <c r="AY395" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ395" t="inlineStr">
@@ -46862,7 +46862,7 @@
       </c>
       <c r="AY396" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ396" t="inlineStr">
@@ -46978,7 +46978,7 @@
       </c>
       <c r="AY397" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ397" t="inlineStr">
@@ -47094,7 +47094,7 @@
       </c>
       <c r="AY398" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ398" t="inlineStr">
@@ -47210,7 +47210,7 @@
       </c>
       <c r="AY399" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ399" t="inlineStr">
@@ -47326,7 +47326,7 @@
       </c>
       <c r="AY400" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ400" t="inlineStr">
@@ -47442,7 +47442,7 @@
       </c>
       <c r="AY401" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ401" t="inlineStr">
@@ -47558,7 +47558,7 @@
       </c>
       <c r="AY402" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ402" t="inlineStr">
@@ -47674,7 +47674,7 @@
       </c>
       <c r="AY403" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ403" t="inlineStr">
@@ -47790,7 +47790,7 @@
       </c>
       <c r="AY404" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ404" t="inlineStr">
@@ -47906,7 +47906,7 @@
       </c>
       <c r="AY405" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ405" t="inlineStr">
@@ -48022,7 +48022,7 @@
       </c>
       <c r="AY406" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ406" t="inlineStr">
@@ -51855,7 +51855,7 @@
       </c>
       <c r="AY439" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ439" t="inlineStr">
@@ -51971,7 +51971,7 @@
       </c>
       <c r="AY440" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ440" t="inlineStr">
@@ -52687,7 +52687,7 @@
       </c>
       <c r="AY446" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ446" t="inlineStr">
@@ -52803,7 +52803,7 @@
       </c>
       <c r="AY447" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ447" t="inlineStr">
@@ -53992,7 +53992,7 @@
       </c>
       <c r="AY457" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ457" t="inlineStr">
@@ -54456,7 +54456,7 @@
       </c>
       <c r="AY461" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ461" t="inlineStr">
@@ -55171,7 +55171,7 @@
       </c>
       <c r="AY467" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ467" t="inlineStr">
@@ -56889,7 +56889,7 @@
       </c>
       <c r="AY481" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ481" t="inlineStr">
@@ -57015,7 +57015,7 @@
       </c>
       <c r="AY482" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ482" t="inlineStr">
@@ -57141,7 +57141,7 @@
       </c>
       <c r="AY483" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ483" t="inlineStr">
@@ -60073,7 +60073,7 @@
       </c>
       <c r="AY508" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ508" t="inlineStr">
@@ -64950,7 +64950,7 @@
       </c>
       <c r="AY550" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ550" t="inlineStr">
@@ -65066,7 +65066,7 @@
       </c>
       <c r="AY551" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ551" t="inlineStr">
@@ -65182,7 +65182,7 @@
       </c>
       <c r="AY552" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ552" t="inlineStr">
@@ -65298,7 +65298,7 @@
       </c>
       <c r="AY553" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ553" t="inlineStr">
@@ -65674,7 +65674,7 @@
       </c>
       <c r="AY556" t="inlineStr">
         <is>
-          <t>Forskningsresan i Naturvårdens Utmarker 2018 Jämtland</t>
+          <t>Forskningsresan i Naturvårdens Utmarker 2026 i Norrbottens län</t>
         </is>
       </c>
       <c r="AZ556" t="inlineStr">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -1407,7 +1407,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1523,7 +1523,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1987,7 +1987,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -4740,7 +4740,7 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q37" t="n">
@@ -4856,7 +4856,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q38" t="n">
@@ -7281,7 +7281,7 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -8433,7 +8433,7 @@
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q68" t="n">
@@ -8557,7 +8557,7 @@
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q69" t="n">
@@ -11576,7 +11576,7 @@
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q94" t="n">
@@ -14524,7 +14524,7 @@
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q119" t="n">
@@ -17351,7 +17351,7 @@
       <c r="I143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q143" t="n">
@@ -17467,7 +17467,7 @@
       <c r="I144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q144" t="n">
@@ -17583,7 +17583,7 @@
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q145" t="n">
@@ -17699,7 +17699,7 @@
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q146" t="n">
@@ -17815,7 +17815,7 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
@@ -17931,7 +17931,7 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
@@ -18047,7 +18047,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q149" t="n">
@@ -18859,7 +18859,7 @@
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q156" t="n">
@@ -21180,7 +21180,7 @@
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q176" t="n">
@@ -25357,7 +25357,7 @@
       <c r="I212" t="inlineStr"/>
       <c r="P212" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q212" t="n">
@@ -25473,7 +25473,7 @@
       <c r="I213" t="inlineStr"/>
       <c r="P213" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q213" t="n">
@@ -25589,7 +25589,7 @@
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
@@ -25705,7 +25705,7 @@
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q215" t="n">
@@ -28829,7 +28829,7 @@
       <c r="I242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q242" t="n">
@@ -29919,7 +29919,7 @@
       <c r="N251" t="inlineStr"/>
       <c r="P251" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q251" t="n">
@@ -30043,7 +30043,7 @@
       <c r="N252" t="inlineStr"/>
       <c r="P252" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q252" t="n">
@@ -30546,7 +30546,7 @@
       <c r="I256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q256" t="n">
@@ -32631,7 +32631,7 @@
       <c r="I274" t="inlineStr"/>
       <c r="P274" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q274" t="n">
@@ -32747,7 +32747,7 @@
       <c r="I275" t="inlineStr"/>
       <c r="P275" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q275" t="n">
@@ -32863,7 +32863,7 @@
       <c r="I276" t="inlineStr"/>
       <c r="P276" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q276" t="n">
@@ -33525,7 +33525,7 @@
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
@@ -39052,7 +39052,7 @@
       </c>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr">
@@ -39173,7 +39173,7 @@
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
@@ -43596,7 +43596,7 @@
       </c>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
@@ -53055,7 +53055,7 @@
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr">
@@ -53871,7 +53871,7 @@
       </c>
       <c r="AX456" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
         </is>
       </c>
       <c r="AY456" t="inlineStr">
@@ -56018,7 +56018,7 @@
       </c>
       <c r="AX474" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
         </is>
       </c>
       <c r="AY474" t="inlineStr">
@@ -57970,7 +57970,7 @@
       </c>
       <c r="AX490" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY490" t="inlineStr">
@@ -58207,7 +58207,7 @@
       </c>
       <c r="AX492" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY492" t="inlineStr">
@@ -58787,7 +58787,7 @@
       </c>
       <c r="AX497" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY497" t="inlineStr">
@@ -73669,7 +73669,7 @@
       <c r="I626" t="inlineStr"/>
       <c r="P626" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q626" t="n">
@@ -77746,7 +77746,7 @@
         <v>608014</v>
       </c>
       <c r="R660" t="n">
-        <v>7309639</v>
+        <v>7309638</v>
       </c>
       <c r="S660" t="n">
         <v>3</v>
@@ -79145,7 +79145,7 @@
       <c r="I672" t="inlineStr"/>
       <c r="P672" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q672" t="n">
@@ -79384,7 +79384,7 @@
         <v>608014</v>
       </c>
       <c r="R674" t="n">
-        <v>7309639</v>
+        <v>7309638</v>
       </c>
       <c r="S674" t="n">
         <v>3</v>
@@ -84254,7 +84254,7 @@
       <c r="N716" t="inlineStr"/>
       <c r="P716" t="inlineStr">
         <is>
-          <t>Tors Gr 4_Laisdalen Päronberget_topo, Pi lm</t>
+          <t>Laisdalen Päronberget, Pi lm</t>
         </is>
       </c>
       <c r="Q716" t="n">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -33525,7 +33525,7 @@
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
@@ -39052,7 +39052,7 @@
       </c>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr">
@@ -39173,7 +39173,7 @@
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
@@ -43596,7 +43596,7 @@
       </c>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
@@ -53055,7 +53055,7 @@
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr">
@@ -53871,7 +53871,7 @@
       </c>
       <c r="AX456" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY456" t="inlineStr">
@@ -56018,7 +56018,7 @@
       </c>
       <c r="AX474" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY474" t="inlineStr">
@@ -57970,7 +57970,7 @@
       </c>
       <c r="AX490" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY490" t="inlineStr">
@@ -58207,7 +58207,7 @@
       </c>
       <c r="AX492" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY492" t="inlineStr">
@@ -58787,7 +58787,7 @@
       </c>
       <c r="AX497" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY497" t="inlineStr">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -34337,7 +34337,7 @@
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
@@ -34453,7 +34453,7 @@
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
@@ -38820,7 +38820,7 @@
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr">
@@ -39884,7 +39884,7 @@
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr">
@@ -40232,7 +40232,7 @@
       </c>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr">
@@ -40348,7 +40348,7 @@
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr">
@@ -42668,7 +42668,7 @@
       </c>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr">
@@ -42784,7 +42784,7 @@
       </c>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr">
@@ -42900,7 +42900,7 @@
       </c>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
@@ -43016,7 +43016,7 @@
       </c>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr">
@@ -43248,7 +43248,7 @@
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
@@ -43364,7 +43364,7 @@
       </c>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
@@ -43480,7 +43480,7 @@
       </c>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
@@ -51038,7 +51038,7 @@
       </c>
       <c r="AX432" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY432" t="inlineStr">
@@ -51154,7 +51154,7 @@
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr">
@@ -52551,7 +52551,7 @@
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr">
@@ -53171,7 +53171,7 @@
       </c>
       <c r="AX450" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY450" t="inlineStr">
@@ -54219,7 +54219,7 @@
       </c>
       <c r="AX459" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY459" t="inlineStr">
@@ -54335,7 +54335,7 @@
       </c>
       <c r="AX460" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY460" t="inlineStr">
@@ -57738,7 +57738,7 @@
       </c>
       <c r="AX488" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY488" t="inlineStr">
@@ -57854,7 +57854,7 @@
       </c>
       <c r="AX489" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY489" t="inlineStr">
@@ -61117,7 +61117,7 @@
       </c>
       <c r="AX517" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY517" t="inlineStr">
@@ -63669,7 +63669,7 @@
       </c>
       <c r="AX539" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
+          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY539" t="inlineStr">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135382792</v>
       </c>
       <c r="B2" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135382849</v>
       </c>
       <c r="B3" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135382856</v>
       </c>
       <c r="B4" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135382857</v>
       </c>
       <c r="B5" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135384234</v>
       </c>
       <c r="B6" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135384235</v>
       </c>
       <c r="B7" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135385147</v>
       </c>
       <c r="B8" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135385148</v>
       </c>
       <c r="B9" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135385226</v>
       </c>
       <c r="B10" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135388256</v>
       </c>
       <c r="B11" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135388260</v>
       </c>
       <c r="B12" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135385153</v>
       </c>
       <c r="B13" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135388254</v>
       </c>
       <c r="B14" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>135384225</v>
       </c>
       <c r="B16" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135393109</v>
       </c>
       <c r="B17" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>135440290</v>
       </c>
       <c r="B18" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>135382845</v>
       </c>
       <c r="B19" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>135356136</v>
       </c>
       <c r="B21" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>135382843</v>
       </c>
       <c r="B22" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>135388250</v>
       </c>
       <c r="B23" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>135378144</v>
       </c>
       <c r="B24" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>135378147</v>
       </c>
       <c r="B25" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>135378156</v>
       </c>
       <c r="B26" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>135378158</v>
       </c>
       <c r="B27" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>135378162</v>
       </c>
       <c r="B28" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>135378168</v>
       </c>
       <c r="B29" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>135382839</v>
       </c>
       <c r="B30" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>135382853</v>
       </c>
       <c r="B31" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>135382858</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>135384223</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>135384230</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>135384236</v>
       </c>
       <c r="B35" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>135384237</v>
       </c>
       <c r="B36" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>135385151</v>
       </c>
       <c r="B37" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>135385156</v>
       </c>
       <c r="B38" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>135393097</v>
       </c>
       <c r="B39" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>135393098</v>
       </c>
       <c r="B40" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>135393101</v>
       </c>
       <c r="B41" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>135393102</v>
       </c>
       <c r="B42" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>135440288</v>
       </c>
       <c r="B43" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>135356134</v>
       </c>
       <c r="B44" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>135378145</v>
       </c>
       <c r="B45" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>135378149</v>
       </c>
       <c r="B46" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>135382793</v>
       </c>
       <c r="B47" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>135382794</v>
       </c>
       <c r="B48" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>135382795</v>
       </c>
       <c r="B49" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>135384227</v>
       </c>
       <c r="B50" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>135384232</v>
       </c>
       <c r="B51" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>135384238</v>
       </c>
       <c r="B52" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>135388255</v>
       </c>
       <c r="B53" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>135388257</v>
       </c>
       <c r="B54" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>135393105</v>
       </c>
       <c r="B55" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>135440284</v>
       </c>
       <c r="B56" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>135440285</v>
       </c>
       <c r="B57" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>135521526</v>
       </c>
       <c r="B58" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>135385154</v>
       </c>
       <c r="B59" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>135422122</v>
       </c>
       <c r="B60" t="n">
-        <v>80492</v>
+        <v>80530</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>135422125</v>
       </c>
       <c r="B61" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>135378148</v>
       </c>
       <c r="B62" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>135378152</v>
       </c>
       <c r="B63" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7868,7 +7868,7 @@
         <v>135378155</v>
       </c>
       <c r="B64" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7994,7 +7994,7 @@
         <v>135378167</v>
       </c>
       <c r="B65" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         <v>135378169</v>
       </c>
       <c r="B66" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>135384239</v>
       </c>
       <c r="B67" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>135385152</v>
       </c>
       <c r="B68" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>135385155</v>
       </c>
       <c r="B69" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>135422128</v>
       </c>
       <c r="B70" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>135521659</v>
       </c>
       <c r="B71" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>135382852</v>
       </c>
       <c r="B72" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>135382859</v>
       </c>
       <c r="B73" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>135388253</v>
       </c>
       <c r="B74" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>135422126</v>
       </c>
       <c r="B75" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>135388249</v>
       </c>
       <c r="B76" t="n">
-        <v>57165</v>
+        <v>57170</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9519,7 +9519,7 @@
         <v>135356132</v>
       </c>
       <c r="B77" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>135356141</v>
       </c>
       <c r="B78" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9781,7 +9781,7 @@
         <v>135382854</v>
       </c>
       <c r="B79" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10143,7 +10143,7 @@
         <v>135422123</v>
       </c>
       <c r="B82" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>135356130</v>
       </c>
       <c r="B83" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>135382846</v>
       </c>
       <c r="B84" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>135356131</v>
       </c>
       <c r="B85" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>135356139</v>
       </c>
       <c r="B86" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>135382842</v>
       </c>
       <c r="B87" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>135422127</v>
       </c>
       <c r="B88" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>135378151</v>
       </c>
       <c r="B89" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>135378157</v>
       </c>
       <c r="B90" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>135378159</v>
       </c>
       <c r="B91" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>135378164</v>
       </c>
       <c r="B92" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>135378166</v>
       </c>
       <c r="B93" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>135388089</v>
       </c>
       <c r="B94" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>135385246</v>
       </c>
       <c r="B95" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>135385253</v>
       </c>
       <c r="B96" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>135378182</v>
       </c>
       <c r="B97" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>135378183</v>
       </c>
       <c r="B98" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>135378194</v>
       </c>
       <c r="B99" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>135385250</v>
       </c>
       <c r="B100" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>135440301</v>
       </c>
       <c r="B101" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>135440302</v>
       </c>
       <c r="B102" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>135378184</v>
       </c>
       <c r="B103" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>135378188</v>
       </c>
       <c r="B104" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>135378195</v>
       </c>
       <c r="B105" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>135385242</v>
       </c>
       <c r="B106" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>135385255</v>
       </c>
       <c r="B107" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13188,7 +13188,7 @@
         <v>135378193</v>
       </c>
       <c r="B108" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>135378185</v>
       </c>
       <c r="B109" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>135378190</v>
       </c>
       <c r="B110" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>135378191</v>
       </c>
       <c r="B111" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>135378196</v>
       </c>
       <c r="B112" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>135385244</v>
       </c>
       <c r="B113" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>135385257</v>
       </c>
       <c r="B114" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>135441451</v>
       </c>
       <c r="B115" t="n">
-        <v>92593</v>
+        <v>92635</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>135356147</v>
       </c>
       <c r="B116" t="n">
-        <v>92201</v>
+        <v>92243</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>135351866</v>
       </c>
       <c r="B117" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>135388280</v>
       </c>
       <c r="B118" t="n">
-        <v>91924</v>
+        <v>91966</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>135385183</v>
       </c>
       <c r="B119" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>135385263</v>
       </c>
       <c r="B120" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>135388278</v>
       </c>
       <c r="B121" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>135393121</v>
       </c>
       <c r="B122" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>135440316</v>
       </c>
       <c r="B123" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>135440315</v>
       </c>
       <c r="B124" t="n">
-        <v>92360</v>
+        <v>92402</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>135356001</v>
       </c>
       <c r="B125" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>135356004</v>
       </c>
       <c r="B126" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>135356007</v>
       </c>
       <c r="B127" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>135382797</v>
       </c>
       <c r="B128" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>135382799</v>
       </c>
       <c r="B129" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>135382863</v>
       </c>
       <c r="B130" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>135382869</v>
       </c>
       <c r="B131" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>135382871</v>
       </c>
       <c r="B132" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>135384240</v>
       </c>
       <c r="B133" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>135384242</v>
       </c>
       <c r="B134" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>135384247</v>
       </c>
       <c r="B135" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>135384250</v>
       </c>
       <c r="B136" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>135384259</v>
       </c>
       <c r="B137" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>135384271</v>
       </c>
       <c r="B138" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>135384289</v>
       </c>
       <c r="B139" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>135384292</v>
       </c>
       <c r="B140" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>135384301</v>
       </c>
       <c r="B141" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>135384306</v>
       </c>
       <c r="B142" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>135385159</v>
       </c>
       <c r="B143" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>135385160</v>
       </c>
       <c r="B144" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>135385174</v>
       </c>
       <c r="B145" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
         <v>135385179</v>
       </c>
       <c r="B146" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>135385181</v>
       </c>
       <c r="B147" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>135385186</v>
       </c>
       <c r="B148" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>135385187</v>
       </c>
       <c r="B149" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>135385274</v>
       </c>
       <c r="B150" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>135388266</v>
       </c>
       <c r="B151" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>135388271</v>
       </c>
       <c r="B152" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>135388277</v>
       </c>
       <c r="B153" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>135388286</v>
       </c>
       <c r="B154" t="n">
-        <v>92795</v>
+        <v>92837</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>135378203</v>
       </c>
       <c r="B155" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>135385170</v>
       </c>
       <c r="B156" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>135385278</v>
       </c>
       <c r="B157" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>135385281</v>
       </c>
       <c r="B158" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>135388265</v>
       </c>
       <c r="B159" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>135393106</v>
       </c>
       <c r="B160" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>135355999</v>
       </c>
       <c r="B161" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>135385260</v>
       </c>
       <c r="B162" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>135385265</v>
       </c>
       <c r="B163" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>135385271</v>
       </c>
       <c r="B164" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>135388289</v>
       </c>
       <c r="B165" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>135440306</v>
       </c>
       <c r="B166" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>135440310</v>
       </c>
       <c r="B167" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>135440313</v>
       </c>
       <c r="B168" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>135388275</v>
       </c>
       <c r="B169" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>135351494</v>
       </c>
       <c r="B170" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>135382872</v>
       </c>
       <c r="B171" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>135382873</v>
       </c>
       <c r="B172" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>135388268</v>
       </c>
       <c r="B173" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>135385269</v>
       </c>
       <c r="B174" t="n">
-        <v>92332</v>
+        <v>92374</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>135388288</v>
       </c>
       <c r="B175" t="n">
-        <v>92332</v>
+        <v>92374</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>135385164</v>
       </c>
       <c r="B176" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>135388281</v>
       </c>
       <c r="B177" t="n">
-        <v>92320</v>
+        <v>92362</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>135393116</v>
       </c>
       <c r="B178" t="n">
-        <v>92199</v>
+        <v>92241</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>135382805</v>
       </c>
       <c r="B179" t="n">
-        <v>91995</v>
+        <v>92037</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>135382800</v>
       </c>
       <c r="B180" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>135382809</v>
       </c>
       <c r="B181" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>135388276</v>
       </c>
       <c r="B182" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>135349889</v>
       </c>
       <c r="B183" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>135351847</v>
       </c>
       <c r="B184" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>135351849</v>
       </c>
       <c r="B185" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>135351856</v>
       </c>
       <c r="B186" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>135351859</v>
       </c>
       <c r="B187" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>135356002</v>
       </c>
       <c r="B188" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>135357671</v>
       </c>
       <c r="B189" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>135357673</v>
       </c>
       <c r="B190" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>135378201</v>
       </c>
       <c r="B191" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>135378202</v>
       </c>
       <c r="B192" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>135378211</v>
       </c>
       <c r="B193" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>135378215</v>
       </c>
       <c r="B194" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>135378216</v>
       </c>
       <c r="B195" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>135378217</v>
       </c>
       <c r="B196" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>135378218</v>
       </c>
       <c r="B197" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>135384241</v>
       </c>
       <c r="B198" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>135384243</v>
       </c>
       <c r="B199" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>135384244</v>
       </c>
       <c r="B200" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>135384253</v>
       </c>
       <c r="B201" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>135384255</v>
       </c>
       <c r="B202" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>135384262</v>
       </c>
       <c r="B203" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>135384274</v>
       </c>
       <c r="B204" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>135384277</v>
       </c>
       <c r="B205" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>135384282</v>
       </c>
       <c r="B206" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>135384287</v>
       </c>
       <c r="B207" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>135384294</v>
       </c>
       <c r="B208" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>135384296</v>
       </c>
       <c r="B209" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>135384310</v>
       </c>
       <c r="B210" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>135384313</v>
       </c>
       <c r="B211" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>135385158</v>
       </c>
       <c r="B212" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>135385175</v>
       </c>
       <c r="B213" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>135385182</v>
       </c>
       <c r="B214" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>135385192</v>
       </c>
       <c r="B215" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>135385267</v>
       </c>
       <c r="B216" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>135385276</v>
       </c>
       <c r="B217" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>135385283</v>
       </c>
       <c r="B218" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>135388270</v>
       </c>
       <c r="B219" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>135388274</v>
       </c>
       <c r="B220" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>135388279</v>
       </c>
       <c r="B221" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>135388282</v>
       </c>
       <c r="B222" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>135388285</v>
       </c>
       <c r="B223" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>135388292</v>
       </c>
       <c r="B224" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>135393096</v>
       </c>
       <c r="B225" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>135440317</v>
       </c>
       <c r="B226" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>135393099</v>
       </c>
       <c r="B227" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>135356000</v>
       </c>
       <c r="B228" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>135356003</v>
       </c>
       <c r="B229" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>135356005</v>
       </c>
       <c r="B230" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>135378198</v>
       </c>
       <c r="B231" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>135378208</v>
       </c>
       <c r="B232" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>135382796</v>
       </c>
       <c r="B233" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>135382801</v>
       </c>
       <c r="B234" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>135382802</v>
       </c>
       <c r="B235" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>135382804</v>
       </c>
       <c r="B236" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         <v>135382807</v>
       </c>
       <c r="B237" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>135382808</v>
       </c>
       <c r="B238" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>135382810</v>
       </c>
       <c r="B239" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>135384280</v>
       </c>
       <c r="B240" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>135384308</v>
       </c>
       <c r="B241" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>135385189</v>
       </c>
       <c r="B242" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>135440308</v>
       </c>
       <c r="B243" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>135385259</v>
       </c>
       <c r="B244" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -29149,7 +29149,7 @@
         <v>135349888</v>
       </c>
       <c r="B245" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>135351846</v>
       </c>
       <c r="B246" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29396,7 +29396,7 @@
         <v>135351854</v>
       </c>
       <c r="B247" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29520,7 +29520,7 @@
         <v>135356143</v>
       </c>
       <c r="B248" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29641,7 +29641,7 @@
         <v>135356144</v>
       </c>
       <c r="B249" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>135358103</v>
       </c>
       <c r="B250" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29883,7 +29883,7 @@
         <v>135385178</v>
       </c>
       <c r="B251" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -30007,7 +30007,7 @@
         <v>135385185</v>
       </c>
       <c r="B252" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -30131,7 +30131,7 @@
         <v>135388284</v>
       </c>
       <c r="B253" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>135354042</v>
       </c>
       <c r="B254" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>135382867</v>
       </c>
       <c r="B255" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30518,7 +30518,7 @@
         <v>135385188</v>
       </c>
       <c r="B256" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30634,7 +30634,7 @@
         <v>135358108</v>
       </c>
       <c r="B257" t="n">
-        <v>56706</v>
+        <v>56711</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30755,7 +30755,7 @@
         <v>135440314</v>
       </c>
       <c r="B258" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>135351853</v>
       </c>
       <c r="B259" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>135358105</v>
       </c>
       <c r="B260" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>135358106</v>
       </c>
       <c r="B261" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>135358107</v>
       </c>
       <c r="B262" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>135393104</v>
       </c>
       <c r="B263" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>135393117</v>
       </c>
       <c r="B264" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>135351858</v>
       </c>
       <c r="B265" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>135351865</v>
       </c>
       <c r="B266" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>135378197</v>
       </c>
       <c r="B267" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>135378199</v>
       </c>
       <c r="B268" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -32023,7 +32023,7 @@
         <v>135378204</v>
       </c>
       <c r="B269" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>135378206</v>
       </c>
       <c r="B270" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>135378209</v>
       </c>
       <c r="B271" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>135378210</v>
       </c>
       <c r="B272" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -32487,7 +32487,7 @@
         <v>135378214</v>
       </c>
       <c r="B273" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>135385167</v>
       </c>
       <c r="B274" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>135385168</v>
       </c>
       <c r="B275" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>135385169</v>
       </c>
       <c r="B276" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>135351803</v>
       </c>
       <c r="B277" t="n">
-        <v>92593</v>
+        <v>92635</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>135355993</v>
       </c>
       <c r="B278" t="n">
-        <v>83353</v>
+        <v>83393</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>135355968</v>
       </c>
       <c r="B279" t="n">
-        <v>78393</v>
+        <v>78431</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>135358086</v>
       </c>
       <c r="B280" t="n">
-        <v>89354</v>
+        <v>89396</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         <v>135351469</v>
       </c>
       <c r="B281" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>135351780</v>
       </c>
       <c r="B282" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>135351789</v>
       </c>
       <c r="B283" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>135351806</v>
       </c>
       <c r="B284" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>135354060</v>
       </c>
       <c r="B285" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>135388262</v>
       </c>
       <c r="B286" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>135349819</v>
       </c>
       <c r="B287" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>135351450</v>
       </c>
       <c r="B288" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
@@ -34356,7 +34356,7 @@
         <v>135351463</v>
       </c>
       <c r="B289" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34453,7 +34453,7 @@
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
@@ -34472,7 +34472,7 @@
         <v>135351811</v>
       </c>
       <c r="B290" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34588,7 +34588,7 @@
         <v>135354052</v>
       </c>
       <c r="B291" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>135354057</v>
       </c>
       <c r="B292" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>135354065</v>
       </c>
       <c r="B293" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>135354068</v>
       </c>
       <c r="B294" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>135354076</v>
       </c>
       <c r="B295" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>135354085</v>
       </c>
       <c r="B296" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>135354104</v>
       </c>
       <c r="B297" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>135355971</v>
       </c>
       <c r="B298" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>135355973</v>
       </c>
       <c r="B299" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>135355982</v>
       </c>
       <c r="B300" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>135355998</v>
       </c>
       <c r="B301" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>135354091</v>
       </c>
       <c r="B303" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>135349862</v>
       </c>
       <c r="B304" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>135351749</v>
       </c>
       <c r="B305" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>135351755</v>
       </c>
       <c r="B306" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -36430,7 +36430,7 @@
         <v>135351760</v>
       </c>
       <c r="B307" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36546,7 +36546,7 @@
         <v>135351781</v>
       </c>
       <c r="B308" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>135351788</v>
       </c>
       <c r="B309" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>135351809</v>
       </c>
       <c r="B310" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>135351831</v>
       </c>
       <c r="B311" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>135354073</v>
       </c>
       <c r="B312" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>135356831</v>
       </c>
       <c r="B313" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>135351466</v>
       </c>
       <c r="B314" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>135351807</v>
       </c>
       <c r="B315" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>135349818</v>
       </c>
       <c r="B317" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>135349820</v>
       </c>
       <c r="B318" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>135351455</v>
       </c>
       <c r="B319" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>135354059</v>
       </c>
       <c r="B320" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>135354063</v>
       </c>
       <c r="B321" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>135354106</v>
       </c>
       <c r="B322" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>135349834</v>
       </c>
       <c r="B323" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>135351791</v>
       </c>
       <c r="B324" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>135355992</v>
       </c>
       <c r="B325" t="n">
-        <v>83363</v>
+        <v>83403</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>135351464</v>
       </c>
       <c r="B327" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr">
@@ -38839,7 +38839,7 @@
         <v>135351748</v>
       </c>
       <c r="B328" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -38955,7 +38955,7 @@
         <v>135351490</v>
       </c>
       <c r="B329" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>135351491</v>
       </c>
       <c r="B330" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>135354094</v>
       </c>
       <c r="B331" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -39323,7 +39323,7 @@
         <v>135354098</v>
       </c>
       <c r="B332" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>135354100</v>
       </c>
       <c r="B333" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>135355991</v>
       </c>
       <c r="B334" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39671,7 +39671,7 @@
         <v>135357665</v>
       </c>
       <c r="B335" t="n">
-        <v>80489</v>
+        <v>80527</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>135351473</v>
       </c>
       <c r="B336" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
       </c>
       <c r="AX336" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY336" t="inlineStr">
@@ -39903,7 +39903,7 @@
         <v>135355983</v>
       </c>
       <c r="B337" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>135358094</v>
       </c>
       <c r="B338" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>135351457</v>
       </c>
       <c r="B339" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
       </c>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr">
@@ -40251,7 +40251,7 @@
         <v>135351471</v>
       </c>
       <c r="B340" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40348,7 +40348,7 @@
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr">
@@ -40367,7 +40367,7 @@
         <v>135358076</v>
       </c>
       <c r="B341" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>135388263</v>
       </c>
       <c r="B342" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>135349829</v>
       </c>
       <c r="B343" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>135349837</v>
       </c>
       <c r="B344" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>135349838</v>
       </c>
       <c r="B345" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>135349843</v>
       </c>
       <c r="B346" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>135349844</v>
       </c>
       <c r="B347" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>135349846</v>
       </c>
       <c r="B348" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>135349848</v>
       </c>
       <c r="B349" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>135349849</v>
       </c>
       <c r="B350" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>135349853</v>
       </c>
       <c r="B351" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>135349855</v>
       </c>
       <c r="B352" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>135349858</v>
       </c>
       <c r="B353" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>135349864</v>
       </c>
       <c r="B354" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>135349865</v>
       </c>
       <c r="B355" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>135349868</v>
       </c>
       <c r="B356" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>135349870</v>
       </c>
       <c r="B357" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>135349877</v>
       </c>
       <c r="B358" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>135349882</v>
       </c>
       <c r="B359" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>135351447</v>
       </c>
       <c r="B360" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
       </c>
       <c r="AX360" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY360" t="inlineStr">
@@ -42687,7 +42687,7 @@
         <v>135351448</v>
       </c>
       <c r="B361" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42784,7 +42784,7 @@
       </c>
       <c r="AX361" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY361" t="inlineStr">
@@ -42803,7 +42803,7 @@
         <v>135351452</v>
       </c>
       <c r="B362" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
       </c>
       <c r="AX362" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY362" t="inlineStr">
@@ -42919,7 +42919,7 @@
         <v>135351453</v>
       </c>
       <c r="B363" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
       </c>
       <c r="AX363" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY363" t="inlineStr">
@@ -43035,7 +43035,7 @@
         <v>135351456</v>
       </c>
       <c r="B364" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>135351458</v>
       </c>
       <c r="B365" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
       </c>
       <c r="AX365" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY365" t="inlineStr">
@@ -43267,7 +43267,7 @@
         <v>135351461</v>
       </c>
       <c r="B366" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -43364,7 +43364,7 @@
       </c>
       <c r="AX366" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY366" t="inlineStr">
@@ -43383,7 +43383,7 @@
         <v>135351465</v>
       </c>
       <c r="B367" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -43480,7 +43480,7 @@
       </c>
       <c r="AX367" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY367" t="inlineStr">
@@ -43499,7 +43499,7 @@
         <v>135351468</v>
       </c>
       <c r="B368" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>135351741</v>
       </c>
       <c r="B369" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>135351744</v>
       </c>
       <c r="B370" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>135351747</v>
       </c>
       <c r="B371" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>135351759</v>
       </c>
       <c r="B372" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>135351765</v>
       </c>
       <c r="B373" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>135351767</v>
       </c>
       <c r="B374" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -44311,7 +44311,7 @@
         <v>135351769</v>
       </c>
       <c r="B375" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>135351777</v>
       </c>
       <c r="B376" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>135351783</v>
       </c>
       <c r="B377" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -44659,7 +44659,7 @@
         <v>135351787</v>
       </c>
       <c r="B378" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>135351790</v>
       </c>
       <c r="B379" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>135351792</v>
       </c>
       <c r="B380" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>135351794</v>
       </c>
       <c r="B381" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>135351801</v>
       </c>
       <c r="B382" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -45252,7 +45252,7 @@
         <v>135351802</v>
       </c>
       <c r="B383" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>135351804</v>
       </c>
       <c r="B384" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -45484,7 +45484,7 @@
         <v>135351808</v>
       </c>
       <c r="B385" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>135351812</v>
       </c>
       <c r="B386" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -45716,7 +45716,7 @@
         <v>135351824</v>
       </c>
       <c r="B387" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>135351825</v>
       </c>
       <c r="B388" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -45948,7 +45948,7 @@
         <v>135351826</v>
       </c>
       <c r="B389" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>135351827</v>
       </c>
       <c r="B390" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>135351828</v>
       </c>
       <c r="B391" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -46296,7 +46296,7 @@
         <v>135351837</v>
       </c>
       <c r="B392" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>135351839</v>
       </c>
       <c r="B393" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>135351845</v>
       </c>
       <c r="B394" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>135354048</v>
       </c>
       <c r="B395" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>135354054</v>
       </c>
       <c r="B396" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -46876,7 +46876,7 @@
         <v>135354056</v>
       </c>
       <c r="B397" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -46992,7 +46992,7 @@
         <v>135354062</v>
       </c>
       <c r="B398" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>135354064</v>
       </c>
       <c r="B399" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>135354067</v>
       </c>
       <c r="B400" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>135354070</v>
       </c>
       <c r="B401" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -47456,7 +47456,7 @@
         <v>135354074</v>
       </c>
       <c r="B402" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>135354077</v>
       </c>
       <c r="B403" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>135354079</v>
       </c>
       <c r="B404" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>135354082</v>
       </c>
       <c r="B405" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>135354103</v>
       </c>
       <c r="B406" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -48036,7 +48036,7 @@
         <v>135355975</v>
       </c>
       <c r="B407" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -48152,7 +48152,7 @@
         <v>135355978</v>
       </c>
       <c r="B408" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>135355979</v>
       </c>
       <c r="B409" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>135355980</v>
       </c>
       <c r="B410" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -48500,7 +48500,7 @@
         <v>135355981</v>
       </c>
       <c r="B411" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -48616,7 +48616,7 @@
         <v>135355984</v>
       </c>
       <c r="B412" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>135355985</v>
       </c>
       <c r="B413" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         <v>135355995</v>
       </c>
       <c r="B414" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>135356827</v>
       </c>
       <c r="B415" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>135356828</v>
       </c>
       <c r="B416" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -49201,7 +49201,7 @@
         <v>135357661</v>
       </c>
       <c r="B417" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -49317,7 +49317,7 @@
         <v>135358079</v>
       </c>
       <c r="B418" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>135358092</v>
       </c>
       <c r="B419" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -49549,7 +49549,7 @@
         <v>135358098</v>
       </c>
       <c r="B420" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -49665,7 +49665,7 @@
         <v>135388259</v>
       </c>
       <c r="B421" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>135388261</v>
       </c>
       <c r="B422" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -49897,7 +49897,7 @@
         <v>135355996</v>
       </c>
       <c r="B423" t="n">
-        <v>78776</v>
+        <v>78814</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>135349814</v>
       </c>
       <c r="B424" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -50129,7 +50129,7 @@
         <v>135349815</v>
       </c>
       <c r="B425" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>135349823</v>
       </c>
       <c r="B426" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -50361,7 +50361,7 @@
         <v>135349824</v>
       </c>
       <c r="B427" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>135349831</v>
       </c>
       <c r="B428" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
         <v>135349840</v>
       </c>
       <c r="B429" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -50709,7 +50709,7 @@
         <v>135349850</v>
       </c>
       <c r="B430" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -50825,7 +50825,7 @@
         <v>135349883</v>
       </c>
       <c r="B431" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>135351460</v>
       </c>
       <c r="B432" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -51038,7 +51038,7 @@
       </c>
       <c r="AX432" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY432" t="inlineStr">
@@ -51057,7 +51057,7 @@
         <v>135351462</v>
       </c>
       <c r="B433" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
       </c>
       <c r="AX433" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY433" t="inlineStr">
@@ -51173,7 +51173,7 @@
         <v>135351751</v>
       </c>
       <c r="B434" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         <v>135351758</v>
       </c>
       <c r="B435" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>135351770</v>
       </c>
       <c r="B436" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>135351797</v>
       </c>
       <c r="B437" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -51637,7 +51637,7 @@
         <v>135351842</v>
       </c>
       <c r="B438" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>135354084</v>
       </c>
       <c r="B439" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>135354105</v>
       </c>
       <c r="B440" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -51985,7 +51985,7 @@
         <v>135355969</v>
       </c>
       <c r="B441" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -52101,7 +52101,7 @@
         <v>135355976</v>
       </c>
       <c r="B442" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -52217,7 +52217,7 @@
         <v>135355977</v>
       </c>
       <c r="B443" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>135355986</v>
       </c>
       <c r="B444" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -52449,7 +52449,7 @@
         <v>135351492</v>
       </c>
       <c r="B445" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -52551,7 +52551,7 @@
       </c>
       <c r="AX445" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY445" t="inlineStr">
@@ -52570,7 +52570,7 @@
         <v>135354096</v>
       </c>
       <c r="B446" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52701,7 +52701,7 @@
         <v>135354099</v>
       </c>
       <c r="B447" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>135349875</v>
       </c>
       <c r="B448" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -52938,7 +52938,7 @@
         <v>135351482</v>
       </c>
       <c r="B449" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>135351483</v>
       </c>
       <c r="B450" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -53171,7 +53171,7 @@
       </c>
       <c r="AX450" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY450" t="inlineStr">
@@ -53190,7 +53190,7 @@
         <v>135351486</v>
       </c>
       <c r="B451" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>135351774</v>
       </c>
       <c r="B452" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -53426,7 +53426,7 @@
         <v>135355988</v>
       </c>
       <c r="B453" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>135355994</v>
       </c>
       <c r="B454" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -53658,7 +53658,7 @@
         <v>135351481</v>
       </c>
       <c r="B455" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>135351487</v>
       </c>
       <c r="B456" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -53890,7 +53890,7 @@
         <v>135354097</v>
       </c>
       <c r="B457" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -54006,7 +54006,7 @@
         <v>135355990</v>
       </c>
       <c r="B458" t="n">
-        <v>80499</v>
+        <v>80537</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>135351484</v>
       </c>
       <c r="B459" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -54219,7 +54219,7 @@
       </c>
       <c r="AX459" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY459" t="inlineStr">
@@ -54238,7 +54238,7 @@
         <v>135351485</v>
       </c>
       <c r="B460" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -54335,7 +54335,7 @@
       </c>
       <c r="AX460" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY460" t="inlineStr">
@@ -54354,7 +54354,7 @@
         <v>135354081</v>
       </c>
       <c r="B461" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>135355987</v>
       </c>
       <c r="B462" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -54586,7 +54586,7 @@
         <v>135358090</v>
       </c>
       <c r="B463" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -54702,7 +54702,7 @@
         <v>135358091</v>
       </c>
       <c r="B464" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -54818,7 +54818,7 @@
         <v>135349860</v>
       </c>
       <c r="B465" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -54939,7 +54939,7 @@
         <v>135351754</v>
       </c>
       <c r="B466" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>135354089</v>
       </c>
       <c r="B467" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -55185,7 +55185,7 @@
         <v>135356818</v>
       </c>
       <c r="B468" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -55407,7 +55407,7 @@
         <v>135349833</v>
       </c>
       <c r="B470" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -55533,7 +55533,7 @@
         <v>135349839</v>
       </c>
       <c r="B471" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -55659,7 +55659,7 @@
         <v>135349847</v>
       </c>
       <c r="B472" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -55785,7 +55785,7 @@
         <v>135349861</v>
       </c>
       <c r="B473" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -55911,7 +55911,7 @@
         <v>135351480</v>
       </c>
       <c r="B474" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -56037,7 +56037,7 @@
         <v>135351750</v>
       </c>
       <c r="B475" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -56166,7 +56166,7 @@
         <v>135351762</v>
       </c>
       <c r="B476" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -56295,7 +56295,7 @@
         <v>135351772</v>
       </c>
       <c r="B477" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -56416,7 +56416,7 @@
         <v>135351778</v>
       </c>
       <c r="B478" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>135351796</v>
       </c>
       <c r="B479" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -56661,7 +56661,7 @@
         <v>135351799</v>
       </c>
       <c r="B480" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -56777,7 +56777,7 @@
         <v>135354087</v>
       </c>
       <c r="B481" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>135354088</v>
       </c>
       <c r="B482" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -57029,7 +57029,7 @@
         <v>135354093</v>
       </c>
       <c r="B483" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -57155,7 +57155,7 @@
         <v>135355972</v>
       </c>
       <c r="B484" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -57386,7 +57386,7 @@
         <v>135351795</v>
       </c>
       <c r="B486" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -57515,7 +57515,7 @@
         <v>135349836</v>
       </c>
       <c r="B487" t="n">
-        <v>57153</v>
+        <v>57158</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -57636,7 +57636,7 @@
         <v>135351472</v>
       </c>
       <c r="B488" t="n">
-        <v>57165</v>
+        <v>57170</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -57738,7 +57738,7 @@
       </c>
       <c r="AX488" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY488" t="inlineStr">
@@ -57757,7 +57757,7 @@
         <v>135351446</v>
       </c>
       <c r="B489" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -57854,7 +57854,7 @@
       </c>
       <c r="AX489" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY489" t="inlineStr">
@@ -57873,7 +57873,7 @@
         <v>135351479</v>
       </c>
       <c r="B490" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -57989,7 +57989,7 @@
         <v>135349830</v>
       </c>
       <c r="B491" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -58110,7 +58110,7 @@
         <v>135351476</v>
       </c>
       <c r="B492" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>135351752</v>
       </c>
       <c r="B493" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>135358077</v>
       </c>
       <c r="B494" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -58458,7 +58458,7 @@
         <v>135358087</v>
       </c>
       <c r="B495" t="n">
-        <v>98066</v>
+        <v>98110</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -58574,7 +58574,7 @@
         <v>135351449</v>
       </c>
       <c r="B496" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>135351477</v>
       </c>
       <c r="B497" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>135357666</v>
       </c>
       <c r="B498" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>135357670</v>
       </c>
       <c r="B499" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -59038,7 +59038,7 @@
         <v>135358081</v>
       </c>
       <c r="B500" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -59154,7 +59154,7 @@
         <v>135358082</v>
       </c>
       <c r="B501" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>135358085</v>
       </c>
       <c r="B502" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -59386,7 +59386,7 @@
         <v>135358089</v>
       </c>
       <c r="B503" t="n">
-        <v>98060</v>
+        <v>98104</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>135349874</v>
       </c>
       <c r="B504" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -59623,7 +59623,7 @@
         <v>135351489</v>
       </c>
       <c r="B505" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -59739,7 +59739,7 @@
         <v>135351743</v>
       </c>
       <c r="B506" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -59855,7 +59855,7 @@
         <v>135351773</v>
       </c>
       <c r="B507" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>135354090</v>
       </c>
       <c r="B508" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -60087,7 +60087,7 @@
         <v>135356125</v>
       </c>
       <c r="B509" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -60208,7 +60208,7 @@
         <v>135356126</v>
       </c>
       <c r="B510" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -60324,7 +60324,7 @@
         <v>135358093</v>
       </c>
       <c r="B511" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>135358096</v>
       </c>
       <c r="B512" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -60556,7 +60556,7 @@
         <v>135358099</v>
       </c>
       <c r="B513" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -60672,7 +60672,7 @@
         <v>135358100</v>
       </c>
       <c r="B514" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -60788,7 +60788,7 @@
         <v>135358101</v>
       </c>
       <c r="B515" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -60904,7 +60904,7 @@
         <v>135358102</v>
       </c>
       <c r="B516" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -61020,7 +61020,7 @@
         <v>135351475</v>
       </c>
       <c r="B517" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -61117,7 +61117,7 @@
       </c>
       <c r="AX517" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY517" t="inlineStr">
@@ -61136,7 +61136,7 @@
         <v>135349813</v>
       </c>
       <c r="B518" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -61252,7 +61252,7 @@
         <v>135349816</v>
       </c>
       <c r="B519" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -61368,7 +61368,7 @@
         <v>135349821</v>
       </c>
       <c r="B520" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -61484,7 +61484,7 @@
         <v>135349826</v>
       </c>
       <c r="B521" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -61600,7 +61600,7 @@
         <v>135349827</v>
       </c>
       <c r="B522" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -61716,7 +61716,7 @@
         <v>135349832</v>
       </c>
       <c r="B523" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -61832,7 +61832,7 @@
         <v>135349841</v>
       </c>
       <c r="B524" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -61948,7 +61948,7 @@
         <v>135349845</v>
       </c>
       <c r="B525" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -62064,7 +62064,7 @@
         <v>135349851</v>
       </c>
       <c r="B526" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>135349854</v>
       </c>
       <c r="B527" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -62296,7 +62296,7 @@
         <v>135349856</v>
       </c>
       <c r="B528" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -62412,7 +62412,7 @@
         <v>135349859</v>
       </c>
       <c r="B529" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -62528,7 +62528,7 @@
         <v>135349869</v>
       </c>
       <c r="B530" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -62644,7 +62644,7 @@
         <v>135349873</v>
       </c>
       <c r="B531" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -62760,7 +62760,7 @@
         <v>135349876</v>
       </c>
       <c r="B532" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -62876,7 +62876,7 @@
         <v>135349878</v>
       </c>
       <c r="B533" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -62992,7 +62992,7 @@
         <v>135349880</v>
       </c>
       <c r="B534" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -63108,7 +63108,7 @@
         <v>135349884</v>
       </c>
       <c r="B535" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -63224,7 +63224,7 @@
         <v>135349885</v>
       </c>
       <c r="B536" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -63340,7 +63340,7 @@
         <v>135349886</v>
       </c>
       <c r="B537" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -63456,7 +63456,7 @@
         <v>135349887</v>
       </c>
       <c r="B538" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -63572,7 +63572,7 @@
         <v>135351451</v>
       </c>
       <c r="B539" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -63669,7 +63669,7 @@
       </c>
       <c r="AX539" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Martin Axegård, Johan Råghall, Torun Jacobsson, Maja Rancic, Petya Valcheva, Tyr Nilsson, Mattias Dalkvist</t>
+          <t>Cecilia Goldkuhl, Mattias Dalkvist, Tyr Nilsson, Petya Valcheva, Maja Rancic, Torun Jacobsson, Johan Råghall, Martin Axegård</t>
         </is>
       </c>
       <c r="AY539" t="inlineStr">
@@ -63688,7 +63688,7 @@
         <v>135351745</v>
       </c>
       <c r="B540" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -63804,7 +63804,7 @@
         <v>135351757</v>
       </c>
       <c r="B541" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -63920,7 +63920,7 @@
         <v>135351763</v>
       </c>
       <c r="B542" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -64036,7 +64036,7 @@
         <v>135351768</v>
       </c>
       <c r="B543" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -64152,7 +64152,7 @@
         <v>135351771</v>
       </c>
       <c r="B544" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -64268,7 +64268,7 @@
         <v>135351776</v>
       </c>
       <c r="B545" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         <v>135351784</v>
       </c>
       <c r="B546" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -64500,7 +64500,7 @@
         <v>135351798</v>
       </c>
       <c r="B547" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -64616,7 +64616,7 @@
         <v>135351800</v>
       </c>
       <c r="B548" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -64732,7 +64732,7 @@
         <v>135351840</v>
       </c>
       <c r="B549" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -64848,7 +64848,7 @@
         <v>135354046</v>
       </c>
       <c r="B550" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -64964,7 +64964,7 @@
         <v>135354061</v>
       </c>
       <c r="B551" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -65080,7 +65080,7 @@
         <v>135354078</v>
       </c>
       <c r="B552" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -65196,7 +65196,7 @@
         <v>135354083</v>
       </c>
       <c r="B553" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -65312,7 +65312,7 @@
         <v>135358078</v>
       </c>
       <c r="B554" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -65428,7 +65428,7 @@
         <v>135351742</v>
       </c>
       <c r="B555" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -65544,7 +65544,7 @@
         <v>135354071</v>
       </c>
       <c r="B556" t="n">
-        <v>92323</v>
+        <v>92365</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65688,7 +65688,7 @@
         <v>135422147</v>
       </c>
       <c r="B557" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -65824,7 +65824,7 @@
         <v>135422165</v>
       </c>
       <c r="B558" t="n">
-        <v>97435</v>
+        <v>97479</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -65960,7 +65960,7 @@
         <v>135349920</v>
       </c>
       <c r="B559" t="n">
-        <v>92369</v>
+        <v>92411</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -66080,7 +66080,7 @@
         <v>135440323</v>
       </c>
       <c r="B560" t="n">
-        <v>83350</v>
+        <v>83390</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -66298,7 +66298,7 @@
         <v>135349899</v>
       </c>
       <c r="B562" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -66414,7 +66414,7 @@
         <v>135393122</v>
       </c>
       <c r="B563" t="n">
-        <v>92245</v>
+        <v>92287</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -66526,7 +66526,7 @@
         <v>135385302</v>
       </c>
       <c r="B564" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -66642,7 +66642,7 @@
         <v>135385308</v>
       </c>
       <c r="B565" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -66758,7 +66758,7 @@
         <v>135385315</v>
       </c>
       <c r="B566" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -66874,7 +66874,7 @@
         <v>135385319</v>
       </c>
       <c r="B567" t="n">
-        <v>79452</v>
+        <v>79490</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -67194,7 +67194,7 @@
         <v>135349895</v>
       </c>
       <c r="B570" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -67310,7 +67310,7 @@
         <v>135349906</v>
       </c>
       <c r="B571" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -67426,7 +67426,7 @@
         <v>135385306</v>
       </c>
       <c r="B572" t="n">
-        <v>91970</v>
+        <v>92012</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -67542,7 +67542,7 @@
         <v>135385240</v>
       </c>
       <c r="B573" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -67658,7 +67658,7 @@
         <v>135393114</v>
       </c>
       <c r="B574" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -67770,7 +67770,7 @@
         <v>135440300</v>
       </c>
       <c r="B575" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -67886,7 +67886,7 @@
         <v>135393138</v>
       </c>
       <c r="B576" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -67998,7 +67998,7 @@
         <v>135393158</v>
       </c>
       <c r="B577" t="n">
-        <v>91988</v>
+        <v>92030</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -68620,7 +68620,7 @@
         <v>135382862</v>
       </c>
       <c r="B583" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -68736,7 +68736,7 @@
         <v>135385323</v>
       </c>
       <c r="B584" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -68852,7 +68852,7 @@
         <v>135422133</v>
       </c>
       <c r="B585" t="n">
-        <v>83222</v>
+        <v>83262</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -68983,7 +68983,7 @@
         <v>135422136</v>
       </c>
       <c r="B586" t="n">
-        <v>92329</v>
+        <v>92371</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -69216,7 +69216,7 @@
         <v>135349911</v>
       </c>
       <c r="B588" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -69332,7 +69332,7 @@
         <v>135393155</v>
       </c>
       <c r="B589" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -69444,7 +69444,7 @@
         <v>135349919</v>
       </c>
       <c r="B590" t="n">
-        <v>92370</v>
+        <v>92412</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -69560,7 +69560,7 @@
         <v>135349892</v>
       </c>
       <c r="B591" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -69676,7 +69676,7 @@
         <v>135349905</v>
       </c>
       <c r="B592" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -69792,7 +69792,7 @@
         <v>135385238</v>
       </c>
       <c r="B593" t="n">
-        <v>91937</v>
+        <v>91979</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -69908,7 +69908,7 @@
         <v>135388294</v>
       </c>
       <c r="B594" t="n">
-        <v>93089</v>
+        <v>93131</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -70033,7 +70033,7 @@
         <v>135388298</v>
       </c>
       <c r="B595" t="n">
-        <v>93089</v>
+        <v>93131</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -70158,7 +70158,7 @@
         <v>135349898</v>
       </c>
       <c r="B596" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -70274,7 +70274,7 @@
         <v>135349900</v>
       </c>
       <c r="B597" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -70390,7 +70390,7 @@
         <v>135349903</v>
       </c>
       <c r="B598" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -70506,7 +70506,7 @@
         <v>135349908</v>
       </c>
       <c r="B599" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -70622,7 +70622,7 @@
         <v>135349917</v>
       </c>
       <c r="B600" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -70738,7 +70738,7 @@
         <v>135378171</v>
       </c>
       <c r="B601" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -70854,7 +70854,7 @@
         <v>135378177</v>
       </c>
       <c r="B602" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -70970,7 +70970,7 @@
         <v>135384317</v>
       </c>
       <c r="B603" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -71086,7 +71086,7 @@
         <v>135384321</v>
       </c>
       <c r="B604" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -71202,7 +71202,7 @@
         <v>135384326</v>
       </c>
       <c r="B605" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -71318,7 +71318,7 @@
         <v>135385234</v>
       </c>
       <c r="B606" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -71434,7 +71434,7 @@
         <v>135385291</v>
       </c>
       <c r="B607" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -71550,7 +71550,7 @@
         <v>135385299</v>
       </c>
       <c r="B608" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -71666,7 +71666,7 @@
         <v>135385304</v>
       </c>
       <c r="B609" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -71782,7 +71782,7 @@
         <v>135385313</v>
       </c>
       <c r="B610" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -71898,7 +71898,7 @@
         <v>135385317</v>
       </c>
       <c r="B611" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -72014,7 +72014,7 @@
         <v>135385321</v>
       </c>
       <c r="B612" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -72130,7 +72130,7 @@
         <v>135385325</v>
       </c>
       <c r="B613" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -72246,7 +72246,7 @@
         <v>135393119</v>
       </c>
       <c r="B614" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -72358,7 +72358,7 @@
         <v>135393137</v>
       </c>
       <c r="B615" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -72470,7 +72470,7 @@
         <v>135422129</v>
       </c>
       <c r="B616" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -72586,7 +72586,7 @@
         <v>135440298</v>
       </c>
       <c r="B617" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -72702,7 +72702,7 @@
         <v>135378172</v>
       </c>
       <c r="B618" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -72818,7 +72818,7 @@
         <v>135378176</v>
       </c>
       <c r="B619" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -72934,7 +72934,7 @@
         <v>135385230</v>
       </c>
       <c r="B620" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -73050,7 +73050,7 @@
         <v>135385287</v>
       </c>
       <c r="B621" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -73166,7 +73166,7 @@
         <v>135385295</v>
       </c>
       <c r="B622" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -73282,7 +73282,7 @@
         <v>135393123</v>
       </c>
       <c r="B623" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -73394,7 +73394,7 @@
         <v>135422132</v>
       </c>
       <c r="B624" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -73525,7 +73525,7 @@
         <v>135440297</v>
       </c>
       <c r="B625" t="n">
-        <v>83358</v>
+        <v>83398</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -73641,7 +73641,7 @@
         <v>135385194</v>
       </c>
       <c r="B626" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -73757,7 +73757,7 @@
         <v>135349918</v>
       </c>
       <c r="B627" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -73878,7 +73878,7 @@
         <v>135349901</v>
       </c>
       <c r="B628" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -74004,7 +74004,7 @@
         <v>135349904</v>
       </c>
       <c r="B629" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -74130,7 +74130,7 @@
         <v>135378174</v>
       </c>
       <c r="B630" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -74256,7 +74256,7 @@
         <v>135378178</v>
       </c>
       <c r="B631" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -74382,7 +74382,7 @@
         <v>135378180</v>
       </c>
       <c r="B632" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -74508,7 +74508,7 @@
         <v>135382861</v>
       </c>
       <c r="B633" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -74629,7 +74629,7 @@
         <v>135422144</v>
       </c>
       <c r="B634" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -74862,7 +74862,7 @@
         <v>135385293</v>
       </c>
       <c r="B636" t="n">
-        <v>57162</v>
+        <v>57167</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -74983,7 +74983,7 @@
         <v>135440320</v>
       </c>
       <c r="B637" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -75201,7 +75201,7 @@
         <v>135349897</v>
       </c>
       <c r="B639" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -75322,7 +75322,7 @@
         <v>135422135</v>
       </c>
       <c r="B640" t="n">
-        <v>58079</v>
+        <v>58084</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -75442,7 +75442,7 @@
         <v>135388293</v>
       </c>
       <c r="B641" t="n">
-        <v>58839</v>
+        <v>58844</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -75558,7 +75558,7 @@
         <v>135422161</v>
       </c>
       <c r="B642" t="n">
-        <v>41606</v>
+        <v>41610</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -75679,7 +75679,7 @@
         <v>135351869</v>
       </c>
       <c r="B643" t="n">
-        <v>99094</v>
+        <v>99141</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -75795,7 +75795,7 @@
         <v>135422162</v>
       </c>
       <c r="B644" t="n">
-        <v>99094</v>
+        <v>99141</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -75925,7 +75925,7 @@
         <v>135351871</v>
       </c>
       <c r="B645" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -76041,7 +76041,7 @@
         <v>135385327</v>
       </c>
       <c r="B646" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -76157,7 +76157,7 @@
         <v>135393145</v>
       </c>
       <c r="B647" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -76269,7 +76269,7 @@
         <v>135422156</v>
       </c>
       <c r="B648" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -76390,7 +76390,7 @@
         <v>135422160</v>
       </c>
       <c r="B649" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -76511,7 +76511,7 @@
         <v>135523737</v>
       </c>
       <c r="B650" t="n">
-        <v>99197</v>
+        <v>99244</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -76632,7 +76632,7 @@
         <v>135422166</v>
       </c>
       <c r="B651" t="n">
-        <v>107943</v>
+        <v>107998</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -76758,7 +76758,7 @@
         <v>135523654</v>
       </c>
       <c r="B652" t="n">
-        <v>107943</v>
+        <v>107998</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -76879,7 +76879,7 @@
         <v>135422142</v>
       </c>
       <c r="B653" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -77000,7 +77000,7 @@
         <v>135393157</v>
       </c>
       <c r="B654" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -77112,7 +77112,7 @@
         <v>135422154</v>
       </c>
       <c r="B655" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -77233,7 +77233,7 @@
         <v>135422169</v>
       </c>
       <c r="B656" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -77354,7 +77354,7 @@
         <v>135393151</v>
       </c>
       <c r="B657" t="n">
-        <v>110023</v>
+        <v>110079</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -77466,7 +77466,7 @@
         <v>135351874</v>
       </c>
       <c r="B658" t="n">
-        <v>110150</v>
+        <v>110206</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -77582,7 +77582,7 @@
         <v>135349921</v>
       </c>
       <c r="B659" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -77707,7 +77707,7 @@
         <v>135349909</v>
       </c>
       <c r="B660" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -77746,7 +77746,7 @@
         <v>608014</v>
       </c>
       <c r="R660" t="n">
-        <v>7309638</v>
+        <v>7309639</v>
       </c>
       <c r="S660" t="n">
         <v>3</v>
@@ -77828,7 +77828,7 @@
         <v>135384319</v>
       </c>
       <c r="B661" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -77944,7 +77944,7 @@
         <v>135384324</v>
       </c>
       <c r="B662" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -78060,7 +78060,7 @@
         <v>135388296</v>
       </c>
       <c r="B663" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -78176,7 +78176,7 @@
         <v>135393149</v>
       </c>
       <c r="B664" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -78288,7 +78288,7 @@
         <v>135422137</v>
       </c>
       <c r="B665" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -78404,7 +78404,7 @@
         <v>135422150</v>
       </c>
       <c r="B666" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -78525,7 +78525,7 @@
         <v>135422155</v>
       </c>
       <c r="B667" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -78646,7 +78646,7 @@
         <v>135422159</v>
       </c>
       <c r="B668" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -78767,7 +78767,7 @@
         <v>135440319</v>
       </c>
       <c r="B669" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -78883,7 +78883,7 @@
         <v>135422167</v>
       </c>
       <c r="B670" t="n">
-        <v>98054</v>
+        <v>98098</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -79000,7 +79000,7 @@
         <v>135523644</v>
       </c>
       <c r="B671" t="n">
-        <v>98054</v>
+        <v>98098</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -79117,7 +79117,7 @@
         <v>135385157</v>
       </c>
       <c r="B672" t="n">
-        <v>98063</v>
+        <v>98107</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -79233,7 +79233,7 @@
         <v>135349896</v>
       </c>
       <c r="B673" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -79349,7 +79349,7 @@
         <v>135349910</v>
       </c>
       <c r="B674" t="n">
-        <v>103764</v>
+        <v>103815</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -79384,7 +79384,7 @@
         <v>608014</v>
       </c>
       <c r="R674" t="n">
-        <v>7309638</v>
+        <v>7309639</v>
       </c>
       <c r="S674" t="n">
         <v>3</v>
@@ -79465,7 +79465,7 @@
         <v>135356148</v>
       </c>
       <c r="B675" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -79581,7 +79581,7 @@
         <v>135393154</v>
       </c>
       <c r="B676" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -79693,7 +79693,7 @@
         <v>135422138</v>
       </c>
       <c r="B677" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -79828,7 +79828,7 @@
         <v>135422163</v>
       </c>
       <c r="B678" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -79963,7 +79963,7 @@
         <v>135422168</v>
       </c>
       <c r="B679" t="n">
-        <v>104707</v>
+        <v>104761</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -80098,7 +80098,7 @@
         <v>135393126</v>
       </c>
       <c r="B680" t="n">
-        <v>100806</v>
+        <v>100854</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -80210,7 +80210,7 @@
         <v>135388299</v>
       </c>
       <c r="B681" t="n">
-        <v>102871</v>
+        <v>102922</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -80326,7 +80326,7 @@
         <v>135422143</v>
       </c>
       <c r="B682" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -80447,7 +80447,7 @@
         <v>135351867</v>
       </c>
       <c r="B683" t="n">
-        <v>99198</v>
+        <v>99245</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -80560,7 +80560,7 @@
         <v>135349891</v>
       </c>
       <c r="B684" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -80676,7 +80676,7 @@
         <v>135393129</v>
       </c>
       <c r="B685" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -80788,7 +80788,7 @@
         <v>135393131</v>
       </c>
       <c r="B686" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -80900,7 +80900,7 @@
         <v>135393150</v>
       </c>
       <c r="B687" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -81012,7 +81012,7 @@
         <v>135422139</v>
       </c>
       <c r="B688" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -81133,7 +81133,7 @@
         <v>135422140</v>
       </c>
       <c r="B689" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -81254,7 +81254,7 @@
         <v>135422152</v>
       </c>
       <c r="B690" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -81375,7 +81375,7 @@
         <v>135523597</v>
       </c>
       <c r="B691" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -81496,7 +81496,7 @@
         <v>135378173</v>
       </c>
       <c r="B692" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -81612,7 +81612,7 @@
         <v>135378175</v>
       </c>
       <c r="B693" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -81728,7 +81728,7 @@
         <v>135378179</v>
       </c>
       <c r="B694" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -81844,7 +81844,7 @@
         <v>135378181</v>
       </c>
       <c r="B695" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -81960,7 +81960,7 @@
         <v>135385232</v>
       </c>
       <c r="B696" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -82076,7 +82076,7 @@
         <v>135385289</v>
       </c>
       <c r="B697" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -82192,7 +82192,7 @@
         <v>135385297</v>
       </c>
       <c r="B698" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -82308,7 +82308,7 @@
         <v>135422134</v>
       </c>
       <c r="B699" t="n">
-        <v>78382</v>
+        <v>78420</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -82439,7 +82439,7 @@
         <v>135422148</v>
       </c>
       <c r="B700" t="n">
-        <v>80444</v>
+        <v>80482</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -82575,7 +82575,7 @@
         <v>135422151</v>
       </c>
       <c r="B701" t="n">
-        <v>87161</v>
+        <v>87201</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -82696,7 +82696,7 @@
         <v>135385236</v>
       </c>
       <c r="B702" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -82812,7 +82812,7 @@
         <v>135385311</v>
       </c>
       <c r="B703" t="n">
-        <v>79396</v>
+        <v>79434</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -83642,7 +83642,7 @@
         <v>135351855</v>
       </c>
       <c r="B711" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -83758,7 +83758,7 @@
         <v>135382864</v>
       </c>
       <c r="B712" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -83874,7 +83874,7 @@
         <v>135385285</v>
       </c>
       <c r="B713" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -84218,7 +84218,7 @@
         <v>135385195</v>
       </c>
       <c r="B716" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135382792</v>
       </c>
       <c r="B2" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135382849</v>
       </c>
       <c r="B3" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135382856</v>
       </c>
       <c r="B4" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135382857</v>
       </c>
       <c r="B5" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135384234</v>
       </c>
       <c r="B6" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135384235</v>
       </c>
       <c r="B7" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135385147</v>
       </c>
       <c r="B8" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135385148</v>
       </c>
       <c r="B9" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1611,7 +1611,7 @@
         <v>135385226</v>
       </c>
       <c r="B10" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1727,7 +1727,7 @@
         <v>135388256</v>
       </c>
       <c r="B11" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1843,7 +1843,7 @@
         <v>135388260</v>
       </c>
       <c r="B12" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135385153</v>
       </c>
       <c r="B13" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135388254</v>
       </c>
       <c r="B14" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>135384225</v>
       </c>
       <c r="B16" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135393109</v>
       </c>
       <c r="B17" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>135440290</v>
       </c>
       <c r="B18" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>135382845</v>
       </c>
       <c r="B19" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>135356136</v>
       </c>
       <c r="B21" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>135382843</v>
       </c>
       <c r="B22" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>135388250</v>
       </c>
       <c r="B23" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>135378144</v>
       </c>
       <c r="B24" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>135378147</v>
       </c>
       <c r="B25" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>135378156</v>
       </c>
       <c r="B26" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>135378158</v>
       </c>
       <c r="B27" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>135378162</v>
       </c>
       <c r="B28" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>135378168</v>
       </c>
       <c r="B29" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>135382839</v>
       </c>
       <c r="B30" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>135382853</v>
       </c>
       <c r="B31" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>135382858</v>
       </c>
       <c r="B32" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         <v>135384223</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
         <v>135384230</v>
       </c>
       <c r="B34" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>135384236</v>
       </c>
       <c r="B35" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>135384237</v>
       </c>
       <c r="B36" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4712,7 +4712,7 @@
         <v>135385151</v>
       </c>
       <c r="B37" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>135385156</v>
       </c>
       <c r="B38" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>135393097</v>
       </c>
       <c r="B39" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>135393098</v>
       </c>
       <c r="B40" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>135393101</v>
       </c>
       <c r="B41" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>135393102</v>
       </c>
       <c r="B42" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>135440288</v>
       </c>
       <c r="B43" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5508,7 +5508,7 @@
         <v>135356134</v>
       </c>
       <c r="B44" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         <v>135378145</v>
       </c>
       <c r="B45" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5745,7 +5745,7 @@
         <v>135378149</v>
       </c>
       <c r="B46" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>135382793</v>
       </c>
       <c r="B47" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5977,7 +5977,7 @@
         <v>135382794</v>
       </c>
       <c r="B48" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6093,7 +6093,7 @@
         <v>135382795</v>
       </c>
       <c r="B49" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>135384227</v>
       </c>
       <c r="B50" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>135384232</v>
       </c>
       <c r="B51" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6441,7 +6441,7 @@
         <v>135384238</v>
       </c>
       <c r="B52" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>135388255</v>
       </c>
       <c r="B53" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>135388257</v>
       </c>
       <c r="B54" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>135393105</v>
       </c>
       <c r="B55" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>135440284</v>
       </c>
       <c r="B56" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>135440285</v>
       </c>
       <c r="B57" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>135521526</v>
       </c>
       <c r="B58" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7253,7 +7253,7 @@
         <v>135385154</v>
       </c>
       <c r="B59" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>135422122</v>
       </c>
       <c r="B60" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>135356130</v>
       </c>
       <c r="B83" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>135382846</v>
       </c>
       <c r="B84" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>135356131</v>
       </c>
       <c r="B85" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>135356139</v>
       </c>
       <c r="B86" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>135382842</v>
       </c>
       <c r="B87" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>135422127</v>
       </c>
       <c r="B88" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>135378151</v>
       </c>
       <c r="B89" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11081,7 +11081,7 @@
         <v>135378157</v>
       </c>
       <c r="B90" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>135378159</v>
       </c>
       <c r="B91" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11313,7 +11313,7 @@
         <v>135378164</v>
       </c>
       <c r="B92" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11429,7 +11429,7 @@
         <v>135378166</v>
       </c>
       <c r="B93" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>135388089</v>
       </c>
       <c r="B94" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11680,7 +11680,7 @@
         <v>135385246</v>
       </c>
       <c r="B95" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11796,7 +11796,7 @@
         <v>135385253</v>
       </c>
       <c r="B96" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11912,7 +11912,7 @@
         <v>135378182</v>
       </c>
       <c r="B97" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>135378183</v>
       </c>
       <c r="B98" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12144,7 +12144,7 @@
         <v>135378194</v>
       </c>
       <c r="B99" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>135385250</v>
       </c>
       <c r="B100" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12376,7 +12376,7 @@
         <v>135440301</v>
       </c>
       <c r="B101" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>135440302</v>
       </c>
       <c r="B102" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>135378184</v>
       </c>
       <c r="B103" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>135378188</v>
       </c>
       <c r="B104" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>135378195</v>
       </c>
       <c r="B105" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>135385242</v>
       </c>
       <c r="B106" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13072,7 +13072,7 @@
         <v>135385255</v>
       </c>
       <c r="B107" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13314,7 +13314,7 @@
         <v>135378185</v>
       </c>
       <c r="B109" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>135378190</v>
       </c>
       <c r="B110" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13546,7 +13546,7 @@
         <v>135378191</v>
       </c>
       <c r="B111" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>135378196</v>
       </c>
       <c r="B112" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
         <v>135385244</v>
       </c>
       <c r="B113" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13894,7 +13894,7 @@
         <v>135385257</v>
       </c>
       <c r="B114" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>135441451</v>
       </c>
       <c r="B115" t="n">
-        <v>92635</v>
+        <v>92662</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>135356147</v>
       </c>
       <c r="B116" t="n">
-        <v>92243</v>
+        <v>92270</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>135351866</v>
       </c>
       <c r="B117" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>135388280</v>
       </c>
       <c r="B118" t="n">
-        <v>91966</v>
+        <v>91993</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>135385183</v>
       </c>
       <c r="B119" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>135385263</v>
       </c>
       <c r="B120" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>135388278</v>
       </c>
       <c r="B121" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>135393121</v>
       </c>
       <c r="B122" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>135440316</v>
       </c>
       <c r="B123" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>135440315</v>
       </c>
       <c r="B124" t="n">
-        <v>92402</v>
+        <v>92429</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15230,7 +15230,7 @@
         <v>135356001</v>
       </c>
       <c r="B125" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15346,7 +15346,7 @@
         <v>135356004</v>
       </c>
       <c r="B126" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15462,7 +15462,7 @@
         <v>135356007</v>
       </c>
       <c r="B127" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>135382797</v>
       </c>
       <c r="B128" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15694,7 +15694,7 @@
         <v>135382799</v>
       </c>
       <c r="B129" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>135382863</v>
       </c>
       <c r="B130" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15926,7 +15926,7 @@
         <v>135382869</v>
       </c>
       <c r="B131" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16042,7 +16042,7 @@
         <v>135382871</v>
       </c>
       <c r="B132" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>135384240</v>
       </c>
       <c r="B133" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16274,7 +16274,7 @@
         <v>135384242</v>
       </c>
       <c r="B134" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16390,7 +16390,7 @@
         <v>135384247</v>
       </c>
       <c r="B135" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16506,7 +16506,7 @@
         <v>135384250</v>
       </c>
       <c r="B136" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>135384259</v>
       </c>
       <c r="B137" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>135384271</v>
       </c>
       <c r="B138" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>135384289</v>
       </c>
       <c r="B139" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16975,7 +16975,7 @@
         <v>135384292</v>
       </c>
       <c r="B140" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17091,7 +17091,7 @@
         <v>135384301</v>
       </c>
       <c r="B141" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
         <v>135384306</v>
       </c>
       <c r="B142" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>135385159</v>
       </c>
       <c r="B143" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17439,7 +17439,7 @@
         <v>135385160</v>
       </c>
       <c r="B144" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17555,7 +17555,7 @@
         <v>135385174</v>
       </c>
       <c r="B145" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
         <v>135385179</v>
       </c>
       <c r="B146" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17787,7 +17787,7 @@
         <v>135385181</v>
       </c>
       <c r="B147" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17903,7 +17903,7 @@
         <v>135385186</v>
       </c>
       <c r="B148" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18019,7 +18019,7 @@
         <v>135385187</v>
       </c>
       <c r="B149" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>135385274</v>
       </c>
       <c r="B150" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>135388266</v>
       </c>
       <c r="B151" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>135388271</v>
       </c>
       <c r="B152" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>135388277</v>
       </c>
       <c r="B153" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>135388286</v>
       </c>
       <c r="B154" t="n">
-        <v>92837</v>
+        <v>92864</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>135378203</v>
       </c>
       <c r="B155" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>135385170</v>
       </c>
       <c r="B156" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>135385278</v>
       </c>
       <c r="B157" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>135385281</v>
       </c>
       <c r="B158" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>135388265</v>
       </c>
       <c r="B159" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>135393106</v>
       </c>
       <c r="B160" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>135355999</v>
       </c>
       <c r="B161" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>135385260</v>
       </c>
       <c r="B162" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>135385265</v>
       </c>
       <c r="B163" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>135385271</v>
       </c>
       <c r="B164" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>135388289</v>
       </c>
       <c r="B165" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>135440306</v>
       </c>
       <c r="B166" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>135440310</v>
       </c>
       <c r="B167" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>135440313</v>
       </c>
       <c r="B168" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>135388275</v>
       </c>
       <c r="B169" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>135351494</v>
       </c>
       <c r="B170" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
         <v>135382872</v>
       </c>
       <c r="B171" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         <v>135382873</v>
       </c>
       <c r="B172" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20799,7 +20799,7 @@
         <v>135388268</v>
       </c>
       <c r="B173" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>135385269</v>
       </c>
       <c r="B174" t="n">
-        <v>92374</v>
+        <v>92401</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>135388288</v>
       </c>
       <c r="B175" t="n">
-        <v>92374</v>
+        <v>92401</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>135385164</v>
       </c>
       <c r="B176" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>135388281</v>
       </c>
       <c r="B177" t="n">
-        <v>92362</v>
+        <v>92389</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>135393116</v>
       </c>
       <c r="B178" t="n">
-        <v>92241</v>
+        <v>92268</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>135382805</v>
       </c>
       <c r="B179" t="n">
-        <v>92037</v>
+        <v>92064</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>135382800</v>
       </c>
       <c r="B180" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>135382809</v>
       </c>
       <c r="B181" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>135388276</v>
       </c>
       <c r="B182" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21965,7 +21965,7 @@
         <v>135349889</v>
       </c>
       <c r="B183" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>135351847</v>
       </c>
       <c r="B184" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>135351849</v>
       </c>
       <c r="B185" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -22313,7 +22313,7 @@
         <v>135351856</v>
       </c>
       <c r="B186" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>135351859</v>
       </c>
       <c r="B187" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>135356002</v>
       </c>
       <c r="B188" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>135357671</v>
       </c>
       <c r="B189" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22777,7 +22777,7 @@
         <v>135357673</v>
       </c>
       <c r="B190" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22893,7 +22893,7 @@
         <v>135378201</v>
       </c>
       <c r="B191" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>135378202</v>
       </c>
       <c r="B192" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>135378211</v>
       </c>
       <c r="B193" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>135378215</v>
       </c>
       <c r="B194" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -23357,7 +23357,7 @@
         <v>135378216</v>
       </c>
       <c r="B195" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23473,7 +23473,7 @@
         <v>135378217</v>
       </c>
       <c r="B196" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23589,7 +23589,7 @@
         <v>135378218</v>
       </c>
       <c r="B197" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23705,7 +23705,7 @@
         <v>135384241</v>
       </c>
       <c r="B198" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>135384243</v>
       </c>
       <c r="B199" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23937,7 +23937,7 @@
         <v>135384244</v>
       </c>
       <c r="B200" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>135384253</v>
       </c>
       <c r="B201" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>135384255</v>
       </c>
       <c r="B202" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24285,7 +24285,7 @@
         <v>135384262</v>
       </c>
       <c r="B203" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>135384274</v>
       </c>
       <c r="B204" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24517,7 +24517,7 @@
         <v>135384277</v>
       </c>
       <c r="B205" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>135384282</v>
       </c>
       <c r="B206" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24749,7 +24749,7 @@
         <v>135384287</v>
       </c>
       <c r="B207" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24865,7 +24865,7 @@
         <v>135384294</v>
       </c>
       <c r="B208" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24981,7 +24981,7 @@
         <v>135384296</v>
       </c>
       <c r="B209" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>135384310</v>
       </c>
       <c r="B210" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>135384313</v>
       </c>
       <c r="B211" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25329,7 +25329,7 @@
         <v>135385158</v>
       </c>
       <c r="B212" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>135385175</v>
       </c>
       <c r="B213" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25561,7 +25561,7 @@
         <v>135385182</v>
       </c>
       <c r="B214" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25677,7 +25677,7 @@
         <v>135385192</v>
       </c>
       <c r="B215" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>135385267</v>
       </c>
       <c r="B216" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>135385276</v>
       </c>
       <c r="B217" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -26025,7 +26025,7 @@
         <v>135385283</v>
       </c>
       <c r="B218" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -26141,7 +26141,7 @@
         <v>135388270</v>
       </c>
       <c r="B219" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26257,7 +26257,7 @@
         <v>135388274</v>
       </c>
       <c r="B220" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26373,7 +26373,7 @@
         <v>135388279</v>
       </c>
       <c r="B221" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>135388282</v>
       </c>
       <c r="B222" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>135388285</v>
       </c>
       <c r="B223" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26721,7 +26721,7 @@
         <v>135388292</v>
       </c>
       <c r="B224" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>135393096</v>
       </c>
       <c r="B225" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26949,7 +26949,7 @@
         <v>135440317</v>
       </c>
       <c r="B226" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>135393099</v>
       </c>
       <c r="B227" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -27177,7 +27177,7 @@
         <v>135356000</v>
       </c>
       <c r="B228" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -27293,7 +27293,7 @@
         <v>135356003</v>
       </c>
       <c r="B229" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -27409,7 +27409,7 @@
         <v>135356005</v>
       </c>
       <c r="B230" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27525,7 +27525,7 @@
         <v>135378198</v>
       </c>
       <c r="B231" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27641,7 +27641,7 @@
         <v>135378208</v>
       </c>
       <c r="B232" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>135382796</v>
       </c>
       <c r="B233" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27873,7 +27873,7 @@
         <v>135382801</v>
       </c>
       <c r="B234" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27989,7 +27989,7 @@
         <v>135382802</v>
       </c>
       <c r="B235" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>135382804</v>
       </c>
       <c r="B236" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -28221,7 +28221,7 @@
         <v>135382807</v>
       </c>
       <c r="B237" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>135382808</v>
       </c>
       <c r="B238" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28453,7 +28453,7 @@
         <v>135382810</v>
       </c>
       <c r="B239" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>135384280</v>
       </c>
       <c r="B240" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>135384308</v>
       </c>
       <c r="B241" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28801,7 +28801,7 @@
         <v>135385189</v>
       </c>
       <c r="B242" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28917,7 +28917,7 @@
         <v>135440308</v>
       </c>
       <c r="B243" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -29033,7 +29033,7 @@
         <v>135385259</v>
       </c>
       <c r="B244" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>135351853</v>
       </c>
       <c r="B259" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>135358105</v>
       </c>
       <c r="B260" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>135358106</v>
       </c>
       <c r="B261" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>135358107</v>
       </c>
       <c r="B262" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>135393104</v>
       </c>
       <c r="B263" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>135393117</v>
       </c>
       <c r="B264" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -31559,7 +31559,7 @@
         <v>135351858</v>
       </c>
       <c r="B265" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -31675,7 +31675,7 @@
         <v>135351865</v>
       </c>
       <c r="B266" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31791,7 +31791,7 @@
         <v>135378197</v>
       </c>
       <c r="B267" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>135378199</v>
       </c>
       <c r="B268" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -32023,7 +32023,7 @@
         <v>135378204</v>
       </c>
       <c r="B269" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -32139,7 +32139,7 @@
         <v>135378206</v>
       </c>
       <c r="B270" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -32255,7 +32255,7 @@
         <v>135378209</v>
       </c>
       <c r="B271" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -32371,7 +32371,7 @@
         <v>135378210</v>
       </c>
       <c r="B272" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -32487,7 +32487,7 @@
         <v>135378214</v>
       </c>
       <c r="B273" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>135385167</v>
       </c>
       <c r="B274" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>135385168</v>
       </c>
       <c r="B275" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32835,7 +32835,7 @@
         <v>135385169</v>
       </c>
       <c r="B276" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>135351803</v>
       </c>
       <c r="B277" t="n">
-        <v>92635</v>
+        <v>92662</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -33067,7 +33067,7 @@
         <v>135355993</v>
       </c>
       <c r="B278" t="n">
-        <v>83393</v>
+        <v>83420</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>135355968</v>
       </c>
       <c r="B279" t="n">
-        <v>78431</v>
+        <v>78458</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>135358086</v>
       </c>
       <c r="B280" t="n">
-        <v>89396</v>
+        <v>89423</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         <v>135351469</v>
       </c>
       <c r="B281" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>135351780</v>
       </c>
       <c r="B282" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>135351789</v>
       </c>
       <c r="B283" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>135351806</v>
       </c>
       <c r="B284" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>135354060</v>
       </c>
       <c r="B285" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>135388262</v>
       </c>
       <c r="B286" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>135349819</v>
       </c>
       <c r="B287" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -34240,7 +34240,7 @@
         <v>135351450</v>
       </c>
       <c r="B288" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>135351463</v>
       </c>
       <c r="B289" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -34472,7 +34472,7 @@
         <v>135351811</v>
       </c>
       <c r="B290" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34588,7 +34588,7 @@
         <v>135354052</v>
       </c>
       <c r="B291" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>135354057</v>
       </c>
       <c r="B292" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34820,7 +34820,7 @@
         <v>135354065</v>
       </c>
       <c r="B293" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34936,7 +34936,7 @@
         <v>135354068</v>
       </c>
       <c r="B294" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -35052,7 +35052,7 @@
         <v>135354076</v>
       </c>
       <c r="B295" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>135354085</v>
       </c>
       <c r="B296" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>135354104</v>
       </c>
       <c r="B297" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -35400,7 +35400,7 @@
         <v>135355971</v>
       </c>
       <c r="B298" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -35516,7 +35516,7 @@
         <v>135355973</v>
       </c>
       <c r="B299" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -35632,7 +35632,7 @@
         <v>135355982</v>
       </c>
       <c r="B300" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -35748,7 +35748,7 @@
         <v>135355998</v>
       </c>
       <c r="B301" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>135354091</v>
       </c>
       <c r="B303" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>135349862</v>
       </c>
       <c r="B304" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>135351749</v>
       </c>
       <c r="B305" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>135351755</v>
       </c>
       <c r="B306" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -36430,7 +36430,7 @@
         <v>135351760</v>
       </c>
       <c r="B307" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36546,7 +36546,7 @@
         <v>135351781</v>
       </c>
       <c r="B308" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>135351788</v>
       </c>
       <c r="B309" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>135351809</v>
       </c>
       <c r="B310" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>135351831</v>
       </c>
       <c r="B311" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>135354073</v>
       </c>
       <c r="B312" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>135356831</v>
       </c>
       <c r="B313" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>135351466</v>
       </c>
       <c r="B314" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>135351807</v>
       </c>
       <c r="B315" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>135349818</v>
       </c>
       <c r="B317" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37692,7 +37692,7 @@
         <v>135349820</v>
       </c>
       <c r="B318" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37808,7 +37808,7 @@
         <v>135351455</v>
       </c>
       <c r="B319" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37924,7 +37924,7 @@
         <v>135354059</v>
       </c>
       <c r="B320" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>135354063</v>
       </c>
       <c r="B321" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -38156,7 +38156,7 @@
         <v>135354106</v>
       </c>
       <c r="B322" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -38272,7 +38272,7 @@
         <v>135349834</v>
       </c>
       <c r="B323" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>135351791</v>
       </c>
       <c r="B324" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -38505,7 +38505,7 @@
         <v>135355992</v>
       </c>
       <c r="B325" t="n">
-        <v>83403</v>
+        <v>83430</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>135351464</v>
       </c>
       <c r="B327" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>135351748</v>
       </c>
       <c r="B328" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -38955,7 +38955,7 @@
         <v>135351490</v>
       </c>
       <c r="B329" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -39071,7 +39071,7 @@
         <v>135351491</v>
       </c>
       <c r="B330" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -39192,7 +39192,7 @@
         <v>135354094</v>
       </c>
       <c r="B331" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -39323,7 +39323,7 @@
         <v>135354098</v>
       </c>
       <c r="B332" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>135354100</v>
       </c>
       <c r="B333" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39555,7 +39555,7 @@
         <v>135355991</v>
       </c>
       <c r="B334" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39671,7 +39671,7 @@
         <v>135357665</v>
       </c>
       <c r="B335" t="n">
-        <v>80527</v>
+        <v>80554</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>135351473</v>
       </c>
       <c r="B336" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>135355983</v>
       </c>
       <c r="B337" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>135358094</v>
       </c>
       <c r="B338" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>135351457</v>
       </c>
       <c r="B339" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>135351471</v>
       </c>
       <c r="B340" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>135358076</v>
       </c>
       <c r="B341" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>135388263</v>
       </c>
       <c r="B342" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>135349829</v>
       </c>
       <c r="B343" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40715,7 +40715,7 @@
         <v>135349837</v>
       </c>
       <c r="B344" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>135349838</v>
       </c>
       <c r="B345" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40947,7 +40947,7 @@
         <v>135349843</v>
       </c>
       <c r="B346" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -41063,7 +41063,7 @@
         <v>135349844</v>
       </c>
       <c r="B347" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -41179,7 +41179,7 @@
         <v>135349846</v>
       </c>
       <c r="B348" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -41295,7 +41295,7 @@
         <v>135349848</v>
       </c>
       <c r="B349" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -41411,7 +41411,7 @@
         <v>135349849</v>
       </c>
       <c r="B350" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -41527,7 +41527,7 @@
         <v>135349853</v>
       </c>
       <c r="B351" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -41643,7 +41643,7 @@
         <v>135349855</v>
       </c>
       <c r="B352" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>135349858</v>
       </c>
       <c r="B353" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41875,7 +41875,7 @@
         <v>135349864</v>
       </c>
       <c r="B354" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>135349865</v>
       </c>
       <c r="B355" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -42107,7 +42107,7 @@
         <v>135349868</v>
       </c>
       <c r="B356" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -42223,7 +42223,7 @@
         <v>135349870</v>
       </c>
       <c r="B357" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -42339,7 +42339,7 @@
         <v>135349877</v>
       </c>
       <c r="B358" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42455,7 +42455,7 @@
         <v>135349882</v>
       </c>
       <c r="B359" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -42571,7 +42571,7 @@
         <v>135351447</v>
       </c>
       <c r="B360" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42687,7 +42687,7 @@
         <v>135351448</v>
       </c>
       <c r="B361" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42803,7 +42803,7 @@
         <v>135351452</v>
       </c>
       <c r="B362" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -42919,7 +42919,7 @@
         <v>135351453</v>
       </c>
       <c r="B363" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>135351456</v>
       </c>
       <c r="B364" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -43151,7 +43151,7 @@
         <v>135351458</v>
       </c>
       <c r="B365" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -43267,7 +43267,7 @@
         <v>135351461</v>
       </c>
       <c r="B366" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -43383,7 +43383,7 @@
         <v>135351465</v>
       </c>
       <c r="B367" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -43499,7 +43499,7 @@
         <v>135351468</v>
       </c>
       <c r="B368" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>135351741</v>
       </c>
       <c r="B369" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -43731,7 +43731,7 @@
         <v>135351744</v>
       </c>
       <c r="B370" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -43847,7 +43847,7 @@
         <v>135351747</v>
       </c>
       <c r="B371" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -43963,7 +43963,7 @@
         <v>135351759</v>
       </c>
       <c r="B372" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>135351765</v>
       </c>
       <c r="B373" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>135351767</v>
       </c>
       <c r="B374" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -44311,7 +44311,7 @@
         <v>135351769</v>
       </c>
       <c r="B375" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -44427,7 +44427,7 @@
         <v>135351777</v>
       </c>
       <c r="B376" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -44543,7 +44543,7 @@
         <v>135351783</v>
       </c>
       <c r="B377" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -44659,7 +44659,7 @@
         <v>135351787</v>
       </c>
       <c r="B378" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -44775,7 +44775,7 @@
         <v>135351790</v>
       </c>
       <c r="B379" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>135351792</v>
       </c>
       <c r="B380" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -45020,7 +45020,7 @@
         <v>135351794</v>
       </c>
       <c r="B381" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -45136,7 +45136,7 @@
         <v>135351801</v>
       </c>
       <c r="B382" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -45252,7 +45252,7 @@
         <v>135351802</v>
       </c>
       <c r="B383" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -45368,7 +45368,7 @@
         <v>135351804</v>
       </c>
       <c r="B384" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -45484,7 +45484,7 @@
         <v>135351808</v>
       </c>
       <c r="B385" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -45600,7 +45600,7 @@
         <v>135351812</v>
       </c>
       <c r="B386" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -45716,7 +45716,7 @@
         <v>135351824</v>
       </c>
       <c r="B387" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -45832,7 +45832,7 @@
         <v>135351825</v>
       </c>
       <c r="B388" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -45948,7 +45948,7 @@
         <v>135351826</v>
       </c>
       <c r="B389" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -46064,7 +46064,7 @@
         <v>135351827</v>
       </c>
       <c r="B390" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -46180,7 +46180,7 @@
         <v>135351828</v>
       </c>
       <c r="B391" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -46296,7 +46296,7 @@
         <v>135351837</v>
       </c>
       <c r="B392" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -46412,7 +46412,7 @@
         <v>135351839</v>
       </c>
       <c r="B393" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>135351845</v>
       </c>
       <c r="B394" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -46644,7 +46644,7 @@
         <v>135354048</v>
       </c>
       <c r="B395" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -46760,7 +46760,7 @@
         <v>135354054</v>
       </c>
       <c r="B396" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -46876,7 +46876,7 @@
         <v>135354056</v>
       </c>
       <c r="B397" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -46992,7 +46992,7 @@
         <v>135354062</v>
       </c>
       <c r="B398" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -47108,7 +47108,7 @@
         <v>135354064</v>
       </c>
       <c r="B399" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -47224,7 +47224,7 @@
         <v>135354067</v>
       </c>
       <c r="B400" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -47340,7 +47340,7 @@
         <v>135354070</v>
       </c>
       <c r="B401" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -47456,7 +47456,7 @@
         <v>135354074</v>
       </c>
       <c r="B402" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -47572,7 +47572,7 @@
         <v>135354077</v>
       </c>
       <c r="B403" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -47688,7 +47688,7 @@
         <v>135354079</v>
       </c>
       <c r="B404" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -47804,7 +47804,7 @@
         <v>135354082</v>
       </c>
       <c r="B405" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -47920,7 +47920,7 @@
         <v>135354103</v>
       </c>
       <c r="B406" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -48036,7 +48036,7 @@
         <v>135355975</v>
       </c>
       <c r="B407" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -48152,7 +48152,7 @@
         <v>135355978</v>
       </c>
       <c r="B408" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -48268,7 +48268,7 @@
         <v>135355979</v>
       </c>
       <c r="B409" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>135355980</v>
       </c>
       <c r="B410" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -48500,7 +48500,7 @@
         <v>135355981</v>
       </c>
       <c r="B411" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -48616,7 +48616,7 @@
         <v>135355984</v>
       </c>
       <c r="B412" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -48732,7 +48732,7 @@
         <v>135355985</v>
       </c>
       <c r="B413" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -48853,7 +48853,7 @@
         <v>135355995</v>
       </c>
       <c r="B414" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -48969,7 +48969,7 @@
         <v>135356827</v>
       </c>
       <c r="B415" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -49085,7 +49085,7 @@
         <v>135356828</v>
       </c>
       <c r="B416" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -49201,7 +49201,7 @@
         <v>135357661</v>
       </c>
       <c r="B417" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -49317,7 +49317,7 @@
         <v>135358079</v>
       </c>
       <c r="B418" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -49433,7 +49433,7 @@
         <v>135358092</v>
       </c>
       <c r="B419" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -49549,7 +49549,7 @@
         <v>135358098</v>
       </c>
       <c r="B420" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -49665,7 +49665,7 @@
         <v>135388259</v>
       </c>
       <c r="B421" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -49781,7 +49781,7 @@
         <v>135388261</v>
       </c>
       <c r="B422" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -49897,7 +49897,7 @@
         <v>135355996</v>
       </c>
       <c r="B423" t="n">
-        <v>78814</v>
+        <v>78841</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>135349814</v>
       </c>
       <c r="B424" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -50129,7 +50129,7 @@
         <v>135349815</v>
       </c>
       <c r="B425" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -50245,7 +50245,7 @@
         <v>135349823</v>
       </c>
       <c r="B426" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -50361,7 +50361,7 @@
         <v>135349824</v>
       </c>
       <c r="B427" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -50477,7 +50477,7 @@
         <v>135349831</v>
       </c>
       <c r="B428" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -50593,7 +50593,7 @@
         <v>135349840</v>
       </c>
       <c r="B429" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -50709,7 +50709,7 @@
         <v>135349850</v>
       </c>
       <c r="B430" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -50825,7 +50825,7 @@
         <v>135349883</v>
       </c>
       <c r="B431" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>135351460</v>
       </c>
       <c r="B432" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -51057,7 +51057,7 @@
         <v>135351462</v>
       </c>
       <c r="B433" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -51173,7 +51173,7 @@
         <v>135351751</v>
       </c>
       <c r="B434" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -51289,7 +51289,7 @@
         <v>135351758</v>
       </c>
       <c r="B435" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -51405,7 +51405,7 @@
         <v>135351770</v>
       </c>
       <c r="B436" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -51521,7 +51521,7 @@
         <v>135351797</v>
       </c>
       <c r="B437" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -51637,7 +51637,7 @@
         <v>135351842</v>
       </c>
       <c r="B438" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -51753,7 +51753,7 @@
         <v>135354084</v>
       </c>
       <c r="B439" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -51869,7 +51869,7 @@
         <v>135354105</v>
       </c>
       <c r="B440" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -51985,7 +51985,7 @@
         <v>135355969</v>
       </c>
       <c r="B441" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -52101,7 +52101,7 @@
         <v>135355976</v>
       </c>
       <c r="B442" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -52217,7 +52217,7 @@
         <v>135355977</v>
       </c>
       <c r="B443" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -52333,7 +52333,7 @@
         <v>135355986</v>
       </c>
       <c r="B444" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -52449,7 +52449,7 @@
         <v>135351492</v>
       </c>
       <c r="B445" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -52570,7 +52570,7 @@
         <v>135354096</v>
       </c>
       <c r="B446" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52701,7 +52701,7 @@
         <v>135354099</v>
       </c>
       <c r="B447" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -52817,7 +52817,7 @@
         <v>135349875</v>
       </c>
       <c r="B448" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -52938,7 +52938,7 @@
         <v>135351482</v>
       </c>
       <c r="B449" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -53074,7 +53074,7 @@
         <v>135351483</v>
       </c>
       <c r="B450" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -53190,7 +53190,7 @@
         <v>135351486</v>
       </c>
       <c r="B451" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -53306,7 +53306,7 @@
         <v>135351774</v>
       </c>
       <c r="B452" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -53426,7 +53426,7 @@
         <v>135355988</v>
       </c>
       <c r="B453" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -53542,7 +53542,7 @@
         <v>135355994</v>
       </c>
       <c r="B454" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -53658,7 +53658,7 @@
         <v>135351481</v>
       </c>
       <c r="B455" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -53774,7 +53774,7 @@
         <v>135351487</v>
       </c>
       <c r="B456" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -53890,7 +53890,7 @@
         <v>135354097</v>
       </c>
       <c r="B457" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -54006,7 +54006,7 @@
         <v>135355990</v>
       </c>
       <c r="B458" t="n">
-        <v>80537</v>
+        <v>80564</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>135351484</v>
       </c>
       <c r="B459" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -54238,7 +54238,7 @@
         <v>135351485</v>
       </c>
       <c r="B460" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -54354,7 +54354,7 @@
         <v>135354081</v>
       </c>
       <c r="B461" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -54470,7 +54470,7 @@
         <v>135355987</v>
       </c>
       <c r="B462" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -54586,7 +54586,7 @@
         <v>135358090</v>
       </c>
       <c r="B463" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -54702,7 +54702,7 @@
         <v>135358091</v>
       </c>
       <c r="B464" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>135351479</v>
       </c>
       <c r="B490" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -57989,7 +57989,7 @@
         <v>135349830</v>
       </c>
       <c r="B491" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -58110,7 +58110,7 @@
         <v>135351476</v>
       </c>
       <c r="B492" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>135351752</v>
       </c>
       <c r="B493" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>135358077</v>
       </c>
       <c r="B494" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -58458,7 +58458,7 @@
         <v>135358087</v>
       </c>
       <c r="B495" t="n">
-        <v>98110</v>
+        <v>98137</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -58574,7 +58574,7 @@
         <v>135351449</v>
       </c>
       <c r="B496" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>135351477</v>
       </c>
       <c r="B497" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>135357666</v>
       </c>
       <c r="B498" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>135357670</v>
       </c>
       <c r="B499" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -59038,7 +59038,7 @@
         <v>135358081</v>
       </c>
       <c r="B500" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -59154,7 +59154,7 @@
         <v>135358082</v>
       </c>
       <c r="B501" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>135358085</v>
       </c>
       <c r="B502" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -59386,7 +59386,7 @@
         <v>135358089</v>
       </c>
       <c r="B503" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>135349874</v>
       </c>
       <c r="B504" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -59623,7 +59623,7 @@
         <v>135351489</v>
       </c>
       <c r="B505" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -59739,7 +59739,7 @@
         <v>135351743</v>
       </c>
       <c r="B506" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -59855,7 +59855,7 @@
         <v>135351773</v>
       </c>
       <c r="B507" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>135354090</v>
       </c>
       <c r="B508" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -60087,7 +60087,7 @@
         <v>135356125</v>
       </c>
       <c r="B509" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -60208,7 +60208,7 @@
         <v>135356126</v>
       </c>
       <c r="B510" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -60324,7 +60324,7 @@
         <v>135358093</v>
       </c>
       <c r="B511" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>135358096</v>
       </c>
       <c r="B512" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -60556,7 +60556,7 @@
         <v>135358099</v>
       </c>
       <c r="B513" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -60672,7 +60672,7 @@
         <v>135358100</v>
       </c>
       <c r="B514" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -60788,7 +60788,7 @@
         <v>135358101</v>
       </c>
       <c r="B515" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -60904,7 +60904,7 @@
         <v>135358102</v>
       </c>
       <c r="B516" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -61020,7 +61020,7 @@
         <v>135351475</v>
       </c>
       <c r="B517" t="n">
-        <v>100854</v>
+        <v>100881</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -61136,7 +61136,7 @@
         <v>135349813</v>
       </c>
       <c r="B518" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -61252,7 +61252,7 @@
         <v>135349816</v>
       </c>
       <c r="B519" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -61368,7 +61368,7 @@
         <v>135349821</v>
       </c>
       <c r="B520" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -61484,7 +61484,7 @@
         <v>135349826</v>
       </c>
       <c r="B521" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -61600,7 +61600,7 @@
         <v>135349827</v>
       </c>
       <c r="B522" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -61716,7 +61716,7 @@
         <v>135349832</v>
       </c>
       <c r="B523" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -61832,7 +61832,7 @@
         <v>135349841</v>
       </c>
       <c r="B524" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -61948,7 +61948,7 @@
         <v>135349845</v>
       </c>
       <c r="B525" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -62064,7 +62064,7 @@
         <v>135349851</v>
       </c>
       <c r="B526" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -62180,7 +62180,7 @@
         <v>135349854</v>
       </c>
       <c r="B527" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -62296,7 +62296,7 @@
         <v>135349856</v>
       </c>
       <c r="B528" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -62412,7 +62412,7 @@
         <v>135349859</v>
       </c>
       <c r="B529" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -62528,7 +62528,7 @@
         <v>135349869</v>
       </c>
       <c r="B530" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -62644,7 +62644,7 @@
         <v>135349873</v>
       </c>
       <c r="B531" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -62760,7 +62760,7 @@
         <v>135349876</v>
       </c>
       <c r="B532" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -62876,7 +62876,7 @@
         <v>135349878</v>
       </c>
       <c r="B533" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -62992,7 +62992,7 @@
         <v>135349880</v>
       </c>
       <c r="B534" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -63108,7 +63108,7 @@
         <v>135349884</v>
       </c>
       <c r="B535" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -63224,7 +63224,7 @@
         <v>135349885</v>
       </c>
       <c r="B536" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -63340,7 +63340,7 @@
         <v>135349886</v>
       </c>
       <c r="B537" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -63456,7 +63456,7 @@
         <v>135349887</v>
       </c>
       <c r="B538" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -63572,7 +63572,7 @@
         <v>135351451</v>
       </c>
       <c r="B539" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -63688,7 +63688,7 @@
         <v>135351745</v>
       </c>
       <c r="B540" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -63804,7 +63804,7 @@
         <v>135351757</v>
       </c>
       <c r="B541" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -63920,7 +63920,7 @@
         <v>135351763</v>
       </c>
       <c r="B542" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -64036,7 +64036,7 @@
         <v>135351768</v>
       </c>
       <c r="B543" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -64152,7 +64152,7 @@
         <v>135351771</v>
       </c>
       <c r="B544" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -64268,7 +64268,7 @@
         <v>135351776</v>
       </c>
       <c r="B545" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -64384,7 +64384,7 @@
         <v>135351784</v>
       </c>
       <c r="B546" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -64500,7 +64500,7 @@
         <v>135351798</v>
       </c>
       <c r="B547" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -64616,7 +64616,7 @@
         <v>135351800</v>
       </c>
       <c r="B548" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -64732,7 +64732,7 @@
         <v>135351840</v>
       </c>
       <c r="B549" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -64848,7 +64848,7 @@
         <v>135354046</v>
       </c>
       <c r="B550" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -64964,7 +64964,7 @@
         <v>135354061</v>
       </c>
       <c r="B551" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -65080,7 +65080,7 @@
         <v>135354078</v>
       </c>
       <c r="B552" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -65196,7 +65196,7 @@
         <v>135354083</v>
       </c>
       <c r="B553" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -65312,7 +65312,7 @@
         <v>135358078</v>
       </c>
       <c r="B554" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -65428,7 +65428,7 @@
         <v>135351742</v>
       </c>
       <c r="B555" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -65544,7 +65544,7 @@
         <v>135354071</v>
       </c>
       <c r="B556" t="n">
-        <v>92365</v>
+        <v>92392</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65688,7 +65688,7 @@
         <v>135422147</v>
       </c>
       <c r="B557" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -65824,7 +65824,7 @@
         <v>135422165</v>
       </c>
       <c r="B558" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -65960,7 +65960,7 @@
         <v>135349920</v>
       </c>
       <c r="B559" t="n">
-        <v>92411</v>
+        <v>92438</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -66080,7 +66080,7 @@
         <v>135440323</v>
       </c>
       <c r="B560" t="n">
-        <v>83390</v>
+        <v>83417</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -66298,7 +66298,7 @@
         <v>135349899</v>
       </c>
       <c r="B562" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -66414,7 +66414,7 @@
         <v>135393122</v>
       </c>
       <c r="B563" t="n">
-        <v>92287</v>
+        <v>92314</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -66526,7 +66526,7 @@
         <v>135385302</v>
       </c>
       <c r="B564" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -66642,7 +66642,7 @@
         <v>135385308</v>
       </c>
       <c r="B565" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -66758,7 +66758,7 @@
         <v>135385315</v>
       </c>
       <c r="B566" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -66874,7 +66874,7 @@
         <v>135385319</v>
       </c>
       <c r="B567" t="n">
-        <v>79490</v>
+        <v>79517</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -67194,7 +67194,7 @@
         <v>135349895</v>
       </c>
       <c r="B570" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -67310,7 +67310,7 @@
         <v>135349906</v>
       </c>
       <c r="B571" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -67426,7 +67426,7 @@
         <v>135385306</v>
       </c>
       <c r="B572" t="n">
-        <v>92012</v>
+        <v>92039</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -67542,7 +67542,7 @@
         <v>135385240</v>
       </c>
       <c r="B573" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -67658,7 +67658,7 @@
         <v>135393114</v>
       </c>
       <c r="B574" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -67770,7 +67770,7 @@
         <v>135440300</v>
       </c>
       <c r="B575" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -67886,7 +67886,7 @@
         <v>135393138</v>
       </c>
       <c r="B576" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -67998,7 +67998,7 @@
         <v>135393158</v>
       </c>
       <c r="B577" t="n">
-        <v>92030</v>
+        <v>92057</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -68620,7 +68620,7 @@
         <v>135382862</v>
       </c>
       <c r="B583" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -68736,7 +68736,7 @@
         <v>135385323</v>
       </c>
       <c r="B584" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -68852,7 +68852,7 @@
         <v>135422133</v>
       </c>
       <c r="B585" t="n">
-        <v>83262</v>
+        <v>83289</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -68983,7 +68983,7 @@
         <v>135422136</v>
       </c>
       <c r="B586" t="n">
-        <v>92371</v>
+        <v>92398</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -69216,7 +69216,7 @@
         <v>135349911</v>
       </c>
       <c r="B588" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -69332,7 +69332,7 @@
         <v>135393155</v>
       </c>
       <c r="B589" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -69444,7 +69444,7 @@
         <v>135349919</v>
       </c>
       <c r="B590" t="n">
-        <v>92412</v>
+        <v>92439</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -69560,7 +69560,7 @@
         <v>135349892</v>
       </c>
       <c r="B591" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -69676,7 +69676,7 @@
         <v>135349905</v>
       </c>
       <c r="B592" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -69792,7 +69792,7 @@
         <v>135385238</v>
       </c>
       <c r="B593" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -69908,7 +69908,7 @@
         <v>135388294</v>
       </c>
       <c r="B594" t="n">
-        <v>93131</v>
+        <v>93158</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -70033,7 +70033,7 @@
         <v>135388298</v>
       </c>
       <c r="B595" t="n">
-        <v>93131</v>
+        <v>93158</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -70158,7 +70158,7 @@
         <v>135349898</v>
       </c>
       <c r="B596" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -70274,7 +70274,7 @@
         <v>135349900</v>
       </c>
       <c r="B597" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -70390,7 +70390,7 @@
         <v>135349903</v>
       </c>
       <c r="B598" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -70506,7 +70506,7 @@
         <v>135349908</v>
       </c>
       <c r="B599" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -70622,7 +70622,7 @@
         <v>135349917</v>
       </c>
       <c r="B600" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -70738,7 +70738,7 @@
         <v>135378171</v>
       </c>
       <c r="B601" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -70854,7 +70854,7 @@
         <v>135378177</v>
       </c>
       <c r="B602" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -70970,7 +70970,7 @@
         <v>135384317</v>
       </c>
       <c r="B603" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -71086,7 +71086,7 @@
         <v>135384321</v>
       </c>
       <c r="B604" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -71202,7 +71202,7 @@
         <v>135384326</v>
       </c>
       <c r="B605" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -71318,7 +71318,7 @@
         <v>135385234</v>
       </c>
       <c r="B606" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -71434,7 +71434,7 @@
         <v>135385291</v>
       </c>
       <c r="B607" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -71550,7 +71550,7 @@
         <v>135385299</v>
       </c>
       <c r="B608" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -71666,7 +71666,7 @@
         <v>135385304</v>
       </c>
       <c r="B609" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -71782,7 +71782,7 @@
         <v>135385313</v>
       </c>
       <c r="B610" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -71898,7 +71898,7 @@
         <v>135385317</v>
       </c>
       <c r="B611" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -72014,7 +72014,7 @@
         <v>135385321</v>
       </c>
       <c r="B612" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -72130,7 +72130,7 @@
         <v>135385325</v>
       </c>
       <c r="B613" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -72246,7 +72246,7 @@
         <v>135393119</v>
       </c>
       <c r="B614" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -72358,7 +72358,7 @@
         <v>135393137</v>
       </c>
       <c r="B615" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -72470,7 +72470,7 @@
         <v>135422129</v>
       </c>
       <c r="B616" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -72586,7 +72586,7 @@
         <v>135440298</v>
       </c>
       <c r="B617" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -72702,7 +72702,7 @@
         <v>135378172</v>
       </c>
       <c r="B618" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -72818,7 +72818,7 @@
         <v>135378176</v>
       </c>
       <c r="B619" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -72934,7 +72934,7 @@
         <v>135385230</v>
       </c>
       <c r="B620" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -73050,7 +73050,7 @@
         <v>135385287</v>
       </c>
       <c r="B621" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -73166,7 +73166,7 @@
         <v>135385295</v>
       </c>
       <c r="B622" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -73282,7 +73282,7 @@
         <v>135393123</v>
       </c>
       <c r="B623" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -73394,7 +73394,7 @@
         <v>135422132</v>
       </c>
       <c r="B624" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -73525,7 +73525,7 @@
         <v>135440297</v>
       </c>
       <c r="B625" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -73641,7 +73641,7 @@
         <v>135385194</v>
       </c>
       <c r="B626" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -75679,7 +75679,7 @@
         <v>135351869</v>
       </c>
       <c r="B643" t="n">
-        <v>99141</v>
+        <v>99168</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -75795,7 +75795,7 @@
         <v>135422162</v>
       </c>
       <c r="B644" t="n">
-        <v>99141</v>
+        <v>99168</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -75925,7 +75925,7 @@
         <v>135351871</v>
       </c>
       <c r="B645" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -76041,7 +76041,7 @@
         <v>135385327</v>
       </c>
       <c r="B646" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -76157,7 +76157,7 @@
         <v>135393145</v>
       </c>
       <c r="B647" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -76269,7 +76269,7 @@
         <v>135422156</v>
       </c>
       <c r="B648" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -76390,7 +76390,7 @@
         <v>135422160</v>
       </c>
       <c r="B649" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -76511,7 +76511,7 @@
         <v>135523737</v>
       </c>
       <c r="B650" t="n">
-        <v>99244</v>
+        <v>99271</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -76632,7 +76632,7 @@
         <v>135422166</v>
       </c>
       <c r="B651" t="n">
-        <v>107998</v>
+        <v>108025</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -76758,7 +76758,7 @@
         <v>135523654</v>
       </c>
       <c r="B652" t="n">
-        <v>107998</v>
+        <v>108025</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -76879,7 +76879,7 @@
         <v>135422142</v>
       </c>
       <c r="B653" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -77000,7 +77000,7 @@
         <v>135393157</v>
       </c>
       <c r="B654" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -77112,7 +77112,7 @@
         <v>135422154</v>
       </c>
       <c r="B655" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -77233,7 +77233,7 @@
         <v>135422169</v>
       </c>
       <c r="B656" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -77354,7 +77354,7 @@
         <v>135393151</v>
       </c>
       <c r="B657" t="n">
-        <v>110079</v>
+        <v>110106</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -77466,7 +77466,7 @@
         <v>135351874</v>
       </c>
       <c r="B658" t="n">
-        <v>110206</v>
+        <v>110233</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -77582,7 +77582,7 @@
         <v>135349921</v>
       </c>
       <c r="B659" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -77707,7 +77707,7 @@
         <v>135349909</v>
       </c>
       <c r="B660" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -77828,7 +77828,7 @@
         <v>135384319</v>
       </c>
       <c r="B661" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -77944,7 +77944,7 @@
         <v>135384324</v>
       </c>
       <c r="B662" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -78060,7 +78060,7 @@
         <v>135388296</v>
       </c>
       <c r="B663" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -78176,7 +78176,7 @@
         <v>135393149</v>
       </c>
       <c r="B664" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -78288,7 +78288,7 @@
         <v>135422137</v>
       </c>
       <c r="B665" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -78404,7 +78404,7 @@
         <v>135422150</v>
       </c>
       <c r="B666" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -78525,7 +78525,7 @@
         <v>135422155</v>
       </c>
       <c r="B667" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -78646,7 +78646,7 @@
         <v>135422159</v>
       </c>
       <c r="B668" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -78767,7 +78767,7 @@
         <v>135440319</v>
       </c>
       <c r="B669" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -78883,7 +78883,7 @@
         <v>135422167</v>
       </c>
       <c r="B670" t="n">
-        <v>98098</v>
+        <v>98125</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -79000,7 +79000,7 @@
         <v>135523644</v>
       </c>
       <c r="B671" t="n">
-        <v>98098</v>
+        <v>98125</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -79117,7 +79117,7 @@
         <v>135385157</v>
       </c>
       <c r="B672" t="n">
-        <v>98107</v>
+        <v>98134</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -79233,7 +79233,7 @@
         <v>135349896</v>
       </c>
       <c r="B673" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -79349,7 +79349,7 @@
         <v>135349910</v>
       </c>
       <c r="B674" t="n">
-        <v>103815</v>
+        <v>103842</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -79465,7 +79465,7 @@
         <v>135356148</v>
       </c>
       <c r="B675" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -79581,7 +79581,7 @@
         <v>135393154</v>
       </c>
       <c r="B676" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -79693,7 +79693,7 @@
         <v>135422138</v>
       </c>
       <c r="B677" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -79828,7 +79828,7 @@
         <v>135422163</v>
       </c>
       <c r="B678" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -79963,7 +79963,7 @@
         <v>135422168</v>
       </c>
       <c r="B679" t="n">
-        <v>104761</v>
+        <v>104788</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -80098,7 +80098,7 @@
         <v>135393126</v>
       </c>
       <c r="B680" t="n">
-        <v>100854</v>
+        <v>100881</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -80210,7 +80210,7 @@
         <v>135388299</v>
       </c>
       <c r="B681" t="n">
-        <v>102922</v>
+        <v>102949</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -80326,7 +80326,7 @@
         <v>135422143</v>
       </c>
       <c r="B682" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -80447,7 +80447,7 @@
         <v>135351867</v>
       </c>
       <c r="B683" t="n">
-        <v>99245</v>
+        <v>99272</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -80560,7 +80560,7 @@
         <v>135349891</v>
       </c>
       <c r="B684" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -80676,7 +80676,7 @@
         <v>135393129</v>
       </c>
       <c r="B685" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -80788,7 +80788,7 @@
         <v>135393131</v>
       </c>
       <c r="B686" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -80900,7 +80900,7 @@
         <v>135393150</v>
       </c>
       <c r="B687" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -81012,7 +81012,7 @@
         <v>135422139</v>
       </c>
       <c r="B688" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -81133,7 +81133,7 @@
         <v>135422140</v>
       </c>
       <c r="B689" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -81254,7 +81254,7 @@
         <v>135422152</v>
       </c>
       <c r="B690" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -81375,7 +81375,7 @@
         <v>135523597</v>
       </c>
       <c r="B691" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -81496,7 +81496,7 @@
         <v>135378173</v>
       </c>
       <c r="B692" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -81612,7 +81612,7 @@
         <v>135378175</v>
       </c>
       <c r="B693" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -81728,7 +81728,7 @@
         <v>135378179</v>
       </c>
       <c r="B694" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -81844,7 +81844,7 @@
         <v>135378181</v>
       </c>
       <c r="B695" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -81960,7 +81960,7 @@
         <v>135385232</v>
       </c>
       <c r="B696" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -82076,7 +82076,7 @@
         <v>135385289</v>
       </c>
       <c r="B697" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -82192,7 +82192,7 @@
         <v>135385297</v>
       </c>
       <c r="B698" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -82308,7 +82308,7 @@
         <v>135422134</v>
       </c>
       <c r="B699" t="n">
-        <v>78420</v>
+        <v>78447</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -82439,7 +82439,7 @@
         <v>135422148</v>
       </c>
       <c r="B700" t="n">
-        <v>80482</v>
+        <v>80509</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -82575,7 +82575,7 @@
         <v>135422151</v>
       </c>
       <c r="B701" t="n">
-        <v>87201</v>
+        <v>87228</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -82696,7 +82696,7 @@
         <v>135385236</v>
       </c>
       <c r="B702" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -82812,7 +82812,7 @@
         <v>135385311</v>
       </c>
       <c r="B703" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -83642,7 +83642,7 @@
         <v>135351855</v>
       </c>
       <c r="B711" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -83758,7 +83758,7 @@
         <v>135382864</v>
       </c>
       <c r="B712" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -83874,7 +83874,7 @@
         <v>135385285</v>
       </c>
       <c r="B713" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -77746,7 +77746,7 @@
         <v>608014</v>
       </c>
       <c r="R660" t="n">
-        <v>7309639</v>
+        <v>7309638</v>
       </c>
       <c r="S660" t="n">
         <v>3</v>
@@ -79384,7 +79384,7 @@
         <v>608014</v>
       </c>
       <c r="R674" t="n">
-        <v>7309639</v>
+        <v>7309638</v>
       </c>
       <c r="S674" t="n">
         <v>3</v>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -77746,7 +77746,7 @@
         <v>608014</v>
       </c>
       <c r="R660" t="n">
-        <v>7309638</v>
+        <v>7309639</v>
       </c>
       <c r="S660" t="n">
         <v>3</v>
@@ -79384,7 +79384,7 @@
         <v>608014</v>
       </c>
       <c r="R674" t="n">
-        <v>7309638</v>
+        <v>7309639</v>
       </c>
       <c r="S674" t="n">
         <v>3</v>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -33525,7 +33525,7 @@
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
@@ -39052,7 +39052,7 @@
       </c>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr">
@@ -39173,7 +39173,7 @@
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
@@ -43596,7 +43596,7 @@
       </c>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
@@ -53055,7 +53055,7 @@
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr">
@@ -53871,7 +53871,7 @@
       </c>
       <c r="AX456" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
         </is>
       </c>
       <c r="AY456" t="inlineStr">
@@ -56018,7 +56018,7 @@
       </c>
       <c r="AX474" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
         </is>
       </c>
       <c r="AY474" t="inlineStr">
@@ -57970,7 +57970,7 @@
       </c>
       <c r="AX490" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY490" t="inlineStr">
@@ -58207,7 +58207,7 @@
       </c>
       <c r="AX492" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY492" t="inlineStr">
@@ -58787,7 +58787,7 @@
       </c>
       <c r="AX497" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
+          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY497" t="inlineStr">
@@ -77746,7 +77746,7 @@
         <v>608014</v>
       </c>
       <c r="R660" t="n">
-        <v>7309638</v>
+        <v>7309639</v>
       </c>
       <c r="S660" t="n">
         <v>3</v>
@@ -79384,7 +79384,7 @@
         <v>608014</v>
       </c>
       <c r="R674" t="n">
-        <v>7309638</v>
+        <v>7309639</v>
       </c>
       <c r="S674" t="n">
         <v>3</v>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -33525,7 +33525,7 @@
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
@@ -39052,7 +39052,7 @@
       </c>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr">
@@ -39173,7 +39173,7 @@
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
@@ -43596,7 +43596,7 @@
       </c>
       <c r="AX368" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY368" t="inlineStr">
@@ -53055,7 +53055,7 @@
       </c>
       <c r="AX449" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY449" t="inlineStr">
@@ -53871,7 +53871,7 @@
       </c>
       <c r="AX456" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY456" t="inlineStr">
@@ -56018,7 +56018,7 @@
       </c>
       <c r="AX474" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY474" t="inlineStr">
@@ -57970,7 +57970,7 @@
       </c>
       <c r="AX490" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY490" t="inlineStr">
@@ -58207,7 +58207,7 @@
       </c>
       <c r="AX492" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY492" t="inlineStr">
@@ -58787,7 +58787,7 @@
       </c>
       <c r="AX497" t="inlineStr">
         <is>
-          <t>Cecilia Goldkuhl, Linda-Marie Grahn, Martin Axegård, Johan Råghall, Maja Rancic, Petya Valcheva, Mattias Dalkvist, Torun Jacobsson, Tyr Nilsson</t>
+          <t>Cecilia Goldkuhl, Tyr Nilsson, Torun Jacobsson, Mattias Dalkvist, Petya Valcheva, Maja Rancic, Johan Råghall, Martin Axegård, Linda-Marie Grahn</t>
         </is>
       </c>
       <c r="AY497" t="inlineStr">

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135382792</v>
       </c>
       <c r="B2" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1959,7 +1959,7 @@
         <v>135385153</v>
       </c>
       <c r="B13" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2075,7 +2075,7 @@
         <v>135388254</v>
       </c>
       <c r="B14" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>135384225</v>
       </c>
       <c r="B16" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135393109</v>
       </c>
       <c r="B17" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>135440290</v>
       </c>
       <c r="B18" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>135382845</v>
       </c>
       <c r="B19" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>135382843</v>
       </c>
       <c r="B22" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>135388250</v>
       </c>
       <c r="B23" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>135356130</v>
       </c>
       <c r="B83" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>135382846</v>
       </c>
       <c r="B84" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10496,7 +10496,7 @@
         <v>135356131</v>
       </c>
       <c r="B85" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10612,7 +10612,7 @@
         <v>135356139</v>
       </c>
       <c r="B86" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>135382842</v>
       </c>
       <c r="B87" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>135422127</v>
       </c>
       <c r="B88" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>135441451</v>
       </c>
       <c r="B115" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>135356147</v>
       </c>
       <c r="B116" t="n">
-        <v>92275</v>
+        <v>92277</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14249,7 +14249,7 @@
         <v>135351866</v>
       </c>
       <c r="B117" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14374,7 +14374,7 @@
         <v>135388280</v>
       </c>
       <c r="B118" t="n">
-        <v>91998</v>
+        <v>92000</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14496,7 +14496,7 @@
         <v>135385183</v>
       </c>
       <c r="B119" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>135385263</v>
       </c>
       <c r="B120" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>135388278</v>
       </c>
       <c r="B121" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14844,7 +14844,7 @@
         <v>135393121</v>
       </c>
       <c r="B122" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>135440316</v>
       </c>
       <c r="B123" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15072,7 +15072,7 @@
         <v>135440315</v>
       </c>
       <c r="B124" t="n">
-        <v>92434</v>
+        <v>92436</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>135388277</v>
       </c>
       <c r="B153" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>135388286</v>
       </c>
       <c r="B154" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>135378203</v>
       </c>
       <c r="B155" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>135385170</v>
       </c>
       <c r="B156" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18947,7 +18947,7 @@
         <v>135385278</v>
       </c>
       <c r="B157" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -19063,7 +19063,7 @@
         <v>135385281</v>
       </c>
       <c r="B158" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>135388265</v>
       </c>
       <c r="B159" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>135393106</v>
       </c>
       <c r="B160" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19407,7 +19407,7 @@
         <v>135355999</v>
       </c>
       <c r="B161" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>135385260</v>
       </c>
       <c r="B162" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>135385265</v>
       </c>
       <c r="B163" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>135385271</v>
       </c>
       <c r="B164" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19871,7 +19871,7 @@
         <v>135388289</v>
       </c>
       <c r="B165" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19987,7 +19987,7 @@
         <v>135440306</v>
       </c>
       <c r="B166" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>135440310</v>
       </c>
       <c r="B167" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20219,7 +20219,7 @@
         <v>135440313</v>
       </c>
       <c r="B168" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>135388275</v>
       </c>
       <c r="B169" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20915,7 +20915,7 @@
         <v>135385269</v>
       </c>
       <c r="B174" t="n">
-        <v>92406</v>
+        <v>92408</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -21036,7 +21036,7 @@
         <v>135388288</v>
       </c>
       <c r="B175" t="n">
-        <v>92406</v>
+        <v>92408</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>135385164</v>
       </c>
       <c r="B176" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>135388281</v>
       </c>
       <c r="B177" t="n">
-        <v>92394</v>
+        <v>92396</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21389,7 +21389,7 @@
         <v>135393116</v>
       </c>
       <c r="B178" t="n">
-        <v>92273</v>
+        <v>92275</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>135382805</v>
       </c>
       <c r="B179" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21617,7 +21617,7 @@
         <v>135382800</v>
       </c>
       <c r="B180" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>135382809</v>
       </c>
       <c r="B181" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>135388276</v>
       </c>
       <c r="B182" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>135351853</v>
       </c>
       <c r="B259" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30987,7 +30987,7 @@
         <v>135358105</v>
       </c>
       <c r="B260" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>135358106</v>
       </c>
       <c r="B261" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -31219,7 +31219,7 @@
         <v>135358107</v>
       </c>
       <c r="B262" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -31335,7 +31335,7 @@
         <v>135393104</v>
       </c>
       <c r="B263" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31447,7 +31447,7 @@
         <v>135393117</v>
       </c>
       <c r="B264" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -32951,7 +32951,7 @@
         <v>135351803</v>
       </c>
       <c r="B277" t="n">
-        <v>92667</v>
+        <v>92669</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>135358086</v>
       </c>
       <c r="B280" t="n">
-        <v>89426</v>
+        <v>89428</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -33428,7 +33428,7 @@
         <v>135351469</v>
       </c>
       <c r="B281" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>135351780</v>
       </c>
       <c r="B282" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>135351789</v>
       </c>
       <c r="B283" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>135351806</v>
       </c>
       <c r="B284" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33892,7 +33892,7 @@
         <v>135354060</v>
       </c>
       <c r="B285" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -34008,7 +34008,7 @@
         <v>135388262</v>
       </c>
       <c r="B286" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -35966,7 +35966,7 @@
         <v>135354091</v>
       </c>
       <c r="B303" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -36082,7 +36082,7 @@
         <v>135349862</v>
       </c>
       <c r="B304" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -36198,7 +36198,7 @@
         <v>135351749</v>
       </c>
       <c r="B305" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>135351755</v>
       </c>
       <c r="B306" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -36430,7 +36430,7 @@
         <v>135351760</v>
       </c>
       <c r="B307" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36546,7 +36546,7 @@
         <v>135351781</v>
       </c>
       <c r="B308" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>135351788</v>
       </c>
       <c r="B309" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>135351809</v>
       </c>
       <c r="B310" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36894,7 +36894,7 @@
         <v>135351831</v>
       </c>
       <c r="B311" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>135354073</v>
       </c>
       <c r="B312" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>135356831</v>
       </c>
       <c r="B313" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>135351466</v>
       </c>
       <c r="B314" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -37358,7 +37358,7 @@
         <v>135351807</v>
       </c>
       <c r="B315" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -38723,7 +38723,7 @@
         <v>135351464</v>
       </c>
       <c r="B327" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>135351748</v>
       </c>
       <c r="B328" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -39787,7 +39787,7 @@
         <v>135351473</v>
       </c>
       <c r="B336" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39903,7 +39903,7 @@
         <v>135355983</v>
       </c>
       <c r="B337" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -40019,7 +40019,7 @@
         <v>135358094</v>
       </c>
       <c r="B338" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>135351457</v>
       </c>
       <c r="B339" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -40251,7 +40251,7 @@
         <v>135351471</v>
       </c>
       <c r="B340" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>135358076</v>
       </c>
       <c r="B341" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -40483,7 +40483,7 @@
         <v>135388263</v>
       </c>
       <c r="B342" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -57873,7 +57873,7 @@
         <v>135351479</v>
       </c>
       <c r="B490" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -57989,7 +57989,7 @@
         <v>135349830</v>
       </c>
       <c r="B491" t="n">
-        <v>111242</v>
+        <v>111244</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -58110,7 +58110,7 @@
         <v>135351476</v>
       </c>
       <c r="B492" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -58226,7 +58226,7 @@
         <v>135351752</v>
       </c>
       <c r="B493" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>135358077</v>
       </c>
       <c r="B494" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -58458,7 +58458,7 @@
         <v>135358087</v>
       </c>
       <c r="B495" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -58574,7 +58574,7 @@
         <v>135351449</v>
       </c>
       <c r="B496" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -58690,7 +58690,7 @@
         <v>135351477</v>
       </c>
       <c r="B497" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -58806,7 +58806,7 @@
         <v>135357666</v>
       </c>
       <c r="B498" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -58922,7 +58922,7 @@
         <v>135357670</v>
       </c>
       <c r="B499" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -59038,7 +59038,7 @@
         <v>135358081</v>
       </c>
       <c r="B500" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -59154,7 +59154,7 @@
         <v>135358082</v>
       </c>
       <c r="B501" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -59270,7 +59270,7 @@
         <v>135358085</v>
       </c>
       <c r="B502" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -59386,7 +59386,7 @@
         <v>135358089</v>
       </c>
       <c r="B503" t="n">
-        <v>98136</v>
+        <v>98138</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -59502,7 +59502,7 @@
         <v>135349874</v>
       </c>
       <c r="B504" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -59623,7 +59623,7 @@
         <v>135351489</v>
       </c>
       <c r="B505" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -59739,7 +59739,7 @@
         <v>135351743</v>
       </c>
       <c r="B506" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -59855,7 +59855,7 @@
         <v>135351773</v>
       </c>
       <c r="B507" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -59971,7 +59971,7 @@
         <v>135354090</v>
       </c>
       <c r="B508" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -60087,7 +60087,7 @@
         <v>135356125</v>
       </c>
       <c r="B509" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -60208,7 +60208,7 @@
         <v>135356126</v>
       </c>
       <c r="B510" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -60324,7 +60324,7 @@
         <v>135358093</v>
       </c>
       <c r="B511" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -60440,7 +60440,7 @@
         <v>135358096</v>
       </c>
       <c r="B512" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -60556,7 +60556,7 @@
         <v>135358099</v>
       </c>
       <c r="B513" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -60672,7 +60672,7 @@
         <v>135358100</v>
       </c>
       <c r="B514" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -60788,7 +60788,7 @@
         <v>135358101</v>
       </c>
       <c r="B515" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -60904,7 +60904,7 @@
         <v>135358102</v>
       </c>
       <c r="B516" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -61020,7 +61020,7 @@
         <v>135351475</v>
       </c>
       <c r="B517" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -65544,7 +65544,7 @@
         <v>135354071</v>
       </c>
       <c r="B556" t="n">
-        <v>92397</v>
+        <v>92399</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65688,7 +65688,7 @@
         <v>135422147</v>
       </c>
       <c r="B557" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -65824,7 +65824,7 @@
         <v>135422165</v>
       </c>
       <c r="B558" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -65960,7 +65960,7 @@
         <v>135349920</v>
       </c>
       <c r="B559" t="n">
-        <v>92443</v>
+        <v>92445</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -66298,7 +66298,7 @@
         <v>135349899</v>
       </c>
       <c r="B562" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -66414,7 +66414,7 @@
         <v>135393122</v>
       </c>
       <c r="B563" t="n">
-        <v>92319</v>
+        <v>92321</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -67194,7 +67194,7 @@
         <v>135349895</v>
       </c>
       <c r="B570" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -67310,7 +67310,7 @@
         <v>135349906</v>
       </c>
       <c r="B571" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -67426,7 +67426,7 @@
         <v>135385306</v>
       </c>
       <c r="B572" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -67542,7 +67542,7 @@
         <v>135385240</v>
       </c>
       <c r="B573" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -67658,7 +67658,7 @@
         <v>135393114</v>
       </c>
       <c r="B574" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -67770,7 +67770,7 @@
         <v>135440300</v>
       </c>
       <c r="B575" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -67886,7 +67886,7 @@
         <v>135393138</v>
       </c>
       <c r="B576" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -67998,7 +67998,7 @@
         <v>135393158</v>
       </c>
       <c r="B577" t="n">
-        <v>92062</v>
+        <v>92064</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -68983,7 +68983,7 @@
         <v>135422136</v>
       </c>
       <c r="B586" t="n">
-        <v>92403</v>
+        <v>92405</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -69216,7 +69216,7 @@
         <v>135349911</v>
       </c>
       <c r="B588" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -69332,7 +69332,7 @@
         <v>135393155</v>
       </c>
       <c r="B589" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -69444,7 +69444,7 @@
         <v>135349919</v>
       </c>
       <c r="B590" t="n">
-        <v>92444</v>
+        <v>92446</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -69560,7 +69560,7 @@
         <v>135349892</v>
       </c>
       <c r="B591" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -69676,7 +69676,7 @@
         <v>135349905</v>
       </c>
       <c r="B592" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -69792,7 +69792,7 @@
         <v>135385238</v>
       </c>
       <c r="B593" t="n">
-        <v>92011</v>
+        <v>92013</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -69908,7 +69908,7 @@
         <v>135388294</v>
       </c>
       <c r="B594" t="n">
-        <v>93163</v>
+        <v>93165</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -70033,7 +70033,7 @@
         <v>135388298</v>
       </c>
       <c r="B595" t="n">
-        <v>93163</v>
+        <v>93165</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -75679,7 +75679,7 @@
         <v>135351869</v>
       </c>
       <c r="B643" t="n">
-        <v>99173</v>
+        <v>99175</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -75795,7 +75795,7 @@
         <v>135422162</v>
       </c>
       <c r="B644" t="n">
-        <v>99173</v>
+        <v>99175</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -75925,7 +75925,7 @@
         <v>135351871</v>
       </c>
       <c r="B645" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -76041,7 +76041,7 @@
         <v>135385327</v>
       </c>
       <c r="B646" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -76157,7 +76157,7 @@
         <v>135393145</v>
       </c>
       <c r="B647" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -76269,7 +76269,7 @@
         <v>135422156</v>
       </c>
       <c r="B648" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -76390,7 +76390,7 @@
         <v>135422160</v>
       </c>
       <c r="B649" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -76511,7 +76511,7 @@
         <v>135523737</v>
       </c>
       <c r="B650" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -76632,7 +76632,7 @@
         <v>135422166</v>
       </c>
       <c r="B651" t="n">
-        <v>108030</v>
+        <v>108032</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -76758,7 +76758,7 @@
         <v>135523654</v>
       </c>
       <c r="B652" t="n">
-        <v>108030</v>
+        <v>108032</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -76879,7 +76879,7 @@
         <v>135422142</v>
       </c>
       <c r="B653" t="n">
-        <v>108292</v>
+        <v>108294</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -77000,7 +77000,7 @@
         <v>135393157</v>
       </c>
       <c r="B654" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -77112,7 +77112,7 @@
         <v>135422154</v>
       </c>
       <c r="B655" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -77233,7 +77233,7 @@
         <v>135422169</v>
       </c>
       <c r="B656" t="n">
-        <v>108362</v>
+        <v>108364</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -77354,7 +77354,7 @@
         <v>135393151</v>
       </c>
       <c r="B657" t="n">
-        <v>110111</v>
+        <v>110113</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -77466,7 +77466,7 @@
         <v>135351874</v>
       </c>
       <c r="B658" t="n">
-        <v>110238</v>
+        <v>110240</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -77582,7 +77582,7 @@
         <v>135349921</v>
       </c>
       <c r="B659" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -77707,7 +77707,7 @@
         <v>135349909</v>
       </c>
       <c r="B660" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -77828,7 +77828,7 @@
         <v>135384319</v>
       </c>
       <c r="B661" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -77944,7 +77944,7 @@
         <v>135384324</v>
       </c>
       <c r="B662" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -78060,7 +78060,7 @@
         <v>135388296</v>
       </c>
       <c r="B663" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -78176,7 +78176,7 @@
         <v>135393149</v>
       </c>
       <c r="B664" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -78288,7 +78288,7 @@
         <v>135422137</v>
       </c>
       <c r="B665" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -78404,7 +78404,7 @@
         <v>135422150</v>
       </c>
       <c r="B666" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -78525,7 +78525,7 @@
         <v>135422155</v>
       </c>
       <c r="B667" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -78646,7 +78646,7 @@
         <v>135422159</v>
       </c>
       <c r="B668" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -78767,7 +78767,7 @@
         <v>135440319</v>
       </c>
       <c r="B669" t="n">
-        <v>106396</v>
+        <v>106398</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -78883,7 +78883,7 @@
         <v>135422167</v>
       </c>
       <c r="B670" t="n">
-        <v>98130</v>
+        <v>98132</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -79000,7 +79000,7 @@
         <v>135523644</v>
       </c>
       <c r="B671" t="n">
-        <v>98130</v>
+        <v>98132</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -79117,7 +79117,7 @@
         <v>135385157</v>
       </c>
       <c r="B672" t="n">
-        <v>98139</v>
+        <v>98141</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -79233,7 +79233,7 @@
         <v>135349896</v>
       </c>
       <c r="B673" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -79349,7 +79349,7 @@
         <v>135349910</v>
       </c>
       <c r="B674" t="n">
-        <v>103847</v>
+        <v>103849</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -79465,7 +79465,7 @@
         <v>135356148</v>
       </c>
       <c r="B675" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -79581,7 +79581,7 @@
         <v>135393154</v>
       </c>
       <c r="B676" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -79693,7 +79693,7 @@
         <v>135422138</v>
       </c>
       <c r="B677" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -79828,7 +79828,7 @@
         <v>135422163</v>
       </c>
       <c r="B678" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -79963,7 +79963,7 @@
         <v>135422168</v>
       </c>
       <c r="B679" t="n">
-        <v>104793</v>
+        <v>104795</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -80098,7 +80098,7 @@
         <v>135393126</v>
       </c>
       <c r="B680" t="n">
-        <v>100886</v>
+        <v>100888</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -80210,7 +80210,7 @@
         <v>135388299</v>
       </c>
       <c r="B681" t="n">
-        <v>102954</v>
+        <v>102956</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -80326,7 +80326,7 @@
         <v>135422143</v>
       </c>
       <c r="B682" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -80447,7 +80447,7 @@
         <v>135351867</v>
       </c>
       <c r="B683" t="n">
-        <v>99277</v>
+        <v>99279</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -80560,7 +80560,7 @@
         <v>135349891</v>
       </c>
       <c r="B684" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -80676,7 +80676,7 @@
         <v>135393129</v>
       </c>
       <c r="B685" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -80788,7 +80788,7 @@
         <v>135393131</v>
       </c>
       <c r="B686" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -80900,7 +80900,7 @@
         <v>135393150</v>
       </c>
       <c r="B687" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -81012,7 +81012,7 @@
         <v>135422139</v>
       </c>
       <c r="B688" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -81133,7 +81133,7 @@
         <v>135422140</v>
       </c>
       <c r="B689" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -81254,7 +81254,7 @@
         <v>135422152</v>
       </c>
       <c r="B690" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -81375,7 +81375,7 @@
         <v>135523597</v>
       </c>
       <c r="B691" t="n">
-        <v>101373</v>
+        <v>101375</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -9516,7 +9516,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135356132</v>
+        <v>135356141</v>
       </c>
       <c r="B77" t="n">
         <v>58141</v>
@@ -9544,11 +9544,7 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr"/>
       <c r="M77" t="inlineStr">
@@ -9563,10 +9559,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>606918</v>
+        <v>606797</v>
       </c>
       <c r="R77" t="n">
-        <v>7311287</v>
+        <v>7310883</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -9598,7 +9594,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9608,19 +9604,19 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>14:15</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Kan det vara lappmes?</t>
+          <t>Varnar</t>
         </is>
       </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="b">
         <v>0</v>
@@ -9643,13 +9639,13 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356132</t>
+          <t>https://artportalen.se/Sighting/135356141</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135356141</v>
+        <v>135382854</v>
       </c>
       <c r="B78" t="n">
         <v>58141</v>
@@ -9677,7 +9673,11 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr">
@@ -9692,10 +9692,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>606797</v>
+        <v>606560</v>
       </c>
       <c r="R78" t="n">
-        <v>7310883</v>
+        <v>7310953</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -9722,27 +9722,22 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:15</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:15</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Varnar</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9772,16 +9767,16 @@
       </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135356141</t>
+          <t>https://artportalen.se/Sighting/135382854</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135382854</v>
+        <v>135356132</v>
       </c>
       <c r="B79" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9789,26 +9784,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>103021</v>
+        <v>103022</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lappmes</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Poecile cinctus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -9825,10 +9820,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>606560</v>
+        <v>606918</v>
       </c>
       <c r="R79" t="n">
-        <v>7310953</v>
+        <v>7311287</v>
       </c>
       <c r="S79" t="n">
         <v>5</v>
@@ -9855,29 +9850,29 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG79" t="b">
         <v>0</v>
@@ -9900,7 +9895,7 @@
       </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135382854</t>
+          <t>https://artportalen.se/Sighting/135356132</t>
         </is>
       </c>
     </row>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -77741,7 +77741,7 @@
         <v>608014</v>
       </c>
       <c r="R660" t="n">
-        <v>7309639</v>
+        <v>7309638</v>
       </c>
       <c r="S660" t="n">
         <v>3</v>
@@ -79379,7 +79379,7 @@
         <v>608014</v>
       </c>
       <c r="R674" t="n">
-        <v>7309639</v>
+        <v>7309638</v>
       </c>
       <c r="S674" t="n">
         <v>3</v>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>135382857</v>
       </c>
       <c r="B5" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135385147</v>
       </c>
       <c r="B8" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135385148</v>
       </c>
       <c r="B9" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         <v>135393109</v>
       </c>
       <c r="B17" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>135440290</v>
       </c>
       <c r="B18" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>135382858</v>
       </c>
       <c r="B32" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
         <v>135393097</v>
       </c>
       <c r="B39" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>135393098</v>
       </c>
       <c r="B40" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>135393101</v>
       </c>
       <c r="B41" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5280,7 +5280,7 @@
         <v>135393102</v>
       </c>
       <c r="B42" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5392,7 +5392,7 @@
         <v>135440288</v>
       </c>
       <c r="B43" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>135393105</v>
       </c>
       <c r="B55" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         <v>135440284</v>
       </c>
       <c r="B56" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>135440285</v>
       </c>
       <c r="B57" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>135521526</v>
       </c>
       <c r="B58" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>135422122</v>
       </c>
       <c r="B60" t="n">
-        <v>80560</v>
+        <v>80562</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7490,7 +7490,7 @@
         <v>135422125</v>
       </c>
       <c r="B61" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>135385152</v>
       </c>
       <c r="B68" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8521,7 +8521,7 @@
         <v>135385155</v>
       </c>
       <c r="B69" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>135422128</v>
       </c>
       <c r="B70" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>135521659</v>
       </c>
       <c r="B71" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>135382852</v>
       </c>
       <c r="B72" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>135422126</v>
       </c>
       <c r="B75" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>135356132</v>
       </c>
       <c r="B79" t="n">
-        <v>58143</v>
+        <v>58145</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>135393108</v>
       </c>
       <c r="B81" t="n">
-        <v>5201</v>
+        <v>5202</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10138,7 +10138,7 @@
         <v>135422123</v>
       </c>
       <c r="B82" t="n">
-        <v>41610</v>
+        <v>41612</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10844,7 +10844,7 @@
         <v>135422127</v>
       </c>
       <c r="B88" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>135440301</v>
       </c>
       <c r="B101" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>135440302</v>
       </c>
       <c r="B102" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -14005,7 +14005,7 @@
         <v>135441451</v>
       </c>
       <c r="B115" t="n">
-        <v>92669</v>
+        <v>92684</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>135385183</v>
       </c>
       <c r="B119" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>135393121</v>
       </c>
       <c r="B122" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14951,7 +14951,7 @@
         <v>135440316</v>
       </c>
       <c r="B123" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>135440315</v>
       </c>
       <c r="B124" t="n">
-        <v>92436</v>
+        <v>92450</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>135382863</v>
       </c>
       <c r="B130" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>135382871</v>
       </c>
       <c r="B132" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>135385160</v>
       </c>
       <c r="B144" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>135385179</v>
       </c>
       <c r="B146" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>135385181</v>
       </c>
       <c r="B147" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>135385186</v>
       </c>
       <c r="B148" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>135385187</v>
       </c>
       <c r="B149" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>135385170</v>
       </c>
       <c r="B156" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -19290,7 +19290,7 @@
         <v>135393106</v>
       </c>
       <c r="B160" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>135440306</v>
       </c>
       <c r="B166" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -20098,7 +20098,7 @@
         <v>135440310</v>
       </c>
       <c r="B167" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>135440313</v>
       </c>
       <c r="B168" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>135382872</v>
       </c>
       <c r="B171" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>135385164</v>
       </c>
       <c r="B176" t="n">
-        <v>92396</v>
+        <v>92408</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>135393116</v>
       </c>
       <c r="B178" t="n">
-        <v>92275</v>
+        <v>92289</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>135385175</v>
       </c>
       <c r="B213" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>135385182</v>
       </c>
       <c r="B214" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -26832,7 +26832,7 @@
         <v>135393096</v>
       </c>
       <c r="B225" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>135440317</v>
       </c>
       <c r="B226" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -27060,7 +27060,7 @@
         <v>135393099</v>
       </c>
       <c r="B227" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -28912,7 +28912,7 @@
         <v>135440308</v>
       </c>
       <c r="B243" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>135385185</v>
       </c>
       <c r="B252" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -30252,7 +30252,7 @@
         <v>135354042</v>
       </c>
       <c r="B254" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>135440314</v>
       </c>
       <c r="B258" t="n">
-        <v>41610</v>
+        <v>41612</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -31330,7 +31330,7 @@
         <v>135393104</v>
       </c>
       <c r="B263" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -31442,7 +31442,7 @@
         <v>135393117</v>
       </c>
       <c r="B264" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>135385167</v>
       </c>
       <c r="B274" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>135385168</v>
       </c>
       <c r="B275" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>135354060</v>
       </c>
       <c r="B285" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>135354052</v>
       </c>
       <c r="B291" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>135354057</v>
       </c>
       <c r="B292" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>135354065</v>
       </c>
       <c r="B293" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>135354068</v>
       </c>
       <c r="B294" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>135354076</v>
       </c>
       <c r="B295" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>135354085</v>
       </c>
       <c r="B296" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>135354104</v>
       </c>
       <c r="B297" t="n">
-        <v>79520</v>
+        <v>79522</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>135354091</v>
       </c>
       <c r="B303" t="n">
-        <v>92046</v>
+        <v>92060</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>135354073</v>
       </c>
       <c r="B312" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>135354059</v>
       </c>
       <c r="B320" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>135354063</v>
       </c>
       <c r="B321" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -38151,7 +38151,7 @@
         <v>135354106</v>
       </c>
       <c r="B322" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -39187,7 +39187,7 @@
         <v>135354094</v>
       </c>
       <c r="B331" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>135354098</v>
       </c>
       <c r="B332" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>135354100</v>
       </c>
       <c r="B333" t="n">
-        <v>80557</v>
+        <v>80559</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>135354048</v>
       </c>
       <c r="B395" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>135354054</v>
       </c>
       <c r="B396" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>135354056</v>
       </c>
       <c r="B397" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>135354062</v>
       </c>
       <c r="B398" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>135354064</v>
       </c>
       <c r="B399" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>135354067</v>
       </c>
       <c r="B400" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>135354070</v>
       </c>
       <c r="B401" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>135354074</v>
       </c>
       <c r="B402" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>135354077</v>
       </c>
       <c r="B403" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>135354079</v>
       </c>
       <c r="B404" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>135354082</v>
       </c>
       <c r="B405" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>135354103</v>
       </c>
       <c r="B406" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>135354084</v>
       </c>
       <c r="B439" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>135354105</v>
       </c>
       <c r="B440" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>135354096</v>
       </c>
       <c r="B446" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52696,7 +52696,7 @@
         <v>135354099</v>
       </c>
       <c r="B447" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         <v>135354097</v>
       </c>
       <c r="B457" t="n">
-        <v>80567</v>
+        <v>80569</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>135354081</v>
       </c>
       <c r="B461" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -55059,7 +55059,7 @@
         <v>135354089</v>
       </c>
       <c r="B467" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -56772,7 +56772,7 @@
         <v>135354087</v>
       </c>
       <c r="B481" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -56898,7 +56898,7 @@
         <v>135354088</v>
       </c>
       <c r="B482" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -57024,7 +57024,7 @@
         <v>135354093</v>
       </c>
       <c r="B483" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -59966,7 +59966,7 @@
         <v>135354090</v>
       </c>
       <c r="B508" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -64843,7 +64843,7 @@
         <v>135354046</v>
       </c>
       <c r="B550" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -64959,7 +64959,7 @@
         <v>135354061</v>
       </c>
       <c r="B551" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -65075,7 +65075,7 @@
         <v>135354078</v>
       </c>
       <c r="B552" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -65191,7 +65191,7 @@
         <v>135354083</v>
       </c>
       <c r="B553" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -65539,7 +65539,7 @@
         <v>135354071</v>
       </c>
       <c r="B556" t="n">
-        <v>92399</v>
+        <v>92411</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -65683,7 +65683,7 @@
         <v>135422147</v>
       </c>
       <c r="B557" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -65819,7 +65819,7 @@
         <v>135422165</v>
       </c>
       <c r="B558" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -66075,7 +66075,7 @@
         <v>135440323</v>
       </c>
       <c r="B560" t="n">
-        <v>83420</v>
+        <v>83422</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -66409,7 +66409,7 @@
         <v>135393122</v>
       </c>
       <c r="B563" t="n">
-        <v>92321</v>
+        <v>92335</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -67653,7 +67653,7 @@
         <v>135393114</v>
       </c>
       <c r="B574" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -67765,7 +67765,7 @@
         <v>135440300</v>
       </c>
       <c r="B575" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -67881,7 +67881,7 @@
         <v>135393138</v>
       </c>
       <c r="B576" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -67993,7 +67993,7 @@
         <v>135393158</v>
       </c>
       <c r="B577" t="n">
-        <v>92064</v>
+        <v>92078</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -68847,7 +68847,7 @@
         <v>135422133</v>
       </c>
       <c r="B585" t="n">
-        <v>83292</v>
+        <v>83294</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -68978,7 +68978,7 @@
         <v>135422136</v>
       </c>
       <c r="B586" t="n">
-        <v>92405</v>
+        <v>92417</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -69327,7 +69327,7 @@
         <v>135393155</v>
       </c>
       <c r="B589" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -69903,7 +69903,7 @@
         <v>135388294</v>
       </c>
       <c r="B594" t="n">
-        <v>93165</v>
+        <v>93180</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -70028,7 +70028,7 @@
         <v>135388298</v>
       </c>
       <c r="B595" t="n">
-        <v>93165</v>
+        <v>93180</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -72241,7 +72241,7 @@
         <v>135393119</v>
       </c>
       <c r="B614" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -72353,7 +72353,7 @@
         <v>135393137</v>
       </c>
       <c r="B615" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -72465,7 +72465,7 @@
         <v>135422129</v>
       </c>
       <c r="B616" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -72581,7 +72581,7 @@
         <v>135440298</v>
       </c>
       <c r="B617" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -73277,7 +73277,7 @@
         <v>135393123</v>
       </c>
       <c r="B623" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -73389,7 +73389,7 @@
         <v>135422132</v>
       </c>
       <c r="B624" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -73520,7 +73520,7 @@
         <v>135440297</v>
       </c>
       <c r="B625" t="n">
-        <v>83428</v>
+        <v>83430</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -73636,7 +73636,7 @@
         <v>135385194</v>
       </c>
       <c r="B626" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -74503,7 +74503,7 @@
         <v>135382861</v>
       </c>
       <c r="B633" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -74624,7 +74624,7 @@
         <v>135422144</v>
       </c>
       <c r="B634" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -74978,7 +74978,7 @@
         <v>135440320</v>
       </c>
       <c r="B637" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -75317,7 +75317,7 @@
         <v>135422135</v>
       </c>
       <c r="B640" t="n">
-        <v>58084</v>
+        <v>58086</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -75553,7 +75553,7 @@
         <v>135422161</v>
       </c>
       <c r="B642" t="n">
-        <v>41610</v>
+        <v>41612</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -75790,7 +75790,7 @@
         <v>135422162</v>
       </c>
       <c r="B644" t="n">
-        <v>99175</v>
+        <v>99192</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -76152,7 +76152,7 @@
         <v>135393145</v>
       </c>
       <c r="B647" t="n">
-        <v>99278</v>
+        <v>99295</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -76264,7 +76264,7 @@
         <v>135422156</v>
       </c>
       <c r="B648" t="n">
-        <v>99278</v>
+        <v>99295</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -76385,7 +76385,7 @@
         <v>135422160</v>
       </c>
       <c r="B649" t="n">
-        <v>99278</v>
+        <v>99295</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -76506,7 +76506,7 @@
         <v>135523737</v>
       </c>
       <c r="B650" t="n">
-        <v>99278</v>
+        <v>99295</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -76627,7 +76627,7 @@
         <v>135422166</v>
       </c>
       <c r="B651" t="n">
-        <v>108032</v>
+        <v>108055</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -76753,7 +76753,7 @@
         <v>135523654</v>
       </c>
       <c r="B652" t="n">
-        <v>108032</v>
+        <v>108055</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -76874,7 +76874,7 @@
         <v>135422142</v>
       </c>
       <c r="B653" t="n">
-        <v>108294</v>
+        <v>108317</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -76995,7 +76995,7 @@
         <v>135393157</v>
       </c>
       <c r="B654" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -77107,7 +77107,7 @@
         <v>135422154</v>
       </c>
       <c r="B655" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -77228,7 +77228,7 @@
         <v>135422169</v>
       </c>
       <c r="B656" t="n">
-        <v>108364</v>
+        <v>108387</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -77349,7 +77349,7 @@
         <v>135393151</v>
       </c>
       <c r="B657" t="n">
-        <v>110113</v>
+        <v>110136</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -78171,7 +78171,7 @@
         <v>135393149</v>
       </c>
       <c r="B664" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -78283,7 +78283,7 @@
         <v>135422137</v>
       </c>
       <c r="B665" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -78399,7 +78399,7 @@
         <v>135422150</v>
       </c>
       <c r="B666" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -78520,7 +78520,7 @@
         <v>135422155</v>
       </c>
       <c r="B667" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -78641,7 +78641,7 @@
         <v>135422159</v>
       </c>
       <c r="B668" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -78762,7 +78762,7 @@
         <v>135440319</v>
       </c>
       <c r="B669" t="n">
-        <v>106398</v>
+        <v>106418</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -78878,7 +78878,7 @@
         <v>135422167</v>
       </c>
       <c r="B670" t="n">
-        <v>98132</v>
+        <v>98149</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -78995,7 +78995,7 @@
         <v>135523644</v>
       </c>
       <c r="B671" t="n">
-        <v>98132</v>
+        <v>98149</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -79112,7 +79112,7 @@
         <v>135385157</v>
       </c>
       <c r="B672" t="n">
-        <v>98141</v>
+        <v>98158</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -79576,7 +79576,7 @@
         <v>135393154</v>
       </c>
       <c r="B676" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -79688,7 +79688,7 @@
         <v>135422138</v>
       </c>
       <c r="B677" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -79823,7 +79823,7 @@
         <v>135422163</v>
       </c>
       <c r="B678" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -79958,7 +79958,7 @@
         <v>135422168</v>
       </c>
       <c r="B679" t="n">
-        <v>104795</v>
+        <v>104815</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -80093,7 +80093,7 @@
         <v>135393126</v>
       </c>
       <c r="B680" t="n">
-        <v>100888</v>
+        <v>100905</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -80321,7 +80321,7 @@
         <v>135422143</v>
       </c>
       <c r="B682" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -80671,7 +80671,7 @@
         <v>135393129</v>
       </c>
       <c r="B685" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -80783,7 +80783,7 @@
         <v>135393131</v>
       </c>
       <c r="B686" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -80895,7 +80895,7 @@
         <v>135393150</v>
       </c>
       <c r="B687" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -81007,7 +81007,7 @@
         <v>135422139</v>
       </c>
       <c r="B688" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -81128,7 +81128,7 @@
         <v>135422140</v>
       </c>
       <c r="B689" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -81249,7 +81249,7 @@
         <v>135422152</v>
       </c>
       <c r="B690" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -81370,7 +81370,7 @@
         <v>135523597</v>
       </c>
       <c r="B691" t="n">
-        <v>101375</v>
+        <v>101392</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -82303,7 +82303,7 @@
         <v>135422134</v>
       </c>
       <c r="B699" t="n">
-        <v>78450</v>
+        <v>78452</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -82434,7 +82434,7 @@
         <v>135422148</v>
       </c>
       <c r="B700" t="n">
-        <v>80512</v>
+        <v>80514</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -82570,7 +82570,7 @@
         <v>135422151</v>
       </c>
       <c r="B701" t="n">
-        <v>87231</v>
+        <v>87233</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -1031,7 +1031,7 @@
         <v>135382857</v>
       </c>
       <c r="B5" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135385147</v>
       </c>
       <c r="B8" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135385148</v>
       </c>
       <c r="B9" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>135382858</v>
       </c>
       <c r="B32" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -7133,7 +7133,7 @@
         <v>135521526</v>
       </c>
       <c r="B58" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -14491,7 +14491,7 @@
         <v>135385183</v>
       </c>
       <c r="B119" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15805,7 +15805,7 @@
         <v>135382863</v>
       </c>
       <c r="B130" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -16037,7 +16037,7 @@
         <v>135382871</v>
       </c>
       <c r="B132" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -17434,7 +17434,7 @@
         <v>135385160</v>
       </c>
       <c r="B144" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17666,7 +17666,7 @@
         <v>135385179</v>
       </c>
       <c r="B146" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17782,7 +17782,7 @@
         <v>135385181</v>
       </c>
       <c r="B147" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>135385186</v>
       </c>
       <c r="B148" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>135385187</v>
       </c>
       <c r="B149" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -18826,7 +18826,7 @@
         <v>135385170</v>
       </c>
       <c r="B156" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>135382872</v>
       </c>
       <c r="B171" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -21147,7 +21147,7 @@
         <v>135385164</v>
       </c>
       <c r="B176" t="n">
-        <v>92408</v>
+        <v>92409</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>135385175</v>
       </c>
       <c r="B213" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25556,7 +25556,7 @@
         <v>135385182</v>
       </c>
       <c r="B214" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>135385167</v>
       </c>
       <c r="B274" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32714,7 +32714,7 @@
         <v>135385168</v>
       </c>
       <c r="B275" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>135354060</v>
       </c>
       <c r="B285" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -34583,7 +34583,7 @@
         <v>135354052</v>
       </c>
       <c r="B291" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34699,7 +34699,7 @@
         <v>135354057</v>
       </c>
       <c r="B292" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>135354065</v>
       </c>
       <c r="B293" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>135354068</v>
       </c>
       <c r="B294" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -35047,7 +35047,7 @@
         <v>135354076</v>
       </c>
       <c r="B295" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -35163,7 +35163,7 @@
         <v>135354085</v>
       </c>
       <c r="B296" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -35279,7 +35279,7 @@
         <v>135354104</v>
       </c>
       <c r="B297" t="n">
-        <v>79522</v>
+        <v>79523</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>135354091</v>
       </c>
       <c r="B303" t="n">
-        <v>92060</v>
+        <v>92061</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>135354073</v>
       </c>
       <c r="B312" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -37919,7 +37919,7 @@
         <v>135354059</v>
       </c>
       <c r="B320" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>135354063</v>
       </c>
       <c r="B321" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -38151,7 +38151,7 @@
         <v>135354106</v>
       </c>
       <c r="B322" t="n">
-        <v>83294</v>
+        <v>83311</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -39187,7 +39187,7 @@
         <v>135354094</v>
       </c>
       <c r="B331" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -39318,7 +39318,7 @@
         <v>135354098</v>
       </c>
       <c r="B332" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>135354100</v>
       </c>
       <c r="B333" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>135354048</v>
       </c>
       <c r="B395" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -46755,7 +46755,7 @@
         <v>135354054</v>
       </c>
       <c r="B396" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -46871,7 +46871,7 @@
         <v>135354056</v>
       </c>
       <c r="B397" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -46987,7 +46987,7 @@
         <v>135354062</v>
       </c>
       <c r="B398" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -47103,7 +47103,7 @@
         <v>135354064</v>
       </c>
       <c r="B399" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -47219,7 +47219,7 @@
         <v>135354067</v>
       </c>
       <c r="B400" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -47335,7 +47335,7 @@
         <v>135354070</v>
       </c>
       <c r="B401" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>135354074</v>
       </c>
       <c r="B402" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>135354077</v>
       </c>
       <c r="B403" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -47683,7 +47683,7 @@
         <v>135354079</v>
       </c>
       <c r="B404" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -47799,7 +47799,7 @@
         <v>135354082</v>
       </c>
       <c r="B405" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -47915,7 +47915,7 @@
         <v>135354103</v>
       </c>
       <c r="B406" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>135354084</v>
       </c>
       <c r="B439" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -51864,7 +51864,7 @@
         <v>135354105</v>
       </c>
       <c r="B440" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -52565,7 +52565,7 @@
         <v>135354096</v>
       </c>
       <c r="B446" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -52696,7 +52696,7 @@
         <v>135354099</v>
       </c>
       <c r="B447" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -53885,7 +53885,7 @@
         <v>135354097</v>
       </c>
       <c r="B457" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>135354081</v>
       </c>
       <c r="B461" t="n">
-        <v>80570</v>
+        <v>80571</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -59966,7 +59966,7 @@
         <v>135354090</v>
       </c>
       <c r="B508" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -64843,7 +64843,7 @@
         <v>135354046</v>
       </c>
       <c r="B550" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -64959,7 +64959,7 @@
         <v>135354061</v>
       </c>
       <c r="B551" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -65075,7 +65075,7 @@
         <v>135354078</v>
       </c>
       <c r="B552" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -65191,7 +65191,7 @@
         <v>135354083</v>
       </c>
       <c r="B553" t="n">
-        <v>78452</v>
+        <v>78453</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -65539,7 +65539,7 @@
         <v>135354071</v>
       </c>
       <c r="B556" t="n">
-        <v>92411</v>
+        <v>92412</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -73636,7 +73636,7 @@
         <v>135385194</v>
       </c>
       <c r="B626" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -76506,7 +76506,7 @@
         <v>135523737</v>
       </c>
       <c r="B650" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -76753,7 +76753,7 @@
         <v>135523654</v>
       </c>
       <c r="B652" t="n">
-        <v>108055</v>
+        <v>108057</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -78995,7 +78995,7 @@
         <v>135523644</v>
       </c>
       <c r="B671" t="n">
-        <v>98149</v>
+        <v>98150</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -79112,7 +79112,7 @@
         <v>135385157</v>
       </c>
       <c r="B672" t="n">
-        <v>98158</v>
+        <v>98159</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -81370,7 +81370,7 @@
         <v>135523597</v>
       </c>
       <c r="B691" t="n">
-        <v>101392</v>
+        <v>101394</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -9872,7 +9872,7 @@
         <v>0</v>
       </c>
       <c r="AE79" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="b">
         <v>0</v>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -33887,7 +33887,7 @@
         <v>135354060</v>
       </c>
       <c r="B285" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>135354091</v>
       </c>
       <c r="B303" t="n">
-        <v>92061</v>
+        <v>92062</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -37005,7 +37005,7 @@
         <v>135354073</v>
       </c>
       <c r="B312" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -59966,7 +59966,7 @@
         <v>135354090</v>
       </c>
       <c r="B508" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -65539,7 +65539,7 @@
         <v>135354071</v>
       </c>
       <c r="B556" t="n">
-        <v>92412</v>
+        <v>92413</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -9776,7 +9776,7 @@
         <v>135356132</v>
       </c>
       <c r="B79" t="n">
-        <v>58145</v>
+        <v>58146</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -74978,7 +74978,7 @@
         <v>135440320</v>
       </c>
       <c r="B637" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -9776,7 +9776,7 @@
         <v>135356132</v>
       </c>
       <c r="B79" t="n">
-        <v>58146</v>
+        <v>58150</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -74978,7 +74978,7 @@
         <v>135440320</v>
       </c>
       <c r="B637" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -9776,7 +9776,7 @@
         <v>135356132</v>
       </c>
       <c r="B79" t="n">
-        <v>58150</v>
+        <v>58151</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -74978,7 +74978,7 @@
         <v>135440320</v>
       </c>
       <c r="B637" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -9776,7 +9776,7 @@
         <v>135356132</v>
       </c>
       <c r="B79" t="n">
-        <v>58151</v>
+        <v>58156</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -74978,7 +74978,7 @@
         <v>135440320</v>
       </c>
       <c r="B637" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>

--- a/artfynd/Laisdalen Björkliden artfynd.xlsx
+++ b/artfynd/Laisdalen Björkliden artfynd.xlsx
@@ -9776,7 +9776,7 @@
         <v>135356132</v>
       </c>
       <c r="B79" t="n">
-        <v>58156</v>
+        <v>58169</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
